--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -8,29 +8,30 @@
   </bookViews>
   <sheets>
     <sheet name="재미 요소 기획" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="게임 개요" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="클래스 &amp; 전직" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="스킬" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="몬스터" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="맵 &amp; 지역" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="장비 &amp; 강화" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="제작" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="교역" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="펫 &amp; 탈것" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="버프 &amp; 변신" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="PvP &amp; 카르마" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="퀘스트" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="상점 &amp; 결제" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="칭호" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="용병 시스템" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="게임 수치" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="몬스터 AI" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="존 몬스터 배합" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="던전 &amp; 레이드" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="경매장 &amp; 거래" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="길드 시스템" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="일일·주간 컨텐츠" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="구현 현황" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="UX 세부 기획" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="게임 개요" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="클래스 &amp; 전직" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="스킬" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="몬스터" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="맵 &amp; 지역" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="장비 &amp; 강화" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="제작" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="교역" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="펫 &amp; 탈것" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="버프 &amp; 변신" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="PvP &amp; 카르마" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="퀘스트" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="상점 &amp; 결제" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="칭호" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="용병 시스템" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="게임 수치" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="몬스터 AI" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="존 몬스터 배합" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="던전 &amp; 레이드" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="경매장 &amp; 거래" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="길드 시스템" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="일일·주간 컨텐츠" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="구현 현황" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3493,6 +3494,655 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>교역품 (20종)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>상품ID</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>기본가격(G)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>goods_silk</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>비단</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>의류/직물</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>높은 가격 변동폭</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>goods_iron</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>철광석</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>광물/금속</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>제작 재료로도 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>goods_herb</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>약초</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>식물/약재</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>물약 제작 재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>goods_gem</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>보석</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>귀금속</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>장신구 제작 재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>goods_wood</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>목재</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>건축/재료</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>기본 제작 재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>goods_leather</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>가죽</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>가공품</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>방어구 제작 재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>goods_spice</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>향신료</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>식품/향료</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>고급 요리 재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>goods_potion</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>물약 원료</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>연금술</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>물약 제작 필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>goods_pearl</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>진주</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>귀금속</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>희귀 교역품</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>goods_crystal</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>마법 수정</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>마법재료</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>강화 재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>goods_wine</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>고급 와인</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>180</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>사치품</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>goods_fur</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>고급 모피</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>가공품</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>방한 재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>goods_incense</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>기호품</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>버프 재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>goods_dye</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>염료</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>가공품</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>스킨 재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>goods_salt</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>소금</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>식품/조미</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>기본 교역품</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>goods_fish</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>건어물</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>식품</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>기본 교역품</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>goods_gold_bar</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>금괴</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>귀금속</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>최고가 교역품</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>goods_dragon_eye</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>용의 눈</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>희귀재료</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>전설 제작 재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>goods_star_dust</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>별의 가루</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>마법재료</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>강화 촉매</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>goods_moonstone</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>월석</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>350</v>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>마법재료</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>장신구 재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>교역 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>가격 변동</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>마을별 0.5~1.5배 가격 랜덤 (10분 주기 변동)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>구매 조건</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>해당 마을 존에 위치해야 구매 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>판매 조건</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>다른 마을로 이동 후 판매 (차익 실현)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>판매 수수료</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>판매가의 10% 수수료</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>마켓 수수료</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>플레이어간 거래 5% 수수료</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>위험 요소</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>PK 사망시 교역품 30% 드롭</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>이익 극대화</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>가격이 낮은 마을에서 매입 → 높은 마을에서 매도</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3822,7 +4472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4400,7 +5050,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4616,7 +5266,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5238,7 +5888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5796,7 +6446,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6153,7 +6803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6425,7 +7075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6939,7 +7589,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7178,7 +7828,1394 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>UI/UX 세부 기획 — 플레이어가 이해할 수 있는 게임</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>핵심 원칙: 모든 정보는 플레이어가 물어보기 전에 보여줘야 한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1. 스킬 상세 패널</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>현재 상태</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>개선안</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>표시 정보</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>UI 위치</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>스킬 목록</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>이름만 표시</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>상세 카드</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>이름/타입/데미지/쿨타임/MP/습득Lv/설명</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>전투 메뉴 → 스킬 패널</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>쿨타임</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>숨김</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>실시간 표시</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>남은 초수 + 원형 프로그레스</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>HUD 하단 스킬 아이콘 5개</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>자동 시전 순서</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>불명확</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>우선순위 표시</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>다음 시전 스킬 이름 + 타이머</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>전투 상태 텍스트 옆</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>MP 비용</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>숨김</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>바 내부 표시</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>스킬 사용 시 MP 바에서 즉시 차감 시각화</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>MP 바 깜빡임</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>2. 장비 비교 시스템</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>현재 상태</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>개선안</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>표시 정보</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>UI 위치</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>인벤 장비</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>이름+등급만</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>상세 카드</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>ATK/DEF/등급/강화/랜덤옵션 전부 표시</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>인벤토리 패널</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>비교</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>현재 vs 신규</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>현재 장착: ATK+10 → 이 아이템: ATK+25 (▲+15)</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>장비 클릭 시 모달</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>색상 코드</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>등급 테두리만</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>수치 색상</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>상승=초록, 하락=빨강, 동일=회색</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>비교 모달 내</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>추천</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>자동 추천</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>현재보다 강한 미장착 장비에 ★ 표시</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>인벤 목록 옆</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>3. 몬스터 정보 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>현재 상태</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>개선안</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>표시 정보</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>UI 위치</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>Unity HP바 위</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>sync에 이름 포함</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>몬스터명 + 등급 색상</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>게임 화면 위</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>색상만</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>아이콘+텍스트</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>일반/엘리트/레어/보스/전설/신화 태그</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>이름표 옆</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>Unity HP바</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>%+수치</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>현재HP/최대HP + % 바</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>이름표 아래</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>속성</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>숨김</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>아이콘</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>화/수/풍/토 속성 아이콘</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>이름표 옆</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>약점</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>숨김</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>힌트</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>유리 속성 → "약점!" 표시</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>속성 아이콘 옆</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>드롭 힌트</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>숨김</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>등급 힌트</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>이 몬스터가 드롭하는 장비 등급 범위</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>도감에서 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>4. 데미지 분석 (전투 통계)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>현재 상태</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>개선안</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>표시 정보</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>UI 위치</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>데미지 숫자</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>합산 숫자만</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>색상+크기 구분</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>일반=흰12px / 크리=빨강18px / 스킬=금16px</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>플로팅 텍스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>데미지 소스</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>전투 로그 상세</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>[그림자 일격] 기본 35 × 3.0 × 1.3(부스트) = 136</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>전투 로그 확장</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>DPS 미터</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>단순 숫자</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>그래프</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>10초 롤링 DPS + 미니 라인 그래프</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>우측 하단</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>피해 받은</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>빨간 숫자</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>몬스터 이름 + 데미지 + 스킬명</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>HP바 옆 플로팅</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>전투 요약</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>세션 통계</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>총 데미지/받은 데미지/회복량/DPS/킬수</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>설정 패널</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>5. 사망 리캡 (Death Recap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>현재 상태</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>개선안</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>표시 정보</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>UI 위치</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>킬러</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>이름만</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>상세 프로필</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>킬러 이름 + 클래스 + 레벨 + 장비</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>사망 화면 상단</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>최종 일격</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>데미지 소스</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>최종 스킬명 + 데미지 + 속성</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>사망 원인 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>피해 타임라인</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>최근 5초 피해</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>시간순 피해 목록 (누가/얼마나/어떤 스킬)</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>사망 화면 중앙</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>생존 통계</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>킬수+시간</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>킬수/레벨/획득 골드/EXP/최고 스트릭</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>사망 화면 하단</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>복수 추적</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>원한 시스템</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>킬러 위치 표시 (PvP 사망 시 30초간)</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>미니맵 빨간 핑</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>6. 파티원 상태 시각화</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>현재 상태</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>개선안</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>표시 정보</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>UI 위치</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>파티원 HP</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>텍스트만</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>실시간 바</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>이름 + HP% 바 + 클래스 아이콘</t>
+        </is>
+      </c>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>화면 좌측 세로</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>파티원 위치</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>미니맵 표시</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>파티원 파란 점 + 이름</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>미니맵</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>거리 표시</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>거리 숫자</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>각 파티원까지 거리 (m 단위)</t>
+        </is>
+      </c>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>파티 프레임 옆</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>버프 공유</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>아이콘 없음</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>공유 버프 표시</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>파티 버프 목록 (전투 함성, 수호 오라 등)</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>파티 프레임 아래</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>7. 미니맵 범례 &amp; 마커</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>현재 상태</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>개선안</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>표시 정보</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>UI 위치</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>범례</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>색상 범례</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>초록=마을, 갈색=사냥터, 빨강=PK, 보라=던전</t>
+        </is>
+      </c>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>미니맵 하단</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>이벤트 마커</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>깜빡이 핑</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>월드보스=빨간핑, 고블린=금핑, 유성우=파란핑</t>
+        </is>
+      </c>
+      <c r="E53" s="24" t="inlineStr">
+        <is>
+          <t>미니맵 위</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>퀘스트 마커</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>노란 화살표</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr">
+        <is>
+          <t>현재 퀘스트 목표 존 방향</t>
+        </is>
+      </c>
+      <c r="E54" s="24" t="inlineStr">
+        <is>
+          <t>미니맵 테두리</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="24" t="inlineStr">
+        <is>
+          <t>플레이어 방향</t>
+        </is>
+      </c>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t>삼각형만</t>
+        </is>
+      </c>
+      <c r="C55" s="24" t="inlineStr">
+        <is>
+          <t>시야 콘</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>플레이어 전방 시야 범위 표시</t>
+        </is>
+      </c>
+      <c r="E55" s="24" t="inlineStr">
+        <is>
+          <t>미니맵 삼각형</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t>8. 설정 &amp; 환경설정 패널</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>현재 상태</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>개선안</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>옵션</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="24" t="inlineStr">
+        <is>
+          <t>사운드</t>
+        </is>
+      </c>
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>ON/OFF만</t>
+        </is>
+      </c>
+      <c r="C59" s="24" t="inlineStr">
+        <is>
+          <t>볼륨 슬라이더</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="inlineStr">
+        <is>
+          <t>BGM 0~100% / SFX 0~100%</t>
+        </is>
+      </c>
+      <c r="E59" s="24" t="inlineStr">
+        <is>
+          <t>BGM:30% SFX:70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>데미지 숫자</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>항상 ON</t>
+        </is>
+      </c>
+      <c r="C60" s="24" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="inlineStr">
+        <is>
+          <t>나의 데미지 / 받는 데미지 / 스킬명 각각 토글</t>
+        </is>
+      </c>
+      <c r="E60" s="24" t="inlineStr">
+        <is>
+          <t>전부 ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="24" t="inlineStr">
+        <is>
+          <t>자동 물약</t>
+        </is>
+      </c>
+      <c r="B61" s="24" t="inlineStr">
+        <is>
+          <t>ON/OFF만</t>
+        </is>
+      </c>
+      <c r="C61" s="24" t="inlineStr">
+        <is>
+          <t>임계값 설정</t>
+        </is>
+      </c>
+      <c r="D61" s="24" t="inlineStr">
+        <is>
+          <t>HP 20%/30%/40%/50% 이하 시 자동 사용</t>
+        </is>
+      </c>
+      <c r="E61" s="24" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="24" t="inlineStr">
+        <is>
+          <t>화면 효과</t>
+        </is>
+      </c>
+      <c r="B62" s="24" t="inlineStr">
+        <is>
+          <t>항상 ON</t>
+        </is>
+      </c>
+      <c r="C62" s="24" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="D62" s="24" t="inlineStr">
+        <is>
+          <t>화면 흔들림 / 플래시 / 피격 효과 각각</t>
+        </is>
+      </c>
+      <c r="E62" s="24" t="inlineStr">
+        <is>
+          <t>전부 ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>알림 필터</t>
+        </is>
+      </c>
+      <c r="B63" s="24" t="inlineStr">
+        <is>
+          <t>전부 표시</t>
+        </is>
+      </c>
+      <c r="C63" s="24" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="D63" s="24" t="inlineStr">
+        <is>
+          <t>서버 공지 / 다른 플레이어 드롭 / 현상금 / 길드</t>
+        </is>
+      </c>
+      <c r="E63" s="24" t="inlineStr">
+        <is>
+          <t>전부 ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="24" t="inlineStr">
+        <is>
+          <t>전투 로그</t>
+        </is>
+      </c>
+      <c r="B64" s="24" t="inlineStr">
+        <is>
+          <t>전부 표시</t>
+        </is>
+      </c>
+      <c r="C64" s="24" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D64" s="24" t="inlineStr">
+        <is>
+          <t>내 데미지 / 받는 피해 / 스킬 / 드롭 / 퀘스트</t>
+        </is>
+      </c>
+      <c r="E64" s="24" t="inlineStr">
+        <is>
+          <t>전부 ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="24" t="inlineStr">
+        <is>
+          <t>자동 장비</t>
+        </is>
+      </c>
+      <c r="B65" s="24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C65" s="24" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="D65" s="24" t="inlineStr">
+        <is>
+          <t>더 강한 장비 드롭 시 자동 장착</t>
+        </is>
+      </c>
+      <c r="E65" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>자동 분해</t>
+        </is>
+      </c>
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C66" s="24" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="D66" s="24" t="inlineStr">
+        <is>
+          <t>설정 등급 이하 장비 자동 분해</t>
+        </is>
+      </c>
+      <c r="E66" s="24" t="inlineStr">
+        <is>
+          <t>OFF (일반 등급)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8007,269 +10044,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A2:B22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="65" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>게임명</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>AutoBattle.io</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>장르</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>실시간 멀티플레이 RPG (거상+리니지클래식+포켓몬스터+알비온온라인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>플랫폼</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>웹 브라우저 (Unity WebGL + HTML UI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>서버</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Node.js + Socket.IO + MySQL (Railway)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>맵 크기</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>1000×1000 (좌표 -500~500)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>최대 동접</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>50명</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>핵심 컨텐츠</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>마을 교역</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>5개 마을 간 교역품 매매로 차익 실현 (거상)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>PvP / 성 점령</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>PK, 카르마, 풀룻, 왕 시스템, 성채 점령 (리니지)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>몬스터 테이밍</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>몬스터 포획 → 용병화, 등급별 확률 (포켓몬)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>풀룻 PK</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>사망시 골드 50% + 인벤토리 30% 드롭 (알비온)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>전직 시스템</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Lv.20 달성 시 상위 클래스로 전직</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>변신 시스템</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>특정 몬스터 처치 후 해당 몬스터로 변신</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>낮/밤 순환</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>10분 주기 낮밤 전환, 밤엔 몬스터 강화</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>장비 강화</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>+1~+10, 7이상 실패시 파괴 위험</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>펫 &amp; 탈것</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>전투 보조 펫 5종, 이동속도 탈것 4종</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>제작 시스템</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>무기/방어구/장신구/소비품 14종 레시피</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>칭호 시스템</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>업적 달성시 칭호 획득 (7종)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>퀘스트</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>일일 퀘스트 3종 + 메인 퀘스트 6종</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>결제 시스템</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Toss Payments 다이아몬드 결제</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8608,7 +10383,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8787,7 +10562,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9034,7 +10809,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9386,7 +11161,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10602,6 +12377,268 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:B22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>게임명</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>AutoBattle.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>장르</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>실시간 멀티플레이 RPG (거상+리니지클래식+포켓몬스터+알비온온라인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>웹 브라우저 (Unity WebGL + HTML UI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>서버</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Node.js + Socket.IO + MySQL (Railway)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>맵 크기</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>1000×1000 (좌표 -500~500)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>최대 동접</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>50명</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>핵심 컨텐츠</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>마을 교역</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>5개 마을 간 교역품 매매로 차익 실현 (거상)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>PvP / 성 점령</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>PK, 카르마, 풀룻, 왕 시스템, 성채 점령 (리니지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>몬스터 테이밍</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>몬스터 포획 → 용병화, 등급별 확률 (포켓몬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>풀룻 PK</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>사망시 골드 50% + 인벤토리 30% 드롭 (알비온)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>전직 시스템</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Lv.20 달성 시 상위 클래스로 전직</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>변신 시스템</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>특정 몬스터 처치 후 해당 몬스터로 변신</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>낮/밤 순환</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>10분 주기 낮밤 전환, 밤엔 몬스터 강화</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>장비 강화</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>+1~+10, 7이상 실패시 파괴 위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>펫 &amp; 탈것</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>전투 보조 펫 5종, 이동속도 탈것 4종</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>제작 시스템</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>무기/방어구/장신구/소비품 14종 레시피</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>칭호 시스템</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>업적 달성시 칭호 획득 (7종)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>퀘스트</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>일일 퀘스트 3종 + 메인 퀘스트 6종</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>결제 시스템</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Toss Payments 다이아몬드 결제</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11151,7 +13188,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12203,7 +14240,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12485,7 +14522,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13480,7 +15517,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14536,7 +16573,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15014,653 +17051,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>교역품 (20종)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>상품ID</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>상품명</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>기본가격(G)</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>분류</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>goods_silk</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>비단</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>의류/직물</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>높은 가격 변동폭</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>goods_iron</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>철광석</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>광물/금속</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>제작 재료로도 사용</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>goods_herb</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>약초</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>식물/약재</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>물약 제작 재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>goods_gem</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>보석</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>귀금속</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>장신구 제작 재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>goods_wood</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>목재</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>건축/재료</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>기본 제작 재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>goods_leather</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>가죽</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>가공품</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>방어구 제작 재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>goods_spice</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>향신료</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>150</v>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>식품/향료</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>고급 요리 재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>goods_potion</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>물약 원료</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>연금술</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>물약 제작 필수</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>goods_pearl</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>진주</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>300</v>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>귀금속</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>희귀 교역품</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>goods_crystal</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>마법 수정</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>마법재료</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>강화 재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>goods_wine</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>고급 와인</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>180</v>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>식품/음료</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>사치품</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>goods_fur</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>고급 모피</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>가공품</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>방한 재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>goods_incense</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>향</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>기호품</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>버프 재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>goods_dye</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>염료</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>가공품</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>스킨 재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>goods_salt</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>소금</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>식품/조미</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>기본 교역품</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>goods_fish</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>건어물</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>식품</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>기본 교역품</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>goods_gold_bar</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>금괴</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>귀금속</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>최고가 교역품</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>goods_dragon_eye</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>용의 눈</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>800</v>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>희귀재료</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>전설 제작 재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>goods_star_dust</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>별의 가루</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>400</v>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>마법재료</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>강화 촉매</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>goods_moonstone</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>월석</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n">
-        <v>350</v>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>마법재료</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>장신구 재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>교역 규칙</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>가격 변동</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>마을별 0.5~1.5배 가격 랜덤 (10분 주기 변동)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>구매 조건</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>해당 마을 존에 위치해야 구매 가능</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>판매 조건</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>다른 마을로 이동 후 판매 (차익 실현)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>판매 수수료</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>판매가의 10% 수수료</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>마켓 수수료</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>플레이어간 거래 5% 수수료</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>위험 요소</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>PK 사망시 교역품 30% 드롭</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>이익 극대화</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>가격이 낮은 마을에서 매입 → 높은 마을에서 매도</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -194,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -246,6 +246,22 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -11167,22 +11183,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>구현 현황 (2026-04-06 기준)</t>
-        </is>
-      </c>
-    </row>
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>구현 현황 최종 (2026-04-06) — 9700+ lines, 123 handlers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -11201,1173 +11218,1405 @@
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>세부 사항</t>
+          <t>세부</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>핵심</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>자동 전투</t>
-        </is>
-      </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>클래스 4종 + 분기 전직 8종</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>평화 모드 자동 사냥, PvP 모드 수동 조이스틱</t>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>어쌔신→쉐도우로드/나이트블레이드, 워리어→워로드/버서커 등</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>핵심</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>클래스 4종</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>클래스별 5스킬 + MP 시스템</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>어쌔신/워리어/나이트/메이지 + 전직 (Lv.20)</t>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>액티브/패시브/궁극기, MP 소모/회복, 쿨타임 HUD</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>핵심</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>클래스별 5스킬</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>자동 전투 + 액티브 부스트</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>액티브+패시브+궁극기, 도발/은신/전투함성 구현</t>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>자동 사냥, 탭 시 5초 x1.3 데미지</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>핵심</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>몬스터 AI 4종</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>50개 존 (2000x2000 맵)</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>wander/charge/aoe/breath 등급별 고유 AI</t>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>마을 8, 사냥터 38, 특수 4, 웨이포인트 이동</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>핵심</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>존별 몬스터 배합</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>몬스터 600마리 + 7등급 + AI 4종</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>18개 존에 등급별 스폰 비율 + 레벨 스케일링</t>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>일반~신화, wander/charge/aoe/breath, 존별 배합</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>핵심</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>존 보너스</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>속성 시스템 + 날씨 연동</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>EXP/골드 보너스, HUD 실시간 표시</t>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>4속성 상성 + 날씨 5종 (비/안개/눈/폭풍) 속성 보너스</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>장비</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>5등급 시스템</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>9부위 × 5등급 = 45+ 종</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>일반→고급→희귀→영웅→전설, 귀속 아이템</t>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>무기/방어구/투구/장갑/신발/반지/목걸이/망토/벨트</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>장비</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>7부위 장비</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>강화 +15 + 잭팟(대성공/기적)</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>무기/방어구/투구/장갑/신발/반지/목걸이 (25종)</t>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>보호/축복 주문서, 대성공+2, 기적=MAX</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>장비</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>강화 +15</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>랜덤 옵션 + 세트 보너스 3종</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>단계별 확률, 보호/축복 주문서, 파괴 리스크</t>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>드래곤/영웅/태초 세트, 등급별 랜덤옵션</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>장비</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>랜덤 옵션</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>룬 14종 + 룬 워드 7종</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>등급별 0~4개, 크리/회피/HP/속도/경험치/골드</t>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>한글 룬 ㄱ~ㅎ, 3개 조합=룬워드, recalcStats 반영</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>장비</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>장비 해제</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>장비 합성 + 옵션 리롤 + 분해</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>착용 중 장비 해제 → 인벤토리 반환</t>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>같은 등급 3개→상위 1개, 100D 리롤, 재료 분해</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>장비 비교 + 레벨 요구 + 귀속</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t>현재 vs 신규 비교 모달, 전설 귀속</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>전투</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>속성 시스템</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>데미지 공식 (속성+날씨+버프)</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>4속성 상성 (화&gt;풍&gt;토&gt;수), 유리+25%/불리-20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>getBuffedStat 적용, 날씨 속성 +15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>전투</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>버프/디버프 14종</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>보스 페이즈 (50%/25% 전환)</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>실시간 UI 표시, DOT/스턴/슬로우/무적 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>분노(ATK x1.3+브레스) → 필사(ATK x1.8+광역)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>전투</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>데미지 숫자</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>킬 스트릭 보상 (x1.5~x5)</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>플로팅 텍스트 (크리:빨강, 스킬:금색)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>10/25/50/100킬 배율, 서버 공지</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>전투</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>크리티컬 루트 (5% 반짝이)</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D19" s="29" t="inlineStr">
+        <is>
+          <t>3초 제한, 희귀~영웅 확정 드롭</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>전투</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>몬스터 공격 경고</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>돌진 0.5초 전 빨간 경고</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>경제</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>마을 교역</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>마을 교역 8마을 20종</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>20종 교역품, 5마을, 10분 가격 변동</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
+        <is>
+          <t>10분 가격 변동, 교역 이익 추적</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>경제</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>경매장</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>경매장 (등록/입찰/만료)</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>등록/즉구/입찰/만료 반환, 수수료 5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>수수료 5%, 24시간 만료, 귀속 체크</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>경제</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>우편 거래</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>우편 거래 + 1:1 거래</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>아이템/골드 전송, 귀속 체크, Lv.15+</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
+        <is>
+          <t>Lv.15+, 50G+수수료, 귀속 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>경제</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>NPC 장비 상점</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>NPC 장비 상점 + 일괄 판매</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
-        <is>
-          <t>골드 9종 + 다이아 2종 장비 판매</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>골드 9종 + 다이아 2종, 등급 이하 일괄 판매</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>던전</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>3종 던전</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>3종 던전 + 파티 입장</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>어둠동굴/지하감옥/드래곤레이드, 파티 입장</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
+        <is>
+          <t>어둠동굴/지하감옥/드래곤레이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>던전</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>무한의 탑</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>무한의 탑 100층</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t>100층, 층수별 보상, 최고 기록 저장</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
+        <is>
+          <t>층수별 보상, 최고 기록 저장</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t>던전</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>월드 보스 3종</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>월드 보스 3종 (페이즈)</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>5분마다 스폰, 기여도 기반 보상, MVP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
+        <is>
+          <t>기여도 기반 보상, MVP, 3페이즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>던전</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>필드 보스</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>시즌 균열 (2주 로테이션)</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>12:00/20:00 고급 사냥터 3곳 스폰</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>테이밍</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>몬스터 테이밍</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
+        <is>
+          <t>4테마, 무한 깊이, 시즌 리더보드+보상</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>소셜</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>혈맹 Lv.1~5 + 스킬/창고/전쟁</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>등급별 포획률, 용병 변환, NPC 판매</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>테이밍</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>용병 시스템</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="D29" s="29" t="inlineStr">
+        <is>
+          <t>기부/레벨업/직위/추방/탈퇴</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>소셜</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>길드 채팅 + 온라인 멤버</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>거리 제한, 소유자 이름, 공격 스타일</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>테이밍</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>자동 군대 소환</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
+        <is>
+          <t>길드원 전용 채팅, 온라인 상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>소셜</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>파티 (EXP 공유/던전)</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>200G/마리, 오너 레벨×80% 스케일링</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>PvP</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>PK/카르마</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="D31" s="29" t="inlineStr">
+        <is>
+          <t>레벨차 패널티, 파티 던전 입장</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>소셜</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>진영 3종 (태양/달/별)</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
-        <is>
-          <t>카오틱, 약탈(인벤30%+골드50%), EXP 손실</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>PvP</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>공성전</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="D32" s="27" t="inlineStr">
+        <is>
+          <t>ATK/EXP/DEF 보너스, 존 점령</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>소셜</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>친구/귓속말 + 이모트 8종</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>5분 점령, 세금 수입 (5분당 500G/인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>PvP</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>아레나</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="D33" s="29" t="inlineStr">
+        <is>
+          <t>온라인 표시, 이모지 브로드캐스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>소셜</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>플레이어 조회</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>1:1 자동 매칭, 포인트 랭킹, 일일 10회</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>PvP</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>혈맹 전쟁</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="D34" s="27" t="inlineStr">
+        <is>
+          <t>타 플레이어 장비/스탯/진영 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>아레나 1v1 + 포인트 랭킹</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>24시간, PK 페널티 면제</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>소셜</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>혈맹</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="D35" s="29" t="inlineStr">
+        <is>
+          <t>자동 매칭, 3분 타임아웃, TOP 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>현상금 게시판</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
-        <is>
-          <t>Lv.1~5, 스킬/창고/기부/전쟁/직위</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>소셜</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>파티</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="D36" s="27" t="inlineStr">
+        <is>
+          <t>10분 갱신, 5분 제한, 역전 보상</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>의뢰 게시판 (플레이어 생성)</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>생성/초대/탈퇴/해산, EXP 공유, 던전 파티 입장</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>소셜</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>친구</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="inlineStr">
+      <c r="D37" s="29" t="inlineStr">
+        <is>
+          <t>자유 타입, 1시간 만료, 10% 수수료</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="inlineStr">
+        <is>
+          <t>트레저 고블린</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D35" s="21" t="inlineStr">
-        <is>
-          <t>요청/수락/삭제, 온라인 표시, 최대 50명</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>소셜</t>
-        </is>
-      </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>귓속말</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="D38" s="27" t="inlineStr">
+        <is>
+          <t>3~8분, 15초 제한, 골드x10+재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>유성우 이벤트</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>1:1 비밀 메시지, XSS 방지</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>소셜</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>채팅</t>
-        </is>
-      </c>
-      <c r="C37" s="20" t="inlineStr">
+      <c r="D39" s="29" t="inlineStr">
+        <is>
+          <t>20~40분, 2분 AOE+파편, 존 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B40" s="25" t="inlineStr">
+        <is>
+          <t>떠돌이 상인</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
-        <is>
-          <t>전체 채팅, 왕[King]/카오틱[PK] 표시</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
+      <c r="D40" s="27" t="inlineStr">
+        <is>
+          <t>8~15분, 90초 한정, 선착순 3딜</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>골드 피버 (PK존 x3)</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D41" s="29" t="inlineStr">
+        <is>
+          <t>15분마다, 3분간</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>낚시 미니게임</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D42" s="27" t="inlineStr">
+        <is>
+          <t>8종 물고기, 낚시 레벨 1~50</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>몬스터 도감 80+종</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D43" s="29" t="inlineStr">
+        <is>
+          <t>마일스톤 10/25/50/전종 보상</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="inlineStr">
+        <is>
+          <t>출석 캘린더 28일</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D44" s="27" t="inlineStr">
+        <is>
+          <t>7일 희귀/14일 전설재료/28일 전설장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>탐험도 50존</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D45" s="29" t="inlineStr">
+        <is>
+          <t>25/50/75/100% 마일스톤 보상</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="25" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>펫 5종</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>프레스티지 (환생) 10단계</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>HP회복/ATK보너스/EXP보너스/자동부활 실제 적용</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="D46" s="27" t="inlineStr">
+        <is>
+          <t>Lv.50 리셋, 영구 보너스, recalcStats 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>탈것 4종</t>
-        </is>
-      </c>
-      <c r="C39" s="20" t="inlineStr">
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>펫 5종 + 탈것 4종</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D39" s="21" t="inlineStr">
-        <is>
-          <t>SPD+30~100%, 이동 로직에 실제 적용</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="D47" s="29" t="inlineStr">
+        <is>
+          <t>HP리젠/ATK/EXP/자동부활 실적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="25" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>칭호 14종</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="B48" s="25" t="inlineStr">
+        <is>
+          <t>칭호 14종 + 효과 적용</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D40" s="19" t="inlineStr">
-        <is>
-          <t>전투/경제/소셜/주간랭킹, 효과 적용</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="D48" s="27" t="inlineStr">
+        <is>
+          <t>전투/경제/주간랭킹, recalcStats 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="24" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
-        <is>
-          <t>퀘스트</t>
-        </is>
-      </c>
-      <c r="C41" s="20" t="inlineStr">
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>퀘스트 21종 + 실시간 진행도</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D41" s="21" t="inlineStr">
-        <is>
-          <t>일일4+주간4+메인10+업적3, 자동 초기화</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+      <c r="D49" s="29" t="inlineStr">
+        <is>
+          <t>일일4/주간4/메인10/업적3, 자동 초기화</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>출석 체크</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="B50" s="25" t="inlineStr">
+        <is>
+          <t>변신 4종 + 제작 50+ 레시피</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>연속 출석, 7일 희귀 상자, 보상 스케일링</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="D50" s="27" t="inlineStr">
+        <is>
+          <t>스탯 버프, 무기/방어/장신구/요리/주문서</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>스탯 포인트</t>
-        </is>
-      </c>
-      <c r="C43" s="20" t="inlineStr">
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>낮/밤 + 날씨 5종</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D43" s="21" t="inlineStr">
-        <is>
-          <t>STR/DEX/INT/CON, 리셋 가능 (골드)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="14" t="inlineStr">
+      <c r="D51" s="29" t="inlineStr">
+        <is>
+          <t>몬스터 강화, 속성 보너스</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="25" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
-        <is>
-          <t>제작</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="B52" s="25" t="inlineStr">
+        <is>
+          <t>주간 랭킹 보상 + 공성 세금</t>
+        </is>
+      </c>
+      <c r="C52" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D44" s="19" t="inlineStr">
-        <is>
-          <t>무기/방어구/장신구/투구/장갑/신발/물약/요리/주문서</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="D52" s="27" t="inlineStr">
+        <is>
+          <t>월요일 보상, 5분당 500G</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="24" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
-        <is>
-          <t>변신</t>
-        </is>
-      </c>
-      <c r="C45" s="20" t="inlineStr">
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>테이밍 + 용병 (등급별 비용)</t>
+        </is>
+      </c>
+      <c r="C53" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D45" s="21" t="inlineStr">
-        <is>
-          <t>슬라임/오크/다크나이트/드래곤, 시간제 스탯 버프</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>시스템</t>
-        </is>
-      </c>
-      <c r="B46" s="14" t="inlineStr">
-        <is>
-          <t>낮/밤</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="D53" s="29" t="inlineStr">
+        <is>
+          <t>50~2000G, 공격 스타일 실적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B54" s="25" t="inlineStr">
+        <is>
+          <t>글래스모피즘 디자인 시스템</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D46" s="19" t="inlineStr">
-        <is>
-          <t>10분 주기, 밤 화면 어두움, 언데드 강화</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>시스템</t>
-        </is>
-      </c>
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>BM 상점</t>
-        </is>
-      </c>
-      <c r="C47" s="20" t="inlineStr">
+      <c r="D54" s="27" t="inlineStr">
+        <is>
+          <t>CSS 변수 16+, .btn/.card 컴포넌트</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="24" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t>모달 시스템 (prompt 0개)</t>
+        </is>
+      </c>
+      <c r="C55" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D47" s="21" t="inlineStr">
-        <is>
-          <t>다이아몬드, 소모품/장비/코스메틱</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t>시스템</t>
-        </is>
-      </c>
-      <c r="B48" s="14" t="inlineStr">
-        <is>
-          <t>랭킹</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="inlineStr">
+      <c r="D55" s="29" t="inlineStr">
+        <is>
+          <t>범용 게임 모달, 외부 클릭 닫기</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B56" s="25" t="inlineStr">
+        <is>
+          <t>레벨업 축하 + 존 공지</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D48" s="19" t="inlineStr">
-        <is>
-          <t>레벨/PvP/골드/아레나 TOP 10~20</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>시스템</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>희귀 상자</t>
-        </is>
-      </c>
-      <c r="C49" s="20" t="inlineStr">
+      <c r="D56" s="27" t="inlineStr">
+        <is>
+          <t>풀스크린 애니메이션, 2.5초</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>DPS 미터 + 세션 스탯</t>
+        </is>
+      </c>
+      <c r="C57" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D49" s="21" t="inlineStr">
-        <is>
-          <t>전설2%/영웅8%/희귀25%/재료25%/골드40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="14" t="inlineStr">
+      <c r="D57" s="29" t="inlineStr">
+        <is>
+          <t>10초 롤링 DPS, ⏱💀💰 실시간</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="24" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
-        <is>
-          <t>모달 시스템</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>스킬 쿨타임 HUD</t>
+        </is>
+      </c>
+      <c r="C58" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D50" s="19" t="inlineStr">
-        <is>
-          <t>prompt/confirm 전면 교체, 외부 클릭 닫기</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="D58" s="29" t="inlineStr">
+        <is>
+          <t>하단 5스킬 바, 1초 갱신</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="24" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>미니맵</t>
-        </is>
-      </c>
-      <c r="C51" s="20" t="inlineStr">
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>캐릭터 프로필</t>
+        </is>
+      </c>
+      <c r="C59" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D51" s="21" t="inlineStr">
-        <is>
-          <t>200px, 24존 이름+색상, 좌표 표시</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="14" t="inlineStr">
+      <c r="D59" s="29" t="inlineStr">
+        <is>
+          <t>원스톱 스탯/장비/업적 시트</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="24" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
-        <is>
-          <t>효과음 12종</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>인벤토리 (등급색+강화+비교+해제)</t>
+        </is>
+      </c>
+      <c r="C60" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D52" s="19" t="inlineStr">
-        <is>
-          <t>Web Audio API (hit/crit/skill/buff/boss/heal 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="D60" s="29" t="inlineStr">
+        <is>
+          <t>장착중 표시, 비교 모달</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="24" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>인벤토리</t>
-        </is>
-      </c>
-      <c r="C53" s="20" t="inlineStr">
+      <c r="B61" s="24" t="inlineStr">
+        <is>
+          <t>미니맵 220px + 50존 + 좌표</t>
+        </is>
+      </c>
+      <c r="C61" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D53" s="21" t="inlineStr">
-        <is>
-          <t>등급 색상, 강화 레벨, 귀속 태그, 장착중 표시</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="14" t="inlineStr">
+      <c r="D61" s="29" t="inlineStr">
+        <is>
+          <t>존 이름/색상/플레이어/몬스터</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="24" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
-        <is>
-          <t>버프 바</t>
-        </is>
-      </c>
-      <c r="C54" s="18" t="inlineStr">
+      <c r="B62" s="24" t="inlineStr">
+        <is>
+          <t>월드 이벤트 로그</t>
+        </is>
+      </c>
+      <c r="C62" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D54" s="19" t="inlineStr">
-        <is>
-          <t>실시간 활성 버프 아이콘+남은시간 표시</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="D62" s="29" t="inlineStr">
+        <is>
+          <t>최근 30건, 시간순</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B63" s="24" t="inlineStr">
+        <is>
+          <t>효과음 12종 + BGM</t>
+        </is>
+      </c>
+      <c r="C63" s="28" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D63" s="29" t="inlineStr">
+        <is>
+          <t>Web Audio API, 기본 ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="24" t="inlineStr">
         <is>
           <t>보안</t>
         </is>
       </c>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>이동 검증</t>
-        </is>
-      </c>
-      <c r="C55" s="20" t="inlineStr">
+      <c r="B64" s="24" t="inlineStr">
+        <is>
+          <t>이동 검증 + 안전지대 보호</t>
+        </is>
+      </c>
+      <c r="C64" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D55" s="21" t="inlineStr">
-        <is>
-          <t>텔레포트 핵 방지 (틱당 3유닛 제한)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="14" t="inlineStr">
+      <c r="D64" s="29" t="inlineStr">
+        <is>
+          <t>텔레포트 핵 방지, 마을 PvP 차단</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="24" t="inlineStr">
         <is>
           <t>보안</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>입력 검증</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="inlineStr">
+      <c r="B65" s="24" t="inlineStr">
+        <is>
+          <t>데이터 영속화 (ext_data)</t>
+        </is>
+      </c>
+      <c r="C65" s="28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D56" s="19" t="inlineStr">
-        <is>
-          <t>NaN/Infinity/맵 경계 체크</t>
+      <c r="D65" s="29" t="inlineStr">
+        <is>
+          <t>35+ 필드 JSON, DB LONGTEXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t>오버플로우 + PvP 쿨타임</t>
+        </is>
+      </c>
+      <c r="C66" s="28" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D66" s="29" t="inlineStr">
+        <is>
+          <t>골드/다이아/레벨 캡, 10초 CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>총계</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>63개 기능 구현 완료</t>
         </is>
       </c>
     </row>

--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -40,7 +40,7 @@
     <sheet name="월드 보스" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="연금술" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="패치 노트" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="v1.9 ~ v1.25" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="v1.9 ~ v1.26" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13685,7 +13685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13726,7 +13726,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -13736,19 +13736,19 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
+          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -13758,19 +13758,19 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
+          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -13780,19 +13780,19 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>경매장 시트 신규 추가</t>
+          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -13802,19 +13802,19 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
+          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -13824,19 +13824,19 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
+          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -13851,14 +13851,14 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>낚시 시트 신규 추가</t>
+          <t>경매장 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -13868,19 +13868,19 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
+          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -13890,19 +13890,19 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
+          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -13917,14 +13917,14 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>보스 러시 시트 신규 추가</t>
+          <t>낚시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -13934,19 +13934,19 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
+          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -13956,19 +13956,19 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
+          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -13983,14 +13983,14 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛 시트 신규 추가</t>
+          <t>보스 러시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -14000,19 +14000,19 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
+          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -14022,19 +14022,19 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>모듈화</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
+          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -14049,14 +14049,14 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트 시트 신규 추가</t>
+          <t>행운의 룰렛 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -14066,19 +14066,19 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
+          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -14088,19 +14088,19 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>모듈화</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
+          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -14115,14 +14115,14 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스 시트 신규 추가</t>
+          <t>축제 이벤트 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -14132,19 +14132,19 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
+          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -14154,19 +14154,19 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아 시트 신규 추가</t>
+          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -14176,19 +14176,19 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
+          <t>시즌 패스 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -14198,19 +14198,19 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>상점 시트 갱신</t>
+          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -14220,19 +14220,19 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
+          <t>무료 다이아 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -14242,19 +14242,19 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>최대 인원 50→100명 (Lv.10 기준)</t>
+          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -14269,14 +14269,14 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>길드(혈맹) 시트 신규 추가</t>
+          <t>상점 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -14286,19 +14286,19 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
+          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -14308,19 +14308,19 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>대사 시스템</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
+          <t>최대 인원 50→100명 (Lv.10 기준)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -14335,14 +14335,14 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>NPC 시트 신규 추가 (11종)</t>
+          <t>길드(혈맹) 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -14352,19 +14352,19 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>각성기</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
+          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -14374,19 +14374,19 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>대사 시스템</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
+          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -14396,19 +14396,19 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
+          <t>NPC 시트 신규 추가 (11종)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -14418,19 +14418,19 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>각성기</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
+          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -14440,19 +14440,19 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
+          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -14462,19 +14462,19 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>교역</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
+          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -14489,14 +14489,14 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
+          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -14506,19 +14506,19 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
+          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -14528,19 +14528,19 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>교역</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>연금술 시트 신규 추가</t>
+          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -14550,19 +14550,19 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
+          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -14572,19 +14572,19 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (이동 +85%, 비행)</t>
+          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -14594,19 +14594,19 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
+          <t>연금술 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -14616,19 +14616,19 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
+          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -14638,19 +14638,19 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
+          <t>페가수스 (이동 +85%, 비행)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -14660,78 +14660,78 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
+          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
+          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
+          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
+          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
         </is>
       </c>
     </row>
@@ -14748,19 +14748,19 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
+          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -14770,19 +14770,19 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>상태이상</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
+          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -14797,14 +14797,14 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
         </is>
       </c>
     </row>
@@ -14836,12 +14836,12 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>컨텐츠</t>
+          <t>상태이상</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
         </is>
       </c>
     </row>
@@ -14863,27 +14863,93 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>컨텐츠</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
           <t>v1.6 이전</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>기반</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>마을/사냥/PvP/카르마/펫/탈것/제작/교역/길드/공성/투기장 등</t>
         </is>
@@ -14903,7 +14969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14950,378 +15016,378 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js 신규</t>
+          <t>lottery → server.js</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>등록 2% + 낙찰 5%</t>
+          <t>첫 모듈 통합 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>활성 한도</t>
+          <t>lottery_status</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>플레이어당 10개</t>
+          <t>상태/가격/상품 풀 조회</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>자기 입찰 금지</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>game/fishing.js 신규</t>
+          <t>lottery_free_spin</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
+          <t>매일 무료 1회 스핀</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 = 20000G + 칭호</t>
+          <t>자정 초기화</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>전설의 비단잉어</t>
+          <t>lottery_paid_spin</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>드래곤 낚싯대 + 가중치 1</t>
+          <t>유료 1회 / 10연속</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>5000G + 평생 행운 +5%</t>
+          <t>count: 1 또는 10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>game/boss_rush.js 신규</t>
+          <t>game/auction.js 신규</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 / HP ×1.35 스케일링</t>
+          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>최종 보상: 200💎 + 용재료 ×5</t>
+          <t>등록 2% + 낙찰 5%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>입장</t>
+          <t>활성 한도</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 / 1000G / 30💎</t>
+          <t>플레이어당 10개</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>랭킹 시스템</t>
+          <t>자기 입찰 금지</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>챔피언 보상</t>
+          <t>game/fishing.js 신규</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
+          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>신화 크라켄 = 20000G + 칭호</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js 신규</t>
+          <t>전설의 비단잉어</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 / 가중치 1000</t>
+          <t>드래곤 낚싯대 + 가중치 1</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 + 유료</t>
+          <t>5000G + 평생 행운 +5%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>영웅 장비 상자</t>
+          <t>game/boss_rush.js 신규</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>확률 0.2% (가장 희귀)</t>
+          <t>20웨이브 / HP ×1.35 스케일링</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>전설 보상</t>
+          <t>최종 보상: 200💎 + 용재료 ×5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>200 다이아</t>
+          <t>입장</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>확률 0.8%</t>
+          <t>매일 무료 3회 / 1000G / 30💎</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>랭킹 시스템</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>신년 축제</t>
+          <t>챔피언 보상</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>1/1 ~ 1/7</t>
+          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>골드 +50% / EXP +30%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>봄꽃 축제</t>
+          <t>game/lottery.js 신규</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>4/1 ~ 4/14</t>
+          <t>10종 보상 / 가중치 1000</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>HP재생 +30% / 드롭 +20%</t>
+          <t>매일 무료 1회 + 유료</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>한여름 밤의 축제</t>
+          <t>영웅 장비 상자</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>7/15 ~ 8/15</t>
+          <t>확률 0.2% (가장 희귀)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>화염 +30% / PvP 보상 +50%</t>
+          <t>전설 보상</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>할로윈 축제</t>
+          <t>200 다이아</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>10/25 ~ 11/1</t>
+          <t>확률 0.8%</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>크리 +10% / 언데드 +50%</t>
+          <t>잭팟</t>
         </is>
       </c>
     </row>
@@ -15338,206 +15404,206 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>겨울 축제</t>
+          <t>신년 축제</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>12/20 ~ 12/31</t>
+          <t>1/1 ~ 1/7</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
+          <t>골드 +50% / EXP +30%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>game/season.js 신규</t>
+          <t>봄꽃 축제</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>15티어 / 30일 / 무료+프리미엄</t>
+          <t>4/1 ~ 4/14</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
+          <t>HP재생 +30% / 드롭 +20%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>XP 획득 7종</t>
+          <t>한여름 밤의 축제</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>퀘/보스/PvP/월드보스/던전/제작</t>
+          <t>7/15 ~ 8/15</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>일일 +200 ~ 월드보스 +500</t>
+          <t>화염 +30% / PvP 보상 +50%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 가격</t>
+          <t>할로윈 축제</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>1500 다이아</t>
+          <t>10/25 ~ 11/1</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>시즌 당 1회</t>
+          <t>크리 +10% / 언데드 +50%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Lv.40 달성</t>
+          <t>겨울 축제</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>각성기 해금 마일스톤</t>
+          <t>12/20 ~ 12/31</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>150💎</t>
+          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Lv.50 달성</t>
+          <t>game/season.js 신규</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>환생 가능 마일스톤</t>
+          <t>15티어 / 30일 / 무료+프리미엄</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>250💎</t>
+          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>첫 환생</t>
+          <t>XP 획득 7종</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>prestige 1차</t>
+          <t>퀘/보스/PvP/월드보스/던전/제작</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>500💎</t>
+          <t>일일 +200 ~ 월드보스 +500</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>첫 월드 보스</t>
+          <t>프리미엄 가격</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 처치 보너스</t>
+          <t>1500 다이아</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>100💎</t>
+          <t>시즌 당 1회</t>
         </is>
       </c>
     </row>
@@ -15554,125 +15620,125 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>업적 50개</t>
+          <t>Lv.40 달성</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>업적 마일스톤</t>
+          <t>각성기 해금 마일스톤</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>200💎</t>
+          <t>150💎</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>불사조 스킨</t>
+          <t>Lv.50 달성</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>환생 가능 마일스톤</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>불사조 깃털 이펙트 (영구)</t>
+          <t>250💎</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>폭풍 스킨</t>
+          <t>첫 환생</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>prestige 1차</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>번개 오라 이펙트 (영구)</t>
+          <t>500💎</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>상점 (편의)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 자동물약</t>
+          <t>첫 월드 보스</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>500 다이아</t>
+          <t>월드 보스 처치 보너스</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>24시간 자동물약 무한</t>
+          <t>100💎</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>상점 (상자)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 보물 상자</t>
+          <t>업적 50개</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>300 다이아</t>
+          <t>업적 마일스톤</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>전설 장비 확정 + 다이아</t>
+          <t>200💎</t>
         </is>
       </c>
     </row>
@@ -15684,130 +15750,130 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>상점 (재료)</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>전설 재료 패키지</t>
+          <t>불사조 스킨</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>600 다이아</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
+          <t>불사조 깃털 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 분노</t>
+          <t>폭풍 스킨</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>크리티컬 +5%</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>60명 정원</t>
+          <t>번개 오라 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.7</t>
+          <t>상점 (편의)</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 신속</t>
+          <t>프리미엄 자동물약</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>이동속도 +10%</t>
+          <t>500 다이아</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>70명 정원</t>
+          <t>24시간 자동물약 무한</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.8</t>
+          <t>상점 (상자)</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 회복</t>
+          <t>프리미엄 보물 상자</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>HP 재생 +50%</t>
+          <t>300 다이아</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>80명 정원</t>
+          <t>전설 장비 확정 + 다이아</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.9</t>
+          <t>상점 (재료)</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 운명</t>
+          <t>전설 재료 패키지</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>회피 +5%</t>
+          <t>600 다이아</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>90명 정원</t>
+          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
         </is>
       </c>
     </row>
@@ -15819,211 +15885,211 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.10</t>
+          <t>혈맹 Lv.6</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 전설</t>
+          <t>혈맹의 분노</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>전 스탯 +5%</t>
+          <t>크리티컬 +5%</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>100명 정원 — 최종</t>
+          <t>60명 정원</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.7</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>점쟁이</t>
+          <t>혈맹의 신속</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
+          <t>이동속도 +10%</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>70명 정원</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.8</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>감정사</t>
+          <t>혈맹의 회복</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
+          <t>HP 재생 +50%</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>80명 정원</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.9</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>수집가</t>
+          <t>혈맹의 운명</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
+          <t>회피 +5%</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>90명 정원</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>각성기 (어쌔신)</t>
+          <t>혈맹 Lv.10</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>천 개의 칼날</t>
+          <t>혈맹의 전설</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
+          <t>전 스탯 +5%</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>100명 정원 — 최종</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>각성기 (워리어)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>대지 가르기</t>
+          <t>점쟁이</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
+          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>각성기 (나이트)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>불멸의 수호자</t>
+          <t>감정사</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>피해 90% 감소 / 도발 / 10초</t>
+          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>각성기 (메이지)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>시간 정지</t>
+          <t>수집가</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
+          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
@@ -16035,17 +16101,17 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>각성기 (클레릭)</t>
+          <t>각성기 (어쌔신)</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>신의 은총</t>
+          <t>천 개의 칼날</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>HP 100% 회복 / 전스탯 +50%</t>
+          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -16057,108 +16123,108 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (워리어)</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>폭풍 정복자</t>
+          <t>대지 가르기</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인 처치</t>
+          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>10,000G + 150다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (나이트)</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>연금술사</t>
+          <t>불멸의 수호자</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>엘릭서 10회 제작</t>
+          <t>피해 90% 감소 / 도발 / 10초</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>5,000G + 80다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (메이지)</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>그림자 정복자</t>
+          <t>시간 정지</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 클리어</t>
+          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>8,000G + 120다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (클레릭)</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>전설의 동반자</t>
+          <t>신의 은총</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>전설급 펫 진화</t>
+          <t>HP 100% 회복 / 전스탯 +50%</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>6,000G + 100다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
@@ -16175,206 +16241,206 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>이국의 상인</t>
+          <t>폭풍 정복자</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>사치품 교역 5회</t>
+          <t>폭풍의 거인 처치</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>4,000G + 60다이아</t>
+          <t>10,000G + 150다이아</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인</t>
+          <t>연금술사</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>HP 100,000 / ATK 140 / DEF 90</t>
+          <t>엘릭서 10회 제작</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>EXP 10000 + 6000G</t>
+          <t>5,000G + 80다이아</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>시간의 수호자</t>
+          <t>그림자 정복자</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>HP 70,000 / ATK 170 / DEF 60</t>
+          <t>그림자 미궁 클리어</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>EXP 9000 + 7000G</t>
+          <t>8,000G + 120다이아</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>교역품</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
+          <t>전설의 동반자</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종</t>
+          <t>전설급 펫 진화</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>기본가 600~900G</t>
+          <t>6,000G + 100다이아</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>타이탄의 엘릭서</t>
+          <t>이국의 상인</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>용재료×3 + 마법재료×10</t>
+          <t>사치품 교역 5회</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>ATK ×1.5 / 30분</t>
+          <t>4,000G + 60다이아</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>강철 엘릭서</t>
+          <t>폭풍의 거인</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>철광석×30 + 마법재료×10</t>
+          <t>HP 100,000 / ATK 140 / DEF 90</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>DEF ×1.5 / 30분</t>
+          <t>EXP 10000 + 6000G</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>질풍 엘릭서</t>
+          <t>시간의 수호자</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>약초×20 + 마법재료×8</t>
+          <t>HP 70,000 / ATK 170 / DEF 60</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>SPD ×1.4 / 20분</t>
+          <t>EXP 9000 + 7000G</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>교역품</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>지혜 엘릭서</t>
+          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>마법수정×5 + 영혼재료×5</t>
+          <t>이국의 사치품 3종</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>EXP ×2.5 / 15분</t>
+          <t>기본가 600~900G</t>
         </is>
       </c>
     </row>
@@ -16391,260 +16457,260 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>행운 엘릭서</t>
+          <t>타이탄의 엘릭서</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>보석×10 + 마법재료×5</t>
+          <t>용재료×3 + 마법재료×10</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>GOLD ×2.0 / 15분</t>
+          <t>ATK ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>불사조 (pet_phoenix)</t>
+          <t>강철 엘릭서</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>불꽃산 보스 50처치</t>
+          <t>철광석×30 + 마법재료×10</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>화염 DMG +20% (진화 +40%)</t>
+          <t>DEF ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>유니콘 (pet_unicorn)</t>
+          <t>질풍 엘릭서</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>다이아 800개</t>
+          <t>약초×20 + 마법재료×8</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>회피 +10% (진화 +20%)</t>
+          <t>SPD ×1.4 / 20분</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (mount_pegasus)</t>
+          <t>지혜 엘릭서</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>다이아 1200개</t>
+          <t>마법수정×5 + 영혼재료×5</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>이동속도 +85% / 비행</t>
+          <t>EXP ×2.5 / 15분</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁</t>
+          <t>행운 엘릭서</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Lv.38 / 8인 파티 / 7스테이지</t>
+          <t>보석×10 + 마법재료×5</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>22000G + 32000EXP</t>
+          <t>GOLD ×2.0 / 15분</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>드롭</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>드래곤 검/망토/투구/장갑</t>
+          <t>불사조 (pet_phoenix)</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 보스 드롭</t>
+          <t>불꽃산 보스 50처치</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>전설급</t>
+          <t>화염 DMG +20% (진화 +40%)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자</t>
+          <t>유니콘 (pet_unicorn)</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>몬스터 10,000 처치</t>
+          <t>다이아 800개</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>ATK +7%</t>
+          <t>회피 +10% (진화 +20%)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>불멸자</t>
+          <t>페가수스 (mount_pegasus)</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>환생 5회</t>
+          <t>다이아 1200개</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>EXP +25%</t>
+          <t>이동속도 +85% / 비행</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>천공의 군주</t>
+          <t>그림자 미궁</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 10회 처치</t>
+          <t>Lv.38 / 8인 파티 / 7스테이지</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>보스DMG +15%</t>
+          <t>22000G + 32000EXP</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>드롭</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>지역 시트 갱신</t>
+          <t>드래곤 검/망토/투구/장갑</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>25→51개 지역 반영</t>
+          <t>그림자 미궁 보스 드롭</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>전설급</t>
         </is>
       </c>
     </row>
@@ -16656,22 +16722,22 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>칭호 시트 갱신</t>
+          <t>공허의 방랑자</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>7→16종 + 효과/색상 추가</t>
+          <t>몬스터 10,000 처치</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ATK +7%</t>
         </is>
       </c>
     </row>
@@ -16683,22 +16749,22 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>출석 캘린더 시트</t>
+          <t>불멸자</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (28일 사이클)</t>
+          <t>환생 5회</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EXP +25%</t>
         </is>
       </c>
     </row>
@@ -16710,22 +16776,22 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>장비 세트 시트</t>
+          <t>천공의 군주</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (드래곤/영웅/태초)</t>
+          <t>월드 보스 10회 처치</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>보스DMG +15%</t>
         </is>
       </c>
     </row>
@@ -16742,12 +16808,12 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>장비 등급 시트</t>
+          <t>지역 시트 갱신</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+          <t>25→51개 지역 반영</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -16769,12 +16835,12 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>디버프 시트</t>
+          <t>칭호 시트 갱신</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+          <t>7→16종 + 효과/색상 추가</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -16796,12 +16862,12 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>패치 노트 시트</t>
+          <t>출석 캘린더 시트</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (히스토리)</t>
+          <t>신규 추가 (28일 사이클)</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
@@ -16813,25 +16879,133 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>장비 세트 시트</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (드래곤/영웅/태초)</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>장비 등급 시트</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>디버프 시트</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>패치 노트 시트</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (히스토리)</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
           <t>v1.10</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>기획서</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>던전 시트</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>신규 추가 (7종 던전)</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -40,7 +40,7 @@
     <sheet name="월드 보스" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="연금술" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="패치 노트" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="v1.9 ~ v1.26" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="v1.9 ~ v1.27" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13685,7 +13685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13726,7 +13726,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -13741,14 +13741,14 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
+          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -13758,19 +13758,19 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
+          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -13780,19 +13780,19 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
+          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -13802,19 +13802,19 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
+          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -13824,19 +13824,19 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
+          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -13846,19 +13846,19 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>경매장 시트 신규 추가</t>
+          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -13868,19 +13868,19 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
+          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -13890,19 +13890,19 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
+          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -13912,19 +13912,19 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>낚시 시트 신규 추가</t>
+          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -13934,19 +13934,19 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
+          <t>경매장 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -13956,19 +13956,19 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
+          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -13978,19 +13978,19 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>보스 러시 시트 신규 추가</t>
+          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -14000,19 +14000,19 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
+          <t>낚시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -14022,19 +14022,19 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
+          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -14044,19 +14044,19 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛 시트 신규 추가</t>
+          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -14066,19 +14066,19 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
+          <t>보스 러시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -14088,19 +14088,19 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>모듈화</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
+          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -14110,19 +14110,19 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트 시트 신규 추가</t>
+          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -14132,19 +14132,19 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
+          <t>행운의 룰렛 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -14154,19 +14154,19 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
+          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -14176,19 +14176,19 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>모듈화</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스 시트 신규 추가</t>
+          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -14198,19 +14198,19 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
+          <t>축제 이벤트 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -14220,19 +14220,19 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아 시트 신규 추가</t>
+          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -14242,19 +14242,19 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
+          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -14269,14 +14269,14 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>상점 시트 갱신</t>
+          <t>시즌 패스 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -14286,19 +14286,19 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
+          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -14308,19 +14308,19 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>최대 인원 50→100명 (Lv.10 기준)</t>
+          <t>무료 다이아 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -14330,19 +14330,19 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>길드(혈맹) 시트 신규 추가</t>
+          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -14352,19 +14352,19 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
+          <t>상점 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -14374,19 +14374,19 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>대사 시스템</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
+          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -14396,19 +14396,19 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>NPC 시트 신규 추가 (11종)</t>
+          <t>최대 인원 50→100명 (Lv.10 기준)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -14418,19 +14418,19 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>각성기</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
+          <t>길드(혈맹) 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -14440,19 +14440,19 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
+          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -14462,19 +14462,19 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>대사 시스템</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
+          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -14489,14 +14489,14 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
+          <t>NPC 시트 신규 추가 (11종)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -14506,19 +14506,19 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>각성기</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
+          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -14528,19 +14528,19 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>교역</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
+          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -14550,19 +14550,19 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
+          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -14572,19 +14572,19 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
+          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -14594,19 +14594,19 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>연금술 시트 신규 추가</t>
+          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -14616,19 +14616,19 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>교역</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
+          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -14638,19 +14638,19 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>페가수스 (이동 +85%, 비행)</t>
+          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -14660,19 +14660,19 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
+          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -14687,14 +14687,14 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
+          <t>연금술 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -14704,19 +14704,19 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
+          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -14726,107 +14726,107 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
+          <t>페가수스 (이동 +85%, 비행)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
+          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
+          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
+          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
+          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -14836,19 +14836,19 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>상태이상</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
+          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -14858,19 +14858,19 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -14880,19 +14880,19 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -14902,12 +14902,12 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>컨텐츠</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
         </is>
       </c>
     </row>
@@ -14924,32 +14924,120 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>상태이상</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>컨텐츠</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
           <t>v1.6 이전</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>기반</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>마을/사냥/PvP/카르마/펫/탈것/제작/교역/길드/공성/투기장 등</t>
         </is>
@@ -14969,7 +15057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15016,7 +15104,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -15026,7 +15114,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>lottery → server.js</t>
+          <t>fishing → server.js</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -15036,29 +15124,29 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>첫 모듈 통합 마일스톤</t>
+          <t>두 번째 모듈 통합</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>lottery_status</t>
+          <t>fishing_status</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>상태/가격/상품 풀 조회</t>
+          <t>지역/낚싯대/미끼/시간대 조회</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -15070,432 +15158,432 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>lottery_free_spin</t>
+          <t>fishing_cast</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 스핀</t>
+          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>자정 초기화</t>
+          <t>전설/신화 → 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>lottery_paid_spin</t>
+          <t>fishing_buy_rod</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>유료 1회 / 10연속</t>
+          <t>낚싯대 구매 (골드/다이아)</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>count: 1 또는 10</t>
+          <t>5등급 모두</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js 신규</t>
+          <t>lottery → server.js</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>등록 2% + 낙찰 5%</t>
+          <t>첫 모듈 통합 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>활성 한도</t>
+          <t>lottery_status</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>플레이어당 10개</t>
+          <t>상태/가격/상품 풀 조회</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>자기 입찰 금지</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>game/fishing.js 신규</t>
+          <t>lottery_free_spin</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
+          <t>매일 무료 1회 스핀</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 = 20000G + 칭호</t>
+          <t>자정 초기화</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>전설의 비단잉어</t>
+          <t>lottery_paid_spin</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>드래곤 낚싯대 + 가중치 1</t>
+          <t>유료 1회 / 10연속</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>5000G + 평생 행운 +5%</t>
+          <t>count: 1 또는 10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>game/boss_rush.js 신규</t>
+          <t>game/auction.js 신규</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 / HP ×1.35 스케일링</t>
+          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>최종 보상: 200💎 + 용재료 ×5</t>
+          <t>등록 2% + 낙찰 5%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>입장</t>
+          <t>활성 한도</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 / 1000G / 30💎</t>
+          <t>플레이어당 10개</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>랭킹 시스템</t>
+          <t>자기 입찰 금지</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>챔피언 보상</t>
+          <t>game/fishing.js 신규</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
+          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>신화 크라켄 = 20000G + 칭호</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js 신규</t>
+          <t>전설의 비단잉어</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 / 가중치 1000</t>
+          <t>드래곤 낚싯대 + 가중치 1</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 + 유료</t>
+          <t>5000G + 평생 행운 +5%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>영웅 장비 상자</t>
+          <t>game/boss_rush.js 신규</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>확률 0.2% (가장 희귀)</t>
+          <t>20웨이브 / HP ×1.35 스케일링</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>전설 보상</t>
+          <t>최종 보상: 200💎 + 용재료 ×5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>200 다이아</t>
+          <t>입장</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>확률 0.8%</t>
+          <t>매일 무료 3회 / 1000G / 30💎</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>랭킹 시스템</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>신년 축제</t>
+          <t>챔피언 보상</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>1/1 ~ 1/7</t>
+          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>골드 +50% / EXP +30%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>봄꽃 축제</t>
+          <t>game/lottery.js 신규</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>4/1 ~ 4/14</t>
+          <t>10종 보상 / 가중치 1000</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>HP재생 +30% / 드롭 +20%</t>
+          <t>매일 무료 1회 + 유료</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>한여름 밤의 축제</t>
+          <t>영웅 장비 상자</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>7/15 ~ 8/15</t>
+          <t>확률 0.2% (가장 희귀)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>화염 +30% / PvP 보상 +50%</t>
+          <t>전설 보상</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>할로윈 축제</t>
+          <t>200 다이아</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>10/25 ~ 11/1</t>
+          <t>확률 0.8%</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>크리 +10% / 언데드 +50%</t>
+          <t>잭팟</t>
         </is>
       </c>
     </row>
@@ -15512,206 +15600,206 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>겨울 축제</t>
+          <t>신년 축제</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>12/20 ~ 12/31</t>
+          <t>1/1 ~ 1/7</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
+          <t>골드 +50% / EXP +30%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>game/season.js 신규</t>
+          <t>봄꽃 축제</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>15티어 / 30일 / 무료+프리미엄</t>
+          <t>4/1 ~ 4/14</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
+          <t>HP재생 +30% / 드롭 +20%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>XP 획득 7종</t>
+          <t>한여름 밤의 축제</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>퀘/보스/PvP/월드보스/던전/제작</t>
+          <t>7/15 ~ 8/15</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>일일 +200 ~ 월드보스 +500</t>
+          <t>화염 +30% / PvP 보상 +50%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 가격</t>
+          <t>할로윈 축제</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>1500 다이아</t>
+          <t>10/25 ~ 11/1</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>시즌 당 1회</t>
+          <t>크리 +10% / 언데드 +50%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Lv.40 달성</t>
+          <t>겨울 축제</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>각성기 해금 마일스톤</t>
+          <t>12/20 ~ 12/31</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>150💎</t>
+          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Lv.50 달성</t>
+          <t>game/season.js 신규</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>환생 가능 마일스톤</t>
+          <t>15티어 / 30일 / 무료+프리미엄</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>250💎</t>
+          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>첫 환생</t>
+          <t>XP 획득 7종</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>prestige 1차</t>
+          <t>퀘/보스/PvP/월드보스/던전/제작</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>500💎</t>
+          <t>일일 +200 ~ 월드보스 +500</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>첫 월드 보스</t>
+          <t>프리미엄 가격</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 처치 보너스</t>
+          <t>1500 다이아</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>100💎</t>
+          <t>시즌 당 1회</t>
         </is>
       </c>
     </row>
@@ -15728,125 +15816,125 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>업적 50개</t>
+          <t>Lv.40 달성</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>업적 마일스톤</t>
+          <t>각성기 해금 마일스톤</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>200💎</t>
+          <t>150💎</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>불사조 스킨</t>
+          <t>Lv.50 달성</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>환생 가능 마일스톤</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>불사조 깃털 이펙트 (영구)</t>
+          <t>250💎</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>폭풍 스킨</t>
+          <t>첫 환생</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>prestige 1차</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>번개 오라 이펙트 (영구)</t>
+          <t>500💎</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>상점 (편의)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 자동물약</t>
+          <t>첫 월드 보스</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>500 다이아</t>
+          <t>월드 보스 처치 보너스</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>24시간 자동물약 무한</t>
+          <t>100💎</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>상점 (상자)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 보물 상자</t>
+          <t>업적 50개</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>300 다이아</t>
+          <t>업적 마일스톤</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>전설 장비 확정 + 다이아</t>
+          <t>200💎</t>
         </is>
       </c>
     </row>
@@ -15858,130 +15946,130 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>상점 (재료)</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>전설 재료 패키지</t>
+          <t>불사조 스킨</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>600 다이아</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
+          <t>불사조 깃털 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 분노</t>
+          <t>폭풍 스킨</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>크리티컬 +5%</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>60명 정원</t>
+          <t>번개 오라 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.7</t>
+          <t>상점 (편의)</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 신속</t>
+          <t>프리미엄 자동물약</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>이동속도 +10%</t>
+          <t>500 다이아</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>70명 정원</t>
+          <t>24시간 자동물약 무한</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.8</t>
+          <t>상점 (상자)</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 회복</t>
+          <t>프리미엄 보물 상자</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>HP 재생 +50%</t>
+          <t>300 다이아</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>80명 정원</t>
+          <t>전설 장비 확정 + 다이아</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.9</t>
+          <t>상점 (재료)</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 운명</t>
+          <t>전설 재료 패키지</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>회피 +5%</t>
+          <t>600 다이아</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>90명 정원</t>
+          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
         </is>
       </c>
     </row>
@@ -15993,211 +16081,211 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.10</t>
+          <t>혈맹 Lv.6</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 전설</t>
+          <t>혈맹의 분노</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>전 스탯 +5%</t>
+          <t>크리티컬 +5%</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>100명 정원 — 최종</t>
+          <t>60명 정원</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.7</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>점쟁이</t>
+          <t>혈맹의 신속</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
+          <t>이동속도 +10%</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>70명 정원</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.8</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>감정사</t>
+          <t>혈맹의 회복</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
+          <t>HP 재생 +50%</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>80명 정원</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.9</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>수집가</t>
+          <t>혈맹의 운명</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
+          <t>회피 +5%</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>90명 정원</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>각성기 (어쌔신)</t>
+          <t>혈맹 Lv.10</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>천 개의 칼날</t>
+          <t>혈맹의 전설</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
+          <t>전 스탯 +5%</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>100명 정원 — 최종</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>각성기 (워리어)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>대지 가르기</t>
+          <t>점쟁이</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
+          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>각성기 (나이트)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>불멸의 수호자</t>
+          <t>감정사</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>피해 90% 감소 / 도발 / 10초</t>
+          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>각성기 (메이지)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>시간 정지</t>
+          <t>수집가</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
+          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
@@ -16209,17 +16297,17 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>각성기 (클레릭)</t>
+          <t>각성기 (어쌔신)</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>신의 은총</t>
+          <t>천 개의 칼날</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>HP 100% 회복 / 전스탯 +50%</t>
+          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -16231,108 +16319,108 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (워리어)</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>폭풍 정복자</t>
+          <t>대지 가르기</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인 처치</t>
+          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>10,000G + 150다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (나이트)</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>연금술사</t>
+          <t>불멸의 수호자</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>엘릭서 10회 제작</t>
+          <t>피해 90% 감소 / 도발 / 10초</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>5,000G + 80다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (메이지)</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>그림자 정복자</t>
+          <t>시간 정지</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 클리어</t>
+          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>8,000G + 120다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (클레릭)</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>전설의 동반자</t>
+          <t>신의 은총</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>전설급 펫 진화</t>
+          <t>HP 100% 회복 / 전스탯 +50%</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>6,000G + 100다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
@@ -16349,206 +16437,206 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>이국의 상인</t>
+          <t>폭풍 정복자</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>사치품 교역 5회</t>
+          <t>폭풍의 거인 처치</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>4,000G + 60다이아</t>
+          <t>10,000G + 150다이아</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인</t>
+          <t>연금술사</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>HP 100,000 / ATK 140 / DEF 90</t>
+          <t>엘릭서 10회 제작</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>EXP 10000 + 6000G</t>
+          <t>5,000G + 80다이아</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>시간의 수호자</t>
+          <t>그림자 정복자</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>HP 70,000 / ATK 170 / DEF 60</t>
+          <t>그림자 미궁 클리어</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>EXP 9000 + 7000G</t>
+          <t>8,000G + 120다이아</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>교역품</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
+          <t>전설의 동반자</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종</t>
+          <t>전설급 펫 진화</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>기본가 600~900G</t>
+          <t>6,000G + 100다이아</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>타이탄의 엘릭서</t>
+          <t>이국의 상인</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>용재료×3 + 마법재료×10</t>
+          <t>사치품 교역 5회</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>ATK ×1.5 / 30분</t>
+          <t>4,000G + 60다이아</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>강철 엘릭서</t>
+          <t>폭풍의 거인</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>철광석×30 + 마법재료×10</t>
+          <t>HP 100,000 / ATK 140 / DEF 90</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>DEF ×1.5 / 30분</t>
+          <t>EXP 10000 + 6000G</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>질풍 엘릭서</t>
+          <t>시간의 수호자</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>약초×20 + 마법재료×8</t>
+          <t>HP 70,000 / ATK 170 / DEF 60</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>SPD ×1.4 / 20분</t>
+          <t>EXP 9000 + 7000G</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>교역품</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>지혜 엘릭서</t>
+          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>마법수정×5 + 영혼재료×5</t>
+          <t>이국의 사치품 3종</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>EXP ×2.5 / 15분</t>
+          <t>기본가 600~900G</t>
         </is>
       </c>
     </row>
@@ -16565,260 +16653,260 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>행운 엘릭서</t>
+          <t>타이탄의 엘릭서</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>보석×10 + 마법재료×5</t>
+          <t>용재료×3 + 마법재료×10</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>GOLD ×2.0 / 15분</t>
+          <t>ATK ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>불사조 (pet_phoenix)</t>
+          <t>강철 엘릭서</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>불꽃산 보스 50처치</t>
+          <t>철광석×30 + 마법재료×10</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>화염 DMG +20% (진화 +40%)</t>
+          <t>DEF ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>유니콘 (pet_unicorn)</t>
+          <t>질풍 엘릭서</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>다이아 800개</t>
+          <t>약초×20 + 마법재료×8</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>회피 +10% (진화 +20%)</t>
+          <t>SPD ×1.4 / 20분</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (mount_pegasus)</t>
+          <t>지혜 엘릭서</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>다이아 1200개</t>
+          <t>마법수정×5 + 영혼재료×5</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>이동속도 +85% / 비행</t>
+          <t>EXP ×2.5 / 15분</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁</t>
+          <t>행운 엘릭서</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Lv.38 / 8인 파티 / 7스테이지</t>
+          <t>보석×10 + 마법재료×5</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>22000G + 32000EXP</t>
+          <t>GOLD ×2.0 / 15분</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>드롭</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>드래곤 검/망토/투구/장갑</t>
+          <t>불사조 (pet_phoenix)</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 보스 드롭</t>
+          <t>불꽃산 보스 50처치</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>전설급</t>
+          <t>화염 DMG +20% (진화 +40%)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자</t>
+          <t>유니콘 (pet_unicorn)</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>몬스터 10,000 처치</t>
+          <t>다이아 800개</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>ATK +7%</t>
+          <t>회피 +10% (진화 +20%)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>불멸자</t>
+          <t>페가수스 (mount_pegasus)</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>환생 5회</t>
+          <t>다이아 1200개</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>EXP +25%</t>
+          <t>이동속도 +85% / 비행</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>천공의 군주</t>
+          <t>그림자 미궁</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 10회 처치</t>
+          <t>Lv.38 / 8인 파티 / 7스테이지</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>보스DMG +15%</t>
+          <t>22000G + 32000EXP</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>드롭</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>지역 시트 갱신</t>
+          <t>드래곤 검/망토/투구/장갑</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>25→51개 지역 반영</t>
+          <t>그림자 미궁 보스 드롭</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>전설급</t>
         </is>
       </c>
     </row>
@@ -16830,22 +16918,22 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>칭호 시트 갱신</t>
+          <t>공허의 방랑자</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>7→16종 + 효과/색상 추가</t>
+          <t>몬스터 10,000 처치</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ATK +7%</t>
         </is>
       </c>
     </row>
@@ -16857,22 +16945,22 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>출석 캘린더 시트</t>
+          <t>불멸자</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (28일 사이클)</t>
+          <t>환생 5회</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EXP +25%</t>
         </is>
       </c>
     </row>
@@ -16884,22 +16972,22 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>장비 세트 시트</t>
+          <t>천공의 군주</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (드래곤/영웅/태초)</t>
+          <t>월드 보스 10회 처치</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>보스DMG +15%</t>
         </is>
       </c>
     </row>
@@ -16916,12 +17004,12 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>장비 등급 시트</t>
+          <t>지역 시트 갱신</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+          <t>25→51개 지역 반영</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
@@ -16943,12 +17031,12 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>디버프 시트</t>
+          <t>칭호 시트 갱신</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+          <t>7→16종 + 효과/색상 추가</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -16970,12 +17058,12 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>패치 노트 시트</t>
+          <t>출석 캘린더 시트</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (히스토리)</t>
+          <t>신규 추가 (28일 사이클)</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
@@ -16987,25 +17075,133 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>장비 세트 시트</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (드래곤/영웅/태초)</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>장비 등급 시트</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>디버프 시트</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>패치 노트 시트</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (히스토리)</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
           <t>v1.10</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>기획서</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>던전 시트</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>신규 추가 (7종 던전)</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="E81" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -40,7 +40,7 @@
     <sheet name="월드 보스" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="연금술" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="패치 노트" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="v1.9 ~ v1.27" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="v1.9 ~ v1.28" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13685,7 +13685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13726,7 +13726,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -13741,14 +13741,14 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
+          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -13758,19 +13758,19 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
+          <t>event_status 소켓 + /status 엔드포인트 노출</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -13780,19 +13780,19 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
+          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -13802,19 +13802,19 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
+          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -13829,14 +13829,14 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
+          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -13846,19 +13846,19 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
+          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -13868,19 +13868,19 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
+          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -13890,19 +13890,19 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
+          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -13912,19 +13912,19 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
+          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -13934,19 +13934,19 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>경매장 시트 신규 추가</t>
+          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -13956,19 +13956,19 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
+          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -13978,19 +13978,19 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
+          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -14000,19 +14000,19 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>낚시 시트 신규 추가</t>
+          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -14022,19 +14022,19 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
+          <t>경매장 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -14044,19 +14044,19 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
+          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -14066,19 +14066,19 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>보스 러시 시트 신규 추가</t>
+          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -14088,19 +14088,19 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
+          <t>낚시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -14110,19 +14110,19 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
+          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -14132,19 +14132,19 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛 시트 신규 추가</t>
+          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -14154,19 +14154,19 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
+          <t>보스 러시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -14176,19 +14176,19 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>모듈화</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
+          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -14198,19 +14198,19 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트 시트 신규 추가</t>
+          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -14220,19 +14220,19 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
+          <t>행운의 룰렛 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -14242,19 +14242,19 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
+          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -14264,19 +14264,19 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>모듈화</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스 시트 신규 추가</t>
+          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -14286,19 +14286,19 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
+          <t>축제 이벤트 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -14308,19 +14308,19 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아 시트 신규 추가</t>
+          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -14330,19 +14330,19 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
+          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -14357,14 +14357,14 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>상점 시트 갱신</t>
+          <t>시즌 패스 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -14374,19 +14374,19 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
+          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -14396,19 +14396,19 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>최대 인원 50→100명 (Lv.10 기준)</t>
+          <t>무료 다이아 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -14418,19 +14418,19 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>길드(혈맹) 시트 신규 추가</t>
+          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -14440,19 +14440,19 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
+          <t>상점 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -14462,19 +14462,19 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>대사 시스템</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
+          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -14484,19 +14484,19 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>NPC 시트 신규 추가 (11종)</t>
+          <t>최대 인원 50→100명 (Lv.10 기준)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -14506,19 +14506,19 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>각성기</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
+          <t>길드(혈맹) 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -14528,19 +14528,19 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
+          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -14550,19 +14550,19 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>대사 시스템</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
+          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -14577,14 +14577,14 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
+          <t>NPC 시트 신규 추가 (11종)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -14594,19 +14594,19 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>각성기</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
+          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -14616,19 +14616,19 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>교역</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
+          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -14638,19 +14638,19 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
+          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -14660,19 +14660,19 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
+          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -14682,19 +14682,19 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>연금술 시트 신규 추가</t>
+          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -14704,19 +14704,19 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>교역</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
+          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -14726,19 +14726,19 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>페가수스 (이동 +85%, 비행)</t>
+          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -14748,19 +14748,19 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
+          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -14775,14 +14775,14 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
+          <t>연금술 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -14792,19 +14792,19 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
+          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -14814,107 +14814,107 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
+          <t>페가수스 (이동 +85%, 비행)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
+          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
+          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
+          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
+          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -14924,19 +14924,19 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>상태이상</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
+          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -14946,19 +14946,19 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -14968,19 +14968,19 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -14990,12 +14990,12 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>컨텐츠</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
         </is>
       </c>
     </row>
@@ -15012,32 +15012,120 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>상태이상</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>컨텐츠</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
           <t>v1.6 이전</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>기반</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>마을/사냥/PvP/카르마/펫/탈것/제작/교역/길드/공성/투기장 등</t>
         </is>
@@ -15057,7 +15145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15104,7 +15192,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -15114,24 +15202,24 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>fishing → server.js</t>
+          <t>event → server.js</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>3번째 모듈 통합</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>두 번째 모듈 통합</t>
+          <t>축제 시스템 활성화</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -15141,78 +15229,78 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>fishing_status</t>
+          <t>event_status</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>지역/낚싯대/미끼/시간대 조회</t>
+          <t>현재 활성 축제 조회</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>이름/기간/버프/한정 보상</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>fishing_cast</t>
+          <t>/status JSON</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
+          <t>festival 필드 추가</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>전설/신화 → 서버 알림</t>
+          <t>대시보드 확인용</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>fishing_buy_rod</t>
+          <t>축제 인사</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>낚싯대 구매 (골드/다이아)</t>
+          <t>30% 확률로 NPC가 축제 대사 출력</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>5등급 모두</t>
+          <t>spring_blossom 등 5종</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -15222,7 +15310,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>lottery → server.js</t>
+          <t>fishing → server.js</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -15232,29 +15320,29 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>첫 모듈 통합 마일스톤</t>
+          <t>두 번째 모듈 통합</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>lottery_status</t>
+          <t>fishing_status</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>상태/가격/상품 풀 조회</t>
+          <t>지역/낚싯대/미끼/시간대 조회</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -15266,432 +15354,432 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>lottery_free_spin</t>
+          <t>fishing_cast</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 스핀</t>
+          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>자정 초기화</t>
+          <t>전설/신화 → 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>lottery_paid_spin</t>
+          <t>fishing_buy_rod</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>유료 1회 / 10연속</t>
+          <t>낚싯대 구매 (골드/다이아)</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>count: 1 또는 10</t>
+          <t>5등급 모두</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js 신규</t>
+          <t>lottery → server.js</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>등록 2% + 낙찰 5%</t>
+          <t>첫 모듈 통합 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>활성 한도</t>
+          <t>lottery_status</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>플레이어당 10개</t>
+          <t>상태/가격/상품 풀 조회</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>자기 입찰 금지</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>game/fishing.js 신규</t>
+          <t>lottery_free_spin</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
+          <t>매일 무료 1회 스핀</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 = 20000G + 칭호</t>
+          <t>자정 초기화</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>전설의 비단잉어</t>
+          <t>lottery_paid_spin</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>드래곤 낚싯대 + 가중치 1</t>
+          <t>유료 1회 / 10연속</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>5000G + 평생 행운 +5%</t>
+          <t>count: 1 또는 10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>game/boss_rush.js 신규</t>
+          <t>game/auction.js 신규</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 / HP ×1.35 스케일링</t>
+          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>최종 보상: 200💎 + 용재료 ×5</t>
+          <t>등록 2% + 낙찰 5%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>입장</t>
+          <t>활성 한도</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 / 1000G / 30💎</t>
+          <t>플레이어당 10개</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>랭킹 시스템</t>
+          <t>자기 입찰 금지</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>챔피언 보상</t>
+          <t>game/fishing.js 신규</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
+          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>신화 크라켄 = 20000G + 칭호</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js 신규</t>
+          <t>전설의 비단잉어</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 / 가중치 1000</t>
+          <t>드래곤 낚싯대 + 가중치 1</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 + 유료</t>
+          <t>5000G + 평생 행운 +5%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>영웅 장비 상자</t>
+          <t>game/boss_rush.js 신규</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>확률 0.2% (가장 희귀)</t>
+          <t>20웨이브 / HP ×1.35 스케일링</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>전설 보상</t>
+          <t>최종 보상: 200💎 + 용재료 ×5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>200 다이아</t>
+          <t>입장</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>확률 0.8%</t>
+          <t>매일 무료 3회 / 1000G / 30💎</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>랭킹 시스템</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>신년 축제</t>
+          <t>챔피언 보상</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>1/1 ~ 1/7</t>
+          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>골드 +50% / EXP +30%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>봄꽃 축제</t>
+          <t>game/lottery.js 신규</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>4/1 ~ 4/14</t>
+          <t>10종 보상 / 가중치 1000</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>HP재생 +30% / 드롭 +20%</t>
+          <t>매일 무료 1회 + 유료</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>한여름 밤의 축제</t>
+          <t>영웅 장비 상자</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>7/15 ~ 8/15</t>
+          <t>확률 0.2% (가장 희귀)</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>화염 +30% / PvP 보상 +50%</t>
+          <t>전설 보상</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>할로윈 축제</t>
+          <t>200 다이아</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>10/25 ~ 11/1</t>
+          <t>확률 0.8%</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>크리 +10% / 언데드 +50%</t>
+          <t>잭팟</t>
         </is>
       </c>
     </row>
@@ -15708,206 +15796,206 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>겨울 축제</t>
+          <t>신년 축제</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>12/20 ~ 12/31</t>
+          <t>1/1 ~ 1/7</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
+          <t>골드 +50% / EXP +30%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>game/season.js 신규</t>
+          <t>봄꽃 축제</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>15티어 / 30일 / 무료+프리미엄</t>
+          <t>4/1 ~ 4/14</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
+          <t>HP재생 +30% / 드롭 +20%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>XP 획득 7종</t>
+          <t>한여름 밤의 축제</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>퀘/보스/PvP/월드보스/던전/제작</t>
+          <t>7/15 ~ 8/15</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>일일 +200 ~ 월드보스 +500</t>
+          <t>화염 +30% / PvP 보상 +50%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 가격</t>
+          <t>할로윈 축제</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>1500 다이아</t>
+          <t>10/25 ~ 11/1</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>시즌 당 1회</t>
+          <t>크리 +10% / 언데드 +50%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Lv.40 달성</t>
+          <t>겨울 축제</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>각성기 해금 마일스톤</t>
+          <t>12/20 ~ 12/31</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>150💎</t>
+          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Lv.50 달성</t>
+          <t>game/season.js 신규</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>환생 가능 마일스톤</t>
+          <t>15티어 / 30일 / 무료+프리미엄</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>250💎</t>
+          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>첫 환생</t>
+          <t>XP 획득 7종</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>prestige 1차</t>
+          <t>퀘/보스/PvP/월드보스/던전/제작</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>500💎</t>
+          <t>일일 +200 ~ 월드보스 +500</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>첫 월드 보스</t>
+          <t>프리미엄 가격</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 처치 보너스</t>
+          <t>1500 다이아</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>100💎</t>
+          <t>시즌 당 1회</t>
         </is>
       </c>
     </row>
@@ -15924,125 +16012,125 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>업적 50개</t>
+          <t>Lv.40 달성</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>업적 마일스톤</t>
+          <t>각성기 해금 마일스톤</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>200💎</t>
+          <t>150💎</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>불사조 스킨</t>
+          <t>Lv.50 달성</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>환생 가능 마일스톤</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>불사조 깃털 이펙트 (영구)</t>
+          <t>250💎</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>폭풍 스킨</t>
+          <t>첫 환생</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>prestige 1차</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>번개 오라 이펙트 (영구)</t>
+          <t>500💎</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>상점 (편의)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 자동물약</t>
+          <t>첫 월드 보스</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>500 다이아</t>
+          <t>월드 보스 처치 보너스</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>24시간 자동물약 무한</t>
+          <t>100💎</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>상점 (상자)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 보물 상자</t>
+          <t>업적 50개</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>300 다이아</t>
+          <t>업적 마일스톤</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>전설 장비 확정 + 다이아</t>
+          <t>200💎</t>
         </is>
       </c>
     </row>
@@ -16054,130 +16142,130 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>상점 (재료)</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>전설 재료 패키지</t>
+          <t>불사조 스킨</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>600 다이아</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
+          <t>불사조 깃털 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 분노</t>
+          <t>폭풍 스킨</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>크리티컬 +5%</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>60명 정원</t>
+          <t>번개 오라 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.7</t>
+          <t>상점 (편의)</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 신속</t>
+          <t>프리미엄 자동물약</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>이동속도 +10%</t>
+          <t>500 다이아</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>70명 정원</t>
+          <t>24시간 자동물약 무한</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.8</t>
+          <t>상점 (상자)</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 회복</t>
+          <t>프리미엄 보물 상자</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>HP 재생 +50%</t>
+          <t>300 다이아</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>80명 정원</t>
+          <t>전설 장비 확정 + 다이아</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.9</t>
+          <t>상점 (재료)</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 운명</t>
+          <t>전설 재료 패키지</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>회피 +5%</t>
+          <t>600 다이아</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>90명 정원</t>
+          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
         </is>
       </c>
     </row>
@@ -16189,211 +16277,211 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.10</t>
+          <t>혈맹 Lv.6</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 전설</t>
+          <t>혈맹의 분노</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>전 스탯 +5%</t>
+          <t>크리티컬 +5%</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>100명 정원 — 최종</t>
+          <t>60명 정원</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.7</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>점쟁이</t>
+          <t>혈맹의 신속</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
+          <t>이동속도 +10%</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>70명 정원</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.8</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>감정사</t>
+          <t>혈맹의 회복</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
+          <t>HP 재생 +50%</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>80명 정원</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.9</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>수집가</t>
+          <t>혈맹의 운명</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
+          <t>회피 +5%</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>90명 정원</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>각성기 (어쌔신)</t>
+          <t>혈맹 Lv.10</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>천 개의 칼날</t>
+          <t>혈맹의 전설</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
+          <t>전 스탯 +5%</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>100명 정원 — 최종</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>각성기 (워리어)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>대지 가르기</t>
+          <t>점쟁이</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
+          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>각성기 (나이트)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>불멸의 수호자</t>
+          <t>감정사</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>피해 90% 감소 / 도발 / 10초</t>
+          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>각성기 (메이지)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>시간 정지</t>
+          <t>수집가</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
+          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
@@ -16405,17 +16493,17 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>각성기 (클레릭)</t>
+          <t>각성기 (어쌔신)</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>신의 은총</t>
+          <t>천 개의 칼날</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>HP 100% 회복 / 전스탯 +50%</t>
+          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -16427,108 +16515,108 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (워리어)</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>폭풍 정복자</t>
+          <t>대지 가르기</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인 처치</t>
+          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>10,000G + 150다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (나이트)</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>연금술사</t>
+          <t>불멸의 수호자</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>엘릭서 10회 제작</t>
+          <t>피해 90% 감소 / 도발 / 10초</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>5,000G + 80다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (메이지)</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>그림자 정복자</t>
+          <t>시간 정지</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 클리어</t>
+          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>8,000G + 120다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (클레릭)</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>전설의 동반자</t>
+          <t>신의 은총</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>전설급 펫 진화</t>
+          <t>HP 100% 회복 / 전스탯 +50%</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>6,000G + 100다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
@@ -16545,206 +16633,206 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>이국의 상인</t>
+          <t>폭풍 정복자</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>사치품 교역 5회</t>
+          <t>폭풍의 거인 처치</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>4,000G + 60다이아</t>
+          <t>10,000G + 150다이아</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인</t>
+          <t>연금술사</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>HP 100,000 / ATK 140 / DEF 90</t>
+          <t>엘릭서 10회 제작</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>EXP 10000 + 6000G</t>
+          <t>5,000G + 80다이아</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>시간의 수호자</t>
+          <t>그림자 정복자</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>HP 70,000 / ATK 170 / DEF 60</t>
+          <t>그림자 미궁 클리어</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>EXP 9000 + 7000G</t>
+          <t>8,000G + 120다이아</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>교역품</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
+          <t>전설의 동반자</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종</t>
+          <t>전설급 펫 진화</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>기본가 600~900G</t>
+          <t>6,000G + 100다이아</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>타이탄의 엘릭서</t>
+          <t>이국의 상인</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>용재료×3 + 마법재료×10</t>
+          <t>사치품 교역 5회</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>ATK ×1.5 / 30분</t>
+          <t>4,000G + 60다이아</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>강철 엘릭서</t>
+          <t>폭풍의 거인</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>철광석×30 + 마법재료×10</t>
+          <t>HP 100,000 / ATK 140 / DEF 90</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>DEF ×1.5 / 30분</t>
+          <t>EXP 10000 + 6000G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>질풍 엘릭서</t>
+          <t>시간의 수호자</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>약초×20 + 마법재료×8</t>
+          <t>HP 70,000 / ATK 170 / DEF 60</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>SPD ×1.4 / 20분</t>
+          <t>EXP 9000 + 7000G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>교역품</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>지혜 엘릭서</t>
+          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>마법수정×5 + 영혼재료×5</t>
+          <t>이국의 사치품 3종</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>EXP ×2.5 / 15분</t>
+          <t>기본가 600~900G</t>
         </is>
       </c>
     </row>
@@ -16761,260 +16849,260 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>행운 엘릭서</t>
+          <t>타이탄의 엘릭서</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>보석×10 + 마법재료×5</t>
+          <t>용재료×3 + 마법재료×10</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>GOLD ×2.0 / 15분</t>
+          <t>ATK ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>불사조 (pet_phoenix)</t>
+          <t>강철 엘릭서</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>불꽃산 보스 50처치</t>
+          <t>철광석×30 + 마법재료×10</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>화염 DMG +20% (진화 +40%)</t>
+          <t>DEF ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>유니콘 (pet_unicorn)</t>
+          <t>질풍 엘릭서</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>다이아 800개</t>
+          <t>약초×20 + 마법재료×8</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>회피 +10% (진화 +20%)</t>
+          <t>SPD ×1.4 / 20분</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (mount_pegasus)</t>
+          <t>지혜 엘릭서</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>다이아 1200개</t>
+          <t>마법수정×5 + 영혼재료×5</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>이동속도 +85% / 비행</t>
+          <t>EXP ×2.5 / 15분</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁</t>
+          <t>행운 엘릭서</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Lv.38 / 8인 파티 / 7스테이지</t>
+          <t>보석×10 + 마법재료×5</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>22000G + 32000EXP</t>
+          <t>GOLD ×2.0 / 15분</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>드롭</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>드래곤 검/망토/투구/장갑</t>
+          <t>불사조 (pet_phoenix)</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 보스 드롭</t>
+          <t>불꽃산 보스 50처치</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>전설급</t>
+          <t>화염 DMG +20% (진화 +40%)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자</t>
+          <t>유니콘 (pet_unicorn)</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>몬스터 10,000 처치</t>
+          <t>다이아 800개</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>ATK +7%</t>
+          <t>회피 +10% (진화 +20%)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>불멸자</t>
+          <t>페가수스 (mount_pegasus)</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>환생 5회</t>
+          <t>다이아 1200개</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>EXP +25%</t>
+          <t>이동속도 +85% / 비행</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>천공의 군주</t>
+          <t>그림자 미궁</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 10회 처치</t>
+          <t>Lv.38 / 8인 파티 / 7스테이지</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>보스DMG +15%</t>
+          <t>22000G + 32000EXP</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>드롭</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>지역 시트 갱신</t>
+          <t>드래곤 검/망토/투구/장갑</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>25→51개 지역 반영</t>
+          <t>그림자 미궁 보스 드롭</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>전설급</t>
         </is>
       </c>
     </row>
@@ -17026,22 +17114,22 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>칭호 시트 갱신</t>
+          <t>공허의 방랑자</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>7→16종 + 효과/색상 추가</t>
+          <t>몬스터 10,000 처치</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ATK +7%</t>
         </is>
       </c>
     </row>
@@ -17053,22 +17141,22 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>출석 캘린더 시트</t>
+          <t>불멸자</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (28일 사이클)</t>
+          <t>환생 5회</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EXP +25%</t>
         </is>
       </c>
     </row>
@@ -17080,22 +17168,22 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>장비 세트 시트</t>
+          <t>천공의 군주</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (드래곤/영웅/태초)</t>
+          <t>월드 보스 10회 처치</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>보스DMG +15%</t>
         </is>
       </c>
     </row>
@@ -17112,12 +17200,12 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>장비 등급 시트</t>
+          <t>지역 시트 갱신</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+          <t>25→51개 지역 반영</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
@@ -17139,12 +17227,12 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>디버프 시트</t>
+          <t>칭호 시트 갱신</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+          <t>7→16종 + 효과/색상 추가</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -17166,12 +17254,12 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>패치 노트 시트</t>
+          <t>출석 캘린더 시트</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (히스토리)</t>
+          <t>신규 추가 (28일 사이클)</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
@@ -17183,25 +17271,133 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>장비 세트 시트</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (드래곤/영웅/태초)</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>장비 등급 시트</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>디버프 시트</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>패치 노트 시트</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (히스토리)</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
           <t>v1.10</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>기획서</t>
         </is>
       </c>
-      <c r="C81" s="8" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>던전 시트</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>신규 추가 (7종 던전)</t>
         </is>
       </c>
-      <c r="E81" s="8" t="inlineStr">
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -40,7 +40,7 @@
     <sheet name="월드 보스" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="연금술" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="패치 노트" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="v1.9 ~ v1.28" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="v1.9 ~ v1.29" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13685,7 +13685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13726,7 +13726,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -13741,14 +13741,14 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
+          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -13758,19 +13758,19 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>event_status 소켓 + /status 엔드포인트 노출</t>
+          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -13780,19 +13780,19 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
+          <t>season_status / season_buy_pass / season_claim</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -13802,19 +13802,19 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
+          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -13829,14 +13829,14 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
+          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -13846,19 +13846,19 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
+          <t>event_status 소켓 + /status 엔드포인트 노출</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -13868,19 +13868,19 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
+          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -13890,19 +13890,19 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
+          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -13917,14 +13917,14 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
+          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -13934,19 +13934,19 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
+          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -13956,19 +13956,19 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
+          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -13978,19 +13978,19 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
+          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -14000,19 +14000,19 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
+          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -14022,19 +14022,19 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>경매장 시트 신규 추가</t>
+          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -14044,19 +14044,19 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
+          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -14066,19 +14066,19 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
+          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -14088,19 +14088,19 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>낚시 시트 신규 추가</t>
+          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -14110,19 +14110,19 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
+          <t>경매장 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -14132,19 +14132,19 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
+          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -14154,19 +14154,19 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>보스 러시 시트 신규 추가</t>
+          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -14176,19 +14176,19 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
+          <t>낚시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -14198,19 +14198,19 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
+          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -14220,19 +14220,19 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛 시트 신규 추가</t>
+          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -14242,19 +14242,19 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
+          <t>보스 러시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -14264,19 +14264,19 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>모듈화</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
+          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -14286,19 +14286,19 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트 시트 신규 추가</t>
+          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -14308,19 +14308,19 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
+          <t>행운의 룰렛 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -14330,19 +14330,19 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
+          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -14352,19 +14352,19 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>모듈화</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스 시트 신규 추가</t>
+          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -14374,19 +14374,19 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
+          <t>축제 이벤트 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -14396,19 +14396,19 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아 시트 신규 추가</t>
+          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -14418,19 +14418,19 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
+          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -14445,14 +14445,14 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>상점 시트 갱신</t>
+          <t>시즌 패스 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -14462,19 +14462,19 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
+          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -14484,19 +14484,19 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>최대 인원 50→100명 (Lv.10 기준)</t>
+          <t>무료 다이아 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -14506,19 +14506,19 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>길드(혈맹) 시트 신규 추가</t>
+          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -14528,19 +14528,19 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
+          <t>상점 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -14550,19 +14550,19 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>대사 시스템</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
+          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -14572,19 +14572,19 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>NPC 시트 신규 추가 (11종)</t>
+          <t>최대 인원 50→100명 (Lv.10 기준)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -14594,19 +14594,19 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>각성기</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
+          <t>길드(혈맹) 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -14616,19 +14616,19 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
+          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -14638,19 +14638,19 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>대사 시스템</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
+          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -14665,14 +14665,14 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
+          <t>NPC 시트 신규 추가 (11종)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -14682,19 +14682,19 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>각성기</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
+          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -14704,19 +14704,19 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>교역</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
+          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -14726,19 +14726,19 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
+          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -14748,19 +14748,19 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
+          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -14770,19 +14770,19 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>연금술 시트 신규 추가</t>
+          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -14792,19 +14792,19 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>교역</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
+          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -14814,19 +14814,19 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>페가수스 (이동 +85%, 비행)</t>
+          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -14836,19 +14836,19 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
+          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -14863,14 +14863,14 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
+          <t>연금술 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -14880,19 +14880,19 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
+          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -14902,107 +14902,107 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
+          <t>페가수스 (이동 +85%, 비행)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
+          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
+          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
+          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
+          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -15012,19 +15012,19 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>상태이상</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
+          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -15034,19 +15034,19 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -15056,19 +15056,19 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -15078,12 +15078,12 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>컨텐츠</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
         </is>
       </c>
     </row>
@@ -15100,32 +15100,120 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>상태이상</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>컨텐츠</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
           <t>v1.6 이전</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>기반</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>마을/사냥/PvP/카르마/펫/탈것/제작/교역/길드/공성/투기장 등</t>
         </is>
@@ -15145,7 +15233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15192,7 +15280,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -15202,159 +15290,159 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>event → server.js</t>
+          <t>season → server.js</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>3번째 모듈 통합</t>
+          <t>4번째 모듈 통합</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>축제 시스템 활성화</t>
+          <t>XP 자동 적립 + 보상 수령</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>event_status</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>현재 활성 축제 조회</t>
+          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>이름/기간/버프/한정 보상</t>
+          <t>SEASON_XP_MAP 매핑</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>/status JSON</t>
+          <t>season_status</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>festival 필드 추가</t>
+          <t>XP/티어/구매여부/수령내역 조회</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>대시보드 확인용</t>
+          <t>15티어 전체</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>축제 인사</t>
+          <t>season_buy_pass</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>30% 확률로 NPC가 축제 대사 출력</t>
+          <t>프리미엄 패스 구매 (1500💎)</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>spring_blossom 등 5종</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>fishing → server.js</t>
+          <t>season_claim</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>티어 보상 수령 (free/premium)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>두 번째 모듈 통합</t>
+          <t>자동 인벤토리 적용</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>fishing_status</t>
+          <t>event → server.js</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>지역/낚싯대/미끼/시간대 조회</t>
+          <t>3번째 모듈 통합</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>축제 시스템 활성화</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -15364,1880 +15452,1880 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>fishing_cast</t>
+          <t>event_status</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
+          <t>현재 활성 축제 조회</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>전설/신화 → 서버 알림</t>
+          <t>이름/기간/버프/한정 보상</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>fishing_buy_rod</t>
+          <t>/status JSON</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>낚싯대 구매 (골드/다이아)</t>
+          <t>festival 필드 추가</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>5등급 모두</t>
+          <t>대시보드 확인용</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>lottery → server.js</t>
+          <t>축제 인사</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>30% 확률로 NPC가 축제 대사 출력</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>첫 모듈 통합 마일스톤</t>
+          <t>spring_blossom 등 5종</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>lottery_status</t>
+          <t>fishing → server.js</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>상태/가격/상품 풀 조회</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>두 번째 모듈 통합</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>lottery_free_spin</t>
+          <t>fishing_status</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 스핀</t>
+          <t>지역/낚싯대/미끼/시간대 조회</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>자정 초기화</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>lottery_paid_spin</t>
+          <t>fishing_cast</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>유료 1회 / 10연속</t>
+          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>count: 1 또는 10</t>
+          <t>전설/신화 → 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js 신규</t>
+          <t>fishing_buy_rod</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
+          <t>낚싯대 구매 (골드/다이아)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>등록 2% + 낙찰 5%</t>
+          <t>5등급 모두</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>활성 한도</t>
+          <t>lottery → server.js</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>플레이어당 10개</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>자기 입찰 금지</t>
+          <t>첫 모듈 통합 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>game/fishing.js 신규</t>
+          <t>lottery_status</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
+          <t>상태/가격/상품 풀 조회</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 = 20000G + 칭호</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>전설의 비단잉어</t>
+          <t>lottery_free_spin</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>드래곤 낚싯대 + 가중치 1</t>
+          <t>매일 무료 1회 스핀</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>5000G + 평생 행운 +5%</t>
+          <t>자정 초기화</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>game/boss_rush.js 신규</t>
+          <t>lottery_paid_spin</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 / HP ×1.35 스케일링</t>
+          <t>유료 1회 / 10연속</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>최종 보상: 200💎 + 용재료 ×5</t>
+          <t>count: 1 또는 10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>입장</t>
+          <t>game/auction.js 신규</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 / 1000G / 30💎</t>
+          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>랭킹 시스템</t>
+          <t>등록 2% + 낙찰 5%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>챔피언 보상</t>
+          <t>활성 한도</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
+          <t>플레이어당 10개</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>자기 입찰 금지</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js 신규</t>
+          <t>game/fishing.js 신규</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 / 가중치 1000</t>
+          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 + 유료</t>
+          <t>신화 크라켄 = 20000G + 칭호</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>영웅 장비 상자</t>
+          <t>전설의 비단잉어</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>확률 0.2% (가장 희귀)</t>
+          <t>드래곤 낚싯대 + 가중치 1</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>전설 보상</t>
+          <t>5000G + 평생 행운 +5%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>200 다이아</t>
+          <t>game/boss_rush.js 신규</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>확률 0.8%</t>
+          <t>20웨이브 / HP ×1.35 스케일링</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>최종 보상: 200💎 + 용재료 ×5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>신년 축제</t>
+          <t>입장</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>1/1 ~ 1/7</t>
+          <t>매일 무료 3회 / 1000G / 30💎</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>골드 +50% / EXP +30%</t>
+          <t>랭킹 시스템</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>봄꽃 축제</t>
+          <t>챔피언 보상</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>4/1 ~ 4/14</t>
+          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>HP재생 +30% / 드롭 +20%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>한여름 밤의 축제</t>
+          <t>game/lottery.js 신규</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>7/15 ~ 8/15</t>
+          <t>10종 보상 / 가중치 1000</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>화염 +30% / PvP 보상 +50%</t>
+          <t>매일 무료 1회 + 유료</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>할로윈 축제</t>
+          <t>영웅 장비 상자</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>10/25 ~ 11/1</t>
+          <t>확률 0.2% (가장 희귀)</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>크리 +10% / 언데드 +50%</t>
+          <t>전설 보상</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>겨울 축제</t>
+          <t>200 다이아</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>12/20 ~ 12/31</t>
+          <t>확률 0.8%</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
+          <t>잭팟</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>game/season.js 신규</t>
+          <t>신년 축제</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>15티어 / 30일 / 무료+프리미엄</t>
+          <t>1/1 ~ 1/7</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
+          <t>골드 +50% / EXP +30%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>XP 획득 7종</t>
+          <t>봄꽃 축제</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>퀘/보스/PvP/월드보스/던전/제작</t>
+          <t>4/1 ~ 4/14</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>일일 +200 ~ 월드보스 +500</t>
+          <t>HP재생 +30% / 드롭 +20%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 가격</t>
+          <t>한여름 밤의 축제</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>1500 다이아</t>
+          <t>7/15 ~ 8/15</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>시즌 당 1회</t>
+          <t>화염 +30% / PvP 보상 +50%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Lv.40 달성</t>
+          <t>할로윈 축제</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>각성기 해금 마일스톤</t>
+          <t>10/25 ~ 11/1</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>150💎</t>
+          <t>크리 +10% / 언데드 +50%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Lv.50 달성</t>
+          <t>겨울 축제</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>환생 가능 마일스톤</t>
+          <t>12/20 ~ 12/31</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>250💎</t>
+          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>첫 환생</t>
+          <t>game/season.js 신규</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>prestige 1차</t>
+          <t>15티어 / 30일 / 무료+프리미엄</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>500💎</t>
+          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>첫 월드 보스</t>
+          <t>XP 획득 7종</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 처치 보너스</t>
+          <t>퀘/보스/PvP/월드보스/던전/제작</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>100💎</t>
+          <t>일일 +200 ~ 월드보스 +500</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>업적 50개</t>
+          <t>프리미엄 가격</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>업적 마일스톤</t>
+          <t>1500 다이아</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>200💎</t>
+          <t>시즌 당 1회</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>불사조 스킨</t>
+          <t>Lv.40 달성</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>각성기 해금 마일스톤</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>불사조 깃털 이펙트 (영구)</t>
+          <t>150💎</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>폭풍 스킨</t>
+          <t>Lv.50 달성</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>환생 가능 마일스톤</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>번개 오라 이펙트 (영구)</t>
+          <t>250💎</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>상점 (편의)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 자동물약</t>
+          <t>첫 환생</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>500 다이아</t>
+          <t>prestige 1차</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>24시간 자동물약 무한</t>
+          <t>500💎</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>상점 (상자)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 보물 상자</t>
+          <t>첫 월드 보스</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>300 다이아</t>
+          <t>월드 보스 처치 보너스</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>전설 장비 확정 + 다이아</t>
+          <t>100💎</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>상점 (재료)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>전설 재료 패키지</t>
+          <t>업적 50개</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>600 다이아</t>
+          <t>업적 마일스톤</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
+          <t>200💎</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 분노</t>
+          <t>불사조 스킨</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>크리티컬 +5%</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>60명 정원</t>
+          <t>불사조 깃털 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.7</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 신속</t>
+          <t>폭풍 스킨</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>이동속도 +10%</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>70명 정원</t>
+          <t>번개 오라 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.8</t>
+          <t>상점 (편의)</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 회복</t>
+          <t>프리미엄 자동물약</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>HP 재생 +50%</t>
+          <t>500 다이아</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>80명 정원</t>
+          <t>24시간 자동물약 무한</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.9</t>
+          <t>상점 (상자)</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 운명</t>
+          <t>프리미엄 보물 상자</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>회피 +5%</t>
+          <t>300 다이아</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>90명 정원</t>
+          <t>전설 장비 확정 + 다이아</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.10</t>
+          <t>상점 (재료)</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 전설</t>
+          <t>전설 재료 패키지</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>전 스탯 +5%</t>
+          <t>600 다이아</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>100명 정원 — 최종</t>
+          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.6</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>점쟁이</t>
+          <t>혈맹의 분노</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
+          <t>크리티컬 +5%</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>60명 정원</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.7</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>감정사</t>
+          <t>혈맹의 신속</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
+          <t>이동속도 +10%</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>70명 정원</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.8</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>수집가</t>
+          <t>혈맹의 회복</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
+          <t>HP 재생 +50%</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>80명 정원</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>각성기 (어쌔신)</t>
+          <t>혈맹 Lv.9</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>천 개의 칼날</t>
+          <t>혈맹의 운명</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
+          <t>회피 +5%</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>90명 정원</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>각성기 (워리어)</t>
+          <t>혈맹 Lv.10</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>대지 가르기</t>
+          <t>혈맹의 전설</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
+          <t>전 스탯 +5%</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>100명 정원 — 최종</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>각성기 (나이트)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>불멸의 수호자</t>
+          <t>점쟁이</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>피해 90% 감소 / 도발 / 10초</t>
+          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>각성기 (메이지)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>시간 정지</t>
+          <t>감정사</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
+          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>각성기 (클레릭)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>신의 은총</t>
+          <t>수집가</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>HP 100% 회복 / 전스탯 +50%</t>
+          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (어쌔신)</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>폭풍 정복자</t>
+          <t>천 개의 칼날</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인 처치</t>
+          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>10,000G + 150다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (워리어)</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>연금술사</t>
+          <t>대지 가르기</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>엘릭서 10회 제작</t>
+          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>5,000G + 80다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (나이트)</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>그림자 정복자</t>
+          <t>불멸의 수호자</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 클리어</t>
+          <t>피해 90% 감소 / 도발 / 10초</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>8,000G + 120다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (메이지)</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>전설의 동반자</t>
+          <t>시간 정지</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>전설급 펫 진화</t>
+          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>6,000G + 100다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (클레릭)</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>이국의 상인</t>
+          <t>신의 은총</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>사치품 교역 5회</t>
+          <t>HP 100% 회복 / 전스탯 +50%</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>4,000G + 60다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인</t>
+          <t>폭풍 정복자</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>HP 100,000 / ATK 140 / DEF 90</t>
+          <t>폭풍의 거인 처치</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>EXP 10000 + 6000G</t>
+          <t>10,000G + 150다이아</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>시간의 수호자</t>
+          <t>연금술사</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>HP 70,000 / ATK 170 / DEF 60</t>
+          <t>엘릭서 10회 제작</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>EXP 9000 + 7000G</t>
+          <t>5,000G + 80다이아</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>교역품</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
+          <t>그림자 정복자</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종</t>
+          <t>그림자 미궁 클리어</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>기본가 600~900G</t>
+          <t>8,000G + 120다이아</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>타이탄의 엘릭서</t>
+          <t>전설의 동반자</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>용재료×3 + 마법재료×10</t>
+          <t>전설급 펫 진화</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>ATK ×1.5 / 30분</t>
+          <t>6,000G + 100다이아</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>강철 엘릭서</t>
+          <t>이국의 상인</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>철광석×30 + 마법재료×10</t>
+          <t>사치품 교역 5회</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>DEF ×1.5 / 30분</t>
+          <t>4,000G + 60다이아</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>질풍 엘릭서</t>
+          <t>폭풍의 거인</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>약초×20 + 마법재료×8</t>
+          <t>HP 100,000 / ATK 140 / DEF 90</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>SPD ×1.4 / 20분</t>
+          <t>EXP 10000 + 6000G</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>지혜 엘릭서</t>
+          <t>시간의 수호자</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>마법수정×5 + 영혼재료×5</t>
+          <t>HP 70,000 / ATK 170 / DEF 60</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>EXP ×2.5 / 15분</t>
+          <t>EXP 9000 + 7000G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>교역품</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>행운 엘릭서</t>
+          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>보석×10 + 마법재료×5</t>
+          <t>이국의 사치품 3종</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>GOLD ×2.0 / 15분</t>
+          <t>기본가 600~900G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>불사조 (pet_phoenix)</t>
+          <t>타이탄의 엘릭서</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>불꽃산 보스 50처치</t>
+          <t>용재료×3 + 마법재료×10</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>화염 DMG +20% (진화 +40%)</t>
+          <t>ATK ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>유니콘 (pet_unicorn)</t>
+          <t>강철 엘릭서</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>다이아 800개</t>
+          <t>철광석×30 + 마법재료×10</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>회피 +10% (진화 +20%)</t>
+          <t>DEF ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (mount_pegasus)</t>
+          <t>질풍 엘릭서</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>다이아 1200개</t>
+          <t>약초×20 + 마법재료×8</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>이동속도 +85% / 비행</t>
+          <t>SPD ×1.4 / 20분</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁</t>
+          <t>지혜 엘릭서</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Lv.38 / 8인 파티 / 7스테이지</t>
+          <t>마법수정×5 + 영혼재료×5</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>22000G + 32000EXP</t>
+          <t>EXP ×2.5 / 15분</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>드롭</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>드래곤 검/망토/투구/장갑</t>
+          <t>행운 엘릭서</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 보스 드롭</t>
+          <t>보석×10 + 마법재료×5</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>전설급</t>
+          <t>GOLD ×2.0 / 15분</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자</t>
+          <t>불사조 (pet_phoenix)</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>몬스터 10,000 처치</t>
+          <t>불꽃산 보스 50처치</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>ATK +7%</t>
+          <t>화염 DMG +20% (진화 +40%)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>불멸자</t>
+          <t>유니콘 (pet_unicorn)</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>환생 5회</t>
+          <t>다이아 800개</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>EXP +25%</t>
+          <t>회피 +10% (진화 +20%)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>천공의 군주</t>
+          <t>페가수스 (mount_pegasus)</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 10회 처치</t>
+          <t>다이아 1200개</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>보스DMG +15%</t>
+          <t>이동속도 +85% / 비행</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>지역 시트 갱신</t>
+          <t>그림자 미궁</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>25→51개 지역 반영</t>
+          <t>Lv.38 / 8인 파티 / 7스테이지</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22000G + 32000EXP</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>드롭</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>칭호 시트 갱신</t>
+          <t>드래곤 검/망토/투구/장갑</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>7→16종 + 효과/색상 추가</t>
+          <t>그림자 미궁 보스 드롭</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>전설급</t>
         </is>
       </c>
     </row>
@@ -17249,22 +17337,22 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>출석 캘린더 시트</t>
+          <t>공허의 방랑자</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (28일 사이클)</t>
+          <t>몬스터 10,000 처치</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ATK +7%</t>
         </is>
       </c>
     </row>
@@ -17276,22 +17364,22 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>장비 세트 시트</t>
+          <t>불멸자</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (드래곤/영웅/태초)</t>
+          <t>환생 5회</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EXP +25%</t>
         </is>
       </c>
     </row>
@@ -17303,22 +17391,22 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>장비 등급 시트</t>
+          <t>천공의 군주</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+          <t>월드 보스 10회 처치</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>보스DMG +15%</t>
         </is>
       </c>
     </row>
@@ -17335,12 +17423,12 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>디버프 시트</t>
+          <t>지역 시트 갱신</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+          <t>25→51개 지역 반영</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -17362,12 +17450,12 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>패치 노트 시트</t>
+          <t>칭호 시트 갱신</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (히스토리)</t>
+          <t>7→16종 + 효과/색상 추가</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -17379,25 +17467,160 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>출석 캘린더 시트</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (28일 사이클)</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>장비 세트 시트</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (드래곤/영웅/태초)</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>장비 등급 시트</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>디버프 시트</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>패치 노트 시트</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (히스토리)</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
           <t>v1.10</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>기획서</t>
         </is>
       </c>
-      <c r="C85" s="8" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>던전 시트</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>신규 추가 (7종 던전)</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -40,7 +40,7 @@
     <sheet name="월드 보스" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="연금술" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="패치 노트" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="v1.9 ~ v1.29" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="v1.9 ~ v1.30" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13685,7 +13685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13726,7 +13726,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -13741,14 +13741,14 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
+          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -13758,19 +13758,19 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
+          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -13785,14 +13785,14 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>season_status / season_buy_pass / season_claim</t>
+          <t>boss_rush_status / enter / advance / abandon</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -13802,19 +13802,19 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
+          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -13829,14 +13829,14 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
+          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -13846,19 +13846,19 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>event_status 소켓 + /status 엔드포인트 노출</t>
+          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -13868,19 +13868,19 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
+          <t>season_status / season_buy_pass / season_claim</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -13890,19 +13890,19 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
+          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -13917,14 +13917,14 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
+          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -13934,19 +13934,19 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
+          <t>event_status 소켓 + /status 엔드포인트 노출</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -13956,19 +13956,19 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
+          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -13978,19 +13978,19 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
+          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -14005,14 +14005,14 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
+          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -14022,19 +14022,19 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
+          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -14044,19 +14044,19 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
+          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -14066,19 +14066,19 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
+          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -14088,19 +14088,19 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
+          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -14110,19 +14110,19 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>경매장 시트 신규 추가</t>
+          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -14132,19 +14132,19 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
+          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -14154,19 +14154,19 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
+          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -14176,19 +14176,19 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>낚시 시트 신규 추가</t>
+          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -14198,19 +14198,19 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
+          <t>경매장 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -14220,19 +14220,19 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
+          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -14242,19 +14242,19 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>보스 러시 시트 신규 추가</t>
+          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -14264,19 +14264,19 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
+          <t>낚시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -14286,19 +14286,19 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
+          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -14308,19 +14308,19 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛 시트 신규 추가</t>
+          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -14330,19 +14330,19 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
+          <t>보스 러시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -14352,19 +14352,19 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>모듈화</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
+          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -14374,19 +14374,19 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트 시트 신규 추가</t>
+          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -14396,19 +14396,19 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
+          <t>행운의 룰렛 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -14418,19 +14418,19 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
+          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -14440,19 +14440,19 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>모듈화</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스 시트 신규 추가</t>
+          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -14462,19 +14462,19 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
+          <t>축제 이벤트 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -14484,19 +14484,19 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아 시트 신규 추가</t>
+          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -14506,19 +14506,19 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
+          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -14533,14 +14533,14 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>상점 시트 갱신</t>
+          <t>시즌 패스 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -14550,19 +14550,19 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
+          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -14572,19 +14572,19 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>최대 인원 50→100명 (Lv.10 기준)</t>
+          <t>무료 다이아 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -14594,19 +14594,19 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>길드(혈맹) 시트 신규 추가</t>
+          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -14616,19 +14616,19 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
+          <t>상점 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -14638,19 +14638,19 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>대사 시스템</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
+          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -14660,19 +14660,19 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>NPC 시트 신규 추가 (11종)</t>
+          <t>최대 인원 50→100명 (Lv.10 기준)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -14682,19 +14682,19 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>각성기</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
+          <t>길드(혈맹) 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -14704,19 +14704,19 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
+          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -14726,19 +14726,19 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>대사 시스템</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
+          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -14753,14 +14753,14 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
+          <t>NPC 시트 신규 추가 (11종)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -14770,19 +14770,19 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>각성기</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
+          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -14792,19 +14792,19 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>교역</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
+          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -14814,19 +14814,19 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
+          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -14836,19 +14836,19 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
+          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -14858,19 +14858,19 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>연금술 시트 신규 추가</t>
+          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -14880,19 +14880,19 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>교역</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
+          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -14902,19 +14902,19 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>페가수스 (이동 +85%, 비행)</t>
+          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -14924,19 +14924,19 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
+          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -14951,14 +14951,14 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
+          <t>연금술 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -14968,19 +14968,19 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
+          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -14990,107 +14990,107 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
+          <t>페가수스 (이동 +85%, 비행)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
+          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
+          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
+          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
+          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -15100,19 +15100,19 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>상태이상</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
+          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -15122,19 +15122,19 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -15144,19 +15144,19 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -15166,12 +15166,12 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>컨텐츠</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
         </is>
       </c>
     </row>
@@ -15188,32 +15188,120 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>상태이상</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>컨텐츠</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
           <t>v1.6 이전</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>기반</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>마을/사냥/PvP/카르마/펫/탈것/제작/교역/길드/공성/투기장 등</t>
         </is>
@@ -15233,7 +15321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15280,7 +15368,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -15290,78 +15378,78 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>season → server.js</t>
+          <t>boss_rush → server.js</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>4번째 모듈 통합</t>
+          <t>5번째 모듈 통합</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>XP 자동 적립 + 보상 수령</t>
+          <t>메모리 세션 기반</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>bossRushSessions</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
+          <t>진행 중 세션 저장</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>SEASON_XP_MAP 매핑</t>
+          <t>currentWave/시간 추적</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>season_status</t>
+          <t>bossRushRanking</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>XP/티어/구매여부/수령내역 조회</t>
+          <t>글로벌 랭킹 TOP 100</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>15티어 전체</t>
+          <t>웨이브 → 시간 정렬</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -15371,24 +15459,24 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>season_buy_pass</t>
+          <t>boss_rush_enter</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 패스 구매 (1500💎)</t>
+          <t>무료/유료/다이아 입장</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>동시 1개 세션 제한</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -15398,159 +15486,159 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>season_claim</t>
+          <t>boss_rush_advance</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>티어 보상 수령 (free/premium)</t>
+          <t>웨이브 클리어 보고</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>자동 인벤토리 적용</t>
+          <t>시간 초과 검증</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>event → server.js</t>
+          <t>풀클리어 보상</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>3번째 모듈 통합</t>
+          <t>20웨이브 누적</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>축제 시스템 활성화</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>event_status</t>
+          <t>season → server.js</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>현재 활성 축제 조회</t>
+          <t>4번째 모듈 통합</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>이름/기간/버프/한정 보상</t>
+          <t>XP 자동 적립 + 보상 수령</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>/status JSON</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>festival 필드 추가</t>
+          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>대시보드 확인용</t>
+          <t>SEASON_XP_MAP 매핑</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>축제 인사</t>
+          <t>season_status</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>30% 확률로 NPC가 축제 대사 출력</t>
+          <t>XP/티어/구매여부/수령내역 조회</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>spring_blossom 등 5종</t>
+          <t>15티어 전체</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>fishing → server.js</t>
+          <t>season_buy_pass</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>프리미엄 패스 구매 (1500💎)</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>두 번째 모듈 통합</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -15560,51 +15648,51 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>fishing_status</t>
+          <t>season_claim</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>지역/낚싯대/미끼/시간대 조회</t>
+          <t>티어 보상 수령 (free/premium)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>자동 인벤토리 적용</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>fishing_cast</t>
+          <t>event → server.js</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
+          <t>3번째 모듈 통합</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>전설/신화 → 서버 알림</t>
+          <t>축제 시스템 활성화</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -15614,1880 +15702,1880 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>fishing_buy_rod</t>
+          <t>event_status</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>낚싯대 구매 (골드/다이아)</t>
+          <t>현재 활성 축제 조회</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>5등급 모두</t>
+          <t>이름/기간/버프/한정 보상</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>lottery → server.js</t>
+          <t>/status JSON</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>festival 필드 추가</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>첫 모듈 통합 마일스톤</t>
+          <t>대시보드 확인용</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>lottery_status</t>
+          <t>축제 인사</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>상태/가격/상품 풀 조회</t>
+          <t>30% 확률로 NPC가 축제 대사 출력</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>spring_blossom 등 5종</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>lottery_free_spin</t>
+          <t>fishing → server.js</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 스핀</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>자정 초기화</t>
+          <t>두 번째 모듈 통합</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>lottery_paid_spin</t>
+          <t>fishing_status</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>유료 1회 / 10연속</t>
+          <t>지역/낚싯대/미끼/시간대 조회</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>count: 1 또는 10</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>game/auction.js 신규</t>
+          <t>fishing_cast</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
+          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>등록 2% + 낙찰 5%</t>
+          <t>전설/신화 → 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>활성 한도</t>
+          <t>fishing_buy_rod</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>플레이어당 10개</t>
+          <t>낚싯대 구매 (골드/다이아)</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>자기 입찰 금지</t>
+          <t>5등급 모두</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>game/fishing.js 신규</t>
+          <t>lottery → server.js</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>신화 크라켄 = 20000G + 칭호</t>
+          <t>첫 모듈 통합 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>전설의 비단잉어</t>
+          <t>lottery_status</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>드래곤 낚싯대 + 가중치 1</t>
+          <t>상태/가격/상품 풀 조회</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>5000G + 평생 행운 +5%</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>game/boss_rush.js 신규</t>
+          <t>lottery_free_spin</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 / HP ×1.35 스케일링</t>
+          <t>매일 무료 1회 스핀</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>최종 보상: 200💎 + 용재료 ×5</t>
+          <t>자정 초기화</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>입장</t>
+          <t>lottery_paid_spin</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 3회 / 1000G / 30💎</t>
+          <t>유료 1회 / 10연속</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>랭킹 시스템</t>
+          <t>count: 1 또는 10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>챔피언 보상</t>
+          <t>game/auction.js 신규</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
+          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>등록 2% + 낙찰 5%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>game/lottery.js 신규</t>
+          <t>활성 한도</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>10종 보상 / 가중치 1000</t>
+          <t>플레이어당 10개</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 + 유료</t>
+          <t>자기 입찰 금지</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>영웅 장비 상자</t>
+          <t>game/fishing.js 신규</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>확률 0.2% (가장 희귀)</t>
+          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>전설 보상</t>
+          <t>신화 크라켄 = 20000G + 칭호</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>200 다이아</t>
+          <t>전설의 비단잉어</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>확률 0.8%</t>
+          <t>드래곤 낚싯대 + 가중치 1</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>5000G + 평생 행운 +5%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>신년 축제</t>
+          <t>game/boss_rush.js 신규</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>1/1 ~ 1/7</t>
+          <t>20웨이브 / HP ×1.35 스케일링</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>골드 +50% / EXP +30%</t>
+          <t>최종 보상: 200💎 + 용재료 ×5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>봄꽃 축제</t>
+          <t>입장</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>4/1 ~ 4/14</t>
+          <t>매일 무료 3회 / 1000G / 30💎</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>HP재생 +30% / 드롭 +20%</t>
+          <t>랭킹 시스템</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>한여름 밤의 축제</t>
+          <t>챔피언 보상</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>7/15 ~ 8/15</t>
+          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>화염 +30% / PvP 보상 +50%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>할로윈 축제</t>
+          <t>game/lottery.js 신규</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>10/25 ~ 11/1</t>
+          <t>10종 보상 / 가중치 1000</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>크리 +10% / 언데드 +50%</t>
+          <t>매일 무료 1회 + 유료</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>겨울 축제</t>
+          <t>영웅 장비 상자</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>12/20 ~ 12/31</t>
+          <t>확률 0.2% (가장 희귀)</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
+          <t>전설 보상</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>game/season.js 신규</t>
+          <t>200 다이아</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>15티어 / 30일 / 무료+프리미엄</t>
+          <t>확률 0.8%</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
+          <t>잭팟</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>XP 획득 7종</t>
+          <t>신년 축제</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>퀘/보스/PvP/월드보스/던전/제작</t>
+          <t>1/1 ~ 1/7</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>일일 +200 ~ 월드보스 +500</t>
+          <t>골드 +50% / EXP +30%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 가격</t>
+          <t>봄꽃 축제</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>1500 다이아</t>
+          <t>4/1 ~ 4/14</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>시즌 당 1회</t>
+          <t>HP재생 +30% / 드롭 +20%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Lv.40 달성</t>
+          <t>한여름 밤의 축제</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>각성기 해금 마일스톤</t>
+          <t>7/15 ~ 8/15</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>150💎</t>
+          <t>화염 +30% / PvP 보상 +50%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Lv.50 달성</t>
+          <t>할로윈 축제</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>환생 가능 마일스톤</t>
+          <t>10/25 ~ 11/1</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>250💎</t>
+          <t>크리 +10% / 언데드 +50%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>첫 환생</t>
+          <t>겨울 축제</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>prestige 1차</t>
+          <t>12/20 ~ 12/31</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>500💎</t>
+          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>첫 월드 보스</t>
+          <t>game/season.js 신규</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 처치 보너스</t>
+          <t>15티어 / 30일 / 무료+프리미엄</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>100💎</t>
+          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>업적 50개</t>
+          <t>XP 획득 7종</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>업적 마일스톤</t>
+          <t>퀘/보스/PvP/월드보스/던전/제작</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>200💎</t>
+          <t>일일 +200 ~ 월드보스 +500</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>불사조 스킨</t>
+          <t>프리미엄 가격</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>1500 다이아</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>불사조 깃털 이펙트 (영구)</t>
+          <t>시즌 당 1회</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>폭풍 스킨</t>
+          <t>Lv.40 달성</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>각성기 해금 마일스톤</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>번개 오라 이펙트 (영구)</t>
+          <t>150💎</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>상점 (편의)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 자동물약</t>
+          <t>Lv.50 달성</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>500 다이아</t>
+          <t>환생 가능 마일스톤</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>24시간 자동물약 무한</t>
+          <t>250💎</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>상점 (상자)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 보물 상자</t>
+          <t>첫 환생</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>300 다이아</t>
+          <t>prestige 1차</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>전설 장비 확정 + 다이아</t>
+          <t>500💎</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>상점 (재료)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>전설 재료 패키지</t>
+          <t>첫 월드 보스</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>600 다이아</t>
+          <t>월드 보스 처치 보너스</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
+          <t>100💎</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 분노</t>
+          <t>업적 50개</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>크리티컬 +5%</t>
+          <t>업적 마일스톤</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>60명 정원</t>
+          <t>200💎</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.7</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 신속</t>
+          <t>불사조 스킨</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>이동속도 +10%</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>70명 정원</t>
+          <t>불사조 깃털 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.8</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 회복</t>
+          <t>폭풍 스킨</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>HP 재생 +50%</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>80명 정원</t>
+          <t>번개 오라 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.9</t>
+          <t>상점 (편의)</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 운명</t>
+          <t>프리미엄 자동물약</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>회피 +5%</t>
+          <t>500 다이아</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>90명 정원</t>
+          <t>24시간 자동물약 무한</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.10</t>
+          <t>상점 (상자)</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 전설</t>
+          <t>프리미엄 보물 상자</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>전 스탯 +5%</t>
+          <t>300 다이아</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>100명 정원 — 최종</t>
+          <t>전설 장비 확정 + 다이아</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>상점 (재료)</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>점쟁이</t>
+          <t>전설 재료 패키지</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
+          <t>600 다이아</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.6</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>감정사</t>
+          <t>혈맹의 분노</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
+          <t>크리티컬 +5%</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>60명 정원</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.7</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>수집가</t>
+          <t>혈맹의 신속</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
+          <t>이동속도 +10%</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>70명 정원</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>각성기 (어쌔신)</t>
+          <t>혈맹 Lv.8</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>천 개의 칼날</t>
+          <t>혈맹의 회복</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
+          <t>HP 재생 +50%</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>80명 정원</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>각성기 (워리어)</t>
+          <t>혈맹 Lv.9</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>대지 가르기</t>
+          <t>혈맹의 운명</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
+          <t>회피 +5%</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>90명 정원</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>각성기 (나이트)</t>
+          <t>혈맹 Lv.10</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>불멸의 수호자</t>
+          <t>혈맹의 전설</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>피해 90% 감소 / 도발 / 10초</t>
+          <t>전 스탯 +5%</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>100명 정원 — 최종</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>각성기 (메이지)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>시간 정지</t>
+          <t>점쟁이</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
+          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>각성기 (클레릭)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>신의 은총</t>
+          <t>감정사</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>HP 100% 회복 / 전스탯 +50%</t>
+          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>폭풍 정복자</t>
+          <t>수집가</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인 처치</t>
+          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>10,000G + 150다이아</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (어쌔신)</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>연금술사</t>
+          <t>천 개의 칼날</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>엘릭서 10회 제작</t>
+          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>5,000G + 80다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (워리어)</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>그림자 정복자</t>
+          <t>대지 가르기</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 클리어</t>
+          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>8,000G + 120다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (나이트)</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>전설의 동반자</t>
+          <t>불멸의 수호자</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>전설급 펫 진화</t>
+          <t>피해 90% 감소 / 도발 / 10초</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>6,000G + 100다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (메이지)</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>이국의 상인</t>
+          <t>시간 정지</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>사치품 교역 5회</t>
+          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>4,000G + 60다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>각성기 (클레릭)</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인</t>
+          <t>신의 은총</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>HP 100,000 / ATK 140 / DEF 90</t>
+          <t>HP 100% 회복 / 전스탯 +50%</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>EXP 10000 + 6000G</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>시간의 수호자</t>
+          <t>폭풍 정복자</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>HP 70,000 / ATK 170 / DEF 60</t>
+          <t>폭풍의 거인 처치</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>EXP 9000 + 7000G</t>
+          <t>10,000G + 150다이아</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>교역품</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
+          <t>연금술사</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종</t>
+          <t>엘릭서 10회 제작</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>기본가 600~900G</t>
+          <t>5,000G + 80다이아</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>타이탄의 엘릭서</t>
+          <t>그림자 정복자</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>용재료×3 + 마법재료×10</t>
+          <t>그림자 미궁 클리어</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>ATK ×1.5 / 30분</t>
+          <t>8,000G + 120다이아</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>강철 엘릭서</t>
+          <t>전설의 동반자</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>철광석×30 + 마법재료×10</t>
+          <t>전설급 펫 진화</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>DEF ×1.5 / 30분</t>
+          <t>6,000G + 100다이아</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>질풍 엘릭서</t>
+          <t>이국의 상인</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>약초×20 + 마법재료×8</t>
+          <t>사치품 교역 5회</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>SPD ×1.4 / 20분</t>
+          <t>4,000G + 60다이아</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>지혜 엘릭서</t>
+          <t>폭풍의 거인</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>마법수정×5 + 영혼재료×5</t>
+          <t>HP 100,000 / ATK 140 / DEF 90</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>EXP ×2.5 / 15분</t>
+          <t>EXP 10000 + 6000G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>행운 엘릭서</t>
+          <t>시간의 수호자</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>보석×10 + 마법재료×5</t>
+          <t>HP 70,000 / ATK 170 / DEF 60</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>GOLD ×2.0 / 15분</t>
+          <t>EXP 9000 + 7000G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>교역품</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>불사조 (pet_phoenix)</t>
+          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>불꽃산 보스 50처치</t>
+          <t>이국의 사치품 3종</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>화염 DMG +20% (진화 +40%)</t>
+          <t>기본가 600~900G</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>유니콘 (pet_unicorn)</t>
+          <t>타이탄의 엘릭서</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>다이아 800개</t>
+          <t>용재료×3 + 마법재료×10</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>회피 +10% (진화 +20%)</t>
+          <t>ATK ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>페가수스 (mount_pegasus)</t>
+          <t>강철 엘릭서</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>다이아 1200개</t>
+          <t>철광석×30 + 마법재료×10</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>이동속도 +85% / 비행</t>
+          <t>DEF ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁</t>
+          <t>질풍 엘릭서</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Lv.38 / 8인 파티 / 7스테이지</t>
+          <t>약초×20 + 마법재료×8</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>22000G + 32000EXP</t>
+          <t>SPD ×1.4 / 20분</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>드롭</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>드래곤 검/망토/투구/장갑</t>
+          <t>지혜 엘릭서</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 보스 드롭</t>
+          <t>마법수정×5 + 영혼재료×5</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>전설급</t>
+          <t>EXP ×2.5 / 15분</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>공허의 방랑자</t>
+          <t>행운 엘릭서</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>몬스터 10,000 처치</t>
+          <t>보석×10 + 마법재료×5</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>ATK +7%</t>
+          <t>GOLD ×2.0 / 15분</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>불멸자</t>
+          <t>불사조 (pet_phoenix)</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>환생 5회</t>
+          <t>불꽃산 보스 50처치</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>EXP +25%</t>
+          <t>화염 DMG +20% (진화 +40%)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>천공의 군주</t>
+          <t>유니콘 (pet_unicorn)</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 10회 처치</t>
+          <t>다이아 800개</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>보스DMG +15%</t>
+          <t>회피 +10% (진화 +20%)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>지역 시트 갱신</t>
+          <t>페가수스 (mount_pegasus)</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>25→51개 지역 반영</t>
+          <t>다이아 1200개</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이동속도 +85% / 비행</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>칭호 시트 갱신</t>
+          <t>그림자 미궁</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>7→16종 + 효과/색상 추가</t>
+          <t>Lv.38 / 8인 파티 / 7스테이지</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22000G + 32000EXP</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>드롭</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>출석 캘린더 시트</t>
+          <t>드래곤 검/망토/투구/장갑</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (28일 사이클)</t>
+          <t>그림자 미궁 보스 드롭</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>전설급</t>
         </is>
       </c>
     </row>
@@ -17499,22 +17587,22 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>장비 세트 시트</t>
+          <t>공허의 방랑자</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (드래곤/영웅/태초)</t>
+          <t>몬스터 10,000 처치</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ATK +7%</t>
         </is>
       </c>
     </row>
@@ -17526,22 +17614,22 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>장비 등급 시트</t>
+          <t>불멸자</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+          <t>환생 5회</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EXP +25%</t>
         </is>
       </c>
     </row>
@@ -17553,22 +17641,22 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>디버프 시트</t>
+          <t>천공의 군주</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+          <t>월드 보스 10회 처치</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>보스DMG +15%</t>
         </is>
       </c>
     </row>
@@ -17585,12 +17673,12 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>패치 노트 시트</t>
+          <t>지역 시트 갱신</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (히스토리)</t>
+          <t>25→51개 지역 반영</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -17602,25 +17690,187 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>칭호 시트 갱신</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>7→16종 + 효과/색상 추가</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>출석 캘린더 시트</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (28일 사이클)</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>장비 세트 시트</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (드래곤/영웅/태초)</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>장비 등급 시트</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>디버프 시트</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>패치 노트 시트</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (히스토리)</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
           <t>v1.10</t>
         </is>
       </c>
-      <c r="B90" s="7" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>기획서</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>던전 시트</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>신규 추가 (7종 던전)</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -40,7 +40,7 @@
     <sheet name="월드 보스" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="연금술" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="패치 노트" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="v1.9 ~ v1.30" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="v1.9 ~ v1.31" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13685,7 +13685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13726,7 +13726,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -13741,14 +13741,14 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
+          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -13758,19 +13758,19 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
+          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -13780,19 +13780,19 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>boss_rush_status / enter / advance / abandon</t>
+          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -13802,19 +13802,19 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
+          <t>auction_list / create / bid / my</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -13824,19 +13824,19 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
+          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -13846,19 +13846,19 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
+          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -13868,19 +13868,19 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>season_status / season_buy_pass / season_claim</t>
+          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -13890,19 +13890,19 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
+          <t>boss_rush_status / enter / advance / abandon</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -13912,19 +13912,19 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
+          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -13934,19 +13934,19 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>event_status 소켓 + /status 엔드포인트 노출</t>
+          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -13956,19 +13956,19 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
+          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -13978,19 +13978,19 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
+          <t>season_status / season_buy_pass / season_claim</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -14000,19 +14000,19 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
+          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -14022,19 +14022,19 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
+          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -14044,19 +14044,19 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
+          <t>event_status 소켓 + /status 엔드포인트 노출</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -14066,19 +14066,19 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
+          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -14088,19 +14088,19 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
+          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -14110,19 +14110,19 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
+          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -14132,19 +14132,19 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
+          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -14154,19 +14154,19 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
+          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -14176,19 +14176,19 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
+          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -14198,19 +14198,19 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>경매장 시트 신규 추가</t>
+          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -14220,19 +14220,19 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
+          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -14242,19 +14242,19 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
+          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -14264,19 +14264,19 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>낚시 시트 신규 추가</t>
+          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -14286,19 +14286,19 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
+          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -14308,19 +14308,19 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
+          <t>경매장 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -14330,19 +14330,19 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>보스 러시 시트 신규 추가</t>
+          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -14352,19 +14352,19 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
+          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -14374,19 +14374,19 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
+          <t>낚시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -14396,19 +14396,19 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛 시트 신규 추가</t>
+          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -14418,19 +14418,19 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
+          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -14440,19 +14440,19 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>모듈화</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
+          <t>보스 러시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -14462,19 +14462,19 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트 시트 신규 추가</t>
+          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -14484,19 +14484,19 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
+          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -14506,19 +14506,19 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
+          <t>행운의 룰렛 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -14528,19 +14528,19 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스 시트 신규 추가</t>
+          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -14550,19 +14550,19 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>모듈화</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
+          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -14577,14 +14577,14 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아 시트 신규 추가</t>
+          <t>축제 이벤트 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -14594,19 +14594,19 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
+          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -14616,19 +14616,19 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>상점 시트 갱신</t>
+          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -14638,19 +14638,19 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
+          <t>시즌 패스 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -14660,19 +14660,19 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>최대 인원 50→100명 (Lv.10 기준)</t>
+          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -14687,14 +14687,14 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>길드(혈맹) 시트 신규 추가</t>
+          <t>무료 다이아 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -14704,19 +14704,19 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
+          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -14726,19 +14726,19 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>대사 시스템</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
+          <t>상점 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -14748,19 +14748,19 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>NPC 시트 신규 추가 (11종)</t>
+          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -14770,19 +14770,19 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>각성기</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
+          <t>최대 인원 50→100명 (Lv.10 기준)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -14797,14 +14797,14 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
+          <t>길드(혈맹) 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -14814,19 +14814,19 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
+          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -14836,19 +14836,19 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>대사 시스템</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
+          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -14858,19 +14858,19 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
+          <t>NPC 시트 신규 추가 (11종)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -14880,19 +14880,19 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>교역</t>
+          <t>각성기</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
+          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -14907,14 +14907,14 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
+          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -14924,19 +14924,19 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
+          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -14951,14 +14951,14 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>연금술 시트 신규 추가</t>
+          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -14968,19 +14968,19 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
+          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -14990,19 +14990,19 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>교역</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>페가수스 (이동 +85%, 비행)</t>
+          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -15012,19 +15012,19 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
+          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -15034,19 +15034,19 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
+          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -15056,19 +15056,19 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
+          <t>연금술 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -15078,129 +15078,129 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
+          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
+          <t>페가수스 (이동 +85%, 비행)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
+          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
+          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
+          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>상태이상</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
+          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -15215,14 +15215,14 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -15232,19 +15232,19 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -15254,19 +15254,19 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>컨텐츠</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -15276,32 +15276,142 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>상태이상</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>컨텐츠</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
           <t>v1.6 이전</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C75" s="8" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>기반</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>마을/사냥/PvP/카르마/펫/탈것/제작/교역/길드/공성/투기장 등</t>
         </is>
@@ -15321,7 +15431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15368,7 +15478,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -15378,78 +15488,78 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>boss_rush → server.js</t>
+          <t>auction → server.js</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>5번째 모듈 통합</t>
+          <t>6번째 (마지막) 모듈 통합</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>메모리 세션 기반</t>
+          <t>자동 정산 + 환불 + 양방향 지급</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>bossRushSessions</t>
+          <t>tickAuctions</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>진행 중 세션 저장</t>
+          <t>10초마다 만료 정산</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>currentWave/시간 추적</t>
+          <t>setInterval 통합</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>bossRushRanking</t>
+          <t>auction_create</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>글로벌 랭킹 TOP 100</t>
+          <t>경매 등록 (등록 수수료 자동 차감)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>웨이브 → 시간 정렬</t>
+          <t>3가지 기간</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -15459,24 +15569,24 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_enter</t>
+          <t>auction_bid</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>무료/유료/다이아 입장</t>
+          <t>입찰 + 이전 입찰자 자동 환불</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>동시 1개 세션 제한</t>
+          <t>스나이핑 방지 연장</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -15486,51 +15596,51 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>boss_rush_advance</t>
+          <t>auction_my</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>웨이브 클리어 보고</t>
+          <t>내 등록/입찰 내역 조회</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>시간 초과 검증</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>풀클리어 보상</t>
+          <t>신규 모듈 6/6</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 누적</t>
+          <t>100% 통합 완료</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>lottery/fishing/event/season/boss_rush/auction</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -15540,78 +15650,78 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>season → server.js</t>
+          <t>boss_rush → server.js</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>4번째 모듈 통합</t>
+          <t>5번째 모듈 통합</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>XP 자동 적립 + 보상 수령</t>
+          <t>메모리 세션 기반</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>bossRushSessions</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
+          <t>진행 중 세션 저장</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>SEASON_XP_MAP 매핑</t>
+          <t>currentWave/시간 추적</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>season_status</t>
+          <t>bossRushRanking</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>XP/티어/구매여부/수령내역 조회</t>
+          <t>글로벌 랭킹 TOP 100</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>15티어 전체</t>
+          <t>웨이브 → 시간 정렬</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -15621,24 +15731,24 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>season_buy_pass</t>
+          <t>boss_rush_enter</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 패스 구매 (1500💎)</t>
+          <t>무료/유료/다이아 입장</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>동시 1개 세션 제한</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -15648,159 +15758,159 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>season_claim</t>
+          <t>boss_rush_advance</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>티어 보상 수령 (free/premium)</t>
+          <t>웨이브 클리어 보고</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>자동 인벤토리 적용</t>
+          <t>시간 초과 검증</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>event → server.js</t>
+          <t>풀클리어 보상</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>3번째 모듈 통합</t>
+          <t>20웨이브 누적</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>축제 시스템 활성화</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>event_status</t>
+          <t>season → server.js</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>현재 활성 축제 조회</t>
+          <t>4번째 모듈 통합</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>이름/기간/버프/한정 보상</t>
+          <t>XP 자동 적립 + 보상 수령</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>/status JSON</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>festival 필드 추가</t>
+          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>대시보드 확인용</t>
+          <t>SEASON_XP_MAP 매핑</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>축제 인사</t>
+          <t>season_status</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>30% 확률로 NPC가 축제 대사 출력</t>
+          <t>XP/티어/구매여부/수령내역 조회</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>spring_blossom 등 5종</t>
+          <t>15티어 전체</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>fishing → server.js</t>
+          <t>season_buy_pass</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>프리미엄 패스 구매 (1500💎)</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>두 번째 모듈 통합</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -15810,51 +15920,51 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>fishing_status</t>
+          <t>season_claim</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>지역/낚싯대/미끼/시간대 조회</t>
+          <t>티어 보상 수령 (free/premium)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>자동 인벤토리 적용</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>fishing_cast</t>
+          <t>event → server.js</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
+          <t>3번째 모듈 통합</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>전설/신화 → 서버 알림</t>
+          <t>축제 시스템 활성화</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -15864,1880 +15974,1880 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>fishing_buy_rod</t>
+          <t>event_status</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>낚싯대 구매 (골드/다이아)</t>
+          <t>현재 활성 축제 조회</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>5등급 모두</t>
+          <t>이름/기간/버프/한정 보상</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>lottery → server.js</t>
+          <t>/status JSON</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>festival 필드 추가</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>첫 모듈 통합 마일스톤</t>
+          <t>대시보드 확인용</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>lottery_status</t>
+          <t>축제 인사</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>상태/가격/상품 풀 조회</t>
+          <t>30% 확률로 NPC가 축제 대사 출력</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>spring_blossom 등 5종</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>lottery_free_spin</t>
+          <t>fishing → server.js</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 스핀</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>자정 초기화</t>
+          <t>두 번째 모듈 통합</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>lottery_paid_spin</t>
+          <t>fishing_status</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>유료 1회 / 10연속</t>
+          <t>지역/낚싯대/미끼/시간대 조회</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>count: 1 또는 10</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>game/auction.js 신규</t>
+          <t>fishing_cast</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
+          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>등록 2% + 낙찰 5%</t>
+          <t>전설/신화 → 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>활성 한도</t>
+          <t>fishing_buy_rod</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>플레이어당 10개</t>
+          <t>낚싯대 구매 (골드/다이아)</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>자기 입찰 금지</t>
+          <t>5등급 모두</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>game/fishing.js 신규</t>
+          <t>lottery → server.js</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>신화 크라켄 = 20000G + 칭호</t>
+          <t>첫 모듈 통합 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>전설의 비단잉어</t>
+          <t>lottery_status</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>드래곤 낚싯대 + 가중치 1</t>
+          <t>상태/가격/상품 풀 조회</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>5000G + 평생 행운 +5%</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>game/boss_rush.js 신규</t>
+          <t>lottery_free_spin</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 / HP ×1.35 스케일링</t>
+          <t>매일 무료 1회 스핀</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>최종 보상: 200💎 + 용재료 ×5</t>
+          <t>자정 초기화</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>입장</t>
+          <t>lottery_paid_spin</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 3회 / 1000G / 30💎</t>
+          <t>유료 1회 / 10연속</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>랭킹 시스템</t>
+          <t>count: 1 또는 10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>챔피언 보상</t>
+          <t>game/auction.js 신규</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
+          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>등록 2% + 낙찰 5%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>game/lottery.js 신규</t>
+          <t>활성 한도</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>10종 보상 / 가중치 1000</t>
+          <t>플레이어당 10개</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 + 유료</t>
+          <t>자기 입찰 금지</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>영웅 장비 상자</t>
+          <t>game/fishing.js 신규</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>확률 0.2% (가장 희귀)</t>
+          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>전설 보상</t>
+          <t>신화 크라켄 = 20000G + 칭호</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>200 다이아</t>
+          <t>전설의 비단잉어</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>확률 0.8%</t>
+          <t>드래곤 낚싯대 + 가중치 1</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>5000G + 평생 행운 +5%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>신년 축제</t>
+          <t>game/boss_rush.js 신규</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>1/1 ~ 1/7</t>
+          <t>20웨이브 / HP ×1.35 스케일링</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>골드 +50% / EXP +30%</t>
+          <t>최종 보상: 200💎 + 용재료 ×5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>봄꽃 축제</t>
+          <t>입장</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>4/1 ~ 4/14</t>
+          <t>매일 무료 3회 / 1000G / 30💎</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>HP재생 +30% / 드롭 +20%</t>
+          <t>랭킹 시스템</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>한여름 밤의 축제</t>
+          <t>챔피언 보상</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>7/15 ~ 8/15</t>
+          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>화염 +30% / PvP 보상 +50%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>할로윈 축제</t>
+          <t>game/lottery.js 신규</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>10/25 ~ 11/1</t>
+          <t>10종 보상 / 가중치 1000</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>크리 +10% / 언데드 +50%</t>
+          <t>매일 무료 1회 + 유료</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>겨울 축제</t>
+          <t>영웅 장비 상자</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>12/20 ~ 12/31</t>
+          <t>확률 0.2% (가장 희귀)</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
+          <t>전설 보상</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>game/season.js 신규</t>
+          <t>200 다이아</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>15티어 / 30일 / 무료+프리미엄</t>
+          <t>확률 0.8%</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
+          <t>잭팟</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>XP 획득 7종</t>
+          <t>신년 축제</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>퀘/보스/PvP/월드보스/던전/제작</t>
+          <t>1/1 ~ 1/7</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>일일 +200 ~ 월드보스 +500</t>
+          <t>골드 +50% / EXP +30%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 가격</t>
+          <t>봄꽃 축제</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>1500 다이아</t>
+          <t>4/1 ~ 4/14</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>시즌 당 1회</t>
+          <t>HP재생 +30% / 드롭 +20%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Lv.40 달성</t>
+          <t>한여름 밤의 축제</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>각성기 해금 마일스톤</t>
+          <t>7/15 ~ 8/15</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>150💎</t>
+          <t>화염 +30% / PvP 보상 +50%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Lv.50 달성</t>
+          <t>할로윈 축제</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>환생 가능 마일스톤</t>
+          <t>10/25 ~ 11/1</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>250💎</t>
+          <t>크리 +10% / 언데드 +50%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>첫 환생</t>
+          <t>겨울 축제</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>prestige 1차</t>
+          <t>12/20 ~ 12/31</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>500💎</t>
+          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>첫 월드 보스</t>
+          <t>game/season.js 신규</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 처치 보너스</t>
+          <t>15티어 / 30일 / 무료+프리미엄</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>100💎</t>
+          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>업적 50개</t>
+          <t>XP 획득 7종</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>업적 마일스톤</t>
+          <t>퀘/보스/PvP/월드보스/던전/제작</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>200💎</t>
+          <t>일일 +200 ~ 월드보스 +500</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>불사조 스킨</t>
+          <t>프리미엄 가격</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>1500 다이아</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>불사조 깃털 이펙트 (영구)</t>
+          <t>시즌 당 1회</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>폭풍 스킨</t>
+          <t>Lv.40 달성</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>각성기 해금 마일스톤</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>번개 오라 이펙트 (영구)</t>
+          <t>150💎</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>상점 (편의)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 자동물약</t>
+          <t>Lv.50 달성</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>500 다이아</t>
+          <t>환생 가능 마일스톤</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>24시간 자동물약 무한</t>
+          <t>250💎</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>상점 (상자)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 보물 상자</t>
+          <t>첫 환생</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>300 다이아</t>
+          <t>prestige 1차</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>전설 장비 확정 + 다이아</t>
+          <t>500💎</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>상점 (재료)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>전설 재료 패키지</t>
+          <t>첫 월드 보스</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>600 다이아</t>
+          <t>월드 보스 처치 보너스</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
+          <t>100💎</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 분노</t>
+          <t>업적 50개</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>크리티컬 +5%</t>
+          <t>업적 마일스톤</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>60명 정원</t>
+          <t>200💎</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.7</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 신속</t>
+          <t>불사조 스킨</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>이동속도 +10%</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>70명 정원</t>
+          <t>불사조 깃털 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.8</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 회복</t>
+          <t>폭풍 스킨</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>HP 재생 +50%</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>80명 정원</t>
+          <t>번개 오라 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.9</t>
+          <t>상점 (편의)</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 운명</t>
+          <t>프리미엄 자동물약</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>회피 +5%</t>
+          <t>500 다이아</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>90명 정원</t>
+          <t>24시간 자동물약 무한</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.10</t>
+          <t>상점 (상자)</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 전설</t>
+          <t>프리미엄 보물 상자</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>전 스탯 +5%</t>
+          <t>300 다이아</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>100명 정원 — 최종</t>
+          <t>전설 장비 확정 + 다이아</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>상점 (재료)</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>점쟁이</t>
+          <t>전설 재료 패키지</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
+          <t>600 다이아</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.6</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>감정사</t>
+          <t>혈맹의 분노</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
+          <t>크리티컬 +5%</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>60명 정원</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.7</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>수집가</t>
+          <t>혈맹의 신속</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
+          <t>이동속도 +10%</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>70명 정원</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>각성기 (어쌔신)</t>
+          <t>혈맹 Lv.8</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>천 개의 칼날</t>
+          <t>혈맹의 회복</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
+          <t>HP 재생 +50%</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>80명 정원</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>각성기 (워리어)</t>
+          <t>혈맹 Lv.9</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>대지 가르기</t>
+          <t>혈맹의 운명</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
+          <t>회피 +5%</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>90명 정원</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>각성기 (나이트)</t>
+          <t>혈맹 Lv.10</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>불멸의 수호자</t>
+          <t>혈맹의 전설</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>피해 90% 감소 / 도발 / 10초</t>
+          <t>전 스탯 +5%</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>100명 정원 — 최종</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>각성기 (메이지)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>시간 정지</t>
+          <t>점쟁이</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
+          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>각성기 (클레릭)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>신의 은총</t>
+          <t>감정사</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>HP 100% 회복 / 전스탯 +50%</t>
+          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>폭풍 정복자</t>
+          <t>수집가</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인 처치</t>
+          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>10,000G + 150다이아</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (어쌔신)</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>연금술사</t>
+          <t>천 개의 칼날</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>엘릭서 10회 제작</t>
+          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>5,000G + 80다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (워리어)</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>그림자 정복자</t>
+          <t>대지 가르기</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 클리어</t>
+          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>8,000G + 120다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (나이트)</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>전설의 동반자</t>
+          <t>불멸의 수호자</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>전설급 펫 진화</t>
+          <t>피해 90% 감소 / 도발 / 10초</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>6,000G + 100다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (메이지)</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>이국의 상인</t>
+          <t>시간 정지</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>사치품 교역 5회</t>
+          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>4,000G + 60다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>각성기 (클레릭)</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인</t>
+          <t>신의 은총</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>HP 100,000 / ATK 140 / DEF 90</t>
+          <t>HP 100% 회복 / 전스탯 +50%</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>EXP 10000 + 6000G</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>시간의 수호자</t>
+          <t>폭풍 정복자</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>HP 70,000 / ATK 170 / DEF 60</t>
+          <t>폭풍의 거인 처치</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>EXP 9000 + 7000G</t>
+          <t>10,000G + 150다이아</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>교역품</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
+          <t>연금술사</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종</t>
+          <t>엘릭서 10회 제작</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>기본가 600~900G</t>
+          <t>5,000G + 80다이아</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>타이탄의 엘릭서</t>
+          <t>그림자 정복자</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>용재료×3 + 마법재료×10</t>
+          <t>그림자 미궁 클리어</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>ATK ×1.5 / 30분</t>
+          <t>8,000G + 120다이아</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>강철 엘릭서</t>
+          <t>전설의 동반자</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>철광석×30 + 마법재료×10</t>
+          <t>전설급 펫 진화</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>DEF ×1.5 / 30분</t>
+          <t>6,000G + 100다이아</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>질풍 엘릭서</t>
+          <t>이국의 상인</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>약초×20 + 마법재료×8</t>
+          <t>사치품 교역 5회</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>SPD ×1.4 / 20분</t>
+          <t>4,000G + 60다이아</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>지혜 엘릭서</t>
+          <t>폭풍의 거인</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>마법수정×5 + 영혼재료×5</t>
+          <t>HP 100,000 / ATK 140 / DEF 90</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>EXP ×2.5 / 15분</t>
+          <t>EXP 10000 + 6000G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>행운 엘릭서</t>
+          <t>시간의 수호자</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>보석×10 + 마법재료×5</t>
+          <t>HP 70,000 / ATK 170 / DEF 60</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>GOLD ×2.0 / 15분</t>
+          <t>EXP 9000 + 7000G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>교역품</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>불사조 (pet_phoenix)</t>
+          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>불꽃산 보스 50처치</t>
+          <t>이국의 사치품 3종</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>화염 DMG +20% (진화 +40%)</t>
+          <t>기본가 600~900G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>유니콘 (pet_unicorn)</t>
+          <t>타이탄의 엘릭서</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>다이아 800개</t>
+          <t>용재료×3 + 마법재료×10</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>회피 +10% (진화 +20%)</t>
+          <t>ATK ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>페가수스 (mount_pegasus)</t>
+          <t>강철 엘릭서</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>다이아 1200개</t>
+          <t>철광석×30 + 마법재료×10</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>이동속도 +85% / 비행</t>
+          <t>DEF ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁</t>
+          <t>질풍 엘릭서</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Lv.38 / 8인 파티 / 7스테이지</t>
+          <t>약초×20 + 마법재료×8</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>22000G + 32000EXP</t>
+          <t>SPD ×1.4 / 20분</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>드롭</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>드래곤 검/망토/투구/장갑</t>
+          <t>지혜 엘릭서</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 보스 드롭</t>
+          <t>마법수정×5 + 영혼재료×5</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>전설급</t>
+          <t>EXP ×2.5 / 15분</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>공허의 방랑자</t>
+          <t>행운 엘릭서</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>몬스터 10,000 처치</t>
+          <t>보석×10 + 마법재료×5</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>ATK +7%</t>
+          <t>GOLD ×2.0 / 15분</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>불멸자</t>
+          <t>불사조 (pet_phoenix)</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>환생 5회</t>
+          <t>불꽃산 보스 50처치</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>EXP +25%</t>
+          <t>화염 DMG +20% (진화 +40%)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>천공의 군주</t>
+          <t>유니콘 (pet_unicorn)</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 10회 처치</t>
+          <t>다이아 800개</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>보스DMG +15%</t>
+          <t>회피 +10% (진화 +20%)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>지역 시트 갱신</t>
+          <t>페가수스 (mount_pegasus)</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>25→51개 지역 반영</t>
+          <t>다이아 1200개</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이동속도 +85% / 비행</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>칭호 시트 갱신</t>
+          <t>그림자 미궁</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>7→16종 + 효과/색상 추가</t>
+          <t>Lv.38 / 8인 파티 / 7스테이지</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22000G + 32000EXP</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>드롭</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>출석 캘린더 시트</t>
+          <t>드래곤 검/망토/투구/장갑</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (28일 사이클)</t>
+          <t>그림자 미궁 보스 드롭</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>전설급</t>
         </is>
       </c>
     </row>
@@ -17749,22 +17859,22 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>장비 세트 시트</t>
+          <t>공허의 방랑자</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (드래곤/영웅/태초)</t>
+          <t>몬스터 10,000 처치</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ATK +7%</t>
         </is>
       </c>
     </row>
@@ -17776,22 +17886,22 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>장비 등급 시트</t>
+          <t>불멸자</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+          <t>환생 5회</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EXP +25%</t>
         </is>
       </c>
     </row>
@@ -17803,22 +17913,22 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>디버프 시트</t>
+          <t>천공의 군주</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+          <t>월드 보스 10회 처치</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>보스DMG +15%</t>
         </is>
       </c>
     </row>
@@ -17835,12 +17945,12 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>패치 노트 시트</t>
+          <t>지역 시트 갱신</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (히스토리)</t>
+          <t>25→51개 지역 반영</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -17852,25 +17962,187 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>칭호 시트 갱신</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>7→16종 + 효과/색상 추가</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>출석 캘린더 시트</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (28일 사이클)</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>장비 세트 시트</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (드래곤/영웅/태초)</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>장비 등급 시트</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>디버프 시트</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>패치 노트 시트</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (히스토리)</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
           <t>v1.10</t>
         </is>
       </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>기획서</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C102" s="7" t="inlineStr">
         <is>
           <t>던전 시트</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D102" s="7" t="inlineStr">
         <is>
           <t>신규 추가 (7종 던전)</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E102" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -28,19 +28,20 @@
     <sheet name="장비 등급" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="디버프 v1.7+" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="던전" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="경매장" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="낚시" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="보스 러시" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="행운의 룰렛" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="축제 이벤트" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="시즌 패스" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="무료 다이아" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="길드 (혈맹)" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="NPC" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="월드 보스" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="연금술" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="패치 노트" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="v1.9 ~ v1.31" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="일일 상점" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="경매장" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="낚시" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="보스 러시" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="행운의 룰렛" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="축제 이벤트" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="시즌 패스" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="무료 다이아" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="길드 (혈맹)" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="NPC" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="월드 보스" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="연금술" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="패치 노트" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="v1.9 ~ v1.32" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6861,6 +6862,572 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>일일 상점 풀 (15종 — v1.32 신규 모듈 game/dailyshop.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>기본가</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>pot_hp_l</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>상급 HP 물약</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>300G</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>매일 6슬롯 풀</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>pot_atk</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>공격 물약</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>500G</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>mat_magic</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>마법재료</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>mat</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>200G</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>mat_soul</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>영혼석</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>mat</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>600G</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>mat_dragon</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>용재료</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>mat</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>2500G</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>protect_scroll</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>보호 주문서</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>80💎</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>bless_scroll</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>축복 주문서</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>40💎</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>rare_box</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>희귀 상자</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>60💎</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>mega_exp</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>메가 EXP 부스터</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>booster</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>100💎</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>mega_gold</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>메가 골드 부스터</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>booster</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>100💎</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>food_king</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>왕의 연회</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>1200G</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>food_all</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>용의 만찬</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>600G</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>goods_phoenix_feather</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>불사조 깃털</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>trade</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>600G</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>v1.13 사치품</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>goods_void_essence</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>공허의 정수</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>trade</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>750G</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>v1.13 사치품</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>goods_celestial_silk</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>천공의 비단</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>trade</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>900G</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>v1.13 사치품</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>일일 상점 시스템</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>슬롯 수</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>6개 (매일 무작위 6종 선출)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>결정적 랜덤</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>시드 = 날짜(YYYY-MM-DD), 모든 플레이어 동일 상품</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>할인율</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>10~50% (슬롯별 무작위)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>구매 제한</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>슬롯당 1회 / 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>수동 갱신</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>30💎로 개인 시드 생성 → 새 6종 + 구매 기록 초기화</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>자동 갱신</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>자정 (다음 날 첫 status 요청 시 자동)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>game/dailyshop.js (신규 파일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7159,7 +7726,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8022,7 +8589,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9239,7 +9806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9750,7 +10317,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10084,7 +10651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10485,7 +11052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10926,393 +11493,6 @@
       <c r="B22" s="3" t="inlineStr">
         <is>
           <t>초반 무료 1500💎 → 28일 출석 + 패치 콘텐츠로 추가 확보 가능</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>혈맹 (10단계 — v1.17 Lv.6-10 신규)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>혈맹 Lv.</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>최대 인원</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>스킬명</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>효과</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>10명</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>혈맹의 힘</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>ATK +5%</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>기본 결성</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>20명</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>혈맹의 방패</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>DEF +5%</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>30명</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>혈맹의 지혜</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>EXP +10%</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>40명</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>혈맹의 축복</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>HP +10%</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>50명</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>혈맹의 영광</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>골드 +10%</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>혈맹의 별 칭호 획득</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>60명</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>혈맹의 분노</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>크리티컬 +5%</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>v1.17 신규</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>70명</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>혈맹의 신속</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>이동속도 +10%</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>v1.17 신규</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>80명</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>혈맹의 회복</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>HP 재생 +50%</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>v1.17 신규</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>90명</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>혈맹의 운명</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>회피 +5%</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>v1.17 신규</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>100명</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>혈맹의 전설</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>전 스탯 +5%</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>v1.17 신규 — 최종 단계</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>혈맹 시스템 요소</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>역할</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>혈맹주(leader) / 간부(officers) / 일반 멤버</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>혈맹 창고</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>공유 인벤토리 (입출고 권한)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>혈맹 스킬</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>혈맹 레벨에 따라 자동 적용 (전 멤버 효과)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>혈맹 전쟁</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>다른 혈맹과 PvP / 영토 점령</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>혈맹 레이드</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>혈맹 단위 던전 / 보스 레이드</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>공성전</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>하늘의 성채 / 북부 요새 점령</t>
         </is>
       </c>
     </row>
@@ -12616,6 +12796,393 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>혈맹 (10단계 — v1.17 Lv.6-10 신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>혈맹 Lv.</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>최대 인원</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>스킬명</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>효과</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>10명</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>혈맹의 힘</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>ATK +5%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>기본 결성</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>20명</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>혈맹의 방패</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>DEF +5%</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>30명</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>혈맹의 지혜</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>EXP +10%</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>40명</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>혈맹의 축복</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>HP +10%</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>50명</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>혈맹의 영광</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>골드 +10%</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>혈맹의 별 칭호 획득</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>60명</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>혈맹의 분노</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>크리티컬 +5%</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>v1.17 신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>70명</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>혈맹의 신속</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>이동속도 +10%</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>v1.17 신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>80명</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>혈맹의 회복</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>HP 재생 +50%</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>v1.17 신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>90명</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>혈맹의 운명</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>회피 +5%</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>v1.17 신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>100명</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>혈맹의 전설</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>전 스탯 +5%</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>v1.17 신규 — 최종 단계</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>혈맹 시스템 요소</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>혈맹주(leader) / 간부(officers) / 일반 멤버</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>혈맹 창고</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>공유 인벤토리 (입출고 권한)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>혈맹 스킬</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>혈맹 레벨에 따라 자동 적용 (전 멤버 효과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>혈맹 전쟁</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>다른 혈맹과 PvP / 영토 점령</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>혈맹 레이드</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>혈맹 단위 던전 / 보스 레이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>공성전</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>하늘의 성채 / 북부 요새 점령</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13008,7 +13575,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13349,7 +13916,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13679,13 +14246,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13726,7 +14293,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -13736,19 +14303,19 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
+          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -13758,19 +14325,19 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
+          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -13780,19 +14347,19 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
+          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -13807,7 +14374,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>auction_list / create / bid / my</t>
+          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
         </is>
       </c>
     </row>
@@ -13824,19 +14391,19 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
+          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -13846,19 +14413,19 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
+          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -13868,19 +14435,19 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
+          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -13895,14 +14462,14 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_status / enter / advance / abandon</t>
+          <t>auction_list / create / bid / my</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -13912,19 +14479,19 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
+          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -13939,14 +14506,14 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
+          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -13956,19 +14523,19 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
+          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -13983,14 +14550,14 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>season_status / season_buy_pass / season_claim</t>
+          <t>boss_rush_status / enter / advance / abandon</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -14000,19 +14567,19 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
+          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -14027,14 +14594,14 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
+          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -14044,19 +14611,19 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>event_status 소켓 + /status 엔드포인트 노출</t>
+          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -14066,19 +14633,19 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
+          <t>season_status / season_buy_pass / season_claim</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -14088,19 +14655,19 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
+          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -14115,14 +14682,14 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
+          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -14132,19 +14699,19 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
+          <t>event_status 소켓 + /status 엔드포인트 노출</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -14154,19 +14721,19 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
+          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -14176,19 +14743,19 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
+          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -14203,14 +14770,14 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
+          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -14220,19 +14787,19 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
+          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -14242,19 +14809,19 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
+          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -14264,19 +14831,19 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
+          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -14286,19 +14853,19 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
+          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -14308,19 +14875,19 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>경매장 시트 신규 추가</t>
+          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -14330,19 +14897,19 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
+          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -14352,19 +14919,19 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
+          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -14374,19 +14941,19 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>낚시 시트 신규 추가</t>
+          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -14396,19 +14963,19 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
+          <t>경매장 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -14418,19 +14985,19 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
+          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -14440,19 +15007,19 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>보스 러시 시트 신규 추가</t>
+          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -14462,19 +15029,19 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
+          <t>낚시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -14484,19 +15051,19 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
+          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -14506,19 +15073,19 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛 시트 신규 추가</t>
+          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -14528,19 +15095,19 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
+          <t>보스 러시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -14550,19 +15117,19 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>모듈화</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
+          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -14572,19 +15139,19 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트 시트 신규 추가</t>
+          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -14594,19 +15161,19 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
+          <t>행운의 룰렛 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -14616,19 +15183,19 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
+          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -14638,19 +15205,19 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>모듈화</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스 시트 신규 추가</t>
+          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -14660,19 +15227,19 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
+          <t>축제 이벤트 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -14682,19 +15249,19 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아 시트 신규 추가</t>
+          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -14704,19 +15271,19 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
+          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -14731,14 +15298,14 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>상점 시트 갱신</t>
+          <t>시즌 패스 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -14748,19 +15315,19 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
+          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -14770,19 +15337,19 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>최대 인원 50→100명 (Lv.10 기준)</t>
+          <t>무료 다이아 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -14792,19 +15359,19 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>길드(혈맹) 시트 신규 추가</t>
+          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -14814,19 +15381,19 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
+          <t>상점 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -14836,19 +15403,19 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>대사 시스템</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
+          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -14858,19 +15425,19 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>NPC 시트 신규 추가 (11종)</t>
+          <t>최대 인원 50→100명 (Lv.10 기준)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -14880,19 +15447,19 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>각성기</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
+          <t>길드(혈맹) 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -14902,19 +15469,19 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
+          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -14924,19 +15491,19 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>대사 시스템</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
+          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -14951,14 +15518,14 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
+          <t>NPC 시트 신규 추가 (11종)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -14968,19 +15535,19 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>각성기</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
+          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -14990,19 +15557,19 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>교역</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
+          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -15012,19 +15579,19 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
+          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -15034,19 +15601,19 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
+          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -15056,19 +15623,19 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>연금술 시트 신규 추가</t>
+          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -15078,19 +15645,19 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>교역</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
+          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -15100,19 +15667,19 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (이동 +85%, 비행)</t>
+          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -15122,19 +15689,19 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
+          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -15149,14 +15716,14 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
+          <t>연금술 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -15166,19 +15733,19 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
+          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -15188,107 +15755,107 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
+          <t>페가수스 (이동 +85%, 비행)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
+          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
+          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
+          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
+          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -15298,19 +15865,19 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>상태이상</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
+          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -15320,19 +15887,19 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -15342,19 +15909,19 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -15364,12 +15931,12 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>컨텐츠</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
         </is>
       </c>
     </row>
@@ -15386,32 +15953,120 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>상태이상</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>컨텐츠</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
           <t>v1.6 이전</t>
         </is>
       </c>
-      <c r="B80" s="7" t="inlineStr">
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>기반</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>마을/사냥/PvP/카르마/펫/탈것/제작/교역/길드/공성/투기장 등</t>
         </is>
@@ -15425,13 +16080,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15478,81 +16133,81 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>auction → server.js</t>
+          <t>game/dailyshop.js</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>6번째 (마지막) 모듈 통합</t>
+          <t>일일 상점 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>자동 정산 + 환불 + 양방향 지급</t>
+          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>결정적 랜덤</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>tickAuctions</t>
+          <t>날짜 시드</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>10초마다 만료 정산</t>
+          <t>모든 플레이어 동일 상품</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>setInterval 통합</t>
+          <t>seededRandom + Fisher-Yates</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>개인 갱신</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>auction_create</t>
+          <t>30💎</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>경매 등록 (등록 수수료 자동 차감)</t>
+          <t>개인 시드 생성</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>3가지 기간</t>
+          <t>구매 기록 초기화</t>
         </is>
       </c>
     </row>
@@ -15564,22 +16219,22 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>auction_bid</t>
+          <t>auction → server.js</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>입찰 + 이전 입찰자 자동 환불</t>
+          <t>6번째 (마지막) 모듈 통합</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>스나이핑 방지 연장</t>
+          <t>자동 정산 + 환불 + 양방향 지급</t>
         </is>
       </c>
     </row>
@@ -15591,22 +16246,22 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>auction_my</t>
+          <t>tickAuctions</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>내 등록/입찰 내역 조회</t>
+          <t>10초마다 만료 정산</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>setInterval 통합</t>
         </is>
       </c>
     </row>
@@ -15618,103 +16273,103 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>신규 모듈 6/6</t>
+          <t>auction_create</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>100% 통합 완료</t>
+          <t>경매 등록 (등록 수수료 자동 차감)</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>lottery/fishing/event/season/boss_rush/auction</t>
+          <t>3가지 기간</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>boss_rush → server.js</t>
+          <t>auction_bid</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>5번째 모듈 통합</t>
+          <t>입찰 + 이전 입찰자 자동 환불</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>메모리 세션 기반</t>
+          <t>스나이핑 방지 연장</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>bossRushSessions</t>
+          <t>auction_my</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>진행 중 세션 저장</t>
+          <t>내 등록/입찰 내역 조회</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>currentWave/시간 추적</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>bossRushRanking</t>
+          <t>신규 모듈 6/6</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>글로벌 랭킹 TOP 100</t>
+          <t>100% 통합 완료</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>웨이브 → 시간 정렬</t>
+          <t>lottery/fishing/event/season/boss_rush/auction</t>
         </is>
       </c>
     </row>
@@ -15726,22 +16381,22 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_enter</t>
+          <t>boss_rush → server.js</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>무료/유료/다이아 입장</t>
+          <t>5번째 모듈 통합</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>동시 1개 세션 제한</t>
+          <t>메모리 세션 기반</t>
         </is>
       </c>
     </row>
@@ -15753,22 +16408,22 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>boss_rush_advance</t>
+          <t>bossRushSessions</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>웨이브 클리어 보고</t>
+          <t>진행 중 세션 저장</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>시간 초과 검증</t>
+          <t>currentWave/시간 추적</t>
         </is>
       </c>
     </row>
@@ -15780,103 +16435,103 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>풀클리어 보상</t>
+          <t>bossRushRanking</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 누적</t>
+          <t>글로벌 랭킹 TOP 100</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>웨이브 → 시간 정렬</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>season → server.js</t>
+          <t>boss_rush_enter</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>4번째 모듈 통합</t>
+          <t>무료/유료/다이아 입장</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>XP 자동 적립 + 보상 수령</t>
+          <t>동시 1개 세션 제한</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>boss_rush_advance</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
+          <t>웨이브 클리어 보고</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>SEASON_XP_MAP 매핑</t>
+          <t>시간 초과 검증</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>season_status</t>
+          <t>풀클리어 보상</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>XP/티어/구매여부/수령내역 조회</t>
+          <t>20웨이브 누적</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>15티어 전체</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
@@ -15888,22 +16543,22 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>season_buy_pass</t>
+          <t>season → server.js</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 패스 구매 (1500💎)</t>
+          <t>4번째 모듈 통합</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>XP 자동 적립 + 보상 수령</t>
         </is>
       </c>
     </row>
@@ -15915,56 +16570,56 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>season_claim</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>티어 보상 수령 (free/premium)</t>
+          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>자동 인벤토리 적용</t>
+          <t>SEASON_XP_MAP 매핑</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>event → server.js</t>
+          <t>season_status</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>3번째 모듈 통합</t>
+          <t>XP/티어/구매여부/수령내역 조회</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>축제 시스템 활성화</t>
+          <t>15티어 전체</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -15974,44 +16629,44 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>event_status</t>
+          <t>season_buy_pass</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>현재 활성 축제 조회</t>
+          <t>프리미엄 패스 구매 (1500💎)</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>이름/기간/버프/한정 보상</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>/status JSON</t>
+          <t>season_claim</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>festival 필드 추가</t>
+          <t>티어 보상 수령 (free/premium)</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>대시보드 확인용</t>
+          <t>자동 인벤토리 적용</t>
         </is>
       </c>
     </row>
@@ -16023,103 +16678,103 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>축제 인사</t>
+          <t>event → server.js</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>30% 확률로 NPC가 축제 대사 출력</t>
+          <t>3번째 모듈 통합</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>spring_blossom 등 5종</t>
+          <t>축제 시스템 활성화</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>fishing → server.js</t>
+          <t>event_status</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>현재 활성 축제 조회</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>두 번째 모듈 통합</t>
+          <t>이름/기간/버프/한정 보상</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>fishing_status</t>
+          <t>/status JSON</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>지역/낚싯대/미끼/시간대 조회</t>
+          <t>festival 필드 추가</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>대시보드 확인용</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>fishing_cast</t>
+          <t>축제 인사</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
+          <t>30% 확률로 NPC가 축제 대사 출력</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>전설/신화 → 서버 알림</t>
+          <t>spring_blossom 등 5종</t>
         </is>
       </c>
     </row>
@@ -16131,103 +16786,103 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>fishing_buy_rod</t>
+          <t>fishing → server.js</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>낚싯대 구매 (골드/다이아)</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>5등급 모두</t>
+          <t>두 번째 모듈 통합</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>lottery → server.js</t>
+          <t>fishing_status</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>지역/낚싯대/미끼/시간대 조회</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>첫 모듈 통합 마일스톤</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>lottery_status</t>
+          <t>fishing_cast</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>상태/가격/상품 풀 조회</t>
+          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>전설/신화 → 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>lottery_free_spin</t>
+          <t>fishing_buy_rod</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 스핀</t>
+          <t>낚싯대 구매 (골드/다이아)</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>자정 초기화</t>
+          <t>5등급 모두</t>
         </is>
       </c>
     </row>
@@ -16239,373 +16894,373 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>lottery_paid_spin</t>
+          <t>lottery → server.js</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>유료 1회 / 10연속</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>count: 1 또는 10</t>
+          <t>첫 모듈 통합 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>game/auction.js 신규</t>
+          <t>lottery_status</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
+          <t>상태/가격/상품 풀 조회</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>등록 2% + 낙찰 5%</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>활성 한도</t>
+          <t>lottery_free_spin</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>플레이어당 10개</t>
+          <t>매일 무료 1회 스핀</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>자기 입찰 금지</t>
+          <t>자정 초기화</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>game/fishing.js 신규</t>
+          <t>lottery_paid_spin</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
+          <t>유료 1회 / 10연속</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>신화 크라켄 = 20000G + 칭호</t>
+          <t>count: 1 또는 10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>전설의 비단잉어</t>
+          <t>game/auction.js 신규</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>드래곤 낚싯대 + 가중치 1</t>
+          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>5000G + 평생 행운 +5%</t>
+          <t>등록 2% + 낙찰 5%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>game/boss_rush.js 신규</t>
+          <t>활성 한도</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 / HP ×1.35 스케일링</t>
+          <t>플레이어당 10개</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>최종 보상: 200💎 + 용재료 ×5</t>
+          <t>자기 입찰 금지</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>입장</t>
+          <t>game/fishing.js 신규</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 3회 / 1000G / 30💎</t>
+          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>랭킹 시스템</t>
+          <t>신화 크라켄 = 20000G + 칭호</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>챔피언 보상</t>
+          <t>전설의 비단잉어</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
+          <t>드래곤 낚싯대 + 가중치 1</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5000G + 평생 행운 +5%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>game/lottery.js 신규</t>
+          <t>game/boss_rush.js 신규</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>10종 보상 / 가중치 1000</t>
+          <t>20웨이브 / HP ×1.35 스케일링</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 + 유료</t>
+          <t>최종 보상: 200💎 + 용재료 ×5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>영웅 장비 상자</t>
+          <t>입장</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>확률 0.2% (가장 희귀)</t>
+          <t>매일 무료 3회 / 1000G / 30💎</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>전설 보상</t>
+          <t>랭킹 시스템</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>200 다이아</t>
+          <t>챔피언 보상</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>확률 0.8%</t>
+          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>신년 축제</t>
+          <t>game/lottery.js 신규</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>1/1 ~ 1/7</t>
+          <t>10종 보상 / 가중치 1000</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>골드 +50% / EXP +30%</t>
+          <t>매일 무료 1회 + 유료</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>봄꽃 축제</t>
+          <t>영웅 장비 상자</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>4/1 ~ 4/14</t>
+          <t>확률 0.2% (가장 희귀)</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>HP재생 +30% / 드롭 +20%</t>
+          <t>전설 보상</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>한여름 밤의 축제</t>
+          <t>200 다이아</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>7/15 ~ 8/15</t>
+          <t>확률 0.8%</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>화염 +30% / PvP 보상 +50%</t>
+          <t>잭팟</t>
         </is>
       </c>
     </row>
@@ -16622,17 +17277,17 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>할로윈 축제</t>
+          <t>신년 축제</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>10/25 ~ 11/1</t>
+          <t>1/1 ~ 1/7</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>크리 +10% / 언데드 +50%</t>
+          <t>골드 +50% / EXP +30%</t>
         </is>
       </c>
     </row>
@@ -16649,179 +17304,179 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>겨울 축제</t>
+          <t>봄꽃 축제</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>12/20 ~ 12/31</t>
+          <t>4/1 ~ 4/14</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
+          <t>HP재생 +30% / 드롭 +20%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>game/season.js 신규</t>
+          <t>한여름 밤의 축제</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>15티어 / 30일 / 무료+프리미엄</t>
+          <t>7/15 ~ 8/15</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
+          <t>화염 +30% / PvP 보상 +50%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>XP 획득 7종</t>
+          <t>할로윈 축제</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>퀘/보스/PvP/월드보스/던전/제작</t>
+          <t>10/25 ~ 11/1</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>일일 +200 ~ 월드보스 +500</t>
+          <t>크리 +10% / 언데드 +50%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 가격</t>
+          <t>겨울 축제</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>1500 다이아</t>
+          <t>12/20 ~ 12/31</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>시즌 당 1회</t>
+          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Lv.40 달성</t>
+          <t>game/season.js 신규</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>각성기 해금 마일스톤</t>
+          <t>15티어 / 30일 / 무료+프리미엄</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>150💎</t>
+          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Lv.50 달성</t>
+          <t>XP 획득 7종</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>환생 가능 마일스톤</t>
+          <t>퀘/보스/PvP/월드보스/던전/제작</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>250💎</t>
+          <t>일일 +200 ~ 월드보스 +500</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>첫 환생</t>
+          <t>프리미엄 가격</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>prestige 1차</t>
+          <t>1500 다이아</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>500💎</t>
+          <t>시즌 당 1회</t>
         </is>
       </c>
     </row>
@@ -16838,17 +17493,17 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>첫 월드 보스</t>
+          <t>Lv.40 달성</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 처치 보너스</t>
+          <t>각성기 해금 마일스톤</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>100💎</t>
+          <t>150💎</t>
         </is>
       </c>
     </row>
@@ -16865,98 +17520,98 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>업적 50개</t>
+          <t>Lv.50 달성</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>업적 마일스톤</t>
+          <t>환생 가능 마일스톤</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>200💎</t>
+          <t>250💎</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>불사조 스킨</t>
+          <t>첫 환생</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>prestige 1차</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>불사조 깃털 이펙트 (영구)</t>
+          <t>500💎</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>폭풍 스킨</t>
+          <t>첫 월드 보스</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>월드 보스 처치 보너스</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>번개 오라 이펙트 (영구)</t>
+          <t>100💎</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>상점 (편의)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 자동물약</t>
+          <t>업적 50개</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>500 다이아</t>
+          <t>업적 마일스톤</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>24시간 자동물약 무한</t>
+          <t>200💎</t>
         </is>
       </c>
     </row>
@@ -16968,22 +17623,22 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>상점 (상자)</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 보물 상자</t>
+          <t>불사조 스킨</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>300 다이아</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>전설 장비 확정 + 다이아</t>
+          <t>불사조 깃털 이펙트 (영구)</t>
         </is>
       </c>
     </row>
@@ -16995,103 +17650,103 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>상점 (재료)</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>전설 재료 패키지</t>
+          <t>폭풍 스킨</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>600 다이아</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
+          <t>번개 오라 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6</t>
+          <t>상점 (편의)</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 분노</t>
+          <t>프리미엄 자동물약</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>크리티컬 +5%</t>
+          <t>500 다이아</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>60명 정원</t>
+          <t>24시간 자동물약 무한</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.7</t>
+          <t>상점 (상자)</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 신속</t>
+          <t>프리미엄 보물 상자</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>이동속도 +10%</t>
+          <t>300 다이아</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>70명 정원</t>
+          <t>전설 장비 확정 + 다이아</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.8</t>
+          <t>상점 (재료)</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 회복</t>
+          <t>전설 재료 패키지</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>HP 재생 +50%</t>
+          <t>600 다이아</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>80명 정원</t>
+          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
         </is>
       </c>
     </row>
@@ -17103,22 +17758,22 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.9</t>
+          <t>혈맹 Lv.6</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 운명</t>
+          <t>혈맹의 분노</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>회피 +5%</t>
+          <t>크리티컬 +5%</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>90명 정원</t>
+          <t>60명 정원</t>
         </is>
       </c>
     </row>
@@ -17130,184 +17785,184 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.10</t>
+          <t>혈맹 Lv.7</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 전설</t>
+          <t>혈맹의 신속</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>전 스탯 +5%</t>
+          <t>이동속도 +10%</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>100명 정원 — 최종</t>
+          <t>70명 정원</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.8</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>점쟁이</t>
+          <t>혈맹의 회복</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
+          <t>HP 재생 +50%</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>80명 정원</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.9</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>감정사</t>
+          <t>혈맹의 운명</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
+          <t>회피 +5%</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>90명 정원</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.10</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>수집가</t>
+          <t>혈맹의 전설</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
+          <t>전 스탯 +5%</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>100명 정원 — 최종</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>각성기 (어쌔신)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>천 개의 칼날</t>
+          <t>점쟁이</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
+          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>각성기 (워리어)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>대지 가르기</t>
+          <t>감정사</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
+          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>각성기 (나이트)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>불멸의 수호자</t>
+          <t>수집가</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>피해 90% 감소 / 도발 / 10초</t>
+          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
@@ -17319,17 +17974,17 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>각성기 (메이지)</t>
+          <t>각성기 (어쌔신)</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>시간 정지</t>
+          <t>천 개의 칼날</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
+          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
@@ -17346,17 +18001,17 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>각성기 (클레릭)</t>
+          <t>각성기 (워리어)</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>신의 은총</t>
+          <t>대지 가르기</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>HP 100% 회복 / 전스탯 +50%</t>
+          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -17368,81 +18023,81 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (나이트)</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>폭풍 정복자</t>
+          <t>불멸의 수호자</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인 처치</t>
+          <t>피해 90% 감소 / 도발 / 10초</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>10,000G + 150다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (메이지)</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>연금술사</t>
+          <t>시간 정지</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>엘릭서 10회 제작</t>
+          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>5,000G + 80다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (클레릭)</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>그림자 정복자</t>
+          <t>신의 은총</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 클리어</t>
+          <t>HP 100% 회복 / 전스탯 +50%</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>8,000G + 120다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
@@ -17459,17 +18114,17 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>전설의 동반자</t>
+          <t>폭풍 정복자</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>전설급 펫 진화</t>
+          <t>폭풍의 거인 처치</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>6,000G + 100다이아</t>
+          <t>10,000G + 150다이아</t>
         </is>
       </c>
     </row>
@@ -17486,179 +18141,179 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>이국의 상인</t>
+          <t>연금술사</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>사치품 교역 5회</t>
+          <t>엘릭서 10회 제작</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>4,000G + 60다이아</t>
+          <t>5,000G + 80다이아</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인</t>
+          <t>그림자 정복자</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>HP 100,000 / ATK 140 / DEF 90</t>
+          <t>그림자 미궁 클리어</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>EXP 10000 + 6000G</t>
+          <t>8,000G + 120다이아</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>시간의 수호자</t>
+          <t>전설의 동반자</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>HP 70,000 / ATK 170 / DEF 60</t>
+          <t>전설급 펫 진화</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>EXP 9000 + 7000G</t>
+          <t>6,000G + 100다이아</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>교역품</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
+          <t>이국의 상인</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종</t>
+          <t>사치품 교역 5회</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>기본가 600~900G</t>
+          <t>4,000G + 60다이아</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>타이탄의 엘릭서</t>
+          <t>폭풍의 거인</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>용재료×3 + 마법재료×10</t>
+          <t>HP 100,000 / ATK 140 / DEF 90</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>ATK ×1.5 / 30분</t>
+          <t>EXP 10000 + 6000G</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>강철 엘릭서</t>
+          <t>시간의 수호자</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>철광석×30 + 마법재료×10</t>
+          <t>HP 70,000 / ATK 170 / DEF 60</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>DEF ×1.5 / 30분</t>
+          <t>EXP 9000 + 7000G</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>교역품</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>질풍 엘릭서</t>
+          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>약초×20 + 마법재료×8</t>
+          <t>이국의 사치품 3종</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>SPD ×1.4 / 20분</t>
+          <t>기본가 600~900G</t>
         </is>
       </c>
     </row>
@@ -17675,17 +18330,17 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>지혜 엘릭서</t>
+          <t>타이탄의 엘릭서</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>마법수정×5 + 영혼재료×5</t>
+          <t>용재료×3 + 마법재료×10</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>EXP ×2.5 / 15분</t>
+          <t>ATK ×1.5 / 30분</t>
         </is>
       </c>
     </row>
@@ -17702,233 +18357,233 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>행운 엘릭서</t>
+          <t>강철 엘릭서</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>보석×10 + 마법재료×5</t>
+          <t>철광석×30 + 마법재료×10</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>GOLD ×2.0 / 15분</t>
+          <t>DEF ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>불사조 (pet_phoenix)</t>
+          <t>질풍 엘릭서</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>불꽃산 보스 50처치</t>
+          <t>약초×20 + 마법재료×8</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>화염 DMG +20% (진화 +40%)</t>
+          <t>SPD ×1.4 / 20분</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>유니콘 (pet_unicorn)</t>
+          <t>지혜 엘릭서</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>다이아 800개</t>
+          <t>마법수정×5 + 영혼재료×5</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>회피 +10% (진화 +20%)</t>
+          <t>EXP ×2.5 / 15분</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>페가수스 (mount_pegasus)</t>
+          <t>행운 엘릭서</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>다이아 1200개</t>
+          <t>보석×10 + 마법재료×5</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>이동속도 +85% / 비행</t>
+          <t>GOLD ×2.0 / 15분</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁</t>
+          <t>불사조 (pet_phoenix)</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Lv.38 / 8인 파티 / 7스테이지</t>
+          <t>불꽃산 보스 50처치</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>22000G + 32000EXP</t>
+          <t>화염 DMG +20% (진화 +40%)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>드롭</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>드래곤 검/망토/투구/장갑</t>
+          <t>유니콘 (pet_unicorn)</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 보스 드롭</t>
+          <t>다이아 800개</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>전설급</t>
+          <t>회피 +10% (진화 +20%)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>공허의 방랑자</t>
+          <t>페가수스 (mount_pegasus)</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>몬스터 10,000 처치</t>
+          <t>다이아 1200개</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>ATK +7%</t>
+          <t>이동속도 +85% / 비행</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>불멸자</t>
+          <t>그림자 미궁</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>환생 5회</t>
+          <t>Lv.38 / 8인 파티 / 7스테이지</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>EXP +25%</t>
+          <t>22000G + 32000EXP</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>드롭</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>천공의 군주</t>
+          <t>드래곤 검/망토/투구/장갑</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 10회 처치</t>
+          <t>그림자 미궁 보스 드롭</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>보스DMG +15%</t>
+          <t>전설급</t>
         </is>
       </c>
     </row>
@@ -17940,22 +18595,22 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>지역 시트 갱신</t>
+          <t>공허의 방랑자</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>25→51개 지역 반영</t>
+          <t>몬스터 10,000 처치</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ATK +7%</t>
         </is>
       </c>
     </row>
@@ -17967,22 +18622,22 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>칭호 시트 갱신</t>
+          <t>불멸자</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>7→16종 + 효과/색상 추가</t>
+          <t>환생 5회</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EXP +25%</t>
         </is>
       </c>
     </row>
@@ -17994,22 +18649,22 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>출석 캘린더 시트</t>
+          <t>천공의 군주</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (28일 사이클)</t>
+          <t>월드 보스 10회 처치</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>보스DMG +15%</t>
         </is>
       </c>
     </row>
@@ -18026,12 +18681,12 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>장비 세트 시트</t>
+          <t>지역 시트 갱신</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (드래곤/영웅/태초)</t>
+          <t>25→51개 지역 반영</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
@@ -18053,12 +18708,12 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>장비 등급 시트</t>
+          <t>칭호 시트 갱신</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+          <t>7→16종 + 효과/색상 추가</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -18080,12 +18735,12 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>디버프 시트</t>
+          <t>출석 캘린더 시트</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+          <t>신규 추가 (28일 사이클)</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
@@ -18107,12 +18762,12 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>패치 노트 시트</t>
+          <t>장비 세트 시트</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (히스토리)</t>
+          <t>신규 추가 (드래곤/영웅/태초)</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -18124,25 +18779,106 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>장비 등급 시트</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>디버프 시트</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>패치 노트 시트</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (히스토리)</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
           <t>v1.10</t>
         </is>
       </c>
-      <c r="B102" s="7" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>기획서</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr">
+      <c r="C105" s="8" t="inlineStr">
         <is>
           <t>던전 시트</t>
         </is>
       </c>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="D105" s="8" t="inlineStr">
         <is>
           <t>신규 추가 (7종 던전)</t>
         </is>
       </c>
-      <c r="E102" s="7" t="inlineStr">
+      <c r="E105" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -28,20 +28,21 @@
     <sheet name="장비 등급" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="디버프 v1.7+" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="던전" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="일일 상점" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="경매장" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="낚시" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="보스 러시" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="행운의 룰렛" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="축제 이벤트" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="시즌 패스" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="무료 다이아" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="길드 (혈맹)" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="NPC" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="월드 보스" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="연금술" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="패치 노트" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="v1.9 ~ v1.32" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="도감" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="일일 상점" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="경매장" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="낚시" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="보스 러시" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="행운의 룰렛" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="축제 이벤트" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="시즌 패스" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="무료 다이아" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="길드 (혈맹)" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="NPC" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="월드 보스" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="연금술" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="패치 노트" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="v1.9 ~ v1.33" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6862,6 +6863,855 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>도감 (5종 × 4단계 = 20 마일스톤 — v1.33 신규 모듈 game/codex.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>아이콘</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>수집 방법</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>요구</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>마일스톤</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>보상 (영구)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>monster</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>몬스터 도감</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>🐲</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>처치/테이밍 자동</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>초보 사냥꾼</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>ATK +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>monster</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>숙련 사냥꾼</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>ATK +5 / DEF +3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>monster</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>베테랑 헌터</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>ATK +10 / DEF +5 / HP +50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>monster</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>전설의 헌터</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>ATK +20 / DEF +10 / HP +150 / 크리 +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>지역 도감</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>🗺️</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>방문 자동 (51개 존)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>여행자</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>SPD +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>탐험가</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>SPD +2 / EXP +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>세계 여행자</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>SPD +3 / EXP +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>지도 정복자</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>SPD +5 / EXP +15% / 드롭 +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>equip</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>장비 도감</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>획득 종류 자동</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>초보 수집가</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>DEF +3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>equip</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>장비 수집가</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>DEF +8 / HP +50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>equip</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>장비 마니아</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>DEF +15 / HP +150 / ATK +5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>equip</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>아머리 마스터</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>DEF +25 / HP +300 / ATK +12 / 크리 +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>어종 도감</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>🐟</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>낚시 자동 (11종, v1.24 연동)</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>초보 낚시꾼</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>GOLD +3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>낚시 애호가</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>GOLD +5% / 드롭 +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>낚시 달인</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>GOLD +10% / 드롭 +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>바다의 친구</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>GOLD +15% / 드롭 +15% / EXP +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>펫 도감</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>🐾</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>보유 종류 자동 (진화형 별도)</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>동물 친구</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>HP +50</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>조련사</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>HP +100 / EXP +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>펫 마스터</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>HP +200 / EXP +10% / ATK +5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>신화의 동반자</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>HP +400 / EXP +15% / ATK +12 / 크리 +3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>도감 시스템</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>자동 기록</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>지역(explore_count) / 어종(낚시 성공) / 기타는 클라이언트 보고</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>중복 방지</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>같은 ID는 1회만 카운트</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>영구 보너스</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>codexBonuses 객체에 누적 저장 (전직/환생 보너스와 별도)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>마일스톤 달성</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>전 서버 알림 + codex_milestone 이벤트 송출</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>game/codex.js (신규 파일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>소켓</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>codex_status / codex_report</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7422,7 +8272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7726,7 +8576,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8589,7 +9439,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9806,7 +10656,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10317,7 +11167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10651,7 +11501,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11047,458 +11897,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>무료 다이아 획득 (13종 — v1.19 마일스톤 5종 신규)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>조건</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>반복</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>보상</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>daily_login</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>매일 접속</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>매일</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>10💎</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>반복</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>first_boss_kill</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>첫 보스 처치</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>일회성</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>50💎</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>level_10</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Lv.10 달성</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>일회성</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>30💎</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>level_20</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Lv.20 달성 (전직)</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>일회성</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>50💎</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>level_30</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Lv.30 달성</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>일회성</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>100💎</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>pvp_10_wins</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>PvP 10승</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>일회성</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>30💎</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>pvp_100_wins</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>PvP 100승</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>일회성</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>100💎</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>weekly_quest</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>주간 퀘스트 완료</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>매주</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>50💎</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>반복</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>level_40</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Lv.40 달성 (각성기 해금)</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>일회성</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>150💎</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>v1.19 신규</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>level_50</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Lv.50 달성 (환생 가능)</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>일회성</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>250💎</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>v1.19 신규</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>first_prestige</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>첫 환생</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>일회성</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>500💎</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>v1.19 신규</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>worldboss_first</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>첫 월드 보스 처치</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>일회성</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>100💎</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>v1.19 신규</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>achievement_50</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>업적 50개 달성</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>일회성</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>200💎</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>v1.19 신규</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>수치 요약</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>일회성 합계 (v1.19 포함)</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>30+50+100+30+100+150+250+500+100+200 + 첫 보스 50 = 1,560💎</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>반복</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>매일 10💎 + 매주 50💎 → 월 약 500💎</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>수익화 균형</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>초반 무료 1500💎 → 28일 출석 + 패치 콘텐츠로 추가 확보 가능</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12799,6 +13197,458 @@
   <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>무료 다이아 획득 (13종 — v1.19 마일스톤 5종 신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>조건</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>반복</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>보상</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>daily_login</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>매일 접속</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>매일</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>10💎</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>반복</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>first_boss_kill</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>첫 보스 처치</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>50💎</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Lv.10 달성</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>30💎</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>level_20</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Lv.20 달성 (전직)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>50💎</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>level_30</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Lv.30 달성</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>100💎</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>pvp_10_wins</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>PvP 10승</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>30💎</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>pvp_100_wins</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>PvP 100승</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>100💎</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>weekly_quest</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>주간 퀘스트 완료</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>매주</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>50💎</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>반복</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>level_40</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Lv.40 달성 (각성기 해금)</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>150💎</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>v1.19 신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>level_50</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Lv.50 달성 (환생 가능)</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>250💎</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>v1.19 신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>first_prestige</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>첫 환생</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>500💎</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>v1.19 신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>worldboss_first</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>첫 월드 보스 처치</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>100💎</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>v1.19 신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>achievement_50</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>업적 50개 달성</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>200💎</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>v1.19 신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>수치 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>일회성 합계 (v1.19 포함)</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>30+50+100+30+100+150+250+500+100+200 + 첫 보스 50 = 1,560💎</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>반복</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>매일 10💎 + 매주 50💎 → 월 약 500💎</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>수익화 균형</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>초반 무료 1500💎 → 28일 출석 + 패치 콘텐츠로 추가 확보 가능</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
@@ -13177,7 +14027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13575,7 +14425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13916,7 +14766,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14246,13 +15096,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14293,7 +15143,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -14308,14 +15158,14 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
+          <t>game/codex.js — 도감 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -14325,19 +15175,19 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>일일 상점</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
+          <t>5개 카테고리 (몬스터/지역/장비/어종/펫) × 4단계 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -14347,19 +15197,19 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>일일 상점</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
+          <t>마일스톤 달성 시 영구 스탯 보너스 + 전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -14369,19 +15219,19 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
+          <t>trackQuest(explore_count) → zone 자동 등록 / fishing_cast → fish 자동 등록</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -14391,19 +15241,19 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
+          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -14413,19 +15263,19 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
+          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -14435,19 +15285,19 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
+          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -14462,7 +15312,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>auction_list / create / bid / my</t>
+          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
         </is>
       </c>
     </row>
@@ -14479,19 +15329,19 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
+          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -14501,19 +15351,19 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
+          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -14523,19 +15373,19 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
+          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -14550,14 +15400,14 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_status / enter / advance / abandon</t>
+          <t>auction_list / create / bid / my</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -14567,19 +15417,19 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
+          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -14594,14 +15444,14 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
+          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -14611,19 +15461,19 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
+          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -14638,14 +15488,14 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>season_status / season_buy_pass / season_claim</t>
+          <t>boss_rush_status / enter / advance / abandon</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -14655,19 +15505,19 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
+          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -14682,14 +15532,14 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
+          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -14699,19 +15549,19 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>event_status 소켓 + /status 엔드포인트 노출</t>
+          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -14721,19 +15571,19 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
+          <t>season_status / season_buy_pass / season_claim</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -14743,19 +15593,19 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
+          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -14770,14 +15620,14 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
+          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -14787,19 +15637,19 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
+          <t>event_status 소켓 + /status 엔드포인트 노출</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -14809,19 +15659,19 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
+          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -14831,19 +15681,19 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
+          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -14858,14 +15708,14 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
+          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -14875,19 +15725,19 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
+          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -14897,19 +15747,19 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
+          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -14919,19 +15769,19 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
+          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -14941,19 +15791,19 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
+          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -14963,19 +15813,19 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>경매장 시트 신규 추가</t>
+          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -14985,19 +15835,19 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
+          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -15007,19 +15857,19 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
+          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -15029,19 +15879,19 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>낚시 시트 신규 추가</t>
+          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -15051,19 +15901,19 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
+          <t>경매장 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -15073,19 +15923,19 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
+          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -15095,19 +15945,19 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>보스 러시 시트 신규 추가</t>
+          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -15117,19 +15967,19 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
+          <t>낚시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -15139,19 +15989,19 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
+          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -15161,19 +16011,19 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛 시트 신규 추가</t>
+          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -15183,19 +16033,19 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
+          <t>보스 러시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -15205,19 +16055,19 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>모듈화</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
+          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -15227,19 +16077,19 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트 시트 신규 추가</t>
+          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -15249,19 +16099,19 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
+          <t>행운의 룰렛 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -15271,19 +16121,19 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
+          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -15293,19 +16143,19 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>모듈화</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스 시트 신규 추가</t>
+          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -15315,19 +16165,19 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
+          <t>축제 이벤트 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -15337,19 +16187,19 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아 시트 신규 추가</t>
+          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -15359,19 +16209,19 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
+          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -15386,14 +16236,14 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>상점 시트 갱신</t>
+          <t>시즌 패스 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -15403,19 +16253,19 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
+          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -15425,19 +16275,19 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>최대 인원 50→100명 (Lv.10 기준)</t>
+          <t>무료 다이아 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -15447,19 +16297,19 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>길드(혈맹) 시트 신규 추가</t>
+          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -15469,19 +16319,19 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
+          <t>상점 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -15491,19 +16341,19 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>대사 시스템</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
+          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -15513,19 +16363,19 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>NPC 시트 신규 추가 (11종)</t>
+          <t>최대 인원 50→100명 (Lv.10 기준)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -15535,19 +16385,19 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>각성기</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
+          <t>길드(혈맹) 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -15557,19 +16407,19 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
+          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -15579,19 +16429,19 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>대사 시스템</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
+          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -15606,14 +16456,14 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
+          <t>NPC 시트 신규 추가 (11종)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -15623,19 +16473,19 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>각성기</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
+          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -15645,19 +16495,19 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>교역</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
+          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -15667,19 +16517,19 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
+          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -15689,19 +16539,19 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
+          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -15711,19 +16561,19 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>연금술 시트 신규 추가</t>
+          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -15733,19 +16583,19 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>교역</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
+          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -15755,19 +16605,19 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (이동 +85%, 비행)</t>
+          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -15777,19 +16627,19 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
+          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -15804,14 +16654,14 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
+          <t>연금술 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -15821,19 +16671,19 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
+          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -15843,107 +16693,107 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
+          <t>페가수스 (이동 +85%, 비행)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
+          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
+          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
+          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
+          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -15953,19 +16803,19 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>상태이상</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
+          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -15975,19 +16825,19 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -15997,19 +16847,19 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -16019,12 +16869,12 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>컨텐츠</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
         </is>
       </c>
     </row>
@@ -16041,32 +16891,120 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>상태이상</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>컨텐츠</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
           <t>v1.6 이전</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C84" s="7" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>기반</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>마을/사냥/PvP/카르마/펫/탈것/제작/교역/길드/공성/투기장 등</t>
         </is>
@@ -16080,13 +17018,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -16133,7 +17071,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -16143,179 +17081,179 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>game/dailyshop.js</t>
+          <t>game/codex.js</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>일일 상점 모듈 생성 + 즉시 통합</t>
+          <t>도감 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
+          <t>5카테고리 × 4마일스톤</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>결정적 랜덤</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>날짜 시드</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>모든 플레이어 동일 상품</t>
+          <t>explore_count → zone 자동 등록</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>seededRandom + Fisher-Yates</t>
+          <t>별도 학습 불필요</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>개인 갱신</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>30💎</t>
+          <t>fishing_cast 훅</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>개인 시드 생성</t>
+          <t>어종 자동 등록</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>구매 기록 초기화</t>
+          <t>v1.24와 자연 연동</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>auction → server.js</t>
+          <t>영구 스탯 보너스</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>6번째 (마지막) 모듈 통합</t>
+          <t>마일스톤 달성 시 누적</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>자동 정산 + 환불 + 양방향 지급</t>
+          <t>codexBonuses 객체</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>tickAuctions</t>
+          <t>game/dailyshop.js</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>10초마다 만료 정산</t>
+          <t>일일 상점 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>setInterval 통합</t>
+          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>결정적 랜덤</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>auction_create</t>
+          <t>날짜 시드</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>경매 등록 (등록 수수료 자동 차감)</t>
+          <t>모든 플레이어 동일 상품</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>3가지 기간</t>
+          <t>seededRandom + Fisher-Yates</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>개인 갱신</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>auction_bid</t>
+          <t>30💎</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>입찰 + 이전 입찰자 자동 환불</t>
+          <t>개인 시드 생성</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>스나이핑 방지 연장</t>
+          <t>구매 기록 초기화</t>
         </is>
       </c>
     </row>
@@ -16327,22 +17265,22 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>auction_my</t>
+          <t>auction → server.js</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>내 등록/입찰 내역 조회</t>
+          <t>6번째 (마지막) 모듈 통합</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>자동 정산 + 환불 + 양방향 지급</t>
         </is>
       </c>
     </row>
@@ -16354,130 +17292,130 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>신규 모듈 6/6</t>
+          <t>tickAuctions</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>100% 통합 완료</t>
+          <t>10초마다 만료 정산</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>lottery/fishing/event/season/boss_rush/auction</t>
+          <t>setInterval 통합</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>boss_rush → server.js</t>
+          <t>auction_create</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>5번째 모듈 통합</t>
+          <t>경매 등록 (등록 수수료 자동 차감)</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>메모리 세션 기반</t>
+          <t>3가지 기간</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>bossRushSessions</t>
+          <t>auction_bid</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>진행 중 세션 저장</t>
+          <t>입찰 + 이전 입찰자 자동 환불</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>currentWave/시간 추적</t>
+          <t>스나이핑 방지 연장</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>bossRushRanking</t>
+          <t>auction_my</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>글로벌 랭킹 TOP 100</t>
+          <t>내 등록/입찰 내역 조회</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>웨이브 → 시간 정렬</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>boss_rush_enter</t>
+          <t>신규 모듈 6/6</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>무료/유료/다이아 입장</t>
+          <t>100% 통합 완료</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>동시 1개 세션 제한</t>
+          <t>lottery/fishing/event/season/boss_rush/auction</t>
         </is>
       </c>
     </row>
@@ -16489,22 +17427,22 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_advance</t>
+          <t>boss_rush → server.js</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>웨이브 클리어 보고</t>
+          <t>5번째 모듈 통합</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>시간 초과 검증</t>
+          <t>메모리 세션 기반</t>
         </is>
       </c>
     </row>
@@ -16516,83 +17454,83 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>풀클리어 보상</t>
+          <t>bossRushSessions</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 누적</t>
+          <t>진행 중 세션 저장</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>currentWave/시간 추적</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>season → server.js</t>
+          <t>bossRushRanking</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>4번째 모듈 통합</t>
+          <t>글로벌 랭킹 TOP 100</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>XP 자동 적립 + 보상 수령</t>
+          <t>웨이브 → 시간 정렬</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>boss_rush_enter</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
+          <t>무료/유료/다이아 입장</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>SEASON_XP_MAP 매핑</t>
+          <t>동시 1개 세션 제한</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -16602,39 +17540,39 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>season_status</t>
+          <t>boss_rush_advance</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>XP/티어/구매여부/수령내역 조회</t>
+          <t>웨이브 클리어 보고</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>15티어 전체</t>
+          <t>시간 초과 검증</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>season_buy_pass</t>
+          <t>풀클리어 보상</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 패스 구매 (1500💎)</t>
+          <t>20웨이브 누적</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -16651,56 +17589,56 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>season_claim</t>
+          <t>season → server.js</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>티어 보상 수령 (free/premium)</t>
+          <t>4번째 모듈 통합</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>자동 인벤토리 적용</t>
+          <t>XP 자동 적립 + 보상 수령</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>event → server.js</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>3번째 모듈 통합</t>
+          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>축제 시스템 활성화</t>
+          <t>SEASON_XP_MAP 매핑</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -16710,78 +17648,78 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>event_status</t>
+          <t>season_status</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>현재 활성 축제 조회</t>
+          <t>XP/티어/구매여부/수령내역 조회</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>이름/기간/버프/한정 보상</t>
+          <t>15티어 전체</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>/status JSON</t>
+          <t>season_buy_pass</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>festival 필드 추가</t>
+          <t>프리미엄 패스 구매 (1500💎)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>대시보드 확인용</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>축제 인사</t>
+          <t>season_claim</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>30% 확률로 NPC가 축제 대사 출력</t>
+          <t>티어 보상 수령 (free/premium)</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>spring_blossom 등 5종</t>
+          <t>자동 인벤토리 적용</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -16791,24 +17729,24 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>fishing → server.js</t>
+          <t>event → server.js</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>3번째 모듈 통합</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>두 번째 모듈 통합</t>
+          <t>축제 시스템 활성화</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -16818,78 +17756,78 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>fishing_status</t>
+          <t>event_status</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>지역/낚싯대/미끼/시간대 조회</t>
+          <t>현재 활성 축제 조회</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>이름/기간/버프/한정 보상</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>fishing_cast</t>
+          <t>/status JSON</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
+          <t>festival 필드 추가</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>전설/신화 → 서버 알림</t>
+          <t>대시보드 확인용</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>fishing_buy_rod</t>
+          <t>축제 인사</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>낚싯대 구매 (골드/다이아)</t>
+          <t>30% 확률로 NPC가 축제 대사 출력</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>5등급 모두</t>
+          <t>spring_blossom 등 5종</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -16899,7 +17837,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>lottery → server.js</t>
+          <t>fishing → server.js</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -16909,29 +17847,29 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>첫 모듈 통합 마일스톤</t>
+          <t>두 번째 모듈 통합</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>lottery_status</t>
+          <t>fishing_status</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>상태/가격/상품 풀 조회</t>
+          <t>지역/낚싯대/미끼/시간대 조회</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -16943,432 +17881,432 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>lottery_free_spin</t>
+          <t>fishing_cast</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 스핀</t>
+          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>자정 초기화</t>
+          <t>전설/신화 → 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>lottery_paid_spin</t>
+          <t>fishing_buy_rod</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>유료 1회 / 10연속</t>
+          <t>낚싯대 구매 (골드/다이아)</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>count: 1 또는 10</t>
+          <t>5등급 모두</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js 신규</t>
+          <t>lottery → server.js</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>등록 2% + 낙찰 5%</t>
+          <t>첫 모듈 통합 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>활성 한도</t>
+          <t>lottery_status</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>플레이어당 10개</t>
+          <t>상태/가격/상품 풀 조회</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>자기 입찰 금지</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>game/fishing.js 신규</t>
+          <t>lottery_free_spin</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
+          <t>매일 무료 1회 스핀</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 = 20000G + 칭호</t>
+          <t>자정 초기화</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>전설의 비단잉어</t>
+          <t>lottery_paid_spin</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>드래곤 낚싯대 + 가중치 1</t>
+          <t>유료 1회 / 10연속</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>5000G + 평생 행운 +5%</t>
+          <t>count: 1 또는 10</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>game/boss_rush.js 신규</t>
+          <t>game/auction.js 신규</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 / HP ×1.35 스케일링</t>
+          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>최종 보상: 200💎 + 용재료 ×5</t>
+          <t>등록 2% + 낙찰 5%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>입장</t>
+          <t>활성 한도</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 / 1000G / 30💎</t>
+          <t>플레이어당 10개</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>랭킹 시스템</t>
+          <t>자기 입찰 금지</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>챔피언 보상</t>
+          <t>game/fishing.js 신규</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
+          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>신화 크라켄 = 20000G + 칭호</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js 신규</t>
+          <t>전설의 비단잉어</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 / 가중치 1000</t>
+          <t>드래곤 낚싯대 + 가중치 1</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 + 유료</t>
+          <t>5000G + 평생 행운 +5%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>영웅 장비 상자</t>
+          <t>game/boss_rush.js 신규</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>확률 0.2% (가장 희귀)</t>
+          <t>20웨이브 / HP ×1.35 스케일링</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>전설 보상</t>
+          <t>최종 보상: 200💎 + 용재료 ×5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>200 다이아</t>
+          <t>입장</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>확률 0.8%</t>
+          <t>매일 무료 3회 / 1000G / 30💎</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>랭킹 시스템</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>신년 축제</t>
+          <t>챔피언 보상</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>1/1 ~ 1/7</t>
+          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>골드 +50% / EXP +30%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>봄꽃 축제</t>
+          <t>game/lottery.js 신규</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>4/1 ~ 4/14</t>
+          <t>10종 보상 / 가중치 1000</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>HP재생 +30% / 드롭 +20%</t>
+          <t>매일 무료 1회 + 유료</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>한여름 밤의 축제</t>
+          <t>영웅 장비 상자</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>7/15 ~ 8/15</t>
+          <t>확률 0.2% (가장 희귀)</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>화염 +30% / PvP 보상 +50%</t>
+          <t>전설 보상</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>할로윈 축제</t>
+          <t>200 다이아</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>10/25 ~ 11/1</t>
+          <t>확률 0.8%</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>크리 +10% / 언데드 +50%</t>
+          <t>잭팟</t>
         </is>
       </c>
     </row>
@@ -17385,206 +18323,206 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>겨울 축제</t>
+          <t>신년 축제</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>12/20 ~ 12/31</t>
+          <t>1/1 ~ 1/7</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
+          <t>골드 +50% / EXP +30%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>game/season.js 신규</t>
+          <t>봄꽃 축제</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>15티어 / 30일 / 무료+프리미엄</t>
+          <t>4/1 ~ 4/14</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
+          <t>HP재생 +30% / 드롭 +20%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>XP 획득 7종</t>
+          <t>한여름 밤의 축제</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>퀘/보스/PvP/월드보스/던전/제작</t>
+          <t>7/15 ~ 8/15</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>일일 +200 ~ 월드보스 +500</t>
+          <t>화염 +30% / PvP 보상 +50%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 가격</t>
+          <t>할로윈 축제</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>1500 다이아</t>
+          <t>10/25 ~ 11/1</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>시즌 당 1회</t>
+          <t>크리 +10% / 언데드 +50%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Lv.40 달성</t>
+          <t>겨울 축제</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>각성기 해금 마일스톤</t>
+          <t>12/20 ~ 12/31</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>150💎</t>
+          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Lv.50 달성</t>
+          <t>game/season.js 신규</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>환생 가능 마일스톤</t>
+          <t>15티어 / 30일 / 무료+프리미엄</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>250💎</t>
+          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>첫 환생</t>
+          <t>XP 획득 7종</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>prestige 1차</t>
+          <t>퀘/보스/PvP/월드보스/던전/제작</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>500💎</t>
+          <t>일일 +200 ~ 월드보스 +500</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>첫 월드 보스</t>
+          <t>프리미엄 가격</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 처치 보너스</t>
+          <t>1500 다이아</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>100💎</t>
+          <t>시즌 당 1회</t>
         </is>
       </c>
     </row>
@@ -17601,125 +18539,125 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>업적 50개</t>
+          <t>Lv.40 달성</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>업적 마일스톤</t>
+          <t>각성기 해금 마일스톤</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>200💎</t>
+          <t>150💎</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>불사조 스킨</t>
+          <t>Lv.50 달성</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>환생 가능 마일스톤</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>불사조 깃털 이펙트 (영구)</t>
+          <t>250💎</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>폭풍 스킨</t>
+          <t>첫 환생</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>prestige 1차</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>번개 오라 이펙트 (영구)</t>
+          <t>500💎</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>상점 (편의)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 자동물약</t>
+          <t>첫 월드 보스</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>500 다이아</t>
+          <t>월드 보스 처치 보너스</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>24시간 자동물약 무한</t>
+          <t>100💎</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>상점 (상자)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 보물 상자</t>
+          <t>업적 50개</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>300 다이아</t>
+          <t>업적 마일스톤</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>전설 장비 확정 + 다이아</t>
+          <t>200💎</t>
         </is>
       </c>
     </row>
@@ -17731,130 +18669,130 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>상점 (재료)</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>전설 재료 패키지</t>
+          <t>불사조 스킨</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>600 다이아</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
+          <t>불사조 깃털 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 분노</t>
+          <t>폭풍 스킨</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>크리티컬 +5%</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>60명 정원</t>
+          <t>번개 오라 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.7</t>
+          <t>상점 (편의)</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 신속</t>
+          <t>프리미엄 자동물약</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>이동속도 +10%</t>
+          <t>500 다이아</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>70명 정원</t>
+          <t>24시간 자동물약 무한</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.8</t>
+          <t>상점 (상자)</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 회복</t>
+          <t>프리미엄 보물 상자</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>HP 재생 +50%</t>
+          <t>300 다이아</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>80명 정원</t>
+          <t>전설 장비 확정 + 다이아</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.9</t>
+          <t>상점 (재료)</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 운명</t>
+          <t>전설 재료 패키지</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>회피 +5%</t>
+          <t>600 다이아</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>90명 정원</t>
+          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
         </is>
       </c>
     </row>
@@ -17866,211 +18804,211 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.10</t>
+          <t>혈맹 Lv.6</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 전설</t>
+          <t>혈맹의 분노</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>전 스탯 +5%</t>
+          <t>크리티컬 +5%</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>100명 정원 — 최종</t>
+          <t>60명 정원</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.7</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>점쟁이</t>
+          <t>혈맹의 신속</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
+          <t>이동속도 +10%</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>70명 정원</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.8</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>감정사</t>
+          <t>혈맹의 회복</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
+          <t>HP 재생 +50%</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>80명 정원</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.9</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>수집가</t>
+          <t>혈맹의 운명</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
+          <t>회피 +5%</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>90명 정원</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>각성기 (어쌔신)</t>
+          <t>혈맹 Lv.10</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>천 개의 칼날</t>
+          <t>혈맹의 전설</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
+          <t>전 스탯 +5%</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>100명 정원 — 최종</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>각성기 (워리어)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>대지 가르기</t>
+          <t>점쟁이</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
+          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>각성기 (나이트)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>불멸의 수호자</t>
+          <t>감정사</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>피해 90% 감소 / 도발 / 10초</t>
+          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>각성기 (메이지)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>시간 정지</t>
+          <t>수집가</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
+          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
@@ -18082,17 +19020,17 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>각성기 (클레릭)</t>
+          <t>각성기 (어쌔신)</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>신의 은총</t>
+          <t>천 개의 칼날</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>HP 100% 회복 / 전스탯 +50%</t>
+          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
@@ -18104,108 +19042,108 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (워리어)</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>폭풍 정복자</t>
+          <t>대지 가르기</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인 처치</t>
+          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>10,000G + 150다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (나이트)</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>연금술사</t>
+          <t>불멸의 수호자</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>엘릭서 10회 제작</t>
+          <t>피해 90% 감소 / 도발 / 10초</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>5,000G + 80다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (메이지)</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>그림자 정복자</t>
+          <t>시간 정지</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 클리어</t>
+          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>8,000G + 120다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (클레릭)</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>전설의 동반자</t>
+          <t>신의 은총</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>전설급 펫 진화</t>
+          <t>HP 100% 회복 / 전스탯 +50%</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>6,000G + 100다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
@@ -18222,206 +19160,206 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>이국의 상인</t>
+          <t>폭풍 정복자</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>사치품 교역 5회</t>
+          <t>폭풍의 거인 처치</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>4,000G + 60다이아</t>
+          <t>10,000G + 150다이아</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인</t>
+          <t>연금술사</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>HP 100,000 / ATK 140 / DEF 90</t>
+          <t>엘릭서 10회 제작</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>EXP 10000 + 6000G</t>
+          <t>5,000G + 80다이아</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>시간의 수호자</t>
+          <t>그림자 정복자</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>HP 70,000 / ATK 170 / DEF 60</t>
+          <t>그림자 미궁 클리어</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>EXP 9000 + 7000G</t>
+          <t>8,000G + 120다이아</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>교역품</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
+          <t>전설의 동반자</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종</t>
+          <t>전설급 펫 진화</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>기본가 600~900G</t>
+          <t>6,000G + 100다이아</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>타이탄의 엘릭서</t>
+          <t>이국의 상인</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>용재료×3 + 마법재료×10</t>
+          <t>사치품 교역 5회</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>ATK ×1.5 / 30분</t>
+          <t>4,000G + 60다이아</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>강철 엘릭서</t>
+          <t>폭풍의 거인</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>철광석×30 + 마법재료×10</t>
+          <t>HP 100,000 / ATK 140 / DEF 90</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>DEF ×1.5 / 30분</t>
+          <t>EXP 10000 + 6000G</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>질풍 엘릭서</t>
+          <t>시간의 수호자</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>약초×20 + 마법재료×8</t>
+          <t>HP 70,000 / ATK 170 / DEF 60</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>SPD ×1.4 / 20분</t>
+          <t>EXP 9000 + 7000G</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>교역품</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>지혜 엘릭서</t>
+          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>마법수정×5 + 영혼재료×5</t>
+          <t>이국의 사치품 3종</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>EXP ×2.5 / 15분</t>
+          <t>기본가 600~900G</t>
         </is>
       </c>
     </row>
@@ -18438,260 +19376,260 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>행운 엘릭서</t>
+          <t>타이탄의 엘릭서</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>보석×10 + 마법재료×5</t>
+          <t>용재료×3 + 마법재료×10</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>GOLD ×2.0 / 15분</t>
+          <t>ATK ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>불사조 (pet_phoenix)</t>
+          <t>강철 엘릭서</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>불꽃산 보스 50처치</t>
+          <t>철광석×30 + 마법재료×10</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>화염 DMG +20% (진화 +40%)</t>
+          <t>DEF ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>유니콘 (pet_unicorn)</t>
+          <t>질풍 엘릭서</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>다이아 800개</t>
+          <t>약초×20 + 마법재료×8</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>회피 +10% (진화 +20%)</t>
+          <t>SPD ×1.4 / 20분</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (mount_pegasus)</t>
+          <t>지혜 엘릭서</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>다이아 1200개</t>
+          <t>마법수정×5 + 영혼재료×5</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>이동속도 +85% / 비행</t>
+          <t>EXP ×2.5 / 15분</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁</t>
+          <t>행운 엘릭서</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Lv.38 / 8인 파티 / 7스테이지</t>
+          <t>보석×10 + 마법재료×5</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>22000G + 32000EXP</t>
+          <t>GOLD ×2.0 / 15분</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>드롭</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>드래곤 검/망토/투구/장갑</t>
+          <t>불사조 (pet_phoenix)</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 보스 드롭</t>
+          <t>불꽃산 보스 50처치</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>전설급</t>
+          <t>화염 DMG +20% (진화 +40%)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자</t>
+          <t>유니콘 (pet_unicorn)</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>몬스터 10,000 처치</t>
+          <t>다이아 800개</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>ATK +7%</t>
+          <t>회피 +10% (진화 +20%)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>불멸자</t>
+          <t>페가수스 (mount_pegasus)</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>환생 5회</t>
+          <t>다이아 1200개</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>EXP +25%</t>
+          <t>이동속도 +85% / 비행</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>천공의 군주</t>
+          <t>그림자 미궁</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 10회 처치</t>
+          <t>Lv.38 / 8인 파티 / 7스테이지</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>보스DMG +15%</t>
+          <t>22000G + 32000EXP</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>드롭</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>지역 시트 갱신</t>
+          <t>드래곤 검/망토/투구/장갑</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>25→51개 지역 반영</t>
+          <t>그림자 미궁 보스 드롭</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>전설급</t>
         </is>
       </c>
     </row>
@@ -18703,22 +19641,22 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>칭호 시트 갱신</t>
+          <t>공허의 방랑자</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>7→16종 + 효과/색상 추가</t>
+          <t>몬스터 10,000 처치</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ATK +7%</t>
         </is>
       </c>
     </row>
@@ -18730,22 +19668,22 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>출석 캘린더 시트</t>
+          <t>불멸자</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (28일 사이클)</t>
+          <t>환생 5회</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EXP +25%</t>
         </is>
       </c>
     </row>
@@ -18757,22 +19695,22 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>장비 세트 시트</t>
+          <t>천공의 군주</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (드래곤/영웅/태초)</t>
+          <t>월드 보스 10회 처치</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>보스DMG +15%</t>
         </is>
       </c>
     </row>
@@ -18789,12 +19727,12 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>장비 등급 시트</t>
+          <t>지역 시트 갱신</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+          <t>25→51개 지역 반영</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
@@ -18816,12 +19754,12 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>디버프 시트</t>
+          <t>칭호 시트 갱신</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+          <t>7→16종 + 효과/색상 추가</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -18843,12 +19781,12 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>패치 노트 시트</t>
+          <t>출석 캘린더 시트</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (히스토리)</t>
+          <t>신규 추가 (28일 사이클)</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
@@ -18860,25 +19798,133 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>장비 세트 시트</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (드래곤/영웅/태초)</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>장비 등급 시트</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>디버프 시트</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>패치 노트 시트</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (히스토리)</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
           <t>v1.10</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>기획서</t>
         </is>
       </c>
-      <c r="C105" s="8" t="inlineStr">
+      <c r="C109" s="8" t="inlineStr">
         <is>
           <t>던전 시트</t>
         </is>
       </c>
-      <c r="D105" s="8" t="inlineStr">
+      <c r="D109" s="8" t="inlineStr">
         <is>
           <t>신규 추가 (7종 던전)</t>
         </is>
       </c>
-      <c r="E105" s="8" t="inlineStr">
+      <c r="E109" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -28,21 +28,22 @@
     <sheet name="장비 등급" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="디버프 v1.7+" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="던전" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="도감" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="일일 상점" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="경매장" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="낚시" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="보스 러시" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="행운의 룰렛" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="축제 이벤트" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="시즌 패스" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="무료 다이아" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="길드 (혈맹)" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="NPC" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="월드 보스" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="연금술" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="패치 노트" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="v1.9 ~ v1.33" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="우편함" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="도감" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="일일 상점" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="경매장" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="낚시" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="보스 러시" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="행운의 룰렛" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="축제 이벤트" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="시즌 패스" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="무료 다이아" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="길드 (혈맹)" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="NPC" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="월드 보스" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="연금술" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="패치 노트" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="v1.9 ~ v1.34" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6863,6 +6864,278 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>우편함 시스템 (v1.34 신규 모듈 game/mail.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>종류</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>용도</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>조건</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>만료</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>시스템 메일</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>이벤트 보상/공지/GM 메시지</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>시스템 자동 발송</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>14일</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>선물 메일</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>플레이어 → 플레이어</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>로그인 중인 수신자</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>7일</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>일반 메일</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>범용</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>30일 (기본)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>첨부 가능 항목</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>검증</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>특수</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>발신자 골드 검증</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>선물 발송 시 2% 수수료</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>diamonds</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>발신자 다이아 검증</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>items</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>발신자 인벤토리 검증</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>itemId → count 매핑</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>제한 / 룰</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>우편함 최대</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>100통 (가득 시 수신 거부)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>일일 선물 한도</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>플레이어당 10회 / 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>선물 수수료</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>골드 첨부의 2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>첨부 미수령 삭제</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>거부 (수령 후에만 삭제 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>만료 처리</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>조회 시 자동 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>기존 시스템</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>인라인 pendingMails 보완 (정식 모듈)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7706,7 +7979,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8272,7 +8545,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8576,7 +8849,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9439,7 +9712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10656,7 +10929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11167,7 +11440,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11496,407 +11769,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>시즌 패스 (15티어 — v1.20 신규 모듈)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>티어</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>필요 XP</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>무료 트랙</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>프리미엄 트랙</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>500G</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>50💎</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>마법재료 ×5</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>용재료 ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>1000G</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>시즌 글로우 스킨</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>800</v>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>EXP 부스터 ×1</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>메가 EXP ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>2000G + 30💎</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>희귀 상자 ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>1700</v>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>영혼석 ×5</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>영혼석 ×15</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>2300</v>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>황금 수프 ×3</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>왕의 연회 ×3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>3000G</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>100💎</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>3800</v>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>용재료 ×1</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>용재료 ×5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>4700</v>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>5000G + 50💎</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>영웅의 갑옷</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>5700</v>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>보호 주문서 ×1</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>보호 주문서 ×3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>6800</v>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>마법재료 ×10</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>타이탄 엘릭서 ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>8000G</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>영웅의 검</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>9300</v>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>80💎</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>200💎</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>10700</v>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>15000G + 100💎</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>태초의 반지 + 시즌 전설 칭호</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>시즌 패스 시스템</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>시즌 기간</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>30일 사이클</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>프리미엄 가격</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>1500 다이아 (시즌당)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>XP 획득</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>일일퀘 +200 / 주간퀘 +800 / 보스 +50 / PvP승 +30 / 월드보스 +500 / 던전 +150 / 제작 +20</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>총 필요 XP</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>10,700 (15티어 만렙)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>보상 트랙</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>무료 (모두 획득) + 프리미엄 (구매자 전용)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>모듈</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>game/season.js (신규 파일, 데이터 + 헬퍼 함수)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13194,6 +13066,407 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>시즌 패스 (15티어 — v1.20 신규 모듈)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>티어</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>필요 XP</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>무료 트랙</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>프리미엄 트랙</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>500G</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>50💎</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>마법재료 ×5</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>용재료 ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>1000G</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>시즌 글로우 스킨</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>EXP 부스터 ×1</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>메가 EXP ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>2000G + 30💎</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>희귀 상자 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>1700</v>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>영혼석 ×5</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>영혼석 ×15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>2300</v>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>황금 수프 ×3</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>왕의 연회 ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>3000G</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>100💎</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>3800</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>용재료 ×1</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>용재료 ×5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>5000G + 50💎</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>영웅의 갑옷</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>5700</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>보호 주문서 ×1</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>보호 주문서 ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>6800</v>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>마법재료 ×10</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>타이탄 엘릭서 ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>8000G</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>영웅의 검</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>9300</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>80💎</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>200💎</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>10700</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>15000G + 100💎</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>태초의 반지 + 시즌 전설 칭호</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>시즌 패스 시스템</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>시즌 기간</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>30일 사이클</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>프리미엄 가격</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>1500 다이아 (시즌당)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>XP 획득</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>일일퀘 +200 / 주간퀘 +800 / 보스 +50 / PvP승 +30 / 월드보스 +500 / 던전 +150 / 제작 +20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>총 필요 XP</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>10,700 (15티어 만렙)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>보상 트랙</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>무료 (모두 획득) + 프리미엄 (구매자 전용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>game/season.js (신규 파일, 데이터 + 헬퍼 함수)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13640,7 +13913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14027,7 +14300,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14425,7 +14698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14766,7 +15039,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15096,13 +15369,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15143,7 +15416,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -15158,14 +15431,14 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>game/codex.js — 도감 시스템 (생성 + 통합 동시)</t>
+          <t>game/mail.js — 정식 우편함 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -15175,19 +15448,19 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>우편함</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>5개 카테고리 (몬스터/지역/장비/어종/펫) × 4단계 마일스톤</t>
+          <t>시스템/선물 메일 + 첨부(골드/다이아/아이템) + 만료/수령 관리</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -15197,19 +15470,19 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>선물</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 달성 시 영구 스탯 보너스 + 전 서버 알림</t>
+          <t>일일 10회 / 골드 첨부 수수료 2% / 7일 만료</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -15219,19 +15492,19 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>trackQuest(explore_count) → zone 자동 등록 / fishing_cast → fish 자동 등록</t>
+          <t>mail_inbox/read/claim/delete/send_gift</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -15246,14 +15519,14 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
+          <t>game/codex.js — 도감 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -15263,19 +15536,19 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>일일 상점</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
+          <t>5개 카테고리 (몬스터/지역/장비/어종/펫) × 4단계 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -15285,19 +15558,19 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>일일 상점</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
+          <t>마일스톤 달성 시 영구 스탯 보너스 + 전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -15307,19 +15580,19 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
+          <t>trackQuest(explore_count) → zone 자동 등록 / fishing_cast → fish 자동 등록</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -15329,19 +15602,19 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
+          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -15351,19 +15624,19 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
+          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -15373,19 +15646,19 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
+          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -15400,7 +15673,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>auction_list / create / bid / my</t>
+          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
         </is>
       </c>
     </row>
@@ -15417,19 +15690,19 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
+          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -15439,19 +15712,19 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
+          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -15461,19 +15734,19 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
+          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -15488,14 +15761,14 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_status / enter / advance / abandon</t>
+          <t>auction_list / create / bid / my</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -15505,19 +15778,19 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
+          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -15532,14 +15805,14 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
+          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -15549,19 +15822,19 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
+          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -15576,14 +15849,14 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>season_status / season_buy_pass / season_claim</t>
+          <t>boss_rush_status / enter / advance / abandon</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -15593,19 +15866,19 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
+          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -15620,14 +15893,14 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
+          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -15637,19 +15910,19 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>event_status 소켓 + /status 엔드포인트 노출</t>
+          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -15659,19 +15932,19 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
+          <t>season_status / season_buy_pass / season_claim</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -15681,19 +15954,19 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
+          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -15708,14 +15981,14 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
+          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -15725,19 +15998,19 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
+          <t>event_status 소켓 + /status 엔드포인트 노출</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -15747,19 +16020,19 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
+          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -15769,19 +16042,19 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
+          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -15796,14 +16069,14 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
+          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -15813,19 +16086,19 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
+          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -15835,19 +16108,19 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
+          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -15857,19 +16130,19 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
+          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -15879,19 +16152,19 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
+          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -15901,19 +16174,19 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>경매장 시트 신규 추가</t>
+          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -15923,19 +16196,19 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
+          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -15945,19 +16218,19 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
+          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -15967,19 +16240,19 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>낚시 시트 신규 추가</t>
+          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -15989,19 +16262,19 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
+          <t>경매장 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -16011,19 +16284,19 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
+          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -16033,19 +16306,19 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>보스 러시 시트 신규 추가</t>
+          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -16055,19 +16328,19 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
+          <t>낚시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -16077,19 +16350,19 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
+          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -16099,19 +16372,19 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛 시트 신규 추가</t>
+          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -16121,19 +16394,19 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
+          <t>보스 러시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -16143,19 +16416,19 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>모듈화</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
+          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -16165,19 +16438,19 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트 시트 신규 추가</t>
+          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -16187,19 +16460,19 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
+          <t>행운의 룰렛 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -16209,19 +16482,19 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
+          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -16231,19 +16504,19 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>모듈화</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스 시트 신규 추가</t>
+          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -16253,19 +16526,19 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
+          <t>축제 이벤트 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -16275,19 +16548,19 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아 시트 신규 추가</t>
+          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -16297,19 +16570,19 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
+          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -16324,14 +16597,14 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>상점 시트 갱신</t>
+          <t>시즌 패스 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -16341,19 +16614,19 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
+          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -16363,19 +16636,19 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>최대 인원 50→100명 (Lv.10 기준)</t>
+          <t>무료 다이아 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -16385,19 +16658,19 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>길드(혈맹) 시트 신규 추가</t>
+          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -16407,19 +16680,19 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
+          <t>상점 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -16429,19 +16702,19 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>대사 시스템</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
+          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -16451,19 +16724,19 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>NPC 시트 신규 추가 (11종)</t>
+          <t>최대 인원 50→100명 (Lv.10 기준)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -16473,19 +16746,19 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>각성기</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
+          <t>길드(혈맹) 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -16495,19 +16768,19 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
+          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -16517,19 +16790,19 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>대사 시스템</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
+          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -16544,14 +16817,14 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
+          <t>NPC 시트 신규 추가 (11종)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -16561,19 +16834,19 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>각성기</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
+          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -16583,19 +16856,19 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>교역</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
+          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -16605,19 +16878,19 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
+          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -16627,19 +16900,19 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
+          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -16649,19 +16922,19 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>연금술 시트 신규 추가</t>
+          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -16671,19 +16944,19 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>교역</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
+          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -16693,19 +16966,19 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (이동 +85%, 비행)</t>
+          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -16715,19 +16988,19 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
+          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -16742,14 +17015,14 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
+          <t>연금술 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -16759,19 +17032,19 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
+          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -16781,107 +17054,107 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
+          <t>페가수스 (이동 +85%, 비행)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
+          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
+          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
+          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
+          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
@@ -16891,19 +17164,19 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>상태이상</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
+          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -16913,19 +17186,19 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
@@ -16935,19 +17208,19 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -16957,12 +17230,12 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>컨텐츠</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
         </is>
       </c>
     </row>
@@ -16979,32 +17252,120 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>상태이상</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>컨텐츠</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
           <t>v1.6 이전</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>기반</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>마을/사냥/PvP/카르마/펫/탈것/제작/교역/길드/공성/투기장 등</t>
         </is>
@@ -17018,13 +17379,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17071,7 +17432,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -17081,105 +17442,105 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>game/codex.js</t>
+          <t>game/mail.js</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>도감 모듈 생성 + 즉시 통합</t>
+          <t>우편함 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>5카테고리 × 4마일스톤</t>
+          <t>시스템/선물 + 첨부 + 만료</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>시스템 메일</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>explore_count → zone 자동 등록</t>
+          <t>이벤트 보상/공지</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>별도 학습 불필요</t>
+          <t>14일 만료</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>fishing_cast 훅</t>
+          <t>선물 메일</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>어종 자동 등록</t>
+          <t>플레이어 간 / 일일 10회</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>v1.24와 자연 연동</t>
+          <t>7일 만료, 수수료 2%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>영구 스탯 보너스</t>
+          <t>발송 시 자원 차감</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>마일스톤 달성 시 누적</t>
+          <t>수신자 우편함 가득 → 거부</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>codexBonuses 객체</t>
+          <t>첨부 미수령 메일 삭제 거부</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -17189,179 +17550,179 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>game/dailyshop.js</t>
+          <t>game/codex.js</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>일일 상점 모듈 생성 + 즉시 통합</t>
+          <t>도감 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
+          <t>5카테고리 × 4마일스톤</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>결정적 랜덤</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>날짜 시드</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>모든 플레이어 동일 상품</t>
+          <t>explore_count → zone 자동 등록</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>seededRandom + Fisher-Yates</t>
+          <t>별도 학습 불필요</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>개인 갱신</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>30💎</t>
+          <t>fishing_cast 훅</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>개인 시드 생성</t>
+          <t>어종 자동 등록</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>구매 기록 초기화</t>
+          <t>v1.24와 자연 연동</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>auction → server.js</t>
+          <t>영구 스탯 보너스</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>6번째 (마지막) 모듈 통합</t>
+          <t>마일스톤 달성 시 누적</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>자동 정산 + 환불 + 양방향 지급</t>
+          <t>codexBonuses 객체</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>tickAuctions</t>
+          <t>game/dailyshop.js</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>10초마다 만료 정산</t>
+          <t>일일 상점 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>setInterval 통합</t>
+          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>결정적 랜덤</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>auction_create</t>
+          <t>날짜 시드</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>경매 등록 (등록 수수료 자동 차감)</t>
+          <t>모든 플레이어 동일 상품</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>3가지 기간</t>
+          <t>seededRandom + Fisher-Yates</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>개인 갱신</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>auction_bid</t>
+          <t>30💎</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>입찰 + 이전 입찰자 자동 환불</t>
+          <t>개인 시드 생성</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>스나이핑 방지 연장</t>
+          <t>구매 기록 초기화</t>
         </is>
       </c>
     </row>
@@ -17373,22 +17734,22 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>auction_my</t>
+          <t>auction → server.js</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>내 등록/입찰 내역 조회</t>
+          <t>6번째 (마지막) 모듈 통합</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>자동 정산 + 환불 + 양방향 지급</t>
         </is>
       </c>
     </row>
@@ -17400,130 +17761,130 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>신규 모듈 6/6</t>
+          <t>tickAuctions</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>100% 통합 완료</t>
+          <t>10초마다 만료 정산</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>lottery/fishing/event/season/boss_rush/auction</t>
+          <t>setInterval 통합</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>boss_rush → server.js</t>
+          <t>auction_create</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>5번째 모듈 통합</t>
+          <t>경매 등록 (등록 수수료 자동 차감)</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>메모리 세션 기반</t>
+          <t>3가지 기간</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>bossRushSessions</t>
+          <t>auction_bid</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>진행 중 세션 저장</t>
+          <t>입찰 + 이전 입찰자 자동 환불</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>currentWave/시간 추적</t>
+          <t>스나이핑 방지 연장</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>bossRushRanking</t>
+          <t>auction_my</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>글로벌 랭킹 TOP 100</t>
+          <t>내 등록/입찰 내역 조회</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>웨이브 → 시간 정렬</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>boss_rush_enter</t>
+          <t>신규 모듈 6/6</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>무료/유료/다이아 입장</t>
+          <t>100% 통합 완료</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>동시 1개 세션 제한</t>
+          <t>lottery/fishing/event/season/boss_rush/auction</t>
         </is>
       </c>
     </row>
@@ -17535,22 +17896,22 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_advance</t>
+          <t>boss_rush → server.js</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>웨이브 클리어 보고</t>
+          <t>5번째 모듈 통합</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>시간 초과 검증</t>
+          <t>메모리 세션 기반</t>
         </is>
       </c>
     </row>
@@ -17562,83 +17923,83 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>풀클리어 보상</t>
+          <t>bossRushSessions</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 누적</t>
+          <t>진행 중 세션 저장</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>currentWave/시간 추적</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>season → server.js</t>
+          <t>bossRushRanking</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>4번째 모듈 통합</t>
+          <t>글로벌 랭킹 TOP 100</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>XP 자동 적립 + 보상 수령</t>
+          <t>웨이브 → 시간 정렬</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>boss_rush_enter</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
+          <t>무료/유료/다이아 입장</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>SEASON_XP_MAP 매핑</t>
+          <t>동시 1개 세션 제한</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -17648,39 +18009,39 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>season_status</t>
+          <t>boss_rush_advance</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>XP/티어/구매여부/수령내역 조회</t>
+          <t>웨이브 클리어 보고</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>15티어 전체</t>
+          <t>시간 초과 검증</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>season_buy_pass</t>
+          <t>풀클리어 보상</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 패스 구매 (1500💎)</t>
+          <t>20웨이브 누적</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -17697,56 +18058,56 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>season_claim</t>
+          <t>season → server.js</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>티어 보상 수령 (free/premium)</t>
+          <t>4번째 모듈 통합</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>자동 인벤토리 적용</t>
+          <t>XP 자동 적립 + 보상 수령</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>event → server.js</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>3번째 모듈 통합</t>
+          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>축제 시스템 활성화</t>
+          <t>SEASON_XP_MAP 매핑</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -17756,78 +18117,78 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>event_status</t>
+          <t>season_status</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>현재 활성 축제 조회</t>
+          <t>XP/티어/구매여부/수령내역 조회</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>이름/기간/버프/한정 보상</t>
+          <t>15티어 전체</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>/status JSON</t>
+          <t>season_buy_pass</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>festival 필드 추가</t>
+          <t>프리미엄 패스 구매 (1500💎)</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>대시보드 확인용</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>축제 인사</t>
+          <t>season_claim</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>30% 확률로 NPC가 축제 대사 출력</t>
+          <t>티어 보상 수령 (free/premium)</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>spring_blossom 등 5종</t>
+          <t>자동 인벤토리 적용</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -17837,24 +18198,24 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>fishing → server.js</t>
+          <t>event → server.js</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>3번째 모듈 통합</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>두 번째 모듈 통합</t>
+          <t>축제 시스템 활성화</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -17864,78 +18225,78 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>fishing_status</t>
+          <t>event_status</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>지역/낚싯대/미끼/시간대 조회</t>
+          <t>현재 활성 축제 조회</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>이름/기간/버프/한정 보상</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>fishing_cast</t>
+          <t>/status JSON</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
+          <t>festival 필드 추가</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>전설/신화 → 서버 알림</t>
+          <t>대시보드 확인용</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>fishing_buy_rod</t>
+          <t>축제 인사</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>낚싯대 구매 (골드/다이아)</t>
+          <t>30% 확률로 NPC가 축제 대사 출력</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>5등급 모두</t>
+          <t>spring_blossom 등 5종</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -17945,7 +18306,7 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>lottery → server.js</t>
+          <t>fishing → server.js</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -17955,29 +18316,29 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>첫 모듈 통합 마일스톤</t>
+          <t>두 번째 모듈 통합</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>lottery_status</t>
+          <t>fishing_status</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>상태/가격/상품 풀 조회</t>
+          <t>지역/낚싯대/미끼/시간대 조회</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -17989,432 +18350,432 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>lottery_free_spin</t>
+          <t>fishing_cast</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 스핀</t>
+          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>자정 초기화</t>
+          <t>전설/신화 → 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>lottery_paid_spin</t>
+          <t>fishing_buy_rod</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>유료 1회 / 10연속</t>
+          <t>낚싯대 구매 (골드/다이아)</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>count: 1 또는 10</t>
+          <t>5등급 모두</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js 신규</t>
+          <t>lottery → server.js</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>등록 2% + 낙찰 5%</t>
+          <t>첫 모듈 통합 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>활성 한도</t>
+          <t>lottery_status</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>플레이어당 10개</t>
+          <t>상태/가격/상품 풀 조회</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>자기 입찰 금지</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>game/fishing.js 신규</t>
+          <t>lottery_free_spin</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
+          <t>매일 무료 1회 스핀</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 = 20000G + 칭호</t>
+          <t>자정 초기화</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>전설의 비단잉어</t>
+          <t>lottery_paid_spin</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>드래곤 낚싯대 + 가중치 1</t>
+          <t>유료 1회 / 10연속</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>5000G + 평생 행운 +5%</t>
+          <t>count: 1 또는 10</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>game/boss_rush.js 신규</t>
+          <t>game/auction.js 신규</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 / HP ×1.35 스케일링</t>
+          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>최종 보상: 200💎 + 용재료 ×5</t>
+          <t>등록 2% + 낙찰 5%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>입장</t>
+          <t>활성 한도</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 / 1000G / 30💎</t>
+          <t>플레이어당 10개</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>랭킹 시스템</t>
+          <t>자기 입찰 금지</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>챔피언 보상</t>
+          <t>game/fishing.js 신규</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
+          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>신화 크라켄 = 20000G + 칭호</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js 신규</t>
+          <t>전설의 비단잉어</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 / 가중치 1000</t>
+          <t>드래곤 낚싯대 + 가중치 1</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 + 유료</t>
+          <t>5000G + 평생 행운 +5%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>영웅 장비 상자</t>
+          <t>game/boss_rush.js 신규</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>확률 0.2% (가장 희귀)</t>
+          <t>20웨이브 / HP ×1.35 스케일링</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>전설 보상</t>
+          <t>최종 보상: 200💎 + 용재료 ×5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>200 다이아</t>
+          <t>입장</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>확률 0.8%</t>
+          <t>매일 무료 3회 / 1000G / 30💎</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>랭킹 시스템</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>신년 축제</t>
+          <t>챔피언 보상</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>1/1 ~ 1/7</t>
+          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>골드 +50% / EXP +30%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>봄꽃 축제</t>
+          <t>game/lottery.js 신규</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>4/1 ~ 4/14</t>
+          <t>10종 보상 / 가중치 1000</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>HP재생 +30% / 드롭 +20%</t>
+          <t>매일 무료 1회 + 유료</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>한여름 밤의 축제</t>
+          <t>영웅 장비 상자</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>7/15 ~ 8/15</t>
+          <t>확률 0.2% (가장 희귀)</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>화염 +30% / PvP 보상 +50%</t>
+          <t>전설 보상</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>할로윈 축제</t>
+          <t>200 다이아</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>10/25 ~ 11/1</t>
+          <t>확률 0.8%</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>크리 +10% / 언데드 +50%</t>
+          <t>잭팟</t>
         </is>
       </c>
     </row>
@@ -18431,206 +18792,206 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>겨울 축제</t>
+          <t>신년 축제</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>12/20 ~ 12/31</t>
+          <t>1/1 ~ 1/7</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
+          <t>골드 +50% / EXP +30%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>game/season.js 신규</t>
+          <t>봄꽃 축제</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>15티어 / 30일 / 무료+프리미엄</t>
+          <t>4/1 ~ 4/14</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
+          <t>HP재생 +30% / 드롭 +20%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>XP 획득 7종</t>
+          <t>한여름 밤의 축제</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>퀘/보스/PvP/월드보스/던전/제작</t>
+          <t>7/15 ~ 8/15</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>일일 +200 ~ 월드보스 +500</t>
+          <t>화염 +30% / PvP 보상 +50%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 가격</t>
+          <t>할로윈 축제</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>1500 다이아</t>
+          <t>10/25 ~ 11/1</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>시즌 당 1회</t>
+          <t>크리 +10% / 언데드 +50%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Lv.40 달성</t>
+          <t>겨울 축제</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>각성기 해금 마일스톤</t>
+          <t>12/20 ~ 12/31</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>150💎</t>
+          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Lv.50 달성</t>
+          <t>game/season.js 신규</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>환생 가능 마일스톤</t>
+          <t>15티어 / 30일 / 무료+프리미엄</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>250💎</t>
+          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>첫 환생</t>
+          <t>XP 획득 7종</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>prestige 1차</t>
+          <t>퀘/보스/PvP/월드보스/던전/제작</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>500💎</t>
+          <t>일일 +200 ~ 월드보스 +500</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>첫 월드 보스</t>
+          <t>프리미엄 가격</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 처치 보너스</t>
+          <t>1500 다이아</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>100💎</t>
+          <t>시즌 당 1회</t>
         </is>
       </c>
     </row>
@@ -18647,125 +19008,125 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>업적 50개</t>
+          <t>Lv.40 달성</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>업적 마일스톤</t>
+          <t>각성기 해금 마일스톤</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>200💎</t>
+          <t>150💎</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>불사조 스킨</t>
+          <t>Lv.50 달성</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>환생 가능 마일스톤</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>불사조 깃털 이펙트 (영구)</t>
+          <t>250💎</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>폭풍 스킨</t>
+          <t>첫 환생</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>prestige 1차</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>번개 오라 이펙트 (영구)</t>
+          <t>500💎</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>상점 (편의)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 자동물약</t>
+          <t>첫 월드 보스</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>500 다이아</t>
+          <t>월드 보스 처치 보너스</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>24시간 자동물약 무한</t>
+          <t>100💎</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>상점 (상자)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 보물 상자</t>
+          <t>업적 50개</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>300 다이아</t>
+          <t>업적 마일스톤</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>전설 장비 확정 + 다이아</t>
+          <t>200💎</t>
         </is>
       </c>
     </row>
@@ -18777,130 +19138,130 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>상점 (재료)</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>전설 재료 패키지</t>
+          <t>불사조 스킨</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>600 다이아</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
+          <t>불사조 깃털 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 분노</t>
+          <t>폭풍 스킨</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>크리티컬 +5%</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>60명 정원</t>
+          <t>번개 오라 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.7</t>
+          <t>상점 (편의)</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 신속</t>
+          <t>프리미엄 자동물약</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>이동속도 +10%</t>
+          <t>500 다이아</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>70명 정원</t>
+          <t>24시간 자동물약 무한</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.8</t>
+          <t>상점 (상자)</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 회복</t>
+          <t>프리미엄 보물 상자</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>HP 재생 +50%</t>
+          <t>300 다이아</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>80명 정원</t>
+          <t>전설 장비 확정 + 다이아</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.9</t>
+          <t>상점 (재료)</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 운명</t>
+          <t>전설 재료 패키지</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>회피 +5%</t>
+          <t>600 다이아</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>90명 정원</t>
+          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
         </is>
       </c>
     </row>
@@ -18912,211 +19273,211 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.10</t>
+          <t>혈맹 Lv.6</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 전설</t>
+          <t>혈맹의 분노</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>전 스탯 +5%</t>
+          <t>크리티컬 +5%</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>100명 정원 — 최종</t>
+          <t>60명 정원</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.7</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>점쟁이</t>
+          <t>혈맹의 신속</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
+          <t>이동속도 +10%</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>70명 정원</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.8</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>감정사</t>
+          <t>혈맹의 회복</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
+          <t>HP 재생 +50%</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>80명 정원</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.9</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>수집가</t>
+          <t>혈맹의 운명</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
+          <t>회피 +5%</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>90명 정원</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>각성기 (어쌔신)</t>
+          <t>혈맹 Lv.10</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>천 개의 칼날</t>
+          <t>혈맹의 전설</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
+          <t>전 스탯 +5%</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>100명 정원 — 최종</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>각성기 (워리어)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>대지 가르기</t>
+          <t>점쟁이</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
+          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>각성기 (나이트)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>불멸의 수호자</t>
+          <t>감정사</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>피해 90% 감소 / 도발 / 10초</t>
+          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>각성기 (메이지)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>시간 정지</t>
+          <t>수집가</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
+          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
@@ -19128,17 +19489,17 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>각성기 (클레릭)</t>
+          <t>각성기 (어쌔신)</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>신의 은총</t>
+          <t>천 개의 칼날</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>HP 100% 회복 / 전스탯 +50%</t>
+          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
@@ -19150,108 +19511,108 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (워리어)</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>폭풍 정복자</t>
+          <t>대지 가르기</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인 처치</t>
+          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>10,000G + 150다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (나이트)</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>연금술사</t>
+          <t>불멸의 수호자</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>엘릭서 10회 제작</t>
+          <t>피해 90% 감소 / 도발 / 10초</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>5,000G + 80다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (메이지)</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>그림자 정복자</t>
+          <t>시간 정지</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 클리어</t>
+          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>8,000G + 120다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (클레릭)</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>전설의 동반자</t>
+          <t>신의 은총</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>전설급 펫 진화</t>
+          <t>HP 100% 회복 / 전스탯 +50%</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>6,000G + 100다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
@@ -19268,206 +19629,206 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>이국의 상인</t>
+          <t>폭풍 정복자</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>사치품 교역 5회</t>
+          <t>폭풍의 거인 처치</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>4,000G + 60다이아</t>
+          <t>10,000G + 150다이아</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인</t>
+          <t>연금술사</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>HP 100,000 / ATK 140 / DEF 90</t>
+          <t>엘릭서 10회 제작</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>EXP 10000 + 6000G</t>
+          <t>5,000G + 80다이아</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>시간의 수호자</t>
+          <t>그림자 정복자</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>HP 70,000 / ATK 170 / DEF 60</t>
+          <t>그림자 미궁 클리어</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>EXP 9000 + 7000G</t>
+          <t>8,000G + 120다이아</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>교역품</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
+          <t>전설의 동반자</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종</t>
+          <t>전설급 펫 진화</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>기본가 600~900G</t>
+          <t>6,000G + 100다이아</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>타이탄의 엘릭서</t>
+          <t>이국의 상인</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>용재료×3 + 마법재료×10</t>
+          <t>사치품 교역 5회</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>ATK ×1.5 / 30분</t>
+          <t>4,000G + 60다이아</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>강철 엘릭서</t>
+          <t>폭풍의 거인</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>철광석×30 + 마법재료×10</t>
+          <t>HP 100,000 / ATK 140 / DEF 90</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>DEF ×1.5 / 30분</t>
+          <t>EXP 10000 + 6000G</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>질풍 엘릭서</t>
+          <t>시간의 수호자</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>약초×20 + 마법재료×8</t>
+          <t>HP 70,000 / ATK 170 / DEF 60</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>SPD ×1.4 / 20분</t>
+          <t>EXP 9000 + 7000G</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>교역품</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>지혜 엘릭서</t>
+          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>마법수정×5 + 영혼재료×5</t>
+          <t>이국의 사치품 3종</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>EXP ×2.5 / 15분</t>
+          <t>기본가 600~900G</t>
         </is>
       </c>
     </row>
@@ -19484,260 +19845,260 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>행운 엘릭서</t>
+          <t>타이탄의 엘릭서</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>보석×10 + 마법재료×5</t>
+          <t>용재료×3 + 마법재료×10</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>GOLD ×2.0 / 15분</t>
+          <t>ATK ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>불사조 (pet_phoenix)</t>
+          <t>강철 엘릭서</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>불꽃산 보스 50처치</t>
+          <t>철광석×30 + 마법재료×10</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>화염 DMG +20% (진화 +40%)</t>
+          <t>DEF ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>유니콘 (pet_unicorn)</t>
+          <t>질풍 엘릭서</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>다이아 800개</t>
+          <t>약초×20 + 마법재료×8</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>회피 +10% (진화 +20%)</t>
+          <t>SPD ×1.4 / 20분</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (mount_pegasus)</t>
+          <t>지혜 엘릭서</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>다이아 1200개</t>
+          <t>마법수정×5 + 영혼재료×5</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>이동속도 +85% / 비행</t>
+          <t>EXP ×2.5 / 15분</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁</t>
+          <t>행운 엘릭서</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Lv.38 / 8인 파티 / 7스테이지</t>
+          <t>보석×10 + 마법재료×5</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>22000G + 32000EXP</t>
+          <t>GOLD ×2.0 / 15분</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>드롭</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>드래곤 검/망토/투구/장갑</t>
+          <t>불사조 (pet_phoenix)</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 보스 드롭</t>
+          <t>불꽃산 보스 50처치</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>전설급</t>
+          <t>화염 DMG +20% (진화 +40%)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자</t>
+          <t>유니콘 (pet_unicorn)</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>몬스터 10,000 처치</t>
+          <t>다이아 800개</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>ATK +7%</t>
+          <t>회피 +10% (진화 +20%)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>불멸자</t>
+          <t>페가수스 (mount_pegasus)</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>환생 5회</t>
+          <t>다이아 1200개</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>EXP +25%</t>
+          <t>이동속도 +85% / 비행</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>천공의 군주</t>
+          <t>그림자 미궁</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 10회 처치</t>
+          <t>Lv.38 / 8인 파티 / 7스테이지</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>보스DMG +15%</t>
+          <t>22000G + 32000EXP</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>드롭</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>지역 시트 갱신</t>
+          <t>드래곤 검/망토/투구/장갑</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>25→51개 지역 반영</t>
+          <t>그림자 미궁 보스 드롭</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>전설급</t>
         </is>
       </c>
     </row>
@@ -19749,22 +20110,22 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>칭호 시트 갱신</t>
+          <t>공허의 방랑자</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>7→16종 + 효과/색상 추가</t>
+          <t>몬스터 10,000 처치</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ATK +7%</t>
         </is>
       </c>
     </row>
@@ -19776,22 +20137,22 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>출석 캘린더 시트</t>
+          <t>불멸자</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (28일 사이클)</t>
+          <t>환생 5회</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EXP +25%</t>
         </is>
       </c>
     </row>
@@ -19803,22 +20164,22 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>장비 세트 시트</t>
+          <t>천공의 군주</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (드래곤/영웅/태초)</t>
+          <t>월드 보스 10회 처치</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>보스DMG +15%</t>
         </is>
       </c>
     </row>
@@ -19835,12 +20196,12 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>장비 등급 시트</t>
+          <t>지역 시트 갱신</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+          <t>25→51개 지역 반영</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
@@ -19862,12 +20223,12 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>디버프 시트</t>
+          <t>칭호 시트 갱신</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+          <t>7→16종 + 효과/색상 추가</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -19889,12 +20250,12 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>패치 노트 시트</t>
+          <t>출석 캘린더 시트</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (히스토리)</t>
+          <t>신규 추가 (28일 사이클)</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
@@ -19906,25 +20267,133 @@
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>장비 세트 시트</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (드래곤/영웅/태초)</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>장비 등급 시트</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>디버프 시트</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>패치 노트 시트</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (히스토리)</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
           <t>v1.10</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>기획서</t>
         </is>
       </c>
-      <c r="C109" s="8" t="inlineStr">
+      <c r="C113" s="8" t="inlineStr">
         <is>
           <t>던전 시트</t>
         </is>
       </c>
-      <c r="D109" s="8" t="inlineStr">
+      <c r="D113" s="8" t="inlineStr">
         <is>
           <t>신규 추가 (7종 던전)</t>
         </is>
       </c>
-      <c r="E109" s="8" t="inlineStr">
+      <c r="E113" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -28,22 +28,23 @@
     <sheet name="장비 등급" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="디버프 v1.7+" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="던전" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="우편함" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="도감" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="일일 상점" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="경매장" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="낚시" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="보스 러시" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="행운의 룰렛" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="축제 이벤트" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="시즌 패스" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="무료 다이아" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="길드 (혈맹)" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="NPC" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="월드 보스" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="연금술" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="패치 노트" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="v1.9 ~ v1.34" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="특성 트리" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="우편함" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="도감" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="일일 상점" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="경매장" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="낚시" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="보스 러시" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="행운의 룰렛" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="축제 이벤트" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="시즌 패스" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="무료 다이아" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="길드 (혈맹)" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="NPC" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="월드 보스" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="연금술" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="패치 노트" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="v1.9 ~ v1.35" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6864,6 +6865,848 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>특성 트리 (3브랜치 × 7노드 = 21노드 — v1.35 신규 모듈 game/skill_tree.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>브랜치</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>아이콘</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>노드명</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>최대 랭크</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>효과</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>요구 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>offense</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>공격력 단련</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>off_atk</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>ATK +3 / 랭크</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>offense</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>크리티컬</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>off_crit</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>크리율 +2% / 랭크</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>offense</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>공격 속도</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>off_speed</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>공속 +5% / 랭크</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>offense</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>관통</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>off_pierce</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>관통 +4% / 랭크</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>offense</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>폭발 일격</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>off_burst</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>크리DMG +10% / 랭크</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>offense</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>마무리 일격</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>off_execute</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>처형 보너스 +15%</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>offense</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>전쟁의 화신</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>off_master</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>ATK +30 / 크리 +5%</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>방어력 단련</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>def_def</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>DEF +3 / 랭크</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>체력 단련</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>def_hp</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>HP +30 / 랭크</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>def_dodge</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>회피 +2% / 랭크</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>재생</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>def_regen</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>HP재생 +10% / 랭크</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>피해 감소</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>def_block</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>피해 -3% / 랭크</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>불굴</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>def_revive</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>부활 확률 +10%</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>불멸의 의지</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>def_master</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>DEF +30 / HP +300</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>경험치 보너스</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>util_exp</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>EXP +3% / 랭크</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>골드 보너스</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>util_gold</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>GOLD +3% / 랭크</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>드롭률</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>util_drop</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>드롭 +3% / 랭크</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>이동 속도</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>util_speed</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>SPD +1 / 랭크</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>행운</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>util_lucky</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>행운 확률 +2% / 랭크</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>정찰</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>util_scout</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>시야 +5</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>운명의 인도자</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>util_master</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>EXP/GOLD +20% / 드롭 +10%</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>특성 트리 시스템</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>포인트 획득</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>레벨업 시 +1 (Lv.50 만렙 = 50 포인트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>게이트</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>상위 노드는 해당 브랜치에 5/10/15/20/25 투자 후 해금</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>리셋 비용</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>100 다이아 → 모든 포인트 환원</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>최대 효과</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>한 브랜치 풀투자 시 마스터 노드 해금 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>game/skill_tree.js (신규 파일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>레벨업 시 awardPoints() 자동 호출 / 소켓 talent_status / spend / reset</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7130,7 +7973,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7979,7 +8822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8545,7 +9388,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8849,7 +9692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9712,7 +10555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10929,7 +11772,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11429,340 +12272,6 @@
       <c r="B23" s="3" t="inlineStr">
         <is>
           <t>행운의 룰렛 30회 → ach_lucky 업적 (기존)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>축제 이벤트 (5종 — v1.21 신규 모듈 game/event.js)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>축제명</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>기간</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>색상</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>글로벌 버프</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>한정 보상</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>NPC 인사</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>new_year</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>신년 축제</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>1/1 ~ 1/7</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>금색</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>골드 +50% / EXP +30%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>새해 칭호 / 황금마 / 천상 스킨</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>새해 복 많이 받으세요!</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>spring_blossom</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>봄꽃 축제</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>4/1 ~ 4/14</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>연분홍</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>HP재생 +30% / 드롭률 +20%</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>벚꽃 칭호 / 체리 요정 펫 / 벚꽃차</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>꽃잎이 흩날리는 계절...</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>midsummer</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>한여름 밤의 축제</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>7/15 ~ 8/15</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>주황</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>화염 DMG +30% / PvP 보상 +50%</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>여름왕 칭호 / 화염 스킨 / 타이탄 엘릭서</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>뜨거운 밤이군요!</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>halloween</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>할로윈 축제</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>10/25 ~ 11/1</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>오렌지</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>크리티컬 +10% / 언데드 DMG +50%</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>호박 칭호 / 유령 펫 / 공허 스킨</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Trick or Treat!</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>winter_festival</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>겨울 축제</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>12/20 ~ 12/31</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>하늘색</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>겨울 전설 칭호 / 순록 / 오로라 스킨</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>메리 크리스마스!</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>축제 이벤트 시스템</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>활성화</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>실제 달력 기준 자동 (서버 시간)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>글로벌 버프</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>모든 플레이어에게 자동 적용</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>한정 보상</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>이벤트 기간 중에만 획득 가능 (영구 소지)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>NPC 대사</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>이벤트 기간 중 모든 NPC에 인사 추가</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>모듈</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>game/event.js (신규 파일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>헬퍼 함수</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>getActiveEvent() / getEventBuff() / isExclusiveRewardActive()</t>
         </is>
       </c>
     </row>
@@ -13066,6 +13575,340 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>축제 이벤트 (5종 — v1.21 신규 모듈 game/event.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>축제명</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>색상</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>글로벌 버프</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>한정 보상</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>NPC 인사</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>new_year</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>신년 축제</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>1/1 ~ 1/7</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>금색</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>골드 +50% / EXP +30%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>새해 칭호 / 황금마 / 천상 스킨</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>새해 복 많이 받으세요!</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>spring_blossom</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>봄꽃 축제</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>4/1 ~ 4/14</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>연분홍</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>HP재생 +30% / 드롭률 +20%</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>벚꽃 칭호 / 체리 요정 펫 / 벚꽃차</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>꽃잎이 흩날리는 계절...</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>midsummer</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>한여름 밤의 축제</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>7/15 ~ 8/15</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>주황</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>화염 DMG +30% / PvP 보상 +50%</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>여름왕 칭호 / 화염 스킨 / 타이탄 엘릭서</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>뜨거운 밤이군요!</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>halloween</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>할로윈 축제</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>10/25 ~ 11/1</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>오렌지</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>크리티컬 +10% / 언데드 DMG +50%</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>호박 칭호 / 유령 펫 / 공허 스킨</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Trick or Treat!</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>winter_festival</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>겨울 축제</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>12/20 ~ 12/31</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>하늘색</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>겨울 전설 칭호 / 순록 / 오로라 스킨</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>메리 크리스마스!</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>축제 이벤트 시스템</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>활성화</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>실제 달력 기준 자동 (서버 시간)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>글로벌 버프</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>모든 플레이어에게 자동 적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>한정 보상</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>이벤트 기간 중에만 획득 가능 (영구 소지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>NPC 대사</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>이벤트 기간 중 모든 NPC에 인사 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>game/event.js (신규 파일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>헬퍼 함수</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>getActiveEvent() / getEventBuff() / isExclusiveRewardActive()</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13461,7 +14304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13913,7 +14756,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14300,7 +15143,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14698,7 +15541,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15039,7 +15882,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15369,13 +16212,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15416,7 +16259,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -15431,14 +16274,14 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>game/mail.js — 정식 우편함 시스템 (생성 + 통합 동시)</t>
+          <t>game/skill_tree.js — 특성 트리 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -15448,19 +16291,19 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>우편함</t>
+          <t>특성 트리</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>시스템/선물 메일 + 첨부(골드/다이아/아이템) + 만료/수령 관리</t>
+          <t>3브랜치 (공격/방어/유틸) × 7노드 = 21노드</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -15470,19 +16313,19 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>선물</t>
+          <t>특성 트리</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>일일 10회 / 골드 첨부 수수료 2% / 7일 만료</t>
+          <t>레벨업 시 1포인트 자동 지급, 100💎로 리셋</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -15492,19 +16335,19 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>게이트</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>mail_inbox/read/claim/delete/send_gift</t>
+          <t>5/10/15/20/25 포인트 투자 시 상위 노드 해금</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -15519,14 +16362,14 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>game/codex.js — 도감 시스템 (생성 + 통합 동시)</t>
+          <t>game/mail.js — 정식 우편함 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -15536,19 +16379,19 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>우편함</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>5개 카테고리 (몬스터/지역/장비/어종/펫) × 4단계 마일스톤</t>
+          <t>시스템/선물 메일 + 첨부(골드/다이아/아이템) + 만료/수령 관리</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -15558,19 +16401,19 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>선물</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 달성 시 영구 스탯 보너스 + 전 서버 알림</t>
+          <t>일일 10회 / 골드 첨부 수수료 2% / 7일 만료</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -15580,19 +16423,19 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>trackQuest(explore_count) → zone 자동 등록 / fishing_cast → fish 자동 등록</t>
+          <t>mail_inbox/read/claim/delete/send_gift</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -15607,14 +16450,14 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
+          <t>game/codex.js — 도감 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -15624,19 +16467,19 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>일일 상점</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
+          <t>5개 카테고리 (몬스터/지역/장비/어종/펫) × 4단계 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -15646,19 +16489,19 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>일일 상점</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
+          <t>마일스톤 달성 시 영구 스탯 보너스 + 전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -15668,19 +16511,19 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
+          <t>trackQuest(explore_count) → zone 자동 등록 / fishing_cast → fish 자동 등록</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -15690,19 +16533,19 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
+          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -15712,19 +16555,19 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
+          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -15734,19 +16577,19 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
+          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -15761,7 +16604,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>auction_list / create / bid / my</t>
+          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
         </is>
       </c>
     </row>
@@ -15778,19 +16621,19 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
+          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -15800,19 +16643,19 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
+          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -15822,19 +16665,19 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
+          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -15849,14 +16692,14 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_status / enter / advance / abandon</t>
+          <t>auction_list / create / bid / my</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -15866,19 +16709,19 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
+          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -15893,14 +16736,14 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
+          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -15910,19 +16753,19 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
+          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -15937,14 +16780,14 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>season_status / season_buy_pass / season_claim</t>
+          <t>boss_rush_status / enter / advance / abandon</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -15954,19 +16797,19 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
+          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -15981,14 +16824,14 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
+          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -15998,19 +16841,19 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>event_status 소켓 + /status 엔드포인트 노출</t>
+          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -16020,19 +16863,19 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
+          <t>season_status / season_buy_pass / season_claim</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -16042,19 +16885,19 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
+          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -16069,14 +16912,14 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
+          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -16086,19 +16929,19 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
+          <t>event_status 소켓 + /status 엔드포인트 노출</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -16108,19 +16951,19 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
+          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -16130,19 +16973,19 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
+          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -16157,14 +17000,14 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
+          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -16174,19 +17017,19 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
+          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -16196,19 +17039,19 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
+          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -16218,19 +17061,19 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
+          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -16240,19 +17083,19 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
+          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -16262,19 +17105,19 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>경매장 시트 신규 추가</t>
+          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -16284,19 +17127,19 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
+          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -16306,19 +17149,19 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
+          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -16328,19 +17171,19 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>낚시 시트 신규 추가</t>
+          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -16350,19 +17193,19 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
+          <t>경매장 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -16372,19 +17215,19 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
+          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -16394,19 +17237,19 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>보스 러시 시트 신규 추가</t>
+          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -16416,19 +17259,19 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
+          <t>낚시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -16438,19 +17281,19 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
+          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -16460,19 +17303,19 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛 시트 신규 추가</t>
+          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -16482,19 +17325,19 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
+          <t>보스 러시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -16504,19 +17347,19 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>모듈화</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
+          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -16526,19 +17369,19 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트 시트 신규 추가</t>
+          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -16548,19 +17391,19 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
+          <t>행운의 룰렛 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -16570,19 +17413,19 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
+          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -16592,19 +17435,19 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>모듈화</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스 시트 신규 추가</t>
+          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -16614,19 +17457,19 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
+          <t>축제 이벤트 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -16636,19 +17479,19 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아 시트 신규 추가</t>
+          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -16658,19 +17501,19 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
+          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -16685,14 +17528,14 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>상점 시트 갱신</t>
+          <t>시즌 패스 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -16702,19 +17545,19 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
+          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -16724,19 +17567,19 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>최대 인원 50→100명 (Lv.10 기준)</t>
+          <t>무료 다이아 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -16746,19 +17589,19 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>길드(혈맹) 시트 신규 추가</t>
+          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -16768,19 +17611,19 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
+          <t>상점 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -16790,19 +17633,19 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>대사 시스템</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
+          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -16812,19 +17655,19 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>NPC 시트 신규 추가 (11종)</t>
+          <t>최대 인원 50→100명 (Lv.10 기준)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -16834,19 +17677,19 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>각성기</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
+          <t>길드(혈맹) 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -16856,19 +17699,19 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
+          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -16878,19 +17721,19 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>대사 시스템</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
+          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -16905,14 +17748,14 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
+          <t>NPC 시트 신규 추가 (11종)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -16922,19 +17765,19 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>각성기</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
+          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -16944,19 +17787,19 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>교역</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
+          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -16966,19 +17809,19 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
+          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -16988,19 +17831,19 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
+          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -17010,19 +17853,19 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>연금술 시트 신규 추가</t>
+          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -17032,19 +17875,19 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>교역</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
+          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -17054,19 +17897,19 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (이동 +85%, 비행)</t>
+          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -17076,19 +17919,19 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
+          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -17103,14 +17946,14 @@
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
+          <t>연금술 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -17120,19 +17963,19 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
+          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -17142,107 +17985,107 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
+          <t>페가수스 (이동 +85%, 비행)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
+          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
+          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
+          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
+          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
@@ -17252,19 +18095,19 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>상태이상</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
+          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -17274,19 +18117,19 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
@@ -17296,19 +18139,19 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -17318,12 +18161,12 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>컨텐츠</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
         </is>
       </c>
     </row>
@@ -17340,32 +18183,120 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>상태이상</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>컨텐츠</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
           <t>v1.6 이전</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>기반</t>
         </is>
       </c>
-      <c r="D92" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>마을/사냥/PvP/카르마/펫/탈것/제작/교역/길드/공성/투기장 등</t>
         </is>
@@ -17379,13 +18310,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17432,7 +18363,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -17442,422 +18373,422 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>game/mail.js</t>
+          <t>game/skill_tree.js</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>우편함 모듈 생성 + 즉시 통합</t>
+          <t>특성 트리 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>시스템/선물 + 첨부 + 만료</t>
+          <t>3브랜치 × 7노드</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>메일</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>시스템 메일</t>
+          <t>레벨업 훅</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>이벤트 보상/공지</t>
+          <t>awardPoints(target, 1) 자동 호출</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>14일 만료</t>
+          <t>별도 학습 불필요</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>메일</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>선물 메일</t>
+          <t>off_master</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>플레이어 간 / 일일 10회</t>
+          <t>전쟁의 화신</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>7일 만료, 수수료 2%</t>
+          <t>ATK +30 / 크리 +5%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>발송 시 자원 차감</t>
+          <t>def_master</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>수신자 우편함 가득 → 거부</t>
+          <t>불멸의 의지</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>첨부 미수령 메일 삭제 거부</t>
+          <t>DEF +30 / HP +300</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>game/codex.js</t>
+          <t>util_master</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>도감 모듈 생성 + 즉시 통합</t>
+          <t>운명의 인도자</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>5카테고리 × 4마일스톤</t>
+          <t>EXP/GOLD +20% / 드롭 +10%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>game/mail.js</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>explore_count → zone 자동 등록</t>
+          <t>우편함 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>별도 학습 불필요</t>
+          <t>시스템/선물 + 첨부 + 만료</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>fishing_cast 훅</t>
+          <t>시스템 메일</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>어종 자동 등록</t>
+          <t>이벤트 보상/공지</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>v1.24와 자연 연동</t>
+          <t>14일 만료</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>영구 스탯 보너스</t>
+          <t>선물 메일</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>마일스톤 달성 시 누적</t>
+          <t>플레이어 간 / 일일 10회</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>codexBonuses 객체</t>
+          <t>7일 만료, 수수료 2%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>game/dailyshop.js</t>
+          <t>발송 시 자원 차감</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>일일 상점 모듈 생성 + 즉시 통합</t>
+          <t>수신자 우편함 가득 → 거부</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
+          <t>첨부 미수령 메일 삭제 거부</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>결정적 랜덤</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>날짜 시드</t>
+          <t>game/codex.js</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>모든 플레이어 동일 상품</t>
+          <t>도감 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>seededRandom + Fisher-Yates</t>
+          <t>5카테고리 × 4마일스톤</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>개인 갱신</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>30💎</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>개인 시드 생성</t>
+          <t>explore_count → zone 자동 등록</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>구매 기록 초기화</t>
+          <t>별도 학습 불필요</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>auction → server.js</t>
+          <t>fishing_cast 훅</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>6번째 (마지막) 모듈 통합</t>
+          <t>어종 자동 등록</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>자동 정산 + 환불 + 양방향 지급</t>
+          <t>v1.24와 자연 연동</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>tickAuctions</t>
+          <t>영구 스탯 보너스</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>10초마다 만료 정산</t>
+          <t>마일스톤 달성 시 누적</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>setInterval 통합</t>
+          <t>codexBonuses 객체</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>auction_create</t>
+          <t>game/dailyshop.js</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>경매 등록 (등록 수수료 자동 차감)</t>
+          <t>일일 상점 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>3가지 기간</t>
+          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>결정적 랜덤</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>auction_bid</t>
+          <t>날짜 시드</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>입찰 + 이전 입찰자 자동 환불</t>
+          <t>모든 플레이어 동일 상품</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>스나이핑 방지 연장</t>
+          <t>seededRandom + Fisher-Yates</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>개인 갱신</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>auction_my</t>
+          <t>30💎</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>내 등록/입찰 내역 조회</t>
+          <t>개인 시드 생성</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>구매 기록 초기화</t>
         </is>
       </c>
     </row>
@@ -17869,110 +18800,110 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>신규 모듈 6/6</t>
+          <t>auction → server.js</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>100% 통합 완료</t>
+          <t>6번째 (마지막) 모듈 통합</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>lottery/fishing/event/season/boss_rush/auction</t>
+          <t>자동 정산 + 환불 + 양방향 지급</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>boss_rush → server.js</t>
+          <t>tickAuctions</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>5번째 모듈 통합</t>
+          <t>10초마다 만료 정산</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>메모리 세션 기반</t>
+          <t>setInterval 통합</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>bossRushSessions</t>
+          <t>auction_create</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>진행 중 세션 저장</t>
+          <t>경매 등록 (등록 수수료 자동 차감)</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>currentWave/시간 추적</t>
+          <t>3가지 기간</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>bossRushRanking</t>
+          <t>auction_bid</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>글로벌 랭킹 TOP 100</t>
+          <t>입찰 + 이전 입찰자 자동 환불</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>웨이브 → 시간 정렬</t>
+          <t>스나이핑 방지 연장</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -17982,44 +18913,44 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>boss_rush_enter</t>
+          <t>auction_my</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>무료/유료/다이아 입장</t>
+          <t>내 등록/입찰 내역 조회</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>동시 1개 세션 제한</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_advance</t>
+          <t>신규 모듈 6/6</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>웨이브 클리어 보고</t>
+          <t>100% 통합 완료</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>시간 초과 검증</t>
+          <t>lottery/fishing/event/season/boss_rush/auction</t>
         </is>
       </c>
     </row>
@@ -18031,83 +18962,83 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>풀클리어 보상</t>
+          <t>boss_rush → server.js</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 누적</t>
+          <t>5번째 모듈 통합</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>메모리 세션 기반</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>season → server.js</t>
+          <t>bossRushSessions</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>4번째 모듈 통합</t>
+          <t>진행 중 세션 저장</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>XP 자동 적립 + 보상 수령</t>
+          <t>currentWave/시간 추적</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>bossRushRanking</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
+          <t>글로벌 랭킹 TOP 100</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>SEASON_XP_MAP 매핑</t>
+          <t>웨이브 → 시간 정렬</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -18117,24 +19048,24 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>season_status</t>
+          <t>boss_rush_enter</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>XP/티어/구매여부/수령내역 조회</t>
+          <t>무료/유료/다이아 입장</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>15티어 전체</t>
+          <t>동시 1개 세션 제한</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -18144,51 +19075,51 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>season_buy_pass</t>
+          <t>boss_rush_advance</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 패스 구매 (1500💎)</t>
+          <t>웨이브 클리어 보고</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>시간 초과 검증</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>season_claim</t>
+          <t>풀클리어 보상</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>티어 보상 수령 (free/premium)</t>
+          <t>20웨이브 누적</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>자동 인벤토리 적용</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -18198,159 +19129,159 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>event → server.js</t>
+          <t>season → server.js</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>3번째 모듈 통합</t>
+          <t>4번째 모듈 통합</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>축제 시스템 활성화</t>
+          <t>XP 자동 적립 + 보상 수령</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>event_status</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>현재 활성 축제 조회</t>
+          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>이름/기간/버프/한정 보상</t>
+          <t>SEASON_XP_MAP 매핑</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>/status JSON</t>
+          <t>season_status</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>festival 필드 추가</t>
+          <t>XP/티어/구매여부/수령내역 조회</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>대시보드 확인용</t>
+          <t>15티어 전체</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>축제 인사</t>
+          <t>season_buy_pass</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>30% 확률로 NPC가 축제 대사 출력</t>
+          <t>프리미엄 패스 구매 (1500💎)</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>spring_blossom 등 5종</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>fishing → server.js</t>
+          <t>season_claim</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>티어 보상 수령 (free/premium)</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>두 번째 모듈 통합</t>
+          <t>자동 인벤토리 적용</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>fishing_status</t>
+          <t>event → server.js</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>지역/낚싯대/미끼/시간대 조회</t>
+          <t>3번째 모듈 통합</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>축제 시스템 활성화</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -18360,1880 +19291,1880 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>fishing_cast</t>
+          <t>event_status</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
+          <t>현재 활성 축제 조회</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>전설/신화 → 서버 알림</t>
+          <t>이름/기간/버프/한정 보상</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>fishing_buy_rod</t>
+          <t>/status JSON</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>낚싯대 구매 (골드/다이아)</t>
+          <t>festival 필드 추가</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>5등급 모두</t>
+          <t>대시보드 확인용</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>lottery → server.js</t>
+          <t>축제 인사</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>30% 확률로 NPC가 축제 대사 출력</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>첫 모듈 통합 마일스톤</t>
+          <t>spring_blossom 등 5종</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>lottery_status</t>
+          <t>fishing → server.js</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>상태/가격/상품 풀 조회</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>두 번째 모듈 통합</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>lottery_free_spin</t>
+          <t>fishing_status</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 스핀</t>
+          <t>지역/낚싯대/미끼/시간대 조회</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>자정 초기화</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>lottery_paid_spin</t>
+          <t>fishing_cast</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>유료 1회 / 10연속</t>
+          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>count: 1 또는 10</t>
+          <t>전설/신화 → 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js 신규</t>
+          <t>fishing_buy_rod</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
+          <t>낚싯대 구매 (골드/다이아)</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>등록 2% + 낙찰 5%</t>
+          <t>5등급 모두</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>활성 한도</t>
+          <t>lottery → server.js</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>플레이어당 10개</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>자기 입찰 금지</t>
+          <t>첫 모듈 통합 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>game/fishing.js 신규</t>
+          <t>lottery_status</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
+          <t>상태/가격/상품 풀 조회</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 = 20000G + 칭호</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>전설의 비단잉어</t>
+          <t>lottery_free_spin</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>드래곤 낚싯대 + 가중치 1</t>
+          <t>매일 무료 1회 스핀</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>5000G + 평생 행운 +5%</t>
+          <t>자정 초기화</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>game/boss_rush.js 신규</t>
+          <t>lottery_paid_spin</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 / HP ×1.35 스케일링</t>
+          <t>유료 1회 / 10연속</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>최종 보상: 200💎 + 용재료 ×5</t>
+          <t>count: 1 또는 10</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>입장</t>
+          <t>game/auction.js 신규</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 / 1000G / 30💎</t>
+          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>랭킹 시스템</t>
+          <t>등록 2% + 낙찰 5%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>챔피언 보상</t>
+          <t>활성 한도</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
+          <t>플레이어당 10개</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>자기 입찰 금지</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js 신규</t>
+          <t>game/fishing.js 신규</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 / 가중치 1000</t>
+          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 + 유료</t>
+          <t>신화 크라켄 = 20000G + 칭호</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>영웅 장비 상자</t>
+          <t>전설의 비단잉어</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>확률 0.2% (가장 희귀)</t>
+          <t>드래곤 낚싯대 + 가중치 1</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>전설 보상</t>
+          <t>5000G + 평생 행운 +5%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>200 다이아</t>
+          <t>game/boss_rush.js 신규</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>확률 0.8%</t>
+          <t>20웨이브 / HP ×1.35 스케일링</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>최종 보상: 200💎 + 용재료 ×5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>신년 축제</t>
+          <t>입장</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>1/1 ~ 1/7</t>
+          <t>매일 무료 3회 / 1000G / 30💎</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>골드 +50% / EXP +30%</t>
+          <t>랭킹 시스템</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>봄꽃 축제</t>
+          <t>챔피언 보상</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>4/1 ~ 4/14</t>
+          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>HP재생 +30% / 드롭 +20%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>한여름 밤의 축제</t>
+          <t>game/lottery.js 신규</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>7/15 ~ 8/15</t>
+          <t>10종 보상 / 가중치 1000</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>화염 +30% / PvP 보상 +50%</t>
+          <t>매일 무료 1회 + 유료</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>할로윈 축제</t>
+          <t>영웅 장비 상자</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>10/25 ~ 11/1</t>
+          <t>확률 0.2% (가장 희귀)</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>크리 +10% / 언데드 +50%</t>
+          <t>전설 보상</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>겨울 축제</t>
+          <t>200 다이아</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>12/20 ~ 12/31</t>
+          <t>확률 0.8%</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
+          <t>잭팟</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>game/season.js 신규</t>
+          <t>신년 축제</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>15티어 / 30일 / 무료+프리미엄</t>
+          <t>1/1 ~ 1/7</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
+          <t>골드 +50% / EXP +30%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>XP 획득 7종</t>
+          <t>봄꽃 축제</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>퀘/보스/PvP/월드보스/던전/제작</t>
+          <t>4/1 ~ 4/14</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>일일 +200 ~ 월드보스 +500</t>
+          <t>HP재생 +30% / 드롭 +20%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 가격</t>
+          <t>한여름 밤의 축제</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>1500 다이아</t>
+          <t>7/15 ~ 8/15</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>시즌 당 1회</t>
+          <t>화염 +30% / PvP 보상 +50%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Lv.40 달성</t>
+          <t>할로윈 축제</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>각성기 해금 마일스톤</t>
+          <t>10/25 ~ 11/1</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>150💎</t>
+          <t>크리 +10% / 언데드 +50%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Lv.50 달성</t>
+          <t>겨울 축제</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>환생 가능 마일스톤</t>
+          <t>12/20 ~ 12/31</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>250💎</t>
+          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>첫 환생</t>
+          <t>game/season.js 신규</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>prestige 1차</t>
+          <t>15티어 / 30일 / 무료+프리미엄</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>500💎</t>
+          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>첫 월드 보스</t>
+          <t>XP 획득 7종</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 처치 보너스</t>
+          <t>퀘/보스/PvP/월드보스/던전/제작</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>100💎</t>
+          <t>일일 +200 ~ 월드보스 +500</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>업적 50개</t>
+          <t>프리미엄 가격</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>업적 마일스톤</t>
+          <t>1500 다이아</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>200💎</t>
+          <t>시즌 당 1회</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>불사조 스킨</t>
+          <t>Lv.40 달성</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>각성기 해금 마일스톤</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>불사조 깃털 이펙트 (영구)</t>
+          <t>150💎</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>폭풍 스킨</t>
+          <t>Lv.50 달성</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>환생 가능 마일스톤</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>번개 오라 이펙트 (영구)</t>
+          <t>250💎</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>상점 (편의)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 자동물약</t>
+          <t>첫 환생</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>500 다이아</t>
+          <t>prestige 1차</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>24시간 자동물약 무한</t>
+          <t>500💎</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>상점 (상자)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 보물 상자</t>
+          <t>첫 월드 보스</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>300 다이아</t>
+          <t>월드 보스 처치 보너스</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>전설 장비 확정 + 다이아</t>
+          <t>100💎</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>상점 (재료)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>전설 재료 패키지</t>
+          <t>업적 50개</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>600 다이아</t>
+          <t>업적 마일스톤</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
+          <t>200💎</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 분노</t>
+          <t>불사조 스킨</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>크리티컬 +5%</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>60명 정원</t>
+          <t>불사조 깃털 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.7</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 신속</t>
+          <t>폭풍 스킨</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>이동속도 +10%</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>70명 정원</t>
+          <t>번개 오라 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.8</t>
+          <t>상점 (편의)</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 회복</t>
+          <t>프리미엄 자동물약</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>HP 재생 +50%</t>
+          <t>500 다이아</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>80명 정원</t>
+          <t>24시간 자동물약 무한</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.9</t>
+          <t>상점 (상자)</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 운명</t>
+          <t>프리미엄 보물 상자</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>회피 +5%</t>
+          <t>300 다이아</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>90명 정원</t>
+          <t>전설 장비 확정 + 다이아</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.10</t>
+          <t>상점 (재료)</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 전설</t>
+          <t>전설 재료 패키지</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>전 스탯 +5%</t>
+          <t>600 다이아</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>100명 정원 — 최종</t>
+          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.6</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>점쟁이</t>
+          <t>혈맹의 분노</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
+          <t>크리티컬 +5%</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>60명 정원</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.7</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>감정사</t>
+          <t>혈맹의 신속</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
+          <t>이동속도 +10%</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>70명 정원</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.8</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>수집가</t>
+          <t>혈맹의 회복</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
+          <t>HP 재생 +50%</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>80명 정원</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>각성기 (어쌔신)</t>
+          <t>혈맹 Lv.9</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>천 개의 칼날</t>
+          <t>혈맹의 운명</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
+          <t>회피 +5%</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>90명 정원</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>각성기 (워리어)</t>
+          <t>혈맹 Lv.10</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>대지 가르기</t>
+          <t>혈맹의 전설</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
+          <t>전 스탯 +5%</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>100명 정원 — 최종</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>각성기 (나이트)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>불멸의 수호자</t>
+          <t>점쟁이</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>피해 90% 감소 / 도발 / 10초</t>
+          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>각성기 (메이지)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>시간 정지</t>
+          <t>감정사</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
+          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>각성기 (클레릭)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>신의 은총</t>
+          <t>수집가</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>HP 100% 회복 / 전스탯 +50%</t>
+          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (어쌔신)</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>폭풍 정복자</t>
+          <t>천 개의 칼날</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인 처치</t>
+          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>10,000G + 150다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (워리어)</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>연금술사</t>
+          <t>대지 가르기</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>엘릭서 10회 제작</t>
+          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>5,000G + 80다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (나이트)</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>그림자 정복자</t>
+          <t>불멸의 수호자</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 클리어</t>
+          <t>피해 90% 감소 / 도발 / 10초</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>8,000G + 120다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (메이지)</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>전설의 동반자</t>
+          <t>시간 정지</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>전설급 펫 진화</t>
+          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>6,000G + 100다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (클레릭)</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>이국의 상인</t>
+          <t>신의 은총</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>사치품 교역 5회</t>
+          <t>HP 100% 회복 / 전스탯 +50%</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>4,000G + 60다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인</t>
+          <t>폭풍 정복자</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>HP 100,000 / ATK 140 / DEF 90</t>
+          <t>폭풍의 거인 처치</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>EXP 10000 + 6000G</t>
+          <t>10,000G + 150다이아</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>시간의 수호자</t>
+          <t>연금술사</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>HP 70,000 / ATK 170 / DEF 60</t>
+          <t>엘릭서 10회 제작</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>EXP 9000 + 7000G</t>
+          <t>5,000G + 80다이아</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>교역품</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
+          <t>그림자 정복자</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종</t>
+          <t>그림자 미궁 클리어</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>기본가 600~900G</t>
+          <t>8,000G + 120다이아</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>타이탄의 엘릭서</t>
+          <t>전설의 동반자</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>용재료×3 + 마법재료×10</t>
+          <t>전설급 펫 진화</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>ATK ×1.5 / 30분</t>
+          <t>6,000G + 100다이아</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>강철 엘릭서</t>
+          <t>이국의 상인</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>철광석×30 + 마법재료×10</t>
+          <t>사치품 교역 5회</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>DEF ×1.5 / 30분</t>
+          <t>4,000G + 60다이아</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>질풍 엘릭서</t>
+          <t>폭풍의 거인</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>약초×20 + 마법재료×8</t>
+          <t>HP 100,000 / ATK 140 / DEF 90</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>SPD ×1.4 / 20분</t>
+          <t>EXP 10000 + 6000G</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>지혜 엘릭서</t>
+          <t>시간의 수호자</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>마법수정×5 + 영혼재료×5</t>
+          <t>HP 70,000 / ATK 170 / DEF 60</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>EXP ×2.5 / 15분</t>
+          <t>EXP 9000 + 7000G</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>교역품</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>행운 엘릭서</t>
+          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>보석×10 + 마법재료×5</t>
+          <t>이국의 사치품 3종</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>GOLD ×2.0 / 15분</t>
+          <t>기본가 600~900G</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>불사조 (pet_phoenix)</t>
+          <t>타이탄의 엘릭서</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>불꽃산 보스 50처치</t>
+          <t>용재료×3 + 마법재료×10</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>화염 DMG +20% (진화 +40%)</t>
+          <t>ATK ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>유니콘 (pet_unicorn)</t>
+          <t>강철 엘릭서</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>다이아 800개</t>
+          <t>철광석×30 + 마법재료×10</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>회피 +10% (진화 +20%)</t>
+          <t>DEF ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (mount_pegasus)</t>
+          <t>질풍 엘릭서</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>다이아 1200개</t>
+          <t>약초×20 + 마법재료×8</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>이동속도 +85% / 비행</t>
+          <t>SPD ×1.4 / 20분</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁</t>
+          <t>지혜 엘릭서</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Lv.38 / 8인 파티 / 7스테이지</t>
+          <t>마법수정×5 + 영혼재료×5</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>22000G + 32000EXP</t>
+          <t>EXP ×2.5 / 15분</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>드롭</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>드래곤 검/망토/투구/장갑</t>
+          <t>행운 엘릭서</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 보스 드롭</t>
+          <t>보석×10 + 마법재료×5</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>전설급</t>
+          <t>GOLD ×2.0 / 15분</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자</t>
+          <t>불사조 (pet_phoenix)</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>몬스터 10,000 처치</t>
+          <t>불꽃산 보스 50처치</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>ATK +7%</t>
+          <t>화염 DMG +20% (진화 +40%)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>불멸자</t>
+          <t>유니콘 (pet_unicorn)</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>환생 5회</t>
+          <t>다이아 800개</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>EXP +25%</t>
+          <t>회피 +10% (진화 +20%)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>천공의 군주</t>
+          <t>페가수스 (mount_pegasus)</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 10회 처치</t>
+          <t>다이아 1200개</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>보스DMG +15%</t>
+          <t>이동속도 +85% / 비행</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>지역 시트 갱신</t>
+          <t>그림자 미궁</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>25→51개 지역 반영</t>
+          <t>Lv.38 / 8인 파티 / 7스테이지</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22000G + 32000EXP</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>드롭</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>칭호 시트 갱신</t>
+          <t>드래곤 검/망토/투구/장갑</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>7→16종 + 효과/색상 추가</t>
+          <t>그림자 미궁 보스 드롭</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>전설급</t>
         </is>
       </c>
     </row>
@@ -20245,22 +21176,22 @@
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>출석 캘린더 시트</t>
+          <t>공허의 방랑자</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (28일 사이클)</t>
+          <t>몬스터 10,000 처치</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ATK +7%</t>
         </is>
       </c>
     </row>
@@ -20272,22 +21203,22 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>장비 세트 시트</t>
+          <t>불멸자</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (드래곤/영웅/태초)</t>
+          <t>환생 5회</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EXP +25%</t>
         </is>
       </c>
     </row>
@@ -20299,22 +21230,22 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>장비 등급 시트</t>
+          <t>천공의 군주</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+          <t>월드 보스 10회 처치</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>보스DMG +15%</t>
         </is>
       </c>
     </row>
@@ -20331,12 +21262,12 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>디버프 시트</t>
+          <t>지역 시트 갱신</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+          <t>25→51개 지역 반영</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -20358,12 +21289,12 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>패치 노트 시트</t>
+          <t>칭호 시트 갱신</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (히스토리)</t>
+          <t>7→16종 + 효과/색상 추가</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
@@ -20375,25 +21306,160 @@
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>출석 캘린더 시트</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (28일 사이클)</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>장비 세트 시트</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (드래곤/영웅/태초)</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>장비 등급 시트</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>디버프 시트</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>패치 노트 시트</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (히스토리)</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
           <t>v1.10</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B118" s="7" t="inlineStr">
         <is>
           <t>기획서</t>
         </is>
       </c>
-      <c r="C113" s="8" t="inlineStr">
+      <c r="C118" s="7" t="inlineStr">
         <is>
           <t>던전 시트</t>
         </is>
       </c>
-      <c r="D113" s="8" t="inlineStr">
+      <c r="D118" s="7" t="inlineStr">
         <is>
           <t>신규 추가 (7종 던전)</t>
         </is>
       </c>
-      <c r="E113" s="8" t="inlineStr">
+      <c r="E118" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -28,23 +28,24 @@
     <sheet name="장비 등급" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="디버프 v1.7+" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="던전" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="특성 트리" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="우편함" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="도감" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="일일 상점" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="경매장" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="낚시" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="보스 러시" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="행운의 룰렛" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="축제 이벤트" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="시즌 패스" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="무료 다이아" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="길드 (혈맹)" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="NPC" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="월드 보스" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="연금술" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="패치 노트" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="v1.9 ~ v1.35" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="농장" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="특성 트리" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="우편함" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="도감" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="일일 상점" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="경매장" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="낚시" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="보스 러시" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="행운의 룰렛" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="축제 이벤트" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="시즌 패스" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="무료 다이아" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="길드 (혈맹)" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="NPC" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="월드 보스" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="연금술" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="패치 노트" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="v1.9 ~ v1.36" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6865,6 +6866,385 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>작물 (7종 — v1.36 신규 모듈 game/farm.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>성장 시간</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>씨앗 가격</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>수확 보상</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>herb</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>약초</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>5분</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>30G</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>약초 ×3 + 20EXP</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>초보용 / 빠른 수확</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>carrot</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>당근</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>10분</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>60G</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>약초 ×2 + 50G + 40EXP</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>초보용</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>wheat</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>밀</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>15분</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>100G</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>물약 원료 ×1 + 100G + 60EXP</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>중급</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>pumpkin</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>호박</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>30분</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>200G</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>향신료 ×1 + 250G + 120EXP</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>중급</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>golden_apple</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>황금 사과</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>1시간</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>500G</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>보석 ×1 + 마법재료 ×2 + 600G</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>고급</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>moonflower</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>달꽃</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>2시간</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>30💎</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>마법재료 ×5 + 영혼석 ×1 + 1500G</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>희귀</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>dragon_fruit</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>용 과일</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>4시간</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>80💎</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>용재료 ×1 + 영혼석 ×3 + 3000G</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>전설</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>농장 시스템</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>기본 슬롯</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>4개</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>최대 슬롯</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>12개 (다이아 확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>슬롯 확장</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>50💎 / 슬롯</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>비료</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>20💎로 50% 시간 단축 (슬롯당 1회)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>AFK 진행</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>오프라인 시간도 카운트 (Date.now() 기반)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>game/farm.js (신규 파일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>farm_status / plant / harvest / fertilize / expand</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7701,7 +8081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7973,7 +8353,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8822,7 +9202,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9388,7 +9768,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9692,7 +10072,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10555,7 +10935,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11767,517 +12147,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>행운의 룰렛 (10종 — v1.22 신규 모듈 game/lottery.js)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>보상명</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>등급</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>색상</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>가중치</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>확률</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>상세</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>common_gold</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>100 골드</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>회색</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>350</v>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>35.0%</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>100 G</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>common_mat</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>마법재료 ×3</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>회색</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>마법재료 ×3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>uncommon_gold</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>500 골드</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>고급</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>녹색</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>150</v>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>15.0%</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>500 G</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>uncommon_food</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>용의 만찬 ×1</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>고급</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>녹색</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>8.0%</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>용의 만찬 ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>rare_diamond</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>20 다이아</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>희귀</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>파랑</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>20 💎</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>rare_soul</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>영혼석 ×5</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>희귀</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>파랑</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>5.0%</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>영혼석 ×5</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>epic_dragon</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>용재료 ×3</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>영웅</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>보라</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>용재료 ×3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>epic_box</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>희귀 상자 ×1</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>영웅</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>보라</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>2.0%</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>희귀 상자 ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>legend_diamond</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>200 다이아</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>전설</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>주황</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>200 💎</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>legend_equip</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>영웅 장비 상자</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>전설</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>주황</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>영웅 장비 상자</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>룰렛 시스템</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>무료 스핀</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>매일 1회 (자정 초기화)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>유료 스핀</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>50 다이아 / 회</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>10연속 스핀</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>450 다이아 (회당 45💎, 10% 할인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>총 가중치</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>1,000 (확률 합계 100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>최고 보상</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>영웅 장비 상자 (0.2%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>모듈</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>game/lottery.js (신규 파일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>업적 연계</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>행운의 룰렛 30회 → ach_lucky 업적 (기존)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13575,6 +13444,517 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>행운의 룰렛 (10종 — v1.22 신규 모듈 game/lottery.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>보상명</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>색상</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>가중치</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>확률</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>common_gold</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>100 골드</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>회색</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>350</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>100 G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>common_mat</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>마법재료 ×3</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>회색</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>마법재료 ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>uncommon_gold</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>500 골드</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>고급</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>녹색</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>500 G</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>uncommon_food</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>용의 만찬 ×1</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>고급</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>녹색</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>8.0%</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>용의 만찬 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>rare_diamond</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>20 다이아</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>희귀</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>파랑</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>20 💎</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>rare_soul</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>영혼석 ×5</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>희귀</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>파랑</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>5.0%</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>영혼석 ×5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>epic_dragon</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>용재료 ×3</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>영웅</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>보라</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>용재료 ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>epic_box</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>희귀 상자 ×1</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>영웅</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>보라</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>희귀 상자 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>legend_diamond</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>200 다이아</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>전설</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>주황</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>200 💎</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>legend_equip</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>영웅 장비 상자</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>전설</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>주황</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>영웅 장비 상자</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>룰렛 시스템</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>무료 스핀</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>매일 1회 (자정 초기화)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>유료 스핀</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>50 다이아 / 회</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>10연속 스핀</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>450 다이아 (회당 45💎, 10% 할인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>총 가중치</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>1,000 (확률 합계 100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>최고 보상</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>영웅 장비 상자 (0.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>game/lottery.js (신규 파일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>업적 연계</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>행운의 룰렛 30회 → ach_lucky 업적 (기존)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13903,7 +14283,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14304,7 +14684,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14756,7 +15136,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15143,7 +15523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15541,7 +15921,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15882,7 +16262,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16212,13 +16592,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16259,7 +16639,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -16274,14 +16654,14 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>game/skill_tree.js — 특성 트리 (생성 + 통합 동시)</t>
+          <t>game/farm.js — 농장 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -16291,19 +16671,19 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>특성 트리</t>
+          <t>농장</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>3브랜치 (공격/방어/유틸) × 7노드 = 21노드</t>
+          <t>7종 작물 (5분~4시간), AFK 진행, 4슬롯 기본 (12슬롯 확장)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -16313,19 +16693,19 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>특성 트리</t>
+          <t>농장</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>레벨업 시 1포인트 자동 지급, 100💎로 리셋</t>
+          <t>비료 (20💎) 50% 시간 단축, 슬롯 확장 50💎</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -16335,19 +16715,19 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>게이트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>5/10/15/20/25 포인트 투자 시 상위 노드 해금</t>
+          <t>farm_status / plant / harvest / fertilize / expand</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -16362,14 +16742,14 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>game/mail.js — 정식 우편함 시스템 (생성 + 통합 동시)</t>
+          <t>game/skill_tree.js — 특성 트리 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -16379,19 +16759,19 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>우편함</t>
+          <t>특성 트리</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>시스템/선물 메일 + 첨부(골드/다이아/아이템) + 만료/수령 관리</t>
+          <t>3브랜치 (공격/방어/유틸) × 7노드 = 21노드</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -16401,19 +16781,19 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>선물</t>
+          <t>특성 트리</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>일일 10회 / 골드 첨부 수수료 2% / 7일 만료</t>
+          <t>레벨업 시 1포인트 자동 지급, 100💎로 리셋</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -16423,19 +16803,19 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>게이트</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>mail_inbox/read/claim/delete/send_gift</t>
+          <t>5/10/15/20/25 포인트 투자 시 상위 노드 해금</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -16450,14 +16830,14 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>game/codex.js — 도감 시스템 (생성 + 통합 동시)</t>
+          <t>game/mail.js — 정식 우편함 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -16467,19 +16847,19 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>우편함</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>5개 카테고리 (몬스터/지역/장비/어종/펫) × 4단계 마일스톤</t>
+          <t>시스템/선물 메일 + 첨부(골드/다이아/아이템) + 만료/수령 관리</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -16489,19 +16869,19 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>선물</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 달성 시 영구 스탯 보너스 + 전 서버 알림</t>
+          <t>일일 10회 / 골드 첨부 수수료 2% / 7일 만료</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -16511,19 +16891,19 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>trackQuest(explore_count) → zone 자동 등록 / fishing_cast → fish 자동 등록</t>
+          <t>mail_inbox/read/claim/delete/send_gift</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -16538,14 +16918,14 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
+          <t>game/codex.js — 도감 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -16555,19 +16935,19 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>일일 상점</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
+          <t>5개 카테고리 (몬스터/지역/장비/어종/펫) × 4단계 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -16577,19 +16957,19 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>일일 상점</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
+          <t>마일스톤 달성 시 영구 스탯 보너스 + 전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -16599,19 +16979,19 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
+          <t>trackQuest(explore_count) → zone 자동 등록 / fishing_cast → fish 자동 등록</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -16621,19 +17001,19 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
+          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -16643,19 +17023,19 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
+          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -16665,19 +17045,19 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
+          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -16692,7 +17072,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>auction_list / create / bid / my</t>
+          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
         </is>
       </c>
     </row>
@@ -16709,19 +17089,19 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
+          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -16731,19 +17111,19 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
+          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -16753,19 +17133,19 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
+          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -16780,14 +17160,14 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_status / enter / advance / abandon</t>
+          <t>auction_list / create / bid / my</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -16797,19 +17177,19 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
+          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -16824,14 +17204,14 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
+          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -16841,19 +17221,19 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
+          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -16868,14 +17248,14 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>season_status / season_buy_pass / season_claim</t>
+          <t>boss_rush_status / enter / advance / abandon</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -16885,19 +17265,19 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
+          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -16912,14 +17292,14 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
+          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -16929,19 +17309,19 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>event_status 소켓 + /status 엔드포인트 노출</t>
+          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -16951,19 +17331,19 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
+          <t>season_status / season_buy_pass / season_claim</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -16973,19 +17353,19 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
+          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -17000,14 +17380,14 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
+          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -17017,19 +17397,19 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
+          <t>event_status 소켓 + /status 엔드포인트 노출</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -17039,19 +17419,19 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
+          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -17061,19 +17441,19 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
+          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -17088,14 +17468,14 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
+          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -17105,19 +17485,19 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
+          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -17127,19 +17507,19 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
+          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -17149,19 +17529,19 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
+          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -17171,19 +17551,19 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
+          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -17193,19 +17573,19 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>경매장 시트 신규 추가</t>
+          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -17215,19 +17595,19 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
+          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -17237,19 +17617,19 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
+          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -17259,19 +17639,19 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>낚시 시트 신규 추가</t>
+          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -17281,19 +17661,19 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
+          <t>경매장 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -17303,19 +17683,19 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
+          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -17325,19 +17705,19 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>보스 러시 시트 신규 추가</t>
+          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -17347,19 +17727,19 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
+          <t>낚시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -17369,19 +17749,19 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
+          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -17391,19 +17771,19 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛 시트 신규 추가</t>
+          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -17413,19 +17793,19 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
+          <t>보스 러시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -17435,19 +17815,19 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>모듈화</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
+          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -17457,19 +17837,19 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트 시트 신규 추가</t>
+          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -17479,19 +17859,19 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
+          <t>행운의 룰렛 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -17501,19 +17881,19 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
+          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -17523,19 +17903,19 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>모듈화</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스 시트 신규 추가</t>
+          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -17545,19 +17925,19 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
+          <t>축제 이벤트 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -17567,19 +17947,19 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아 시트 신규 추가</t>
+          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -17589,19 +17969,19 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
+          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -17616,14 +17996,14 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>상점 시트 갱신</t>
+          <t>시즌 패스 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -17633,19 +18013,19 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
+          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -17655,19 +18035,19 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>최대 인원 50→100명 (Lv.10 기준)</t>
+          <t>무료 다이아 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -17677,19 +18057,19 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>길드(혈맹) 시트 신규 추가</t>
+          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -17699,19 +18079,19 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
+          <t>상점 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -17721,19 +18101,19 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>대사 시스템</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
+          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -17743,19 +18123,19 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>NPC 시트 신규 추가 (11종)</t>
+          <t>최대 인원 50→100명 (Lv.10 기준)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -17765,19 +18145,19 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>각성기</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
+          <t>길드(혈맹) 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -17787,19 +18167,19 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
+          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -17809,19 +18189,19 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>대사 시스템</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
+          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -17836,14 +18216,14 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
+          <t>NPC 시트 신규 추가 (11종)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -17853,19 +18233,19 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>각성기</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
+          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -17875,19 +18255,19 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>교역</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
+          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -17897,19 +18277,19 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
+          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -17919,19 +18299,19 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
+          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -17941,19 +18321,19 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>연금술 시트 신규 추가</t>
+          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -17963,19 +18343,19 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>교역</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
+          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -17985,19 +18365,19 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (이동 +85%, 비행)</t>
+          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
@@ -18007,19 +18387,19 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
+          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -18034,14 +18414,14 @@
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
+          <t>연금술 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
@@ -18051,19 +18431,19 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
+          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -18073,107 +18453,107 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
+          <t>페가수스 (이동 +85%, 비행)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
+          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
+          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
+          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
+          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
@@ -18183,19 +18563,19 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>상태이상</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
+          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -18205,19 +18585,19 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
@@ -18227,19 +18607,19 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -18249,12 +18629,12 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>컨텐츠</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
         </is>
       </c>
     </row>
@@ -18271,32 +18651,120 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>상태이상</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>컨텐츠</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
           <t>v1.6 이전</t>
         </is>
       </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C100" s="7" t="inlineStr">
         <is>
           <t>기반</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>마을/사냥/PvP/카르마/펫/탈것/제작/교역/길드/공성/투기장 등</t>
         </is>
@@ -18310,13 +18778,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18363,7 +18831,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -18373,98 +18841,98 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>game/skill_tree.js</t>
+          <t>game/farm.js</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>특성 트리 모듈 생성 + 즉시 통합</t>
+          <t>농장 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>3브랜치 × 7노드</t>
+          <t>7작물 / AFK 진행</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>작물 (전설)</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>레벨업 훅</t>
+          <t>용 과일</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>awardPoints(target, 1) 자동 호출</t>
+          <t>4시간 / 80💎</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>별도 학습 불필요</t>
+          <t>용재료 ×1 + 영혼석 ×3 + 3000G</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>마스터 노드</t>
+          <t>작물 (희귀)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>off_master</t>
+          <t>달꽃</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>전쟁의 화신</t>
+          <t>2시간 / 30💎</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>ATK +30 / 크리 +5%</t>
+          <t>마법재료 ×5 + 영혼석 ×1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>마스터 노드</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>def_master</t>
+          <t>비료</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>불멸의 의지</t>
+          <t>20💎 / 50% 시간 단축</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>DEF +30 / HP +300</t>
+          <t>슬롯당 1회</t>
         </is>
       </c>
     </row>
@@ -18476,137 +18944,137 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>마스터 노드</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>util_master</t>
+          <t>game/skill_tree.js</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>운명의 인도자</t>
+          <t>특성 트리 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>EXP/GOLD +20% / 드롭 +10%</t>
+          <t>3브랜치 × 7노드</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>game/mail.js</t>
+          <t>레벨업 훅</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>우편함 모듈 생성 + 즉시 통합</t>
+          <t>awardPoints(target, 1) 자동 호출</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>시스템/선물 + 첨부 + 만료</t>
+          <t>별도 학습 불필요</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>메일</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>시스템 메일</t>
+          <t>off_master</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>이벤트 보상/공지</t>
+          <t>전쟁의 화신</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>14일 만료</t>
+          <t>ATK +30 / 크리 +5%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>메일</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>선물 메일</t>
+          <t>def_master</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>플레이어 간 / 일일 10회</t>
+          <t>불멸의 의지</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>7일 만료, 수수료 2%</t>
+          <t>DEF +30 / HP +300</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>발송 시 자원 차감</t>
+          <t>util_master</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>수신자 우편함 가득 → 거부</t>
+          <t>운명의 인도자</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>첨부 미수령 메일 삭제 거부</t>
+          <t>EXP/GOLD +20% / 드롭 +10%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -18616,105 +19084,105 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>game/codex.js</t>
+          <t>game/mail.js</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>도감 모듈 생성 + 즉시 통합</t>
+          <t>우편함 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>5카테고리 × 4마일스톤</t>
+          <t>시스템/선물 + 첨부 + 만료</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>시스템 메일</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>explore_count → zone 자동 등록</t>
+          <t>이벤트 보상/공지</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>별도 학습 불필요</t>
+          <t>14일 만료</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>fishing_cast 훅</t>
+          <t>선물 메일</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>어종 자동 등록</t>
+          <t>플레이어 간 / 일일 10회</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>v1.24와 자연 연동</t>
+          <t>7일 만료, 수수료 2%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>영구 스탯 보너스</t>
+          <t>발송 시 자원 차감</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 달성 시 누적</t>
+          <t>수신자 우편함 가득 → 거부</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>codexBonuses 객체</t>
+          <t>첨부 미수령 메일 삭제 거부</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -18724,179 +19192,179 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>game/dailyshop.js</t>
+          <t>game/codex.js</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>일일 상점 모듈 생성 + 즉시 통합</t>
+          <t>도감 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
+          <t>5카테고리 × 4마일스톤</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>결정적 랜덤</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>날짜 시드</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>모든 플레이어 동일 상품</t>
+          <t>explore_count → zone 자동 등록</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>seededRandom + Fisher-Yates</t>
+          <t>별도 학습 불필요</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>개인 갱신</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>30💎</t>
+          <t>fishing_cast 훅</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>개인 시드 생성</t>
+          <t>어종 자동 등록</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>구매 기록 초기화</t>
+          <t>v1.24와 자연 연동</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>auction → server.js</t>
+          <t>영구 스탯 보너스</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>6번째 (마지막) 모듈 통합</t>
+          <t>마일스톤 달성 시 누적</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>자동 정산 + 환불 + 양방향 지급</t>
+          <t>codexBonuses 객체</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>tickAuctions</t>
+          <t>game/dailyshop.js</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>10초마다 만료 정산</t>
+          <t>일일 상점 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>setInterval 통합</t>
+          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>결정적 랜덤</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>auction_create</t>
+          <t>날짜 시드</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>경매 등록 (등록 수수료 자동 차감)</t>
+          <t>모든 플레이어 동일 상품</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>3가지 기간</t>
+          <t>seededRandom + Fisher-Yates</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>개인 갱신</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>auction_bid</t>
+          <t>30💎</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>입찰 + 이전 입찰자 자동 환불</t>
+          <t>개인 시드 생성</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>스나이핑 방지 연장</t>
+          <t>구매 기록 초기화</t>
         </is>
       </c>
     </row>
@@ -18908,22 +19376,22 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>auction_my</t>
+          <t>auction → server.js</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>내 등록/입찰 내역 조회</t>
+          <t>6번째 (마지막) 모듈 통합</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>자동 정산 + 환불 + 양방향 지급</t>
         </is>
       </c>
     </row>
@@ -18935,130 +19403,130 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>신규 모듈 6/6</t>
+          <t>tickAuctions</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>100% 통합 완료</t>
+          <t>10초마다 만료 정산</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>lottery/fishing/event/season/boss_rush/auction</t>
+          <t>setInterval 통합</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>boss_rush → server.js</t>
+          <t>auction_create</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>5번째 모듈 통합</t>
+          <t>경매 등록 (등록 수수료 자동 차감)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>메모리 세션 기반</t>
+          <t>3가지 기간</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>bossRushSessions</t>
+          <t>auction_bid</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>진행 중 세션 저장</t>
+          <t>입찰 + 이전 입찰자 자동 환불</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>currentWave/시간 추적</t>
+          <t>스나이핑 방지 연장</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>bossRushRanking</t>
+          <t>auction_my</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>글로벌 랭킹 TOP 100</t>
+          <t>내 등록/입찰 내역 조회</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>웨이브 → 시간 정렬</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_enter</t>
+          <t>신규 모듈 6/6</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>무료/유료/다이아 입장</t>
+          <t>100% 통합 완료</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>동시 1개 세션 제한</t>
+          <t>lottery/fishing/event/season/boss_rush/auction</t>
         </is>
       </c>
     </row>
@@ -19070,22 +19538,22 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>boss_rush_advance</t>
+          <t>boss_rush → server.js</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>웨이브 클리어 보고</t>
+          <t>5번째 모듈 통합</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>시간 초과 검증</t>
+          <t>메모리 세션 기반</t>
         </is>
       </c>
     </row>
@@ -19097,83 +19565,83 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>풀클리어 보상</t>
+          <t>bossRushSessions</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 누적</t>
+          <t>진행 중 세션 저장</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>currentWave/시간 추적</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>season → server.js</t>
+          <t>bossRushRanking</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>4번째 모듈 통합</t>
+          <t>글로벌 랭킹 TOP 100</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>XP 자동 적립 + 보상 수령</t>
+          <t>웨이브 → 시간 정렬</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>boss_rush_enter</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
+          <t>무료/유료/다이아 입장</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>SEASON_XP_MAP 매핑</t>
+          <t>동시 1개 세션 제한</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -19183,39 +19651,39 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>season_status</t>
+          <t>boss_rush_advance</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>XP/티어/구매여부/수령내역 조회</t>
+          <t>웨이브 클리어 보고</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>15티어 전체</t>
+          <t>시간 초과 검증</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>season_buy_pass</t>
+          <t>풀클리어 보상</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 패스 구매 (1500💎)</t>
+          <t>20웨이브 누적</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -19232,56 +19700,56 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>season_claim</t>
+          <t>season → server.js</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>티어 보상 수령 (free/premium)</t>
+          <t>4번째 모듈 통합</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>자동 인벤토리 적용</t>
+          <t>XP 자동 적립 + 보상 수령</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>event → server.js</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>3번째 모듈 통합</t>
+          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>축제 시스템 활성화</t>
+          <t>SEASON_XP_MAP 매핑</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -19291,78 +19759,78 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>event_status</t>
+          <t>season_status</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>현재 활성 축제 조회</t>
+          <t>XP/티어/구매여부/수령내역 조회</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>이름/기간/버프/한정 보상</t>
+          <t>15티어 전체</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>/status JSON</t>
+          <t>season_buy_pass</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>festival 필드 추가</t>
+          <t>프리미엄 패스 구매 (1500💎)</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>대시보드 확인용</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>축제 인사</t>
+          <t>season_claim</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>30% 확률로 NPC가 축제 대사 출력</t>
+          <t>티어 보상 수령 (free/premium)</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>spring_blossom 등 5종</t>
+          <t>자동 인벤토리 적용</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -19372,24 +19840,24 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>fishing → server.js</t>
+          <t>event → server.js</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>3번째 모듈 통합</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>두 번째 모듈 통합</t>
+          <t>축제 시스템 활성화</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -19399,78 +19867,78 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>fishing_status</t>
+          <t>event_status</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>지역/낚싯대/미끼/시간대 조회</t>
+          <t>현재 활성 축제 조회</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>이름/기간/버프/한정 보상</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>fishing_cast</t>
+          <t>/status JSON</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
+          <t>festival 필드 추가</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>전설/신화 → 서버 알림</t>
+          <t>대시보드 확인용</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>fishing_buy_rod</t>
+          <t>축제 인사</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>낚싯대 구매 (골드/다이아)</t>
+          <t>30% 확률로 NPC가 축제 대사 출력</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>5등급 모두</t>
+          <t>spring_blossom 등 5종</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -19480,7 +19948,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>lottery → server.js</t>
+          <t>fishing → server.js</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -19490,29 +19958,29 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>첫 모듈 통합 마일스톤</t>
+          <t>두 번째 모듈 통합</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>lottery_status</t>
+          <t>fishing_status</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>상태/가격/상품 풀 조회</t>
+          <t>지역/낚싯대/미끼/시간대 조회</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -19524,432 +19992,432 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>lottery_free_spin</t>
+          <t>fishing_cast</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 스핀</t>
+          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>자정 초기화</t>
+          <t>전설/신화 → 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>lottery_paid_spin</t>
+          <t>fishing_buy_rod</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>유료 1회 / 10연속</t>
+          <t>낚싯대 구매 (골드/다이아)</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>count: 1 또는 10</t>
+          <t>5등급 모두</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>game/auction.js 신규</t>
+          <t>lottery → server.js</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>등록 2% + 낙찰 5%</t>
+          <t>첫 모듈 통합 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>활성 한도</t>
+          <t>lottery_status</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>플레이어당 10개</t>
+          <t>상태/가격/상품 풀 조회</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>자기 입찰 금지</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>game/fishing.js 신규</t>
+          <t>lottery_free_spin</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
+          <t>매일 무료 1회 스핀</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>신화 크라켄 = 20000G + 칭호</t>
+          <t>자정 초기화</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>전설의 비단잉어</t>
+          <t>lottery_paid_spin</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>드래곤 낚싯대 + 가중치 1</t>
+          <t>유료 1회 / 10연속</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>5000G + 평생 행운 +5%</t>
+          <t>count: 1 또는 10</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>game/boss_rush.js 신규</t>
+          <t>game/auction.js 신규</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 / HP ×1.35 스케일링</t>
+          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>최종 보상: 200💎 + 용재료 ×5</t>
+          <t>등록 2% + 낙찰 5%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>입장</t>
+          <t>활성 한도</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 3회 / 1000G / 30💎</t>
+          <t>플레이어당 10개</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>랭킹 시스템</t>
+          <t>자기 입찰 금지</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>챔피언 보상</t>
+          <t>game/fishing.js 신규</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
+          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>신화 크라켄 = 20000G + 칭호</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>game/lottery.js 신규</t>
+          <t>전설의 비단잉어</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>10종 보상 / 가중치 1000</t>
+          <t>드래곤 낚싯대 + 가중치 1</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 + 유료</t>
+          <t>5000G + 평생 행운 +5%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>영웅 장비 상자</t>
+          <t>game/boss_rush.js 신규</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>확률 0.2% (가장 희귀)</t>
+          <t>20웨이브 / HP ×1.35 스케일링</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>전설 보상</t>
+          <t>최종 보상: 200💎 + 용재료 ×5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>200 다이아</t>
+          <t>입장</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>확률 0.8%</t>
+          <t>매일 무료 3회 / 1000G / 30💎</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>랭킹 시스템</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>신년 축제</t>
+          <t>챔피언 보상</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>1/1 ~ 1/7</t>
+          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>골드 +50% / EXP +30%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>봄꽃 축제</t>
+          <t>game/lottery.js 신규</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>4/1 ~ 4/14</t>
+          <t>10종 보상 / 가중치 1000</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>HP재생 +30% / 드롭 +20%</t>
+          <t>매일 무료 1회 + 유료</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>한여름 밤의 축제</t>
+          <t>영웅 장비 상자</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>7/15 ~ 8/15</t>
+          <t>확률 0.2% (가장 희귀)</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>화염 +30% / PvP 보상 +50%</t>
+          <t>전설 보상</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>할로윈 축제</t>
+          <t>200 다이아</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>10/25 ~ 11/1</t>
+          <t>확률 0.8%</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>크리 +10% / 언데드 +50%</t>
+          <t>잭팟</t>
         </is>
       </c>
     </row>
@@ -19966,206 +20434,206 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>겨울 축제</t>
+          <t>신년 축제</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>12/20 ~ 12/31</t>
+          <t>1/1 ~ 1/7</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
+          <t>골드 +50% / EXP +30%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>game/season.js 신규</t>
+          <t>봄꽃 축제</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>15티어 / 30일 / 무료+프리미엄</t>
+          <t>4/1 ~ 4/14</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
+          <t>HP재생 +30% / 드롭 +20%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>XP 획득 7종</t>
+          <t>한여름 밤의 축제</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>퀘/보스/PvP/월드보스/던전/제작</t>
+          <t>7/15 ~ 8/15</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>일일 +200 ~ 월드보스 +500</t>
+          <t>화염 +30% / PvP 보상 +50%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 가격</t>
+          <t>할로윈 축제</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>1500 다이아</t>
+          <t>10/25 ~ 11/1</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>시즌 당 1회</t>
+          <t>크리 +10% / 언데드 +50%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>Lv.40 달성</t>
+          <t>겨울 축제</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>각성기 해금 마일스톤</t>
+          <t>12/20 ~ 12/31</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>150💎</t>
+          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Lv.50 달성</t>
+          <t>game/season.js 신규</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>환생 가능 마일스톤</t>
+          <t>15티어 / 30일 / 무료+프리미엄</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>250💎</t>
+          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>첫 환생</t>
+          <t>XP 획득 7종</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>prestige 1차</t>
+          <t>퀘/보스/PvP/월드보스/던전/제작</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>500💎</t>
+          <t>일일 +200 ~ 월드보스 +500</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>첫 월드 보스</t>
+          <t>프리미엄 가격</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 처치 보너스</t>
+          <t>1500 다이아</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>100💎</t>
+          <t>시즌 당 1회</t>
         </is>
       </c>
     </row>
@@ -20182,125 +20650,125 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>업적 50개</t>
+          <t>Lv.40 달성</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>업적 마일스톤</t>
+          <t>각성기 해금 마일스톤</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>200💎</t>
+          <t>150💎</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>불사조 스킨</t>
+          <t>Lv.50 달성</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>환생 가능 마일스톤</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>불사조 깃털 이펙트 (영구)</t>
+          <t>250💎</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>폭풍 스킨</t>
+          <t>첫 환생</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>prestige 1차</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>번개 오라 이펙트 (영구)</t>
+          <t>500💎</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>상점 (편의)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 자동물약</t>
+          <t>첫 월드 보스</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>500 다이아</t>
+          <t>월드 보스 처치 보너스</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>24시간 자동물약 무한</t>
+          <t>100💎</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>상점 (상자)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 보물 상자</t>
+          <t>업적 50개</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>300 다이아</t>
+          <t>업적 마일스톤</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>전설 장비 확정 + 다이아</t>
+          <t>200💎</t>
         </is>
       </c>
     </row>
@@ -20312,130 +20780,130 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>상점 (재료)</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>전설 재료 패키지</t>
+          <t>불사조 스킨</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>600 다이아</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
+          <t>불사조 깃털 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 분노</t>
+          <t>폭풍 스킨</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>크리티컬 +5%</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>60명 정원</t>
+          <t>번개 오라 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.7</t>
+          <t>상점 (편의)</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 신속</t>
+          <t>프리미엄 자동물약</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>이동속도 +10%</t>
+          <t>500 다이아</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>70명 정원</t>
+          <t>24시간 자동물약 무한</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.8</t>
+          <t>상점 (상자)</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 회복</t>
+          <t>프리미엄 보물 상자</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>HP 재생 +50%</t>
+          <t>300 다이아</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>80명 정원</t>
+          <t>전설 장비 확정 + 다이아</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.9</t>
+          <t>상점 (재료)</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 운명</t>
+          <t>전설 재료 패키지</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>회피 +5%</t>
+          <t>600 다이아</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>90명 정원</t>
+          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
         </is>
       </c>
     </row>
@@ -20447,211 +20915,211 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.10</t>
+          <t>혈맹 Lv.6</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 전설</t>
+          <t>혈맹의 분노</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>전 스탯 +5%</t>
+          <t>크리티컬 +5%</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>100명 정원 — 최종</t>
+          <t>60명 정원</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.7</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>점쟁이</t>
+          <t>혈맹의 신속</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
+          <t>이동속도 +10%</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>70명 정원</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.8</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>감정사</t>
+          <t>혈맹의 회복</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
+          <t>HP 재생 +50%</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>80명 정원</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.9</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>수집가</t>
+          <t>혈맹의 운명</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
+          <t>회피 +5%</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>90명 정원</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>각성기 (어쌔신)</t>
+          <t>혈맹 Lv.10</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>천 개의 칼날</t>
+          <t>혈맹의 전설</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
+          <t>전 스탯 +5%</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>100명 정원 — 최종</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>각성기 (워리어)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>대지 가르기</t>
+          <t>점쟁이</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
+          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>각성기 (나이트)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>불멸의 수호자</t>
+          <t>감정사</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>피해 90% 감소 / 도발 / 10초</t>
+          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>각성기 (메이지)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>시간 정지</t>
+          <t>수집가</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
+          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
@@ -20663,17 +21131,17 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>각성기 (클레릭)</t>
+          <t>각성기 (어쌔신)</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>신의 은총</t>
+          <t>천 개의 칼날</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>HP 100% 회복 / 전스탯 +50%</t>
+          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -20685,108 +21153,108 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (워리어)</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>폭풍 정복자</t>
+          <t>대지 가르기</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인 처치</t>
+          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>10,000G + 150다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (나이트)</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>연금술사</t>
+          <t>불멸의 수호자</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>엘릭서 10회 제작</t>
+          <t>피해 90% 감소 / 도발 / 10초</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>5,000G + 80다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (메이지)</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>그림자 정복자</t>
+          <t>시간 정지</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 클리어</t>
+          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>8,000G + 120다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (클레릭)</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>전설의 동반자</t>
+          <t>신의 은총</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>전설급 펫 진화</t>
+          <t>HP 100% 회복 / 전스탯 +50%</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>6,000G + 100다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
@@ -20803,206 +21271,206 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>이국의 상인</t>
+          <t>폭풍 정복자</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>사치품 교역 5회</t>
+          <t>폭풍의 거인 처치</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>4,000G + 60다이아</t>
+          <t>10,000G + 150다이아</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인</t>
+          <t>연금술사</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>HP 100,000 / ATK 140 / DEF 90</t>
+          <t>엘릭서 10회 제작</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>EXP 10000 + 6000G</t>
+          <t>5,000G + 80다이아</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>시간의 수호자</t>
+          <t>그림자 정복자</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>HP 70,000 / ATK 170 / DEF 60</t>
+          <t>그림자 미궁 클리어</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>EXP 9000 + 7000G</t>
+          <t>8,000G + 120다이아</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>교역품</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
+          <t>전설의 동반자</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종</t>
+          <t>전설급 펫 진화</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>기본가 600~900G</t>
+          <t>6,000G + 100다이아</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>타이탄의 엘릭서</t>
+          <t>이국의 상인</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>용재료×3 + 마법재료×10</t>
+          <t>사치품 교역 5회</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>ATK ×1.5 / 30분</t>
+          <t>4,000G + 60다이아</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>강철 엘릭서</t>
+          <t>폭풍의 거인</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>철광석×30 + 마법재료×10</t>
+          <t>HP 100,000 / ATK 140 / DEF 90</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>DEF ×1.5 / 30분</t>
+          <t>EXP 10000 + 6000G</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>질풍 엘릭서</t>
+          <t>시간의 수호자</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>약초×20 + 마법재료×8</t>
+          <t>HP 70,000 / ATK 170 / DEF 60</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>SPD ×1.4 / 20분</t>
+          <t>EXP 9000 + 7000G</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>교역품</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>지혜 엘릭서</t>
+          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>마법수정×5 + 영혼재료×5</t>
+          <t>이국의 사치품 3종</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>EXP ×2.5 / 15분</t>
+          <t>기본가 600~900G</t>
         </is>
       </c>
     </row>
@@ -21019,260 +21487,260 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>행운 엘릭서</t>
+          <t>타이탄의 엘릭서</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>보석×10 + 마법재료×5</t>
+          <t>용재료×3 + 마법재료×10</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>GOLD ×2.0 / 15분</t>
+          <t>ATK ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>불사조 (pet_phoenix)</t>
+          <t>강철 엘릭서</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>불꽃산 보스 50처치</t>
+          <t>철광석×30 + 마법재료×10</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>화염 DMG +20% (진화 +40%)</t>
+          <t>DEF ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>유니콘 (pet_unicorn)</t>
+          <t>질풍 엘릭서</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>다이아 800개</t>
+          <t>약초×20 + 마법재료×8</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>회피 +10% (진화 +20%)</t>
+          <t>SPD ×1.4 / 20분</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>페가수스 (mount_pegasus)</t>
+          <t>지혜 엘릭서</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>다이아 1200개</t>
+          <t>마법수정×5 + 영혼재료×5</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>이동속도 +85% / 비행</t>
+          <t>EXP ×2.5 / 15분</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁</t>
+          <t>행운 엘릭서</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Lv.38 / 8인 파티 / 7스테이지</t>
+          <t>보석×10 + 마법재료×5</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>22000G + 32000EXP</t>
+          <t>GOLD ×2.0 / 15분</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>드롭</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>드래곤 검/망토/투구/장갑</t>
+          <t>불사조 (pet_phoenix)</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 보스 드롭</t>
+          <t>불꽃산 보스 50처치</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>전설급</t>
+          <t>화염 DMG +20% (진화 +40%)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>공허의 방랑자</t>
+          <t>유니콘 (pet_unicorn)</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>몬스터 10,000 처치</t>
+          <t>다이아 800개</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>ATK +7%</t>
+          <t>회피 +10% (진화 +20%)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>불멸자</t>
+          <t>페가수스 (mount_pegasus)</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>환생 5회</t>
+          <t>다이아 1200개</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>EXP +25%</t>
+          <t>이동속도 +85% / 비행</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>천공의 군주</t>
+          <t>그림자 미궁</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 10회 처치</t>
+          <t>Lv.38 / 8인 파티 / 7스테이지</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>보스DMG +15%</t>
+          <t>22000G + 32000EXP</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>드롭</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>지역 시트 갱신</t>
+          <t>드래곤 검/망토/투구/장갑</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>25→51개 지역 반영</t>
+          <t>그림자 미궁 보스 드롭</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>전설급</t>
         </is>
       </c>
     </row>
@@ -21284,22 +21752,22 @@
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>칭호 시트 갱신</t>
+          <t>공허의 방랑자</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>7→16종 + 효과/색상 추가</t>
+          <t>몬스터 10,000 처치</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ATK +7%</t>
         </is>
       </c>
     </row>
@@ -21311,22 +21779,22 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>출석 캘린더 시트</t>
+          <t>불멸자</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (28일 사이클)</t>
+          <t>환생 5회</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EXP +25%</t>
         </is>
       </c>
     </row>
@@ -21338,22 +21806,22 @@
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>장비 세트 시트</t>
+          <t>천공의 군주</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (드래곤/영웅/태초)</t>
+          <t>월드 보스 10회 처치</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>보스DMG +15%</t>
         </is>
       </c>
     </row>
@@ -21370,12 +21838,12 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>장비 등급 시트</t>
+          <t>지역 시트 갱신</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+          <t>25→51개 지역 반영</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -21397,12 +21865,12 @@
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>디버프 시트</t>
+          <t>칭호 시트 갱신</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+          <t>7→16종 + 효과/색상 추가</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
@@ -21424,12 +21892,12 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>패치 노트 시트</t>
+          <t>출석 캘린더 시트</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (히스토리)</t>
+          <t>신규 추가 (28일 사이클)</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -21441,25 +21909,133 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>장비 세트 시트</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (드래곤/영웅/태초)</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>장비 등급 시트</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>디버프 시트</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>패치 노트 시트</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (히스토리)</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
           <t>v1.10</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr">
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>기획서</t>
         </is>
       </c>
-      <c r="C118" s="7" t="inlineStr">
+      <c r="C122" s="7" t="inlineStr">
         <is>
           <t>던전 시트</t>
         </is>
       </c>
-      <c r="D118" s="7" t="inlineStr">
+      <c r="D122" s="7" t="inlineStr">
         <is>
           <t>신규 추가 (7종 던전)</t>
         </is>
       </c>
-      <c r="E118" s="7" t="inlineStr">
+      <c r="E122" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -45,7 +45,7 @@
     <sheet name="월드 보스" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="연금술" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="패치 노트" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="v1.9 ~ v1.36" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="v1.9 ~ v1.37" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16598,7 +16598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16639,7 +16639,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -16649,19 +16649,19 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>신규 모듈</t>
+          <t>리팩토링</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>game/farm.js — 농장 시스템 (생성 + 통합 동시)</t>
+          <t>Phase 1: 순수 데이터 6종 추출 → game/data/world_data.js</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -16671,19 +16671,19 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>농장</t>
+          <t>리팩토링</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>7종 작물 (5분~4시간), AFK 진행, 4슬롯 기본 (12슬롯 확장)</t>
+          <t>server.js 9622 → 9517줄 (-105줄)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -16693,19 +16693,19 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>농장</t>
+          <t>리팩토링</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>비료 (20💎) 50% 시간 단축, 슬롯 확장 50💎</t>
+          <t>MONSTER_TIERS / KARMA / WORLD_BOSS_TYPES / DUNGEONS / ELEMENT_BONUS / ATTENDANCE_REWARDS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -16715,19 +16715,19 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>버그 수정</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>farm_status / plant / harvest / fertilize / expand</t>
+          <t>MONSTER_TIERS의 깨진 한글 (드래���→드래곤) 함께 수정</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -16742,14 +16742,14 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>game/skill_tree.js — 특성 트리 (생성 + 통합 동시)</t>
+          <t>game/farm.js — 농장 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -16759,19 +16759,19 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>특성 트리</t>
+          <t>농장</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>3브랜치 (공격/방어/유틸) × 7노드 = 21노드</t>
+          <t>7종 작물 (5분~4시간), AFK 진행, 4슬롯 기본 (12슬롯 확장)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -16781,19 +16781,19 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>특성 트리</t>
+          <t>농장</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>레벨업 시 1포인트 자동 지급, 100💎로 리셋</t>
+          <t>비료 (20💎) 50% 시간 단축, 슬롯 확장 50💎</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -16803,19 +16803,19 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>게이트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>5/10/15/20/25 포인트 투자 시 상위 노드 해금</t>
+          <t>farm_status / plant / harvest / fertilize / expand</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -16830,14 +16830,14 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>game/mail.js — 정식 우편함 시스템 (생성 + 통합 동시)</t>
+          <t>game/skill_tree.js — 특성 트리 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -16847,19 +16847,19 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>우편함</t>
+          <t>특성 트리</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>시스템/선물 메일 + 첨부(골드/다이아/아이템) + 만료/수령 관리</t>
+          <t>3브랜치 (공격/방어/유틸) × 7노드 = 21노드</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -16869,19 +16869,19 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>선물</t>
+          <t>특성 트리</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>일일 10회 / 골드 첨부 수수료 2% / 7일 만료</t>
+          <t>레벨업 시 1포인트 자동 지급, 100💎로 리셋</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -16891,19 +16891,19 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>게이트</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>mail_inbox/read/claim/delete/send_gift</t>
+          <t>5/10/15/20/25 포인트 투자 시 상위 노드 해금</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -16918,14 +16918,14 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>game/codex.js — 도감 시스템 (생성 + 통합 동시)</t>
+          <t>game/mail.js — 정식 우편함 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -16935,19 +16935,19 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>우편함</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>5개 카테고리 (몬스터/지역/장비/어종/펫) × 4단계 마일스톤</t>
+          <t>시스템/선물 메일 + 첨부(골드/다이아/아이템) + 만료/수령 관리</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -16957,19 +16957,19 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>선물</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 달성 시 영구 스탯 보너스 + 전 서버 알림</t>
+          <t>일일 10회 / 골드 첨부 수수료 2% / 7일 만료</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -16979,19 +16979,19 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>trackQuest(explore_count) → zone 자동 등록 / fishing_cast → fish 자동 등록</t>
+          <t>mail_inbox/read/claim/delete/send_gift</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -17006,14 +17006,14 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
+          <t>game/codex.js — 도감 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -17023,19 +17023,19 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>일일 상점</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
+          <t>5개 카테고리 (몬스터/지역/장비/어종/펫) × 4단계 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -17045,19 +17045,19 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>일일 상점</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
+          <t>마일스톤 달성 시 영구 스탯 보너스 + 전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -17067,19 +17067,19 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
+          <t>trackQuest(explore_count) → zone 자동 등록 / fishing_cast → fish 자동 등록</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -17089,19 +17089,19 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
+          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -17111,19 +17111,19 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
+          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -17133,19 +17133,19 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
+          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -17160,7 +17160,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>auction_list / create / bid / my</t>
+          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
         </is>
       </c>
     </row>
@@ -17177,19 +17177,19 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
+          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -17199,19 +17199,19 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
+          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -17221,19 +17221,19 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
+          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -17248,14 +17248,14 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_status / enter / advance / abandon</t>
+          <t>auction_list / create / bid / my</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -17265,19 +17265,19 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
+          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -17292,14 +17292,14 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
+          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -17309,19 +17309,19 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
+          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -17336,14 +17336,14 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>season_status / season_buy_pass / season_claim</t>
+          <t>boss_rush_status / enter / advance / abandon</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -17353,19 +17353,19 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
+          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -17380,14 +17380,14 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
+          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -17397,19 +17397,19 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>event_status 소켓 + /status 엔드포인트 노출</t>
+          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -17419,19 +17419,19 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
+          <t>season_status / season_buy_pass / season_claim</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -17441,19 +17441,19 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
+          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -17468,14 +17468,14 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
+          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -17485,19 +17485,19 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
+          <t>event_status 소켓 + /status 엔드포인트 노출</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -17507,19 +17507,19 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
+          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -17529,19 +17529,19 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
+          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -17556,14 +17556,14 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
+          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -17573,19 +17573,19 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
+          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -17595,19 +17595,19 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
+          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -17617,19 +17617,19 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
+          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -17639,19 +17639,19 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
+          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -17661,19 +17661,19 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>경매장 시트 신규 추가</t>
+          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -17683,19 +17683,19 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
+          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -17705,19 +17705,19 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
+          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -17727,19 +17727,19 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>낚시 시트 신규 추가</t>
+          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -17749,19 +17749,19 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
+          <t>경매장 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -17771,19 +17771,19 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
+          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -17793,19 +17793,19 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>보스 러시 시트 신규 추가</t>
+          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -17815,19 +17815,19 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
+          <t>낚시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -17837,19 +17837,19 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
+          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -17859,19 +17859,19 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛 시트 신규 추가</t>
+          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -17881,19 +17881,19 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
+          <t>보스 러시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -17903,19 +17903,19 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>모듈화</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
+          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -17925,19 +17925,19 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트 시트 신규 추가</t>
+          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -17947,19 +17947,19 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
+          <t>행운의 룰렛 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -17969,19 +17969,19 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
+          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -17991,19 +17991,19 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>모듈화</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스 시트 신규 추가</t>
+          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -18013,19 +18013,19 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
+          <t>축제 이벤트 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -18035,19 +18035,19 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아 시트 신규 추가</t>
+          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -18057,19 +18057,19 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
+          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -18084,14 +18084,14 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>상점 시트 갱신</t>
+          <t>시즌 패스 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -18101,19 +18101,19 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
+          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -18123,19 +18123,19 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>최대 인원 50→100명 (Lv.10 기준)</t>
+          <t>무료 다이아 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -18145,19 +18145,19 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>길드(혈맹) 시트 신규 추가</t>
+          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -18167,19 +18167,19 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
+          <t>상점 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -18189,19 +18189,19 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>대사 시스템</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
+          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -18211,19 +18211,19 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>NPC 시트 신규 추가 (11종)</t>
+          <t>최대 인원 50→100명 (Lv.10 기준)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -18233,19 +18233,19 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>각성기</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
+          <t>길드(혈맹) 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -18255,19 +18255,19 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
+          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -18277,19 +18277,19 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>대사 시스템</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
+          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -18304,14 +18304,14 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
+          <t>NPC 시트 신규 추가 (11종)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -18321,19 +18321,19 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>각성기</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
+          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -18343,19 +18343,19 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>교역</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
+          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -18365,19 +18365,19 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
+          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
@@ -18387,19 +18387,19 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
+          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -18409,19 +18409,19 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>연금술 시트 신규 추가</t>
+          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
@@ -18431,19 +18431,19 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>교역</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
+          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -18453,19 +18453,19 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (이동 +85%, 비행)</t>
+          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
@@ -18475,19 +18475,19 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
+          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -18502,14 +18502,14 @@
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
+          <t>연금술 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
@@ -18519,19 +18519,19 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
+          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -18541,107 +18541,107 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
+          <t>페가수스 (이동 +85%, 비행)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
+          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
+          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
+          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
+          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
@@ -18651,19 +18651,19 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>상태이상</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
+          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -18673,19 +18673,19 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
@@ -18695,19 +18695,19 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -18717,12 +18717,12 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>컨텐츠</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
         </is>
       </c>
     </row>
@@ -18739,32 +18739,120 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>상태이상</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>컨텐츠</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
           <t>v1.6 이전</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>기반</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t>마을/사냥/PvP/카르마/펫/탈것/제작/교역/길드/공성/투기장 등</t>
         </is>
@@ -18784,7 +18872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18831,81 +18919,81 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>리팩토링</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>game/farm.js</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>농장 모듈 생성 + 즉시 통합</t>
+          <t>game/data/world_data.js 추출</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>7작물 / AFK 진행</t>
+          <t>-105줄 (9622→9517)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>작물 (전설)</t>
+          <t>마스터 플랜</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>용 과일</t>
+          <t>5단계 분리</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>4시간 / 80💎</t>
+          <t>Phase 2: ZONES / 3: 장비 / 4: 퀘스트 / 5: 상점</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>용재료 ×1 + 영혼석 ×3 + 3000G</t>
+          <t>각 phase = 1 커밋</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>작물 (희귀)</t>
+          <t>버그 수정</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>달꽃</t>
+          <t>MONSTER_TIERS</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>2시간 / 30💎</t>
+          <t>깨진 한글 동시 수정</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>마법재료 ×5 + 영혼석 ×1</t>
+          <t>드래곤 / 고대 드래곤</t>
         </is>
       </c>
     </row>
@@ -18917,103 +19005,103 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>비료</t>
+          <t>game/farm.js</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>20💎 / 50% 시간 단축</t>
+          <t>농장 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>슬롯당 1회</t>
+          <t>7작물 / AFK 진행</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>작물 (전설)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>game/skill_tree.js</t>
+          <t>용 과일</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>특성 트리 모듈 생성 + 즉시 통합</t>
+          <t>4시간 / 80💎</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>3브랜치 × 7노드</t>
+          <t>용재료 ×1 + 영혼석 ×3 + 3000G</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>작물 (희귀)</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>레벨업 훅</t>
+          <t>달꽃</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>awardPoints(target, 1) 자동 호출</t>
+          <t>2시간 / 30💎</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>별도 학습 불필요</t>
+          <t>마법재료 ×5 + 영혼석 ×1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>마스터 노드</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>off_master</t>
+          <t>비료</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>전쟁의 화신</t>
+          <t>20💎 / 50% 시간 단축</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>ATK +30 / 크리 +5%</t>
+          <t>슬롯당 1회</t>
         </is>
       </c>
     </row>
@@ -19025,22 +19113,22 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>마스터 노드</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>def_master</t>
+          <t>game/skill_tree.js</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>불멸의 의지</t>
+          <t>특성 트리 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>DEF +30 / HP +300</t>
+          <t>3브랜치 × 7노드</t>
         </is>
       </c>
     </row>
@@ -19052,103 +19140,103 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>마스터 노드</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>util_master</t>
+          <t>레벨업 훅</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>운명의 인도자</t>
+          <t>awardPoints(target, 1) 자동 호출</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>EXP/GOLD +20% / 드롭 +10%</t>
+          <t>별도 학습 불필요</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>game/mail.js</t>
+          <t>off_master</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>우편함 모듈 생성 + 즉시 통합</t>
+          <t>전쟁의 화신</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>시스템/선물 + 첨부 + 만료</t>
+          <t>ATK +30 / 크리 +5%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>메일</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>시스템 메일</t>
+          <t>def_master</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>이벤트 보상/공지</t>
+          <t>불멸의 의지</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>14일 만료</t>
+          <t>DEF +30 / HP +300</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>메일</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>선물 메일</t>
+          <t>util_master</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>플레이어 간 / 일일 10회</t>
+          <t>운명의 인도자</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>7일 만료, 수수료 2%</t>
+          <t>EXP/GOLD +20% / 드롭 +10%</t>
         </is>
       </c>
     </row>
@@ -19160,103 +19248,103 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>발송 시 자원 차감</t>
+          <t>game/mail.js</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>수신자 우편함 가득 → 거부</t>
+          <t>우편함 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>첨부 미수령 메일 삭제 거부</t>
+          <t>시스템/선물 + 첨부 + 만료</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>game/codex.js</t>
+          <t>시스템 메일</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>도감 모듈 생성 + 즉시 통합</t>
+          <t>이벤트 보상/공지</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>5카테고리 × 4마일스톤</t>
+          <t>14일 만료</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>선물 메일</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>explore_count → zone 자동 등록</t>
+          <t>플레이어 간 / 일일 10회</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>별도 학습 불필요</t>
+          <t>7일 만료, 수수료 2%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>fishing_cast 훅</t>
+          <t>발송 시 자원 차감</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>어종 자동 등록</t>
+          <t>수신자 우편함 가득 → 거부</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>v1.24와 자연 연동</t>
+          <t>첨부 미수령 메일 삭제 거부</t>
         </is>
       </c>
     </row>
@@ -19268,184 +19356,184 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>영구 스탯 보너스</t>
+          <t>game/codex.js</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 달성 시 누적</t>
+          <t>도감 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>codexBonuses 객체</t>
+          <t>5카테고리 × 4마일스톤</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>game/dailyshop.js</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>일일 상점 모듈 생성 + 즉시 통합</t>
+          <t>explore_count → zone 자동 등록</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
+          <t>별도 학습 불필요</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>결정적 랜덤</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>날짜 시드</t>
+          <t>fishing_cast 훅</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>모든 플레이어 동일 상품</t>
+          <t>어종 자동 등록</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>seededRandom + Fisher-Yates</t>
+          <t>v1.24와 자연 연동</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>개인 갱신</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>30💎</t>
+          <t>영구 스탯 보너스</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>개인 시드 생성</t>
+          <t>마일스톤 달성 시 누적</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>구매 기록 초기화</t>
+          <t>codexBonuses 객체</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>auction → server.js</t>
+          <t>game/dailyshop.js</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>6번째 (마지막) 모듈 통합</t>
+          <t>일일 상점 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>자동 정산 + 환불 + 양방향 지급</t>
+          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>결정적 랜덤</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>tickAuctions</t>
+          <t>날짜 시드</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>10초마다 만료 정산</t>
+          <t>모든 플레이어 동일 상품</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>setInterval 통합</t>
+          <t>seededRandom + Fisher-Yates</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>개인 갱신</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>auction_create</t>
+          <t>30💎</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>경매 등록 (등록 수수료 자동 차감)</t>
+          <t>개인 시드 생성</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>3가지 기간</t>
+          <t>구매 기록 초기화</t>
         </is>
       </c>
     </row>
@@ -19457,22 +19545,22 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>auction_bid</t>
+          <t>auction → server.js</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>입찰 + 이전 입찰자 자동 환불</t>
+          <t>6번째 (마지막) 모듈 통합</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>스나이핑 방지 연장</t>
+          <t>자동 정산 + 환불 + 양방향 지급</t>
         </is>
       </c>
     </row>
@@ -19484,22 +19572,22 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>auction_my</t>
+          <t>tickAuctions</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>내 등록/입찰 내역 조회</t>
+          <t>10초마다 만료 정산</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>setInterval 통합</t>
         </is>
       </c>
     </row>
@@ -19511,103 +19599,103 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>신규 모듈 6/6</t>
+          <t>auction_create</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>100% 통합 완료</t>
+          <t>경매 등록 (등록 수수료 자동 차감)</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>lottery/fishing/event/season/boss_rush/auction</t>
+          <t>3가지 기간</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>boss_rush → server.js</t>
+          <t>auction_bid</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>5번째 모듈 통합</t>
+          <t>입찰 + 이전 입찰자 자동 환불</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>메모리 세션 기반</t>
+          <t>스나이핑 방지 연장</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>bossRushSessions</t>
+          <t>auction_my</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>진행 중 세션 저장</t>
+          <t>내 등록/입찰 내역 조회</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>currentWave/시간 추적</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>bossRushRanking</t>
+          <t>신규 모듈 6/6</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>글로벌 랭킹 TOP 100</t>
+          <t>100% 통합 완료</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>웨이브 → 시간 정렬</t>
+          <t>lottery/fishing/event/season/boss_rush/auction</t>
         </is>
       </c>
     </row>
@@ -19619,22 +19707,22 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_enter</t>
+          <t>boss_rush → server.js</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>무료/유료/다이아 입장</t>
+          <t>5번째 모듈 통합</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>동시 1개 세션 제한</t>
+          <t>메모리 세션 기반</t>
         </is>
       </c>
     </row>
@@ -19646,22 +19734,22 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>boss_rush_advance</t>
+          <t>bossRushSessions</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>웨이브 클리어 보고</t>
+          <t>진행 중 세션 저장</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>시간 초과 검증</t>
+          <t>currentWave/시간 추적</t>
         </is>
       </c>
     </row>
@@ -19673,103 +19761,103 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>풀클리어 보상</t>
+          <t>bossRushRanking</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 누적</t>
+          <t>글로벌 랭킹 TOP 100</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>웨이브 → 시간 정렬</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>season → server.js</t>
+          <t>boss_rush_enter</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>4번째 모듈 통합</t>
+          <t>무료/유료/다이아 입장</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>XP 자동 적립 + 보상 수령</t>
+          <t>동시 1개 세션 제한</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>boss_rush_advance</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
+          <t>웨이브 클리어 보고</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>SEASON_XP_MAP 매핑</t>
+          <t>시간 초과 검증</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>season_status</t>
+          <t>풀클리어 보상</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>XP/티어/구매여부/수령내역 조회</t>
+          <t>20웨이브 누적</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>15티어 전체</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
@@ -19781,22 +19869,22 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>season_buy_pass</t>
+          <t>season → server.js</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 패스 구매 (1500💎)</t>
+          <t>4번째 모듈 통합</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>XP 자동 적립 + 보상 수령</t>
         </is>
       </c>
     </row>
@@ -19808,56 +19896,56 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>season_claim</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>티어 보상 수령 (free/premium)</t>
+          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>자동 인벤토리 적용</t>
+          <t>SEASON_XP_MAP 매핑</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>event → server.js</t>
+          <t>season_status</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>3번째 모듈 통합</t>
+          <t>XP/티어/구매여부/수령내역 조회</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>축제 시스템 활성화</t>
+          <t>15티어 전체</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -19867,44 +19955,44 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>event_status</t>
+          <t>season_buy_pass</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>현재 활성 축제 조회</t>
+          <t>프리미엄 패스 구매 (1500💎)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>이름/기간/버프/한정 보상</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>/status JSON</t>
+          <t>season_claim</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>festival 필드 추가</t>
+          <t>티어 보상 수령 (free/premium)</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>대시보드 확인용</t>
+          <t>자동 인벤토리 적용</t>
         </is>
       </c>
     </row>
@@ -19916,103 +20004,103 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>축제 인사</t>
+          <t>event → server.js</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>30% 확률로 NPC가 축제 대사 출력</t>
+          <t>3번째 모듈 통합</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>spring_blossom 등 5종</t>
+          <t>축제 시스템 활성화</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>fishing → server.js</t>
+          <t>event_status</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>현재 활성 축제 조회</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>두 번째 모듈 통합</t>
+          <t>이름/기간/버프/한정 보상</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>fishing_status</t>
+          <t>/status JSON</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>지역/낚싯대/미끼/시간대 조회</t>
+          <t>festival 필드 추가</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>대시보드 확인용</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>fishing_cast</t>
+          <t>축제 인사</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
+          <t>30% 확률로 NPC가 축제 대사 출력</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>전설/신화 → 서버 알림</t>
+          <t>spring_blossom 등 5종</t>
         </is>
       </c>
     </row>
@@ -20024,103 +20112,103 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>fishing_buy_rod</t>
+          <t>fishing → server.js</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>낚싯대 구매 (골드/다이아)</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>5등급 모두</t>
+          <t>두 번째 모듈 통합</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>lottery → server.js</t>
+          <t>fishing_status</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>지역/낚싯대/미끼/시간대 조회</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>첫 모듈 통합 마일스톤</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>lottery_status</t>
+          <t>fishing_cast</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>상태/가격/상품 풀 조회</t>
+          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>전설/신화 → 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>lottery_free_spin</t>
+          <t>fishing_buy_rod</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 스핀</t>
+          <t>낚싯대 구매 (골드/다이아)</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>자정 초기화</t>
+          <t>5등급 모두</t>
         </is>
       </c>
     </row>
@@ -20132,373 +20220,373 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>lottery_paid_spin</t>
+          <t>lottery → server.js</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>유료 1회 / 10연속</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>count: 1 또는 10</t>
+          <t>첫 모듈 통합 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>game/auction.js 신규</t>
+          <t>lottery_status</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
+          <t>상태/가격/상품 풀 조회</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>등록 2% + 낙찰 5%</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>활성 한도</t>
+          <t>lottery_free_spin</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>플레이어당 10개</t>
+          <t>매일 무료 1회 스핀</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>자기 입찰 금지</t>
+          <t>자정 초기화</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>game/fishing.js 신규</t>
+          <t>lottery_paid_spin</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
+          <t>유료 1회 / 10연속</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>신화 크라켄 = 20000G + 칭호</t>
+          <t>count: 1 또는 10</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>전설의 비단잉어</t>
+          <t>game/auction.js 신규</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>드래곤 낚싯대 + 가중치 1</t>
+          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>5000G + 평생 행운 +5%</t>
+          <t>등록 2% + 낙찰 5%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>game/boss_rush.js 신규</t>
+          <t>활성 한도</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 / HP ×1.35 스케일링</t>
+          <t>플레이어당 10개</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>최종 보상: 200💎 + 용재료 ×5</t>
+          <t>자기 입찰 금지</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>입장</t>
+          <t>game/fishing.js 신규</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 3회 / 1000G / 30💎</t>
+          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>랭킹 시스템</t>
+          <t>신화 크라켄 = 20000G + 칭호</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>챔피언 보상</t>
+          <t>전설의 비단잉어</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
+          <t>드래곤 낚싯대 + 가중치 1</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5000G + 평생 행운 +5%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>game/lottery.js 신규</t>
+          <t>game/boss_rush.js 신규</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>10종 보상 / 가중치 1000</t>
+          <t>20웨이브 / HP ×1.35 스케일링</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 + 유료</t>
+          <t>최종 보상: 200💎 + 용재료 ×5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>영웅 장비 상자</t>
+          <t>입장</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>확률 0.2% (가장 희귀)</t>
+          <t>매일 무료 3회 / 1000G / 30💎</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>전설 보상</t>
+          <t>랭킹 시스템</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>200 다이아</t>
+          <t>챔피언 보상</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>확률 0.8%</t>
+          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>신년 축제</t>
+          <t>game/lottery.js 신규</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>1/1 ~ 1/7</t>
+          <t>10종 보상 / 가중치 1000</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>골드 +50% / EXP +30%</t>
+          <t>매일 무료 1회 + 유료</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>봄꽃 축제</t>
+          <t>영웅 장비 상자</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>4/1 ~ 4/14</t>
+          <t>확률 0.2% (가장 희귀)</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>HP재생 +30% / 드롭 +20%</t>
+          <t>전설 보상</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>한여름 밤의 축제</t>
+          <t>200 다이아</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>7/15 ~ 8/15</t>
+          <t>확률 0.8%</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>화염 +30% / PvP 보상 +50%</t>
+          <t>잭팟</t>
         </is>
       </c>
     </row>
@@ -20515,17 +20603,17 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>할로윈 축제</t>
+          <t>신년 축제</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>10/25 ~ 11/1</t>
+          <t>1/1 ~ 1/7</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>크리 +10% / 언데드 +50%</t>
+          <t>골드 +50% / EXP +30%</t>
         </is>
       </c>
     </row>
@@ -20542,179 +20630,179 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>겨울 축제</t>
+          <t>봄꽃 축제</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>12/20 ~ 12/31</t>
+          <t>4/1 ~ 4/14</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
+          <t>HP재생 +30% / 드롭 +20%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>game/season.js 신규</t>
+          <t>한여름 밤의 축제</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>15티어 / 30일 / 무료+프리미엄</t>
+          <t>7/15 ~ 8/15</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
+          <t>화염 +30% / PvP 보상 +50%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>XP 획득 7종</t>
+          <t>할로윈 축제</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>퀘/보스/PvP/월드보스/던전/제작</t>
+          <t>10/25 ~ 11/1</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>일일 +200 ~ 월드보스 +500</t>
+          <t>크리 +10% / 언데드 +50%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 가격</t>
+          <t>겨울 축제</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>1500 다이아</t>
+          <t>12/20 ~ 12/31</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>시즌 당 1회</t>
+          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Lv.40 달성</t>
+          <t>game/season.js 신규</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>각성기 해금 마일스톤</t>
+          <t>15티어 / 30일 / 무료+프리미엄</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>150💎</t>
+          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Lv.50 달성</t>
+          <t>XP 획득 7종</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>환생 가능 마일스톤</t>
+          <t>퀘/보스/PvP/월드보스/던전/제작</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>250💎</t>
+          <t>일일 +200 ~ 월드보스 +500</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>첫 환생</t>
+          <t>프리미엄 가격</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>prestige 1차</t>
+          <t>1500 다이아</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>500💎</t>
+          <t>시즌 당 1회</t>
         </is>
       </c>
     </row>
@@ -20731,17 +20819,17 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>첫 월드 보스</t>
+          <t>Lv.40 달성</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 처치 보너스</t>
+          <t>각성기 해금 마일스톤</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>100💎</t>
+          <t>150💎</t>
         </is>
       </c>
     </row>
@@ -20758,98 +20846,98 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>업적 50개</t>
+          <t>Lv.50 달성</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>업적 마일스톤</t>
+          <t>환생 가능 마일스톤</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>200💎</t>
+          <t>250💎</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>불사조 스킨</t>
+          <t>첫 환생</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>prestige 1차</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>불사조 깃털 이펙트 (영구)</t>
+          <t>500💎</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>폭풍 스킨</t>
+          <t>첫 월드 보스</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>월드 보스 처치 보너스</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>번개 오라 이펙트 (영구)</t>
+          <t>100💎</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>상점 (편의)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 자동물약</t>
+          <t>업적 50개</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>500 다이아</t>
+          <t>업적 마일스톤</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>24시간 자동물약 무한</t>
+          <t>200💎</t>
         </is>
       </c>
     </row>
@@ -20861,22 +20949,22 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>상점 (상자)</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 보물 상자</t>
+          <t>불사조 스킨</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>300 다이아</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>전설 장비 확정 + 다이아</t>
+          <t>불사조 깃털 이펙트 (영구)</t>
         </is>
       </c>
     </row>
@@ -20888,103 +20976,103 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>상점 (재료)</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>전설 재료 패키지</t>
+          <t>폭풍 스킨</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>600 다이아</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
+          <t>번개 오라 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6</t>
+          <t>상점 (편의)</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 분노</t>
+          <t>프리미엄 자동물약</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>크리티컬 +5%</t>
+          <t>500 다이아</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>60명 정원</t>
+          <t>24시간 자동물약 무한</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.7</t>
+          <t>상점 (상자)</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 신속</t>
+          <t>프리미엄 보물 상자</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>이동속도 +10%</t>
+          <t>300 다이아</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>70명 정원</t>
+          <t>전설 장비 확정 + 다이아</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.8</t>
+          <t>상점 (재료)</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 회복</t>
+          <t>전설 재료 패키지</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>HP 재생 +50%</t>
+          <t>600 다이아</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>80명 정원</t>
+          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
         </is>
       </c>
     </row>
@@ -20996,22 +21084,22 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.9</t>
+          <t>혈맹 Lv.6</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 운명</t>
+          <t>혈맹의 분노</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>회피 +5%</t>
+          <t>크리티컬 +5%</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>90명 정원</t>
+          <t>60명 정원</t>
         </is>
       </c>
     </row>
@@ -21023,184 +21111,184 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.10</t>
+          <t>혈맹 Lv.7</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 전설</t>
+          <t>혈맹의 신속</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>전 스탯 +5%</t>
+          <t>이동속도 +10%</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>100명 정원 — 최종</t>
+          <t>70명 정원</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.8</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>점쟁이</t>
+          <t>혈맹의 회복</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
+          <t>HP 재생 +50%</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>80명 정원</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.9</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>감정사</t>
+          <t>혈맹의 운명</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
+          <t>회피 +5%</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>90명 정원</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.10</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>수집가</t>
+          <t>혈맹의 전설</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
+          <t>전 스탯 +5%</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>100명 정원 — 최종</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>각성기 (어쌔신)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>천 개의 칼날</t>
+          <t>점쟁이</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
+          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>각성기 (워리어)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>대지 가르기</t>
+          <t>감정사</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
+          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>각성기 (나이트)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>불멸의 수호자</t>
+          <t>수집가</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>피해 90% 감소 / 도발 / 10초</t>
+          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
@@ -21212,17 +21300,17 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>각성기 (메이지)</t>
+          <t>각성기 (어쌔신)</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>시간 정지</t>
+          <t>천 개의 칼날</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
+          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
@@ -21239,17 +21327,17 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>각성기 (클레릭)</t>
+          <t>각성기 (워리어)</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>신의 은총</t>
+          <t>대지 가르기</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>HP 100% 회복 / 전스탯 +50%</t>
+          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -21261,81 +21349,81 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (나이트)</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>폭풍 정복자</t>
+          <t>불멸의 수호자</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인 처치</t>
+          <t>피해 90% 감소 / 도발 / 10초</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>10,000G + 150다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (메이지)</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>연금술사</t>
+          <t>시간 정지</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>엘릭서 10회 제작</t>
+          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>5,000G + 80다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (클레릭)</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>그림자 정복자</t>
+          <t>신의 은총</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 클리어</t>
+          <t>HP 100% 회복 / 전스탯 +50%</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>8,000G + 120다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
@@ -21352,17 +21440,17 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>전설의 동반자</t>
+          <t>폭풍 정복자</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>전설급 펫 진화</t>
+          <t>폭풍의 거인 처치</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>6,000G + 100다이아</t>
+          <t>10,000G + 150다이아</t>
         </is>
       </c>
     </row>
@@ -21379,179 +21467,179 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>이국의 상인</t>
+          <t>연금술사</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>사치품 교역 5회</t>
+          <t>엘릭서 10회 제작</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>4,000G + 60다이아</t>
+          <t>5,000G + 80다이아</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인</t>
+          <t>그림자 정복자</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>HP 100,000 / ATK 140 / DEF 90</t>
+          <t>그림자 미궁 클리어</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>EXP 10000 + 6000G</t>
+          <t>8,000G + 120다이아</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>시간의 수호자</t>
+          <t>전설의 동반자</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>HP 70,000 / ATK 170 / DEF 60</t>
+          <t>전설급 펫 진화</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>EXP 9000 + 7000G</t>
+          <t>6,000G + 100다이아</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>교역품</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
+          <t>이국의 상인</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종</t>
+          <t>사치품 교역 5회</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>기본가 600~900G</t>
+          <t>4,000G + 60다이아</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>타이탄의 엘릭서</t>
+          <t>폭풍의 거인</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>용재료×3 + 마법재료×10</t>
+          <t>HP 100,000 / ATK 140 / DEF 90</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>ATK ×1.5 / 30분</t>
+          <t>EXP 10000 + 6000G</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>강철 엘릭서</t>
+          <t>시간의 수호자</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>철광석×30 + 마법재료×10</t>
+          <t>HP 70,000 / ATK 170 / DEF 60</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>DEF ×1.5 / 30분</t>
+          <t>EXP 9000 + 7000G</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>교역품</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>질풍 엘릭서</t>
+          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>약초×20 + 마법재료×8</t>
+          <t>이국의 사치품 3종</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>SPD ×1.4 / 20분</t>
+          <t>기본가 600~900G</t>
         </is>
       </c>
     </row>
@@ -21568,17 +21656,17 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>지혜 엘릭서</t>
+          <t>타이탄의 엘릭서</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>마법수정×5 + 영혼재료×5</t>
+          <t>용재료×3 + 마법재료×10</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>EXP ×2.5 / 15분</t>
+          <t>ATK ×1.5 / 30분</t>
         </is>
       </c>
     </row>
@@ -21595,233 +21683,233 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>행운 엘릭서</t>
+          <t>강철 엘릭서</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>보석×10 + 마법재료×5</t>
+          <t>철광석×30 + 마법재료×10</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>GOLD ×2.0 / 15분</t>
+          <t>DEF ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>불사조 (pet_phoenix)</t>
+          <t>질풍 엘릭서</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>불꽃산 보스 50처치</t>
+          <t>약초×20 + 마법재료×8</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>화염 DMG +20% (진화 +40%)</t>
+          <t>SPD ×1.4 / 20분</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>유니콘 (pet_unicorn)</t>
+          <t>지혜 엘릭서</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>다이아 800개</t>
+          <t>마법수정×5 + 영혼재료×5</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>회피 +10% (진화 +20%)</t>
+          <t>EXP ×2.5 / 15분</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>페가수스 (mount_pegasus)</t>
+          <t>행운 엘릭서</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>다이아 1200개</t>
+          <t>보석×10 + 마법재료×5</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>이동속도 +85% / 비행</t>
+          <t>GOLD ×2.0 / 15분</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁</t>
+          <t>불사조 (pet_phoenix)</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>Lv.38 / 8인 파티 / 7스테이지</t>
+          <t>불꽃산 보스 50처치</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>22000G + 32000EXP</t>
+          <t>화염 DMG +20% (진화 +40%)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>드롭</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>드래곤 검/망토/투구/장갑</t>
+          <t>유니콘 (pet_unicorn)</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 보스 드롭</t>
+          <t>다이아 800개</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>전설급</t>
+          <t>회피 +10% (진화 +20%)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>공허의 방랑자</t>
+          <t>페가수스 (mount_pegasus)</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>몬스터 10,000 처치</t>
+          <t>다이아 1200개</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>ATK +7%</t>
+          <t>이동속도 +85% / 비행</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>불멸자</t>
+          <t>그림자 미궁</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>환생 5회</t>
+          <t>Lv.38 / 8인 파티 / 7스테이지</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>EXP +25%</t>
+          <t>22000G + 32000EXP</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>드롭</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>천공의 군주</t>
+          <t>드래곤 검/망토/투구/장갑</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 10회 처치</t>
+          <t>그림자 미궁 보스 드롭</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>보스DMG +15%</t>
+          <t>전설급</t>
         </is>
       </c>
     </row>
@@ -21833,22 +21921,22 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>지역 시트 갱신</t>
+          <t>공허의 방랑자</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>25→51개 지역 반영</t>
+          <t>몬스터 10,000 처치</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ATK +7%</t>
         </is>
       </c>
     </row>
@@ -21860,22 +21948,22 @@
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>칭호 시트 갱신</t>
+          <t>불멸자</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>7→16종 + 효과/색상 추가</t>
+          <t>환생 5회</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EXP +25%</t>
         </is>
       </c>
     </row>
@@ -21887,22 +21975,22 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>출석 캘린더 시트</t>
+          <t>천공의 군주</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (28일 사이클)</t>
+          <t>월드 보스 10회 처치</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>보스DMG +15%</t>
         </is>
       </c>
     </row>
@@ -21919,12 +22007,12 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>장비 세트 시트</t>
+          <t>지역 시트 갱신</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (드래곤/영웅/태초)</t>
+          <t>25→51개 지역 반영</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
@@ -21946,12 +22034,12 @@
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>장비 등급 시트</t>
+          <t>칭호 시트 갱신</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+          <t>7→16종 + 효과/색상 추가</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -21973,12 +22061,12 @@
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>디버프 시트</t>
+          <t>출석 캘린더 시트</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+          <t>신규 추가 (28일 사이클)</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
@@ -22000,12 +22088,12 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>패치 노트 시트</t>
+          <t>장비 세트 시트</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (히스토리)</t>
+          <t>신규 추가 (드래곤/영웅/태초)</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -22017,25 +22105,106 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>장비 등급 시트</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>디버프 시트</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>패치 노트 시트</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (히스토리)</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
           <t>v1.10</t>
         </is>
       </c>
-      <c r="B122" s="7" t="inlineStr">
+      <c r="B125" s="8" t="inlineStr">
         <is>
           <t>기획서</t>
         </is>
       </c>
-      <c r="C122" s="7" t="inlineStr">
+      <c r="C125" s="8" t="inlineStr">
         <is>
           <t>던전 시트</t>
         </is>
       </c>
-      <c r="D122" s="7" t="inlineStr">
+      <c r="D125" s="8" t="inlineStr">
         <is>
           <t>신규 추가 (7종 던전)</t>
         </is>
       </c>
-      <c r="E122" s="7" t="inlineStr">
+      <c r="E125" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -45,7 +45,7 @@
     <sheet name="월드 보스" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="연금술" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="패치 노트" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="v1.9 ~ v1.37" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="v1.9 ~ v1.38" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16598,7 +16598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16639,7 +16639,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -16654,14 +16654,14 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Phase 1: 순수 데이터 6종 추출 → game/data/world_data.js</t>
+          <t>Phase 2: 지역 데이터 8종 추출 → game/data/zones.js (459줄)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -16676,14 +16676,14 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>server.js 9622 → 9517줄 (-105줄)</t>
+          <t>server.js 9517 → 9103줄 (-414줄)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>MONSTER_TIERS / KARMA / WORLD_BOSS_TYPES / DUNGEONS / ELEMENT_BONUS / ATTENDANCE_REWARDS</t>
+          <t>ZONES(53)/ZONE_AMBIENCE(52)/MONSTER_LORE(79)/ZONE_CONNECTIONS(50)/TERRAIN_BARRIERS/ROADS/ZONE_MONSTERS/ZONE_MONSTER_NAMES</t>
         </is>
       </c>
     </row>
@@ -16715,19 +16715,19 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>버그 수정</t>
+          <t>리팩토링</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>MONSTER_TIERS의 깨진 한글 (드래���→드래곤) 함께 수정</t>
+          <t>Phase 1: 순수 데이터 6종 추출 → game/data/world_data.js</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -16737,19 +16737,19 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>신규 모듈</t>
+          <t>리팩토링</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>game/farm.js — 농장 시스템 (생성 + 통합 동시)</t>
+          <t>server.js 9622 → 9517줄 (-105줄)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -16759,19 +16759,19 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>농장</t>
+          <t>리팩토링</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>7종 작물 (5분~4시간), AFK 진행, 4슬롯 기본 (12슬롯 확장)</t>
+          <t>MONSTER_TIERS / KARMA / WORLD_BOSS_TYPES / DUNGEONS / ELEMENT_BONUS / ATTENDANCE_REWARDS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -16781,12 +16781,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>농장</t>
+          <t>버그 수정</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>비료 (20💎) 50% 시간 단축, 슬롯 확장 50💎</t>
+          <t>MONSTER_TIERS의 깨진 한글 (드래���→드래곤) 함께 수정</t>
         </is>
       </c>
     </row>
@@ -16803,19 +16803,19 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>farm_status / plant / harvest / fertilize / expand</t>
+          <t>game/farm.js — 농장 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -16825,19 +16825,19 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>신규 모듈</t>
+          <t>농장</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>game/skill_tree.js — 특성 트리 (생성 + 통합 동시)</t>
+          <t>7종 작물 (5분~4시간), AFK 진행, 4슬롯 기본 (12슬롯 확장)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -16847,19 +16847,19 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>특성 트리</t>
+          <t>농장</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>3브랜치 (공격/방어/유틸) × 7노드 = 21노드</t>
+          <t>비료 (20💎) 50% 시간 단축, 슬롯 확장 50💎</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -16869,12 +16869,12 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>특성 트리</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>레벨업 시 1포인트 자동 지급, 100💎로 리셋</t>
+          <t>farm_status / plant / harvest / fertilize / expand</t>
         </is>
       </c>
     </row>
@@ -16891,19 +16891,19 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>게이트</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>5/10/15/20/25 포인트 투자 시 상위 노드 해금</t>
+          <t>game/skill_tree.js — 특성 트리 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -16913,19 +16913,19 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>신규 모듈</t>
+          <t>특성 트리</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>game/mail.js — 정식 우편함 시스템 (생성 + 통합 동시)</t>
+          <t>3브랜치 (공격/방어/유틸) × 7노드 = 21노드</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -16935,19 +16935,19 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>우편함</t>
+          <t>특성 트리</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>시스템/선물 메일 + 첨부(골드/다이아/아이템) + 만료/수령 관리</t>
+          <t>레벨업 시 1포인트 자동 지급, 100💎로 리셋</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -16957,12 +16957,12 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>선물</t>
+          <t>게이트</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>일일 10회 / 골드 첨부 수수료 2% / 7일 만료</t>
+          <t>5/10/15/20/25 포인트 투자 시 상위 노드 해금</t>
         </is>
       </c>
     </row>
@@ -16979,19 +16979,19 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>mail_inbox/read/claim/delete/send_gift</t>
+          <t>game/mail.js — 정식 우편함 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -17001,19 +17001,19 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>신규 모듈</t>
+          <t>우편함</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>game/codex.js — 도감 시스템 (생성 + 통합 동시)</t>
+          <t>시스템/선물 메일 + 첨부(골드/다이아/아이템) + 만료/수령 관리</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -17023,19 +17023,19 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>선물</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>5개 카테고리 (몬스터/지역/장비/어종/펫) × 4단계 마일스톤</t>
+          <t>일일 10회 / 골드 첨부 수수료 2% / 7일 만료</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -17045,12 +17045,12 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 달성 시 영구 스탯 보너스 + 전 서버 알림</t>
+          <t>mail_inbox/read/claim/delete/send_gift</t>
         </is>
       </c>
     </row>
@@ -17067,19 +17067,19 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>trackQuest(explore_count) → zone 자동 등록 / fishing_cast → fish 자동 등록</t>
+          <t>game/codex.js — 도감 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -17089,19 +17089,19 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>신규 모듈</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
+          <t>5개 카테고리 (몬스터/지역/장비/어종/펫) × 4단계 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -17111,19 +17111,19 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>일일 상점</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
+          <t>마일스톤 달성 시 영구 스탯 보너스 + 전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -17133,12 +17133,12 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>일일 상점</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
+          <t>trackQuest(explore_count) → zone 자동 등록 / fishing_cast → fish 자동 등록</t>
         </is>
       </c>
     </row>
@@ -17155,19 +17155,19 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
+          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -17177,19 +17177,19 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
+          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -17199,19 +17199,19 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
+          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
+          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
         </is>
       </c>
     </row>
@@ -17243,12 +17243,12 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>auction_list / create / bid / my</t>
+          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
         </is>
       </c>
     </row>
@@ -17265,19 +17265,19 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
+          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -17287,19 +17287,19 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
+          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -17309,19 +17309,19 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
+          <t>auction_list / create / bid / my</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -17331,12 +17331,12 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_status / enter / advance / abandon</t>
+          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
         </is>
       </c>
     </row>
@@ -17353,19 +17353,19 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
+          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -17375,19 +17375,19 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
+          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -17397,19 +17397,19 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
+          <t>boss_rush_status / enter / advance / abandon</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -17419,12 +17419,12 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>season_status / season_buy_pass / season_claim</t>
+          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
         </is>
       </c>
     </row>
@@ -17441,19 +17441,19 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
+          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -17463,19 +17463,19 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
+          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -17485,19 +17485,19 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>event_status 소켓 + /status 엔드포인트 노출</t>
+          <t>season_status / season_buy_pass / season_claim</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -17507,12 +17507,12 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
+          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
         </is>
       </c>
     </row>
@@ -17529,19 +17529,19 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
+          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -17551,19 +17551,19 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
+          <t>event_status 소켓 + /status 엔드포인트 노출</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -17573,19 +17573,19 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
+          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -17595,12 +17595,12 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
+          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
         </is>
       </c>
     </row>
@@ -17617,19 +17617,19 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
+          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -17639,19 +17639,19 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
+          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -17661,19 +17661,19 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
+          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -17683,19 +17683,19 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
+          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -17705,19 +17705,19 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
+          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -17727,19 +17727,19 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
+          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -17749,19 +17749,19 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>경매장 시트 신규 추가</t>
+          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -17771,19 +17771,19 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
+          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -17793,19 +17793,19 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
+          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -17820,14 +17820,14 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>낚시 시트 신규 추가</t>
+          <t>경매장 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -17837,19 +17837,19 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
+          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -17859,19 +17859,19 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
+          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -17886,14 +17886,14 @@
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>보스 러시 시트 신규 추가</t>
+          <t>낚시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -17903,19 +17903,19 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
+          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -17925,19 +17925,19 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
+          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -17952,14 +17952,14 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛 시트 신규 추가</t>
+          <t>보스 러시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -17969,19 +17969,19 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
+          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -17991,19 +17991,19 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>모듈화</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
+          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -18018,14 +18018,14 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트 시트 신규 추가</t>
+          <t>행운의 룰렛 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -18035,19 +18035,19 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
+          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -18057,19 +18057,19 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>모듈화</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
+          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -18084,14 +18084,14 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스 시트 신규 추가</t>
+          <t>축제 이벤트 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -18101,19 +18101,19 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
+          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -18123,19 +18123,19 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아 시트 신규 추가</t>
+          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -18145,19 +18145,19 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
+          <t>시즌 패스 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -18167,19 +18167,19 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>상점 시트 갱신</t>
+          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -18189,19 +18189,19 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
+          <t>무료 다이아 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -18211,19 +18211,19 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>최대 인원 50→100명 (Lv.10 기준)</t>
+          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -18238,14 +18238,14 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>길드(혈맹) 시트 신규 추가</t>
+          <t>상점 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -18255,19 +18255,19 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
+          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -18277,19 +18277,19 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>대사 시스템</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
+          <t>최대 인원 50→100명 (Lv.10 기준)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -18304,14 +18304,14 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>NPC 시트 신규 추가 (11종)</t>
+          <t>길드(혈맹) 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -18321,19 +18321,19 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>각성기</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
+          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -18343,19 +18343,19 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>대사 시스템</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
+          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -18365,19 +18365,19 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
+          <t>NPC 시트 신규 추가 (11종)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
@@ -18387,19 +18387,19 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>각성기</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
+          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -18409,19 +18409,19 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
+          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
@@ -18431,19 +18431,19 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>교역</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
+          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -18458,14 +18458,14 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
+          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
@@ -18475,19 +18475,19 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
+          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -18497,19 +18497,19 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>교역</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>연금술 시트 신규 추가</t>
+          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
@@ -18519,19 +18519,19 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
+          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -18541,19 +18541,19 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (이동 +85%, 비행)</t>
+          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
@@ -18563,19 +18563,19 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
+          <t>연금술 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -18585,19 +18585,19 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
+          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
@@ -18607,19 +18607,19 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
+          <t>페가수스 (이동 +85%, 비행)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -18629,78 +18629,78 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
+          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
+          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
+          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
+          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
         </is>
       </c>
     </row>
@@ -18717,19 +18717,19 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
+          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
@@ -18739,19 +18739,19 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>상태이상</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
+          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -18766,14 +18766,14 @@
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
         </is>
       </c>
     </row>
@@ -18805,12 +18805,12 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>컨텐츠</t>
+          <t>상태이상</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
         </is>
       </c>
     </row>
@@ -18832,27 +18832,93 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>컨텐츠</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
           <t>v1.6 이전</t>
         </is>
       </c>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C104" s="7" t="inlineStr">
+      <c r="C107" s="8" t="inlineStr">
         <is>
           <t>기반</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr">
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>마을/사냥/PvP/카르마/펫/탈것/제작/교역/길드/공성/투기장 등</t>
         </is>
@@ -18872,7 +18938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18919,7 +18985,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -18929,152 +18995,152 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Phase 1</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>game/data/world_data.js 추출</t>
+          <t>game/data/zones.js 추출</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>-105줄 (9622→9517)</t>
+          <t>-414줄 (9517→9103)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>마스터 플랜</t>
+          <t>분리</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>5단계 분리</t>
+          <t>지역 8종</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Phase 2: ZONES / 3: 장비 / 4: 퀘스트 / 5: 상점</t>
+          <t>ZONES/ZONE_AMBIENCE/MONSTER_LORE/등</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>각 phase = 1 커밋</t>
+          <t>함수(isOnRoad/isBlocked) 유지</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>버그 수정</t>
+          <t>진척</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>MONSTER_TIERS</t>
+          <t>-519줄 누적</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>깨진 한글 동시 수정</t>
+          <t>9622 → 9103</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>드래곤 / 고대 드래곤</t>
+          <t>-5.4%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>리팩토링</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>game/farm.js</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>농장 모듈 생성 + 즉시 통합</t>
+          <t>game/data/world_data.js 추출</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>7작물 / AFK 진행</t>
+          <t>-105줄 (9622→9517)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>작물 (전설)</t>
+          <t>마스터 플랜</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>용 과일</t>
+          <t>5단계 분리</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>4시간 / 80💎</t>
+          <t>Phase 2: ZONES / 3: 장비 / 4: 퀘스트 / 5: 상점</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>용재료 ×1 + 영혼석 ×3 + 3000G</t>
+          <t>각 phase = 1 커밋</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>작물 (희귀)</t>
+          <t>버그 수정</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>달꽃</t>
+          <t>MONSTER_TIERS</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>2시간 / 30💎</t>
+          <t>깨진 한글 동시 수정</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>마법재료 ×5 + 영혼석 ×1</t>
+          <t>드래곤 / 고대 드래곤</t>
         </is>
       </c>
     </row>
@@ -19086,103 +19152,103 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>비료</t>
+          <t>game/farm.js</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>20💎 / 50% 시간 단축</t>
+          <t>농장 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>슬롯당 1회</t>
+          <t>7작물 / AFK 진행</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>작물 (전설)</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>game/skill_tree.js</t>
+          <t>용 과일</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>특성 트리 모듈 생성 + 즉시 통합</t>
+          <t>4시간 / 80💎</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>3브랜치 × 7노드</t>
+          <t>용재료 ×1 + 영혼석 ×3 + 3000G</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>작물 (희귀)</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>레벨업 훅</t>
+          <t>달꽃</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>awardPoints(target, 1) 자동 호출</t>
+          <t>2시간 / 30💎</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>별도 학습 불필요</t>
+          <t>마법재료 ×5 + 영혼석 ×1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>마스터 노드</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>off_master</t>
+          <t>비료</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>전쟁의 화신</t>
+          <t>20💎 / 50% 시간 단축</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>ATK +30 / 크리 +5%</t>
+          <t>슬롯당 1회</t>
         </is>
       </c>
     </row>
@@ -19194,22 +19260,22 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>마스터 노드</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>def_master</t>
+          <t>game/skill_tree.js</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>불멸의 의지</t>
+          <t>특성 트리 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>DEF +30 / HP +300</t>
+          <t>3브랜치 × 7노드</t>
         </is>
       </c>
     </row>
@@ -19221,103 +19287,103 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>마스터 노드</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>util_master</t>
+          <t>레벨업 훅</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>운명의 인도자</t>
+          <t>awardPoints(target, 1) 자동 호출</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>EXP/GOLD +20% / 드롭 +10%</t>
+          <t>별도 학습 불필요</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>game/mail.js</t>
+          <t>off_master</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>우편함 모듈 생성 + 즉시 통합</t>
+          <t>전쟁의 화신</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>시스템/선물 + 첨부 + 만료</t>
+          <t>ATK +30 / 크리 +5%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>메일</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>시스템 메일</t>
+          <t>def_master</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>이벤트 보상/공지</t>
+          <t>불멸의 의지</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>14일 만료</t>
+          <t>DEF +30 / HP +300</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>메일</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>선물 메일</t>
+          <t>util_master</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>플레이어 간 / 일일 10회</t>
+          <t>운명의 인도자</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>7일 만료, 수수료 2%</t>
+          <t>EXP/GOLD +20% / 드롭 +10%</t>
         </is>
       </c>
     </row>
@@ -19329,103 +19395,103 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>발송 시 자원 차감</t>
+          <t>game/mail.js</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>수신자 우편함 가득 → 거부</t>
+          <t>우편함 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>첨부 미수령 메일 삭제 거부</t>
+          <t>시스템/선물 + 첨부 + 만료</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>game/codex.js</t>
+          <t>시스템 메일</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>도감 모듈 생성 + 즉시 통합</t>
+          <t>이벤트 보상/공지</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>5카테고리 × 4마일스톤</t>
+          <t>14일 만료</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>선물 메일</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>explore_count → zone 자동 등록</t>
+          <t>플레이어 간 / 일일 10회</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>별도 학습 불필요</t>
+          <t>7일 만료, 수수료 2%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>fishing_cast 훅</t>
+          <t>발송 시 자원 차감</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>어종 자동 등록</t>
+          <t>수신자 우편함 가득 → 거부</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>v1.24와 자연 연동</t>
+          <t>첨부 미수령 메일 삭제 거부</t>
         </is>
       </c>
     </row>
@@ -19437,184 +19503,184 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>영구 스탯 보너스</t>
+          <t>game/codex.js</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>마일스톤 달성 시 누적</t>
+          <t>도감 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>codexBonuses 객체</t>
+          <t>5카테고리 × 4마일스톤</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>game/dailyshop.js</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>일일 상점 모듈 생성 + 즉시 통합</t>
+          <t>explore_count → zone 자동 등록</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
+          <t>별도 학습 불필요</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>결정적 랜덤</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>날짜 시드</t>
+          <t>fishing_cast 훅</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>모든 플레이어 동일 상품</t>
+          <t>어종 자동 등록</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>seededRandom + Fisher-Yates</t>
+          <t>v1.24와 자연 연동</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>개인 갱신</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>30💎</t>
+          <t>영구 스탯 보너스</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>개인 시드 생성</t>
+          <t>마일스톤 달성 시 누적</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>구매 기록 초기화</t>
+          <t>codexBonuses 객체</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>auction → server.js</t>
+          <t>game/dailyshop.js</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>6번째 (마지막) 모듈 통합</t>
+          <t>일일 상점 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>자동 정산 + 환불 + 양방향 지급</t>
+          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>결정적 랜덤</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>tickAuctions</t>
+          <t>날짜 시드</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>10초마다 만료 정산</t>
+          <t>모든 플레이어 동일 상품</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>setInterval 통합</t>
+          <t>seededRandom + Fisher-Yates</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>개인 갱신</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>auction_create</t>
+          <t>30💎</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>경매 등록 (등록 수수료 자동 차감)</t>
+          <t>개인 시드 생성</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>3가지 기간</t>
+          <t>구매 기록 초기화</t>
         </is>
       </c>
     </row>
@@ -19626,22 +19692,22 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>auction_bid</t>
+          <t>auction → server.js</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>입찰 + 이전 입찰자 자동 환불</t>
+          <t>6번째 (마지막) 모듈 통합</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>스나이핑 방지 연장</t>
+          <t>자동 정산 + 환불 + 양방향 지급</t>
         </is>
       </c>
     </row>
@@ -19653,22 +19719,22 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>auction_my</t>
+          <t>tickAuctions</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>내 등록/입찰 내역 조회</t>
+          <t>10초마다 만료 정산</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>setInterval 통합</t>
         </is>
       </c>
     </row>
@@ -19680,103 +19746,103 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>신규 모듈 6/6</t>
+          <t>auction_create</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>100% 통합 완료</t>
+          <t>경매 등록 (등록 수수료 자동 차감)</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>lottery/fishing/event/season/boss_rush/auction</t>
+          <t>3가지 기간</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>boss_rush → server.js</t>
+          <t>auction_bid</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>5번째 모듈 통합</t>
+          <t>입찰 + 이전 입찰자 자동 환불</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>메모리 세션 기반</t>
+          <t>스나이핑 방지 연장</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>bossRushSessions</t>
+          <t>auction_my</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>진행 중 세션 저장</t>
+          <t>내 등록/입찰 내역 조회</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>currentWave/시간 추적</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>bossRushRanking</t>
+          <t>신규 모듈 6/6</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>글로벌 랭킹 TOP 100</t>
+          <t>100% 통합 완료</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>웨이브 → 시간 정렬</t>
+          <t>lottery/fishing/event/season/boss_rush/auction</t>
         </is>
       </c>
     </row>
@@ -19788,22 +19854,22 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>boss_rush_enter</t>
+          <t>boss_rush → server.js</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>무료/유료/다이아 입장</t>
+          <t>5번째 모듈 통합</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>동시 1개 세션 제한</t>
+          <t>메모리 세션 기반</t>
         </is>
       </c>
     </row>
@@ -19815,22 +19881,22 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_advance</t>
+          <t>bossRushSessions</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>웨이브 클리어 보고</t>
+          <t>진행 중 세션 저장</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>시간 초과 검증</t>
+          <t>currentWave/시간 추적</t>
         </is>
       </c>
     </row>
@@ -19842,103 +19908,103 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>풀클리어 보상</t>
+          <t>bossRushRanking</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 누적</t>
+          <t>글로벌 랭킹 TOP 100</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>웨이브 → 시간 정렬</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>season → server.js</t>
+          <t>boss_rush_enter</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>4번째 모듈 통합</t>
+          <t>무료/유료/다이아 입장</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>XP 자동 적립 + 보상 수령</t>
+          <t>동시 1개 세션 제한</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>boss_rush_advance</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
+          <t>웨이브 클리어 보고</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>SEASON_XP_MAP 매핑</t>
+          <t>시간 초과 검증</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>season_status</t>
+          <t>풀클리어 보상</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>XP/티어/구매여부/수령내역 조회</t>
+          <t>20웨이브 누적</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>15티어 전체</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
@@ -19950,22 +20016,22 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>season_buy_pass</t>
+          <t>season → server.js</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 패스 구매 (1500💎)</t>
+          <t>4번째 모듈 통합</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>XP 자동 적립 + 보상 수령</t>
         </is>
       </c>
     </row>
@@ -19977,56 +20043,56 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>season_claim</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>티어 보상 수령 (free/premium)</t>
+          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>자동 인벤토리 적용</t>
+          <t>SEASON_XP_MAP 매핑</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>event → server.js</t>
+          <t>season_status</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>3번째 모듈 통합</t>
+          <t>XP/티어/구매여부/수령내역 조회</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>축제 시스템 활성화</t>
+          <t>15티어 전체</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -20036,44 +20102,44 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>event_status</t>
+          <t>season_buy_pass</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>현재 활성 축제 조회</t>
+          <t>프리미엄 패스 구매 (1500💎)</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>이름/기간/버프/한정 보상</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>/status JSON</t>
+          <t>season_claim</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>festival 필드 추가</t>
+          <t>티어 보상 수령 (free/premium)</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>대시보드 확인용</t>
+          <t>자동 인벤토리 적용</t>
         </is>
       </c>
     </row>
@@ -20085,103 +20151,103 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>축제 인사</t>
+          <t>event → server.js</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>30% 확률로 NPC가 축제 대사 출력</t>
+          <t>3번째 모듈 통합</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>spring_blossom 등 5종</t>
+          <t>축제 시스템 활성화</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>fishing → server.js</t>
+          <t>event_status</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>현재 활성 축제 조회</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>두 번째 모듈 통합</t>
+          <t>이름/기간/버프/한정 보상</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>fishing_status</t>
+          <t>/status JSON</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>지역/낚싯대/미끼/시간대 조회</t>
+          <t>festival 필드 추가</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>대시보드 확인용</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>fishing_cast</t>
+          <t>축제 인사</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
+          <t>30% 확률로 NPC가 축제 대사 출력</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>전설/신화 → 서버 알림</t>
+          <t>spring_blossom 등 5종</t>
         </is>
       </c>
     </row>
@@ -20193,103 +20259,103 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>fishing_buy_rod</t>
+          <t>fishing → server.js</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>낚싯대 구매 (골드/다이아)</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>5등급 모두</t>
+          <t>두 번째 모듈 통합</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>lottery → server.js</t>
+          <t>fishing_status</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>지역/낚싯대/미끼/시간대 조회</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>첫 모듈 통합 마일스톤</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>lottery_status</t>
+          <t>fishing_cast</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>상태/가격/상품 풀 조회</t>
+          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>전설/신화 → 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>lottery_free_spin</t>
+          <t>fishing_buy_rod</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 스핀</t>
+          <t>낚싯대 구매 (골드/다이아)</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>자정 초기화</t>
+          <t>5등급 모두</t>
         </is>
       </c>
     </row>
@@ -20301,373 +20367,373 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>lottery_paid_spin</t>
+          <t>lottery → server.js</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>유료 1회 / 10연속</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>count: 1 또는 10</t>
+          <t>첫 모듈 통합 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js 신규</t>
+          <t>lottery_status</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
+          <t>상태/가격/상품 풀 조회</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>등록 2% + 낙찰 5%</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>활성 한도</t>
+          <t>lottery_free_spin</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>플레이어당 10개</t>
+          <t>매일 무료 1회 스핀</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>자기 입찰 금지</t>
+          <t>자정 초기화</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>game/fishing.js 신규</t>
+          <t>lottery_paid_spin</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
+          <t>유료 1회 / 10연속</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 = 20000G + 칭호</t>
+          <t>count: 1 또는 10</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>전설의 비단잉어</t>
+          <t>game/auction.js 신규</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>드래곤 낚싯대 + 가중치 1</t>
+          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>5000G + 평생 행운 +5%</t>
+          <t>등록 2% + 낙찰 5%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>game/boss_rush.js 신규</t>
+          <t>활성 한도</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 / HP ×1.35 스케일링</t>
+          <t>플레이어당 10개</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>최종 보상: 200💎 + 용재료 ×5</t>
+          <t>자기 입찰 금지</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>입장</t>
+          <t>game/fishing.js 신규</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 / 1000G / 30💎</t>
+          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>랭킹 시스템</t>
+          <t>신화 크라켄 = 20000G + 칭호</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>챔피언 보상</t>
+          <t>전설의 비단잉어</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
+          <t>드래곤 낚싯대 + 가중치 1</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5000G + 평생 행운 +5%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js 신규</t>
+          <t>game/boss_rush.js 신규</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 / 가중치 1000</t>
+          <t>20웨이브 / HP ×1.35 스케일링</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 + 유료</t>
+          <t>최종 보상: 200💎 + 용재료 ×5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>영웅 장비 상자</t>
+          <t>입장</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>확률 0.2% (가장 희귀)</t>
+          <t>매일 무료 3회 / 1000G / 30💎</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>전설 보상</t>
+          <t>랭킹 시스템</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>200 다이아</t>
+          <t>챔피언 보상</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>확률 0.8%</t>
+          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>신년 축제</t>
+          <t>game/lottery.js 신규</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>1/1 ~ 1/7</t>
+          <t>10종 보상 / 가중치 1000</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>골드 +50% / EXP +30%</t>
+          <t>매일 무료 1회 + 유료</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>봄꽃 축제</t>
+          <t>영웅 장비 상자</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>4/1 ~ 4/14</t>
+          <t>확률 0.2% (가장 희귀)</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>HP재생 +30% / 드롭 +20%</t>
+          <t>전설 보상</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>한여름 밤의 축제</t>
+          <t>200 다이아</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>7/15 ~ 8/15</t>
+          <t>확률 0.8%</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>화염 +30% / PvP 보상 +50%</t>
+          <t>잭팟</t>
         </is>
       </c>
     </row>
@@ -20684,17 +20750,17 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>할로윈 축제</t>
+          <t>신년 축제</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>10/25 ~ 11/1</t>
+          <t>1/1 ~ 1/7</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>크리 +10% / 언데드 +50%</t>
+          <t>골드 +50% / EXP +30%</t>
         </is>
       </c>
     </row>
@@ -20711,179 +20777,179 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>겨울 축제</t>
+          <t>봄꽃 축제</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>12/20 ~ 12/31</t>
+          <t>4/1 ~ 4/14</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
+          <t>HP재생 +30% / 드롭 +20%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>game/season.js 신규</t>
+          <t>한여름 밤의 축제</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>15티어 / 30일 / 무료+프리미엄</t>
+          <t>7/15 ~ 8/15</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
+          <t>화염 +30% / PvP 보상 +50%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>XP 획득 7종</t>
+          <t>할로윈 축제</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>퀘/보스/PvP/월드보스/던전/제작</t>
+          <t>10/25 ~ 11/1</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>일일 +200 ~ 월드보스 +500</t>
+          <t>크리 +10% / 언데드 +50%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 가격</t>
+          <t>겨울 축제</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>1500 다이아</t>
+          <t>12/20 ~ 12/31</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>시즌 당 1회</t>
+          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Lv.40 달성</t>
+          <t>game/season.js 신규</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>각성기 해금 마일스톤</t>
+          <t>15티어 / 30일 / 무료+프리미엄</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>150💎</t>
+          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>Lv.50 달성</t>
+          <t>XP 획득 7종</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>환생 가능 마일스톤</t>
+          <t>퀘/보스/PvP/월드보스/던전/제작</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>250💎</t>
+          <t>일일 +200 ~ 월드보스 +500</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>첫 환생</t>
+          <t>프리미엄 가격</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>prestige 1차</t>
+          <t>1500 다이아</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>500💎</t>
+          <t>시즌 당 1회</t>
         </is>
       </c>
     </row>
@@ -20900,17 +20966,17 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>첫 월드 보스</t>
+          <t>Lv.40 달성</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 처치 보너스</t>
+          <t>각성기 해금 마일스톤</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>100💎</t>
+          <t>150💎</t>
         </is>
       </c>
     </row>
@@ -20927,98 +20993,98 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>업적 50개</t>
+          <t>Lv.50 달성</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>업적 마일스톤</t>
+          <t>환생 가능 마일스톤</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>200💎</t>
+          <t>250💎</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>불사조 스킨</t>
+          <t>첫 환생</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>prestige 1차</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>불사조 깃털 이펙트 (영구)</t>
+          <t>500💎</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>폭풍 스킨</t>
+          <t>첫 월드 보스</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>월드 보스 처치 보너스</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>번개 오라 이펙트 (영구)</t>
+          <t>100💎</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>상점 (편의)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 자동물약</t>
+          <t>업적 50개</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>500 다이아</t>
+          <t>업적 마일스톤</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>24시간 자동물약 무한</t>
+          <t>200💎</t>
         </is>
       </c>
     </row>
@@ -21030,22 +21096,22 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>상점 (상자)</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 보물 상자</t>
+          <t>불사조 스킨</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>300 다이아</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>전설 장비 확정 + 다이아</t>
+          <t>불사조 깃털 이펙트 (영구)</t>
         </is>
       </c>
     </row>
@@ -21057,103 +21123,103 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>상점 (재료)</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>전설 재료 패키지</t>
+          <t>폭풍 스킨</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>600 다이아</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
+          <t>번개 오라 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6</t>
+          <t>상점 (편의)</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 분노</t>
+          <t>프리미엄 자동물약</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>크리티컬 +5%</t>
+          <t>500 다이아</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>60명 정원</t>
+          <t>24시간 자동물약 무한</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.7</t>
+          <t>상점 (상자)</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 신속</t>
+          <t>프리미엄 보물 상자</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>이동속도 +10%</t>
+          <t>300 다이아</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>70명 정원</t>
+          <t>전설 장비 확정 + 다이아</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.8</t>
+          <t>상점 (재료)</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 회복</t>
+          <t>전설 재료 패키지</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>HP 재생 +50%</t>
+          <t>600 다이아</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>80명 정원</t>
+          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
         </is>
       </c>
     </row>
@@ -21165,22 +21231,22 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.9</t>
+          <t>혈맹 Lv.6</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 운명</t>
+          <t>혈맹의 분노</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>회피 +5%</t>
+          <t>크리티컬 +5%</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>90명 정원</t>
+          <t>60명 정원</t>
         </is>
       </c>
     </row>
@@ -21192,184 +21258,184 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.10</t>
+          <t>혈맹 Lv.7</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 전설</t>
+          <t>혈맹의 신속</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>전 스탯 +5%</t>
+          <t>이동속도 +10%</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>100명 정원 — 최종</t>
+          <t>70명 정원</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.8</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>점쟁이</t>
+          <t>혈맹의 회복</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
+          <t>HP 재생 +50%</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>80명 정원</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.9</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>감정사</t>
+          <t>혈맹의 운명</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
+          <t>회피 +5%</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>90명 정원</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.10</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>수집가</t>
+          <t>혈맹의 전설</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
+          <t>전 스탯 +5%</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>100명 정원 — 최종</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>각성기 (어쌔신)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>천 개의 칼날</t>
+          <t>점쟁이</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
+          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>각성기 (워리어)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>대지 가르기</t>
+          <t>감정사</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
+          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>각성기 (나이트)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>불멸의 수호자</t>
+          <t>수집가</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>피해 90% 감소 / 도발 / 10초</t>
+          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
@@ -21381,17 +21447,17 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>각성기 (메이지)</t>
+          <t>각성기 (어쌔신)</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>시간 정지</t>
+          <t>천 개의 칼날</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
+          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -21408,17 +21474,17 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>각성기 (클레릭)</t>
+          <t>각성기 (워리어)</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>신의 은총</t>
+          <t>대지 가르기</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>HP 100% 회복 / 전스탯 +50%</t>
+          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
@@ -21430,81 +21496,81 @@
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (나이트)</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>폭풍 정복자</t>
+          <t>불멸의 수호자</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인 처치</t>
+          <t>피해 90% 감소 / 도발 / 10초</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>10,000G + 150다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (메이지)</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>연금술사</t>
+          <t>시간 정지</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>엘릭서 10회 제작</t>
+          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>5,000G + 80다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (클레릭)</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>그림자 정복자</t>
+          <t>신의 은총</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 클리어</t>
+          <t>HP 100% 회복 / 전스탯 +50%</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>8,000G + 120다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
@@ -21521,17 +21587,17 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>전설의 동반자</t>
+          <t>폭풍 정복자</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>전설급 펫 진화</t>
+          <t>폭풍의 거인 처치</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>6,000G + 100다이아</t>
+          <t>10,000G + 150다이아</t>
         </is>
       </c>
     </row>
@@ -21548,179 +21614,179 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>이국의 상인</t>
+          <t>연금술사</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>사치품 교역 5회</t>
+          <t>엘릭서 10회 제작</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>4,000G + 60다이아</t>
+          <t>5,000G + 80다이아</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인</t>
+          <t>그림자 정복자</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>HP 100,000 / ATK 140 / DEF 90</t>
+          <t>그림자 미궁 클리어</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>EXP 10000 + 6000G</t>
+          <t>8,000G + 120다이아</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>시간의 수호자</t>
+          <t>전설의 동반자</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>HP 70,000 / ATK 170 / DEF 60</t>
+          <t>전설급 펫 진화</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>EXP 9000 + 7000G</t>
+          <t>6,000G + 100다이아</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>교역품</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
+          <t>이국의 상인</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종</t>
+          <t>사치품 교역 5회</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>기본가 600~900G</t>
+          <t>4,000G + 60다이아</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>타이탄의 엘릭서</t>
+          <t>폭풍의 거인</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>용재료×3 + 마법재료×10</t>
+          <t>HP 100,000 / ATK 140 / DEF 90</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>ATK ×1.5 / 30분</t>
+          <t>EXP 10000 + 6000G</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>강철 엘릭서</t>
+          <t>시간의 수호자</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>철광석×30 + 마법재료×10</t>
+          <t>HP 70,000 / ATK 170 / DEF 60</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>DEF ×1.5 / 30분</t>
+          <t>EXP 9000 + 7000G</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>교역품</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>질풍 엘릭서</t>
+          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>약초×20 + 마법재료×8</t>
+          <t>이국의 사치품 3종</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>SPD ×1.4 / 20분</t>
+          <t>기본가 600~900G</t>
         </is>
       </c>
     </row>
@@ -21737,17 +21803,17 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>지혜 엘릭서</t>
+          <t>타이탄의 엘릭서</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>마법수정×5 + 영혼재료×5</t>
+          <t>용재료×3 + 마법재료×10</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>EXP ×2.5 / 15분</t>
+          <t>ATK ×1.5 / 30분</t>
         </is>
       </c>
     </row>
@@ -21764,233 +21830,233 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>행운 엘릭서</t>
+          <t>강철 엘릭서</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>보석×10 + 마법재료×5</t>
+          <t>철광석×30 + 마법재료×10</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>GOLD ×2.0 / 15분</t>
+          <t>DEF ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>불사조 (pet_phoenix)</t>
+          <t>질풍 엘릭서</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>불꽃산 보스 50처치</t>
+          <t>약초×20 + 마법재료×8</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>화염 DMG +20% (진화 +40%)</t>
+          <t>SPD ×1.4 / 20분</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>유니콘 (pet_unicorn)</t>
+          <t>지혜 엘릭서</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>다이아 800개</t>
+          <t>마법수정×5 + 영혼재료×5</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>회피 +10% (진화 +20%)</t>
+          <t>EXP ×2.5 / 15분</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (mount_pegasus)</t>
+          <t>행운 엘릭서</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>다이아 1200개</t>
+          <t>보석×10 + 마법재료×5</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>이동속도 +85% / 비행</t>
+          <t>GOLD ×2.0 / 15분</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁</t>
+          <t>불사조 (pet_phoenix)</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Lv.38 / 8인 파티 / 7스테이지</t>
+          <t>불꽃산 보스 50처치</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>22000G + 32000EXP</t>
+          <t>화염 DMG +20% (진화 +40%)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>드롭</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>드래곤 검/망토/투구/장갑</t>
+          <t>유니콘 (pet_unicorn)</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 보스 드롭</t>
+          <t>다이아 800개</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>전설급</t>
+          <t>회피 +10% (진화 +20%)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자</t>
+          <t>페가수스 (mount_pegasus)</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>몬스터 10,000 처치</t>
+          <t>다이아 1200개</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>ATK +7%</t>
+          <t>이동속도 +85% / 비행</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>불멸자</t>
+          <t>그림자 미궁</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>환생 5회</t>
+          <t>Lv.38 / 8인 파티 / 7스테이지</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>EXP +25%</t>
+          <t>22000G + 32000EXP</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>드롭</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>천공의 군주</t>
+          <t>드래곤 검/망토/투구/장갑</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 10회 처치</t>
+          <t>그림자 미궁 보스 드롭</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>보스DMG +15%</t>
+          <t>전설급</t>
         </is>
       </c>
     </row>
@@ -22002,22 +22068,22 @@
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>지역 시트 갱신</t>
+          <t>공허의 방랑자</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>25→51개 지역 반영</t>
+          <t>몬스터 10,000 처치</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ATK +7%</t>
         </is>
       </c>
     </row>
@@ -22029,22 +22095,22 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>칭호 시트 갱신</t>
+          <t>불멸자</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>7→16종 + 효과/색상 추가</t>
+          <t>환생 5회</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EXP +25%</t>
         </is>
       </c>
     </row>
@@ -22056,22 +22122,22 @@
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>출석 캘린더 시트</t>
+          <t>천공의 군주</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (28일 사이클)</t>
+          <t>월드 보스 10회 처치</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>보스DMG +15%</t>
         </is>
       </c>
     </row>
@@ -22088,12 +22154,12 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>장비 세트 시트</t>
+          <t>지역 시트 갱신</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (드래곤/영웅/태초)</t>
+          <t>25→51개 지역 반영</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -22115,12 +22181,12 @@
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>장비 등급 시트</t>
+          <t>칭호 시트 갱신</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+          <t>7→16종 + 효과/색상 추가</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
@@ -22142,12 +22208,12 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>디버프 시트</t>
+          <t>출석 캘린더 시트</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+          <t>신규 추가 (28일 사이클)</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -22169,12 +22235,12 @@
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>패치 노트 시트</t>
+          <t>장비 세트 시트</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (히스토리)</t>
+          <t>신규 추가 (드래곤/영웅/태초)</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
@@ -22186,25 +22252,106 @@
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>장비 등급 시트</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>디버프 시트</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>패치 노트 시트</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (히스토리)</t>
+        </is>
+      </c>
+      <c r="E127" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
           <t>v1.10</t>
         </is>
       </c>
-      <c r="B125" s="8" t="inlineStr">
+      <c r="B128" s="7" t="inlineStr">
         <is>
           <t>기획서</t>
         </is>
       </c>
-      <c r="C125" s="8" t="inlineStr">
+      <c r="C128" s="7" t="inlineStr">
         <is>
           <t>던전 시트</t>
         </is>
       </c>
-      <c r="D125" s="8" t="inlineStr">
+      <c r="D128" s="7" t="inlineStr">
         <is>
           <t>신규 추가 (7종 던전)</t>
         </is>
       </c>
-      <c r="E125" s="8" t="inlineStr">
+      <c r="E128" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -45,7 +45,7 @@
     <sheet name="월드 보스" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="연금술" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="패치 노트" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="v1.9 ~ v1.38" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="v1.9 ~ v1.39" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16598,7 +16598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16639,7 +16639,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.38</t>
+          <t>v1.39</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -16654,14 +16654,14 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Phase 2: 지역 데이터 8종 추출 → game/data/zones.js (459줄)</t>
+          <t>Phase 3: 장비 데이터 6종 추출 → game/data/equipment.js (123줄)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.38</t>
+          <t>v1.39</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -16676,14 +16676,14 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>server.js 9517 → 9103줄 (-414줄)</t>
+          <t>server.js 9103 → 9007줄 (-96줄)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.38</t>
+          <t>v1.39</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -16698,14 +16698,14 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>ZONES(53)/ZONE_AMBIENCE(52)/MONSTER_LORE(79)/ZONE_CONNECTIONS(50)/TERRAIN_BARRIERS/ROADS/ZONE_MONSTERS/ZONE_MONSTER_NAMES</t>
+          <t>EQUIPMENT_SLOTS/SETS/GRADE_INFO/RANDOM_OPTIONS/EQUIP_STATS(44)/EQUIP_DESCRIPTIONS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -16720,14 +16720,14 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Phase 1: 순수 데이터 6종 추출 → game/data/world_data.js</t>
+          <t>Phase 2: 지역 데이터 8종 추출 → game/data/zones.js (459줄)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -16742,14 +16742,14 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>server.js 9622 → 9517줄 (-105줄)</t>
+          <t>server.js 9517 → 9103줄 (-414줄)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>MONSTER_TIERS / KARMA / WORLD_BOSS_TYPES / DUNGEONS / ELEMENT_BONUS / ATTENDANCE_REWARDS</t>
+          <t>ZONES(53)/ZONE_AMBIENCE(52)/MONSTER_LORE(79)/ZONE_CONNECTIONS(50)/TERRAIN_BARRIERS/ROADS/ZONE_MONSTERS/ZONE_MONSTER_NAMES</t>
         </is>
       </c>
     </row>
@@ -16781,19 +16781,19 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>버그 수정</t>
+          <t>리팩토링</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>MONSTER_TIERS의 깨진 한글 (드래���→드래곤) 함께 수정</t>
+          <t>Phase 1: 순수 데이터 6종 추출 → game/data/world_data.js</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -16803,19 +16803,19 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>신규 모듈</t>
+          <t>리팩토링</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>game/farm.js — 농장 시스템 (생성 + 통합 동시)</t>
+          <t>server.js 9622 → 9517줄 (-105줄)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -16825,19 +16825,19 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>농장</t>
+          <t>리팩토링</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>7종 작물 (5분~4시간), AFK 진행, 4슬롯 기본 (12슬롯 확장)</t>
+          <t>MONSTER_TIERS / KARMA / WORLD_BOSS_TYPES / DUNGEONS / ELEMENT_BONUS / ATTENDANCE_REWARDS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -16847,12 +16847,12 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>농장</t>
+          <t>버그 수정</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>비료 (20💎) 50% 시간 단축, 슬롯 확장 50💎</t>
+          <t>MONSTER_TIERS의 깨진 한글 (드래���→드래곤) 함께 수정</t>
         </is>
       </c>
     </row>
@@ -16869,19 +16869,19 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>farm_status / plant / harvest / fertilize / expand</t>
+          <t>game/farm.js — 농장 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -16891,19 +16891,19 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>신규 모듈</t>
+          <t>농장</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>game/skill_tree.js — 특성 트리 (생성 + 통합 동시)</t>
+          <t>7종 작물 (5분~4시간), AFK 진행, 4슬롯 기본 (12슬롯 확장)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -16913,19 +16913,19 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>특성 트리</t>
+          <t>농장</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>3브랜치 (공격/방어/유틸) × 7노드 = 21노드</t>
+          <t>비료 (20💎) 50% 시간 단축, 슬롯 확장 50💎</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -16935,12 +16935,12 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>특성 트리</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>레벨업 시 1포인트 자동 지급, 100💎로 리셋</t>
+          <t>farm_status / plant / harvest / fertilize / expand</t>
         </is>
       </c>
     </row>
@@ -16957,19 +16957,19 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>게이트</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>5/10/15/20/25 포인트 투자 시 상위 노드 해금</t>
+          <t>game/skill_tree.js — 특성 트리 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -16979,19 +16979,19 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>신규 모듈</t>
+          <t>특성 트리</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>game/mail.js — 정식 우편함 시스템 (생성 + 통합 동시)</t>
+          <t>3브랜치 (공격/방어/유틸) × 7노드 = 21노드</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -17001,19 +17001,19 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>우편함</t>
+          <t>특성 트리</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>시스템/선물 메일 + 첨부(골드/다이아/아이템) + 만료/수령 관리</t>
+          <t>레벨업 시 1포인트 자동 지급, 100💎로 리셋</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -17023,12 +17023,12 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>선물</t>
+          <t>게이트</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>일일 10회 / 골드 첨부 수수료 2% / 7일 만료</t>
+          <t>5/10/15/20/25 포인트 투자 시 상위 노드 해금</t>
         </is>
       </c>
     </row>
@@ -17045,19 +17045,19 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>mail_inbox/read/claim/delete/send_gift</t>
+          <t>game/mail.js — 정식 우편함 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -17067,19 +17067,19 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>신규 모듈</t>
+          <t>우편함</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>game/codex.js — 도감 시스템 (생성 + 통합 동시)</t>
+          <t>시스템/선물 메일 + 첨부(골드/다이아/아이템) + 만료/수령 관리</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -17089,19 +17089,19 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>선물</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>5개 카테고리 (몬스터/지역/장비/어종/펫) × 4단계 마일스톤</t>
+          <t>일일 10회 / 골드 첨부 수수료 2% / 7일 만료</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -17111,12 +17111,12 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>마일스톤 달성 시 영구 스탯 보너스 + 전 서버 알림</t>
+          <t>mail_inbox/read/claim/delete/send_gift</t>
         </is>
       </c>
     </row>
@@ -17133,19 +17133,19 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>trackQuest(explore_count) → zone 자동 등록 / fishing_cast → fish 자동 등록</t>
+          <t>game/codex.js — 도감 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -17155,19 +17155,19 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>신규 모듈</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
+          <t>5개 카테고리 (몬스터/지역/장비/어종/펫) × 4단계 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -17177,19 +17177,19 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>일일 상점</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
+          <t>마일스톤 달성 시 영구 스탯 보너스 + 전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -17199,12 +17199,12 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>일일 상점</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
+          <t>trackQuest(explore_count) → zone 자동 등록 / fishing_cast → fish 자동 등록</t>
         </is>
       </c>
     </row>
@@ -17221,19 +17221,19 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
+          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -17243,19 +17243,19 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
+          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -17265,19 +17265,19 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
+          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -17287,12 +17287,12 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
+          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
         </is>
       </c>
     </row>
@@ -17309,12 +17309,12 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>auction_list / create / bid / my</t>
+          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
         </is>
       </c>
     </row>
@@ -17331,19 +17331,19 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
+          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -17353,19 +17353,19 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
+          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -17375,19 +17375,19 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
+          <t>auction_list / create / bid / my</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -17397,12 +17397,12 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>boss_rush_status / enter / advance / abandon</t>
+          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
         </is>
       </c>
     </row>
@@ -17419,19 +17419,19 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
+          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -17441,19 +17441,19 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
+          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -17463,19 +17463,19 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
+          <t>boss_rush_status / enter / advance / abandon</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -17485,12 +17485,12 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>season_status / season_buy_pass / season_claim</t>
+          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
         </is>
       </c>
     </row>
@@ -17507,19 +17507,19 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
+          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -17529,19 +17529,19 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
+          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -17551,19 +17551,19 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>event_status 소켓 + /status 엔드포인트 노출</t>
+          <t>season_status / season_buy_pass / season_claim</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -17573,12 +17573,12 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
+          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
         </is>
       </c>
     </row>
@@ -17595,19 +17595,19 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
+          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -17617,19 +17617,19 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
+          <t>event_status 소켓 + /status 엔드포인트 노출</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -17639,19 +17639,19 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
+          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -17661,12 +17661,12 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
+          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
         </is>
       </c>
     </row>
@@ -17683,19 +17683,19 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
+          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -17705,19 +17705,19 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
+          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -17727,19 +17727,19 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
+          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -17749,19 +17749,19 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
+          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -17771,19 +17771,19 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
+          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -17793,19 +17793,19 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
+          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -17815,19 +17815,19 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>경매장 시트 신규 추가</t>
+          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -17837,19 +17837,19 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
+          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -17859,19 +17859,19 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
+          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -17886,14 +17886,14 @@
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>낚시 시트 신규 추가</t>
+          <t>경매장 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -17903,19 +17903,19 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
+          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -17925,19 +17925,19 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
+          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -17952,14 +17952,14 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>보스 러시 시트 신규 추가</t>
+          <t>낚시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -17969,19 +17969,19 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
+          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -17991,19 +17991,19 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
+          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -18018,14 +18018,14 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛 시트 신규 추가</t>
+          <t>보스 러시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -18035,19 +18035,19 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
+          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -18057,19 +18057,19 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>모듈화</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
+          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -18084,14 +18084,14 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트 시트 신규 추가</t>
+          <t>행운의 룰렛 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -18101,19 +18101,19 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
+          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -18123,19 +18123,19 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>모듈화</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
+          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -18150,14 +18150,14 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스 시트 신규 추가</t>
+          <t>축제 이벤트 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -18167,19 +18167,19 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
+          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -18189,19 +18189,19 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아 시트 신규 추가</t>
+          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -18211,19 +18211,19 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
+          <t>시즌 패스 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -18233,19 +18233,19 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>상점 시트 갱신</t>
+          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -18255,19 +18255,19 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
+          <t>무료 다이아 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -18277,19 +18277,19 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>최대 인원 50→100명 (Lv.10 기준)</t>
+          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -18304,14 +18304,14 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>길드(혈맹) 시트 신규 추가</t>
+          <t>상점 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -18321,19 +18321,19 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
+          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -18343,19 +18343,19 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>대사 시스템</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
+          <t>최대 인원 50→100명 (Lv.10 기준)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -18370,14 +18370,14 @@
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>NPC 시트 신규 추가 (11종)</t>
+          <t>길드(혈맹) 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
@@ -18387,19 +18387,19 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>각성기</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
+          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -18409,19 +18409,19 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>대사 시스템</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
+          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
@@ -18431,19 +18431,19 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
+          <t>NPC 시트 신규 추가 (11종)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -18453,19 +18453,19 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>각성기</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
+          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
@@ -18475,19 +18475,19 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
+          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -18497,19 +18497,19 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>교역</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
+          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
@@ -18524,14 +18524,14 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
+          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -18541,19 +18541,19 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
+          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
@@ -18563,19 +18563,19 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>교역</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>연금술 시트 신규 추가</t>
+          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -18585,19 +18585,19 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
+          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
@@ -18607,19 +18607,19 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>페가수스 (이동 +85%, 비행)</t>
+          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -18629,19 +18629,19 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
+          <t>연금술 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
@@ -18651,19 +18651,19 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
+          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -18673,19 +18673,19 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
+          <t>페가수스 (이동 +85%, 비행)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
@@ -18695,78 +18695,78 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
+          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
+          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
+          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
+          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
         </is>
       </c>
     </row>
@@ -18783,19 +18783,19 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
+          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -18805,19 +18805,19 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>상태이상</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
+          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
@@ -18832,14 +18832,14 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
         </is>
       </c>
     </row>
@@ -18871,12 +18871,12 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>컨텐츠</t>
+          <t>상태이상</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
         </is>
       </c>
     </row>
@@ -18898,27 +18898,93 @@
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>컨텐츠</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
           <t>v1.6 이전</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C107" s="8" t="inlineStr">
+      <c r="C110" s="7" t="inlineStr">
         <is>
           <t>기반</t>
         </is>
       </c>
-      <c r="D107" s="8" t="inlineStr">
+      <c r="D110" s="7" t="inlineStr">
         <is>
           <t>마을/사냥/PvP/카르마/펫/탈것/제작/교역/길드/공성/투기장 등</t>
         </is>
@@ -18938,7 +19004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18985,7 +19051,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.38</t>
+          <t>v1.39</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -18995,24 +19061,24 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Phase 2</t>
+          <t>Phase 3</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>game/data/zones.js 추출</t>
+          <t>game/data/equipment.js 추출</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>-414줄 (9517→9103)</t>
+          <t>-96줄 (9103→9007)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.38</t>
+          <t>v1.39</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -19022,24 +19088,24 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>지역 8종</t>
+          <t>장비 6종</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>ZONES/ZONE_AMBIENCE/MONSTER_LORE/등</t>
+          <t>SLOTS/SETS/GRADE/RAND/STATS/DESC</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>함수(isOnRoad/isBlocked) 유지</t>
+          <t>generateRandomOptions 함수 유지</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.38</t>
+          <t>v1.39</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -19049,24 +19115,24 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>-519줄 누적</t>
+          <t>-615줄 누적</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>9622 → 9103</t>
+          <t>9622 → 9007</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-6.4%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -19076,152 +19142,152 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Phase 1</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>game/data/world_data.js 추출</t>
+          <t>game/data/zones.js 추출</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>-105줄 (9622→9517)</t>
+          <t>-414줄 (9517→9103)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>마스터 플랜</t>
+          <t>분리</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>5단계 분리</t>
+          <t>지역 8종</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Phase 2: ZONES / 3: 장비 / 4: 퀘스트 / 5: 상점</t>
+          <t>ZONES/ZONE_AMBIENCE/MONSTER_LORE/등</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>각 phase = 1 커밋</t>
+          <t>함수(isOnRoad/isBlocked) 유지</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>버그 수정</t>
+          <t>진척</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>MONSTER_TIERS</t>
+          <t>-519줄 누적</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>깨진 한글 동시 수정</t>
+          <t>9622 → 9103</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>드래곤 / 고대 드래곤</t>
+          <t>-5.4%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>리팩토링</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>game/farm.js</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>농장 모듈 생성 + 즉시 통합</t>
+          <t>game/data/world_data.js 추출</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>7작물 / AFK 진행</t>
+          <t>-105줄 (9622→9517)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>작물 (전설)</t>
+          <t>마스터 플랜</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>용 과일</t>
+          <t>5단계 분리</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>4시간 / 80💎</t>
+          <t>Phase 2: ZONES / 3: 장비 / 4: 퀘스트 / 5: 상점</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>용재료 ×1 + 영혼석 ×3 + 3000G</t>
+          <t>각 phase = 1 커밋</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>작물 (희귀)</t>
+          <t>버그 수정</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>달꽃</t>
+          <t>MONSTER_TIERS</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>2시간 / 30💎</t>
+          <t>깨진 한글 동시 수정</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>마법재료 ×5 + 영혼석 ×1</t>
+          <t>드래곤 / 고대 드래곤</t>
         </is>
       </c>
     </row>
@@ -19233,103 +19299,103 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>비료</t>
+          <t>game/farm.js</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>20💎 / 50% 시간 단축</t>
+          <t>농장 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>슬롯당 1회</t>
+          <t>7작물 / AFK 진행</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>작물 (전설)</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>game/skill_tree.js</t>
+          <t>용 과일</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>특성 트리 모듈 생성 + 즉시 통합</t>
+          <t>4시간 / 80💎</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>3브랜치 × 7노드</t>
+          <t>용재료 ×1 + 영혼석 ×3 + 3000G</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>작물 (희귀)</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>레벨업 훅</t>
+          <t>달꽃</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>awardPoints(target, 1) 자동 호출</t>
+          <t>2시간 / 30💎</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>별도 학습 불필요</t>
+          <t>마법재료 ×5 + 영혼석 ×1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>마스터 노드</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>off_master</t>
+          <t>비료</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>전쟁의 화신</t>
+          <t>20💎 / 50% 시간 단축</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>ATK +30 / 크리 +5%</t>
+          <t>슬롯당 1회</t>
         </is>
       </c>
     </row>
@@ -19341,22 +19407,22 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>마스터 노드</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>def_master</t>
+          <t>game/skill_tree.js</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>불멸의 의지</t>
+          <t>특성 트리 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>DEF +30 / HP +300</t>
+          <t>3브랜치 × 7노드</t>
         </is>
       </c>
     </row>
@@ -19368,103 +19434,103 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>마스터 노드</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>util_master</t>
+          <t>레벨업 훅</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>운명의 인도자</t>
+          <t>awardPoints(target, 1) 자동 호출</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>EXP/GOLD +20% / 드롭 +10%</t>
+          <t>별도 학습 불필요</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>game/mail.js</t>
+          <t>off_master</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>우편함 모듈 생성 + 즉시 통합</t>
+          <t>전쟁의 화신</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>시스템/선물 + 첨부 + 만료</t>
+          <t>ATK +30 / 크리 +5%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>메일</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>시스템 메일</t>
+          <t>def_master</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>이벤트 보상/공지</t>
+          <t>불멸의 의지</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>14일 만료</t>
+          <t>DEF +30 / HP +300</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>메일</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>선물 메일</t>
+          <t>util_master</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>플레이어 간 / 일일 10회</t>
+          <t>운명의 인도자</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>7일 만료, 수수료 2%</t>
+          <t>EXP/GOLD +20% / 드롭 +10%</t>
         </is>
       </c>
     </row>
@@ -19476,103 +19542,103 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>발송 시 자원 차감</t>
+          <t>game/mail.js</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>수신자 우편함 가득 → 거부</t>
+          <t>우편함 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>첨부 미수령 메일 삭제 거부</t>
+          <t>시스템/선물 + 첨부 + 만료</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>game/codex.js</t>
+          <t>시스템 메일</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>도감 모듈 생성 + 즉시 통합</t>
+          <t>이벤트 보상/공지</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>5카테고리 × 4마일스톤</t>
+          <t>14일 만료</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>선물 메일</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>explore_count → zone 자동 등록</t>
+          <t>플레이어 간 / 일일 10회</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>별도 학습 불필요</t>
+          <t>7일 만료, 수수료 2%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>fishing_cast 훅</t>
+          <t>발송 시 자원 차감</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>어종 자동 등록</t>
+          <t>수신자 우편함 가득 → 거부</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>v1.24와 자연 연동</t>
+          <t>첨부 미수령 메일 삭제 거부</t>
         </is>
       </c>
     </row>
@@ -19584,184 +19650,184 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>영구 스탯 보너스</t>
+          <t>game/codex.js</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 달성 시 누적</t>
+          <t>도감 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>codexBonuses 객체</t>
+          <t>5카테고리 × 4마일스톤</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>game/dailyshop.js</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>일일 상점 모듈 생성 + 즉시 통합</t>
+          <t>explore_count → zone 자동 등록</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
+          <t>별도 학습 불필요</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>결정적 랜덤</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>날짜 시드</t>
+          <t>fishing_cast 훅</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>모든 플레이어 동일 상품</t>
+          <t>어종 자동 등록</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>seededRandom + Fisher-Yates</t>
+          <t>v1.24와 자연 연동</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>개인 갱신</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>30💎</t>
+          <t>영구 스탯 보너스</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>개인 시드 생성</t>
+          <t>마일스톤 달성 시 누적</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>구매 기록 초기화</t>
+          <t>codexBonuses 객체</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>auction → server.js</t>
+          <t>game/dailyshop.js</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>6번째 (마지막) 모듈 통합</t>
+          <t>일일 상점 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>자동 정산 + 환불 + 양방향 지급</t>
+          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>결정적 랜덤</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>tickAuctions</t>
+          <t>날짜 시드</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>10초마다 만료 정산</t>
+          <t>모든 플레이어 동일 상품</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>setInterval 통합</t>
+          <t>seededRandom + Fisher-Yates</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>개인 갱신</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>auction_create</t>
+          <t>30💎</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>경매 등록 (등록 수수료 자동 차감)</t>
+          <t>개인 시드 생성</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>3가지 기간</t>
+          <t>구매 기록 초기화</t>
         </is>
       </c>
     </row>
@@ -19773,22 +19839,22 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>auction_bid</t>
+          <t>auction → server.js</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>입찰 + 이전 입찰자 자동 환불</t>
+          <t>6번째 (마지막) 모듈 통합</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>스나이핑 방지 연장</t>
+          <t>자동 정산 + 환불 + 양방향 지급</t>
         </is>
       </c>
     </row>
@@ -19800,22 +19866,22 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>auction_my</t>
+          <t>tickAuctions</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>내 등록/입찰 내역 조회</t>
+          <t>10초마다 만료 정산</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>setInterval 통합</t>
         </is>
       </c>
     </row>
@@ -19827,103 +19893,103 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>신규 모듈 6/6</t>
+          <t>auction_create</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>100% 통합 완료</t>
+          <t>경매 등록 (등록 수수료 자동 차감)</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>lottery/fishing/event/season/boss_rush/auction</t>
+          <t>3가지 기간</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>boss_rush → server.js</t>
+          <t>auction_bid</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>5번째 모듈 통합</t>
+          <t>입찰 + 이전 입찰자 자동 환불</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>메모리 세션 기반</t>
+          <t>스나이핑 방지 연장</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>bossRushSessions</t>
+          <t>auction_my</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>진행 중 세션 저장</t>
+          <t>내 등록/입찰 내역 조회</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>currentWave/시간 추적</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>bossRushRanking</t>
+          <t>신규 모듈 6/6</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>글로벌 랭킹 TOP 100</t>
+          <t>100% 통합 완료</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>웨이브 → 시간 정렬</t>
+          <t>lottery/fishing/event/season/boss_rush/auction</t>
         </is>
       </c>
     </row>
@@ -19935,22 +20001,22 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_enter</t>
+          <t>boss_rush → server.js</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>무료/유료/다이아 입장</t>
+          <t>5번째 모듈 통합</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>동시 1개 세션 제한</t>
+          <t>메모리 세션 기반</t>
         </is>
       </c>
     </row>
@@ -19962,22 +20028,22 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>boss_rush_advance</t>
+          <t>bossRushSessions</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>웨이브 클리어 보고</t>
+          <t>진행 중 세션 저장</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>시간 초과 검증</t>
+          <t>currentWave/시간 추적</t>
         </is>
       </c>
     </row>
@@ -19989,103 +20055,103 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>풀클리어 보상</t>
+          <t>bossRushRanking</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 누적</t>
+          <t>글로벌 랭킹 TOP 100</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>웨이브 → 시간 정렬</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>season → server.js</t>
+          <t>boss_rush_enter</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>4번째 모듈 통합</t>
+          <t>무료/유료/다이아 입장</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>XP 자동 적립 + 보상 수령</t>
+          <t>동시 1개 세션 제한</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>boss_rush_advance</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
+          <t>웨이브 클리어 보고</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>SEASON_XP_MAP 매핑</t>
+          <t>시간 초과 검증</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>season_status</t>
+          <t>풀클리어 보상</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>XP/티어/구매여부/수령내역 조회</t>
+          <t>20웨이브 누적</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>15티어 전체</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
@@ -20097,22 +20163,22 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>season_buy_pass</t>
+          <t>season → server.js</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 패스 구매 (1500💎)</t>
+          <t>4번째 모듈 통합</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>XP 자동 적립 + 보상 수령</t>
         </is>
       </c>
     </row>
@@ -20124,56 +20190,56 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>season_claim</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>티어 보상 수령 (free/premium)</t>
+          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>자동 인벤토리 적용</t>
+          <t>SEASON_XP_MAP 매핑</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>event → server.js</t>
+          <t>season_status</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>3번째 모듈 통합</t>
+          <t>XP/티어/구매여부/수령내역 조회</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>축제 시스템 활성화</t>
+          <t>15티어 전체</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -20183,44 +20249,44 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>event_status</t>
+          <t>season_buy_pass</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>현재 활성 축제 조회</t>
+          <t>프리미엄 패스 구매 (1500💎)</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>이름/기간/버프/한정 보상</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>/status JSON</t>
+          <t>season_claim</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>festival 필드 추가</t>
+          <t>티어 보상 수령 (free/premium)</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>대시보드 확인용</t>
+          <t>자동 인벤토리 적용</t>
         </is>
       </c>
     </row>
@@ -20232,103 +20298,103 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>축제 인사</t>
+          <t>event → server.js</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>30% 확률로 NPC가 축제 대사 출력</t>
+          <t>3번째 모듈 통합</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>spring_blossom 등 5종</t>
+          <t>축제 시스템 활성화</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>fishing → server.js</t>
+          <t>event_status</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>현재 활성 축제 조회</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>두 번째 모듈 통합</t>
+          <t>이름/기간/버프/한정 보상</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>fishing_status</t>
+          <t>/status JSON</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>지역/낚싯대/미끼/시간대 조회</t>
+          <t>festival 필드 추가</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>대시보드 확인용</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>fishing_cast</t>
+          <t>축제 인사</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
+          <t>30% 확률로 NPC가 축제 대사 출력</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>전설/신화 → 서버 알림</t>
+          <t>spring_blossom 등 5종</t>
         </is>
       </c>
     </row>
@@ -20340,103 +20406,103 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>fishing_buy_rod</t>
+          <t>fishing → server.js</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>낚싯대 구매 (골드/다이아)</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>5등급 모두</t>
+          <t>두 번째 모듈 통합</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>lottery → server.js</t>
+          <t>fishing_status</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>지역/낚싯대/미끼/시간대 조회</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>첫 모듈 통합 마일스톤</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>lottery_status</t>
+          <t>fishing_cast</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>상태/가격/상품 풀 조회</t>
+          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>전설/신화 → 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>lottery_free_spin</t>
+          <t>fishing_buy_rod</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 스핀</t>
+          <t>낚싯대 구매 (골드/다이아)</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>자정 초기화</t>
+          <t>5등급 모두</t>
         </is>
       </c>
     </row>
@@ -20448,373 +20514,373 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>lottery_paid_spin</t>
+          <t>lottery → server.js</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>유료 1회 / 10연속</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>count: 1 또는 10</t>
+          <t>첫 모듈 통합 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>game/auction.js 신규</t>
+          <t>lottery_status</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
+          <t>상태/가격/상품 풀 조회</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>등록 2% + 낙찰 5%</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>활성 한도</t>
+          <t>lottery_free_spin</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>플레이어당 10개</t>
+          <t>매일 무료 1회 스핀</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>자기 입찰 금지</t>
+          <t>자정 초기화</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>game/fishing.js 신규</t>
+          <t>lottery_paid_spin</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
+          <t>유료 1회 / 10연속</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>신화 크라켄 = 20000G + 칭호</t>
+          <t>count: 1 또는 10</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>전설의 비단잉어</t>
+          <t>game/auction.js 신규</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>드래곤 낚싯대 + 가중치 1</t>
+          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>5000G + 평생 행운 +5%</t>
+          <t>등록 2% + 낙찰 5%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>game/boss_rush.js 신규</t>
+          <t>활성 한도</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>20웨이브 / HP ×1.35 스케일링</t>
+          <t>플레이어당 10개</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>최종 보상: 200💎 + 용재료 ×5</t>
+          <t>자기 입찰 금지</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>입장</t>
+          <t>game/fishing.js 신규</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 3회 / 1000G / 30💎</t>
+          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>랭킹 시스템</t>
+          <t>신화 크라켄 = 20000G + 칭호</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>챔피언 보상</t>
+          <t>전설의 비단잉어</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
+          <t>드래곤 낚싯대 + 가중치 1</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5000G + 평생 행운 +5%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>game/lottery.js 신규</t>
+          <t>game/boss_rush.js 신규</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>10종 보상 / 가중치 1000</t>
+          <t>20웨이브 / HP ×1.35 스케일링</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 + 유료</t>
+          <t>최종 보상: 200💎 + 용재료 ×5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>영웅 장비 상자</t>
+          <t>입장</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>확률 0.2% (가장 희귀)</t>
+          <t>매일 무료 3회 / 1000G / 30💎</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>전설 보상</t>
+          <t>랭킹 시스템</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>200 다이아</t>
+          <t>챔피언 보상</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>확률 0.8%</t>
+          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>신년 축제</t>
+          <t>game/lottery.js 신규</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>1/1 ~ 1/7</t>
+          <t>10종 보상 / 가중치 1000</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>골드 +50% / EXP +30%</t>
+          <t>매일 무료 1회 + 유료</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>봄꽃 축제</t>
+          <t>영웅 장비 상자</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>4/1 ~ 4/14</t>
+          <t>확률 0.2% (가장 희귀)</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>HP재생 +30% / 드롭 +20%</t>
+          <t>전설 보상</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>룰렛 (전설)</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>한여름 밤의 축제</t>
+          <t>200 다이아</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>7/15 ~ 8/15</t>
+          <t>확률 0.8%</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>화염 +30% / PvP 보상 +50%</t>
+          <t>잭팟</t>
         </is>
       </c>
     </row>
@@ -20831,17 +20897,17 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>할로윈 축제</t>
+          <t>신년 축제</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>10/25 ~ 11/1</t>
+          <t>1/1 ~ 1/7</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>크리 +10% / 언데드 +50%</t>
+          <t>골드 +50% / EXP +30%</t>
         </is>
       </c>
     </row>
@@ -20858,179 +20924,179 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>겨울 축제</t>
+          <t>봄꽃 축제</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>12/20 ~ 12/31</t>
+          <t>4/1 ~ 4/14</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
+          <t>HP재생 +30% / 드롭 +20%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>game/season.js 신규</t>
+          <t>한여름 밤의 축제</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>15티어 / 30일 / 무료+프리미엄</t>
+          <t>7/15 ~ 8/15</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
+          <t>화염 +30% / PvP 보상 +50%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>XP 획득 7종</t>
+          <t>할로윈 축제</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>퀘/보스/PvP/월드보스/던전/제작</t>
+          <t>10/25 ~ 11/1</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>일일 +200 ~ 월드보스 +500</t>
+          <t>크리 +10% / 언데드 +50%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 가격</t>
+          <t>겨울 축제</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>1500 다이아</t>
+          <t>12/20 ~ 12/31</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>시즌 당 1회</t>
+          <t>골드 +30% / EXP +30% / 드롭 +30%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>Lv.40 달성</t>
+          <t>game/season.js 신규</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>각성기 해금 마일스톤</t>
+          <t>15티어 / 30일 / 무료+프리미엄</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>150💎</t>
+          <t>만렙 보상: 태초 반지 + 시즌 칭호</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Lv.50 달성</t>
+          <t>XP 획득 7종</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>환생 가능 마일스톤</t>
+          <t>퀘/보스/PvP/월드보스/던전/제작</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>250💎</t>
+          <t>일일 +200 ~ 월드보스 +500</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>첫 환생</t>
+          <t>프리미엄 가격</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>prestige 1차</t>
+          <t>1500 다이아</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>500💎</t>
+          <t>시즌 당 1회</t>
         </is>
       </c>
     </row>
@@ -21047,17 +21113,17 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>첫 월드 보스</t>
+          <t>Lv.40 달성</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 처치 보너스</t>
+          <t>각성기 해금 마일스톤</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>100💎</t>
+          <t>150💎</t>
         </is>
       </c>
     </row>
@@ -21074,98 +21140,98 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>업적 50개</t>
+          <t>Lv.50 달성</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>업적 마일스톤</t>
+          <t>환생 가능 마일스톤</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>200💎</t>
+          <t>250💎</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>불사조 스킨</t>
+          <t>첫 환생</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>prestige 1차</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>불사조 깃털 이펙트 (영구)</t>
+          <t>500💎</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>상점 (스킨)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>폭풍 스킨</t>
+          <t>첫 월드 보스</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>1200 다이아</t>
+          <t>월드 보스 처치 보너스</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>번개 오라 이펙트 (영구)</t>
+          <t>100💎</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>상점 (편의)</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 자동물약</t>
+          <t>업적 50개</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>500 다이아</t>
+          <t>업적 마일스톤</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>24시간 자동물약 무한</t>
+          <t>200💎</t>
         </is>
       </c>
     </row>
@@ -21177,22 +21243,22 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>상점 (상자)</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>프리미엄 보물 상자</t>
+          <t>불사조 스킨</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>300 다이아</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>전설 장비 확정 + 다이아</t>
+          <t>불사조 깃털 이펙트 (영구)</t>
         </is>
       </c>
     </row>
@@ -21204,103 +21270,103 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>상점 (재료)</t>
+          <t>상점 (스킨)</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>전설 재료 패키지</t>
+          <t>폭풍 스킨</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>600 다이아</t>
+          <t>1200 다이아</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
+          <t>번개 오라 이펙트 (영구)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6</t>
+          <t>상점 (편의)</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 분노</t>
+          <t>프리미엄 자동물약</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>크리티컬 +5%</t>
+          <t>500 다이아</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>60명 정원</t>
+          <t>24시간 자동물약 무한</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.7</t>
+          <t>상점 (상자)</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 신속</t>
+          <t>프리미엄 보물 상자</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>이동속도 +10%</t>
+          <t>300 다이아</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>70명 정원</t>
+          <t>전설 장비 확정 + 다이아</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.8</t>
+          <t>상점 (재료)</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 회복</t>
+          <t>전설 재료 패키지</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>HP 재생 +50%</t>
+          <t>600 다이아</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>80명 정원</t>
+          <t>용재료×10 + 영혼석×20 + 마법재료×20</t>
         </is>
       </c>
     </row>
@@ -21312,22 +21378,22 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.9</t>
+          <t>혈맹 Lv.6</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>혈맹의 운명</t>
+          <t>혈맹의 분노</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>회피 +5%</t>
+          <t>크리티컬 +5%</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>90명 정원</t>
+          <t>60명 정원</t>
         </is>
       </c>
     </row>
@@ -21339,184 +21405,184 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>혈맹 Lv.10</t>
+          <t>혈맹 Lv.7</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>혈맹의 전설</t>
+          <t>혈맹의 신속</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>전 스탯 +5%</t>
+          <t>이동속도 +10%</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>100명 정원 — 최종</t>
+          <t>70명 정원</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.8</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>점쟁이</t>
+          <t>혈맹의 회복</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
+          <t>HP 재생 +50%</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>80명 정원</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.9</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>감정사</t>
+          <t>혈맹의 운명</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
+          <t>회피 +5%</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>90명 정원</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹 Lv.10</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>수집가</t>
+          <t>혈맹의 전설</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
+          <t>전 스탯 +5%</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>상황 대사 4종</t>
+          <t>100명 정원 — 최종</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>각성기 (어쌔신)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>천 개의 칼날</t>
+          <t>점쟁이</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
+          <t>운세 / 행운 버프 (밤·카르마 반응)</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>각성기 (워리어)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>대지 가르기</t>
+          <t>감정사</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
+          <t>미감정 장비 감정 (Lv.30+ 특수)</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>각성기 (나이트)</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>불멸의 수호자</t>
+          <t>수집가</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>피해 90% 감소 / 도발 / 10초</t>
+          <t>희귀 아이템 매입 (골드 50000+ 특별)</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Lv.40</t>
+          <t>상황 대사 4종</t>
         </is>
       </c>
     </row>
@@ -21528,17 +21594,17 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>각성기 (메이지)</t>
+          <t>각성기 (어쌔신)</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>시간 정지</t>
+          <t>천 개의 칼날</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
+          <t>3.5배 × 7타 / 광역 / 쿨150초</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
@@ -21555,17 +21621,17 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>각성기 (클레릭)</t>
+          <t>각성기 (워리어)</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>신의 은총</t>
+          <t>대지 가르기</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>HP 100% 회복 / 전스탯 +50%</t>
+          <t>6.0배 / 광역 5범위 / 스턴 2초</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -21577,81 +21643,81 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (나이트)</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>폭풍 정복자</t>
+          <t>불멸의 수호자</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인 처치</t>
+          <t>피해 90% 감소 / 도발 / 10초</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>10,000G + 150다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (메이지)</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>연금술사</t>
+          <t>시간 정지</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>엘릭서 10회 제작</t>
+          <t>12.0배 / 광역 6범위 / 슬로우 90%</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>5,000G + 80다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>각성기 (클레릭)</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>그림자 정복자</t>
+          <t>신의 은총</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁 클리어</t>
+          <t>HP 100% 회복 / 전스탯 +50%</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>8,000G + 120다이아</t>
+          <t>Lv.40</t>
         </is>
       </c>
     </row>
@@ -21668,17 +21734,17 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>전설의 동반자</t>
+          <t>폭풍 정복자</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>전설급 펫 진화</t>
+          <t>폭풍의 거인 처치</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>6,000G + 100다이아</t>
+          <t>10,000G + 150다이아</t>
         </is>
       </c>
     </row>
@@ -21695,179 +21761,179 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>이국의 상인</t>
+          <t>연금술사</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>사치품 교역 5회</t>
+          <t>엘릭서 10회 제작</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>4,000G + 60다이아</t>
+          <t>5,000G + 80다이아</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>폭풍의 거인</t>
+          <t>그림자 정복자</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>HP 100,000 / ATK 140 / DEF 90</t>
+          <t>그림자 미궁 클리어</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>EXP 10000 + 6000G</t>
+          <t>8,000G + 120다이아</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>시간의 수호자</t>
+          <t>전설의 동반자</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>HP 70,000 / ATK 170 / DEF 60</t>
+          <t>전설급 펫 진화</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>EXP 9000 + 7000G</t>
+          <t>6,000G + 100다이아</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>교역품</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
+          <t>이국의 상인</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종</t>
+          <t>사치품 교역 5회</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>기본가 600~900G</t>
+          <t>4,000G + 60다이아</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>타이탄의 엘릭서</t>
+          <t>폭풍의 거인</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>용재료×3 + 마법재료×10</t>
+          <t>HP 100,000 / ATK 140 / DEF 90</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>ATK ×1.5 / 30분</t>
+          <t>EXP 10000 + 6000G</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>강철 엘릭서</t>
+          <t>시간의 수호자</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>철광석×30 + 마법재료×10</t>
+          <t>HP 70,000 / ATK 170 / DEF 60</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>DEF ×1.5 / 30분</t>
+          <t>EXP 9000 + 7000G</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>교역품</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>질풍 엘릭서</t>
+          <t>불사조 깃털 / 공허의 정수 / 천공의 비단</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>약초×20 + 마법재료×8</t>
+          <t>이국의 사치품 3종</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>SPD ×1.4 / 20분</t>
+          <t>기본가 600~900G</t>
         </is>
       </c>
     </row>
@@ -21884,17 +21950,17 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>지혜 엘릭서</t>
+          <t>타이탄의 엘릭서</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>마법수정×5 + 영혼재료×5</t>
+          <t>용재료×3 + 마법재료×10</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>EXP ×2.5 / 15분</t>
+          <t>ATK ×1.5 / 30분</t>
         </is>
       </c>
     </row>
@@ -21911,233 +21977,233 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>행운 엘릭서</t>
+          <t>강철 엘릭서</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>보석×10 + 마법재료×5</t>
+          <t>철광석×30 + 마법재료×10</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>GOLD ×2.0 / 15분</t>
+          <t>DEF ×1.5 / 30분</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>불사조 (pet_phoenix)</t>
+          <t>질풍 엘릭서</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>불꽃산 보스 50처치</t>
+          <t>약초×20 + 마법재료×8</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>화염 DMG +20% (진화 +40%)</t>
+          <t>SPD ×1.4 / 20분</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>유니콘 (pet_unicorn)</t>
+          <t>지혜 엘릭서</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>다이아 800개</t>
+          <t>마법수정×5 + 영혼재료×5</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>회피 +10% (진화 +20%)</t>
+          <t>EXP ×2.5 / 15분</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>페가수스 (mount_pegasus)</t>
+          <t>행운 엘릭서</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>다이아 1200개</t>
+          <t>보석×10 + 마법재료×5</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>이동속도 +85% / 비행</t>
+          <t>GOLD ×2.0 / 15분</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>그림자 미궁</t>
+          <t>불사조 (pet_phoenix)</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>Lv.38 / 8인 파티 / 7스테이지</t>
+          <t>불꽃산 보스 50처치</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>22000G + 32000EXP</t>
+          <t>화염 DMG +20% (진화 +40%)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>드롭</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>드래곤 검/망토/투구/장갑</t>
+          <t>유니콘 (pet_unicorn)</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 보스 드롭</t>
+          <t>다이아 800개</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>전설급</t>
+          <t>회피 +10% (진화 +20%)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>공허의 방랑자</t>
+          <t>페가수스 (mount_pegasus)</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>몬스터 10,000 처치</t>
+          <t>다이아 1200개</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>ATK +7%</t>
+          <t>이동속도 +85% / 비행</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>불멸자</t>
+          <t>그림자 미궁</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>환생 5회</t>
+          <t>Lv.38 / 8인 파티 / 7스테이지</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>EXP +25%</t>
+          <t>22000G + 32000EXP</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>드롭</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>천공의 군주</t>
+          <t>드래곤 검/망토/투구/장갑</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 10회 처치</t>
+          <t>그림자 미궁 보스 드롭</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>보스DMG +15%</t>
+          <t>전설급</t>
         </is>
       </c>
     </row>
@@ -22149,22 +22215,22 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>지역 시트 갱신</t>
+          <t>공허의 방랑자</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>25→51개 지역 반영</t>
+          <t>몬스터 10,000 처치</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ATK +7%</t>
         </is>
       </c>
     </row>
@@ -22176,22 +22242,22 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>칭호 시트 갱신</t>
+          <t>불멸자</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>7→16종 + 효과/색상 추가</t>
+          <t>환생 5회</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EXP +25%</t>
         </is>
       </c>
     </row>
@@ -22203,22 +22269,22 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>출석 캘린더 시트</t>
+          <t>천공의 군주</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (28일 사이클)</t>
+          <t>월드 보스 10회 처치</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>보스DMG +15%</t>
         </is>
       </c>
     </row>
@@ -22235,12 +22301,12 @@
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>장비 세트 시트</t>
+          <t>지역 시트 갱신</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (드래곤/영웅/태초)</t>
+          <t>25→51개 지역 반영</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
@@ -22262,12 +22328,12 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>장비 등급 시트</t>
+          <t>칭호 시트 갱신</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+          <t>7→16종 + 효과/색상 추가</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -22289,12 +22355,12 @@
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>디버프 시트</t>
+          <t>출석 캘린더 시트</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+          <t>신규 추가 (28일 사이클)</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
@@ -22316,12 +22382,12 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>패치 노트 시트</t>
+          <t>장비 세트 시트</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>신규 추가 (히스토리)</t>
+          <t>신규 추가 (드래곤/영웅/태초)</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -22333,25 +22399,106 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>장비 등급 시트</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (5등급 + 랜덤 옵션 7종)</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>디버프 시트</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t>신규 추가 (10종, v1.7 5종 포함)</t>
+        </is>
+      </c>
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>패치 노트 시트</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>신규 추가 (히스토리)</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
           <t>v1.10</t>
         </is>
       </c>
-      <c r="B128" s="7" t="inlineStr">
+      <c r="B131" s="8" t="inlineStr">
         <is>
           <t>기획서</t>
         </is>
       </c>
-      <c r="C128" s="7" t="inlineStr">
+      <c r="C131" s="8" t="inlineStr">
         <is>
           <t>던전 시트</t>
         </is>
       </c>
-      <c r="D128" s="7" t="inlineStr">
+      <c r="D131" s="8" t="inlineStr">
         <is>
           <t>신규 추가 (7종 던전)</t>
         </is>
       </c>
-      <c r="E128" s="7" t="inlineStr">
+      <c r="E131" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/AutoBattle_io_기획서.xlsx
+++ b/AutoBattle_io_기획서.xlsx
@@ -45,7 +45,7 @@
     <sheet name="월드 보스" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="연금술" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="패치 노트" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="v1.9 ~ v1.39" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="v1.9 ~ v1.40" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16598,7 +16598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16639,7 +16639,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.39</t>
+          <t>v1.40</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -16654,14 +16654,14 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Phase 3: 장비 데이터 6종 추출 → game/data/equipment.js (123줄)</t>
+          <t>Phase 4: 퀘스트/스킬/전직 추출 → game/data/quests.js (149줄)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.39</t>
+          <t>v1.40</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -16676,14 +16676,14 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>server.js 9103 → 9007줄 (-96줄)</t>
+          <t>server.js 9007 → 8868줄 (-139줄)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.39</t>
+          <t>v1.40</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -16698,14 +16698,14 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>EQUIPMENT_SLOTS/SETS/GRADE_INFO/RANDOM_OPTIONS/EQUIP_STATS(44)/EQUIP_DESCRIPTIONS</t>
+          <t>QUESTS(63)/SKILLS(5클래스×6)/CLASS_ADVANCE(5)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.38</t>
+          <t>v1.39</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -16720,14 +16720,14 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Phase 2: 지역 데이터 8종 추출 → game/data/zones.js (459줄)</t>
+          <t>Phase 3: 장비 데이터 6종 추출 → game/data/equipment.js (123줄)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.38</t>
+          <t>v1.39</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -16742,14 +16742,14 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>server.js 9517 → 9103줄 (-414줄)</t>
+          <t>server.js 9103 → 9007줄 (-96줄)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.38</t>
+          <t>v1.39</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -16764,14 +16764,14 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>ZONES(53)/ZONE_AMBIENCE(52)/MONSTER_LORE(79)/ZONE_CONNECTIONS(50)/TERRAIN_BARRIERS/ROADS/ZONE_MONSTERS/ZONE_MONSTER_NAMES</t>
+          <t>EQUIPMENT_SLOTS/SETS/GRADE_INFO/RANDOM_OPTIONS/EQUIP_STATS(44)/EQUIP_DESCRIPTIONS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -16786,14 +16786,14 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Phase 1: 순수 데이터 6종 추출 → game/data/world_data.js</t>
+          <t>Phase 2: 지역 데이터 8종 추출 → game/data/zones.js (459줄)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -16808,14 +16808,14 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>server.js 9622 → 9517줄 (-105줄)</t>
+          <t>server.js 9517 → 9103줄 (-414줄)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -16830,7 +16830,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>MONSTER_TIERS / KARMA / WORLD_BOSS_TYPES / DUNGEONS / ELEMENT_BONUS / ATTENDANCE_REWARDS</t>
+          <t>ZONES(53)/ZONE_AMBIENCE(52)/MONSTER_LORE(79)/ZONE_CONNECTIONS(50)/TERRAIN_BARRIERS/ROADS/ZONE_MONSTERS/ZONE_MONSTER_NAMES</t>
         </is>
       </c>
     </row>
@@ -16847,19 +16847,19 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>버그 수정</t>
+          <t>리팩토링</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>MONSTER_TIERS의 깨진 한글 (드래���→드래곤) 함께 수정</t>
+          <t>Phase 1: 순수 데이터 6종 추출 → game/data/world_data.js</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -16869,19 +16869,19 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>신규 모듈</t>
+          <t>리팩토링</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>game/farm.js — 농장 시스템 (생성 + 통합 동시)</t>
+          <t>server.js 9622 → 9517줄 (-105줄)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -16891,19 +16891,19 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>농장</t>
+          <t>리팩토링</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>7종 작물 (5분~4시간), AFK 진행, 4슬롯 기본 (12슬롯 확장)</t>
+          <t>MONSTER_TIERS / KARMA / WORLD_BOSS_TYPES / DUNGEONS / ELEMENT_BONUS / ATTENDANCE_REWARDS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -16913,12 +16913,12 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>농장</t>
+          <t>버그 수정</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>비료 (20💎) 50% 시간 단축, 슬롯 확장 50💎</t>
+          <t>MONSTER_TIERS의 깨진 한글 (드래���→드래곤) 함께 수정</t>
         </is>
       </c>
     </row>
@@ -16935,19 +16935,19 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>farm_status / plant / harvest / fertilize / expand</t>
+          <t>game/farm.js — 농장 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -16957,19 +16957,19 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>신규 모듈</t>
+          <t>농장</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>game/skill_tree.js — 특성 트리 (생성 + 통합 동시)</t>
+          <t>7종 작물 (5분~4시간), AFK 진행, 4슬롯 기본 (12슬롯 확장)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -16979,19 +16979,19 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>특성 트리</t>
+          <t>농장</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>3브랜치 (공격/방어/유틸) × 7노드 = 21노드</t>
+          <t>비료 (20💎) 50% 시간 단축, 슬롯 확장 50💎</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -17001,12 +17001,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>특성 트리</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>레벨업 시 1포인트 자동 지급, 100💎로 리셋</t>
+          <t>farm_status / plant / harvest / fertilize / expand</t>
         </is>
       </c>
     </row>
@@ -17023,19 +17023,19 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>게이트</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>5/10/15/20/25 포인트 투자 시 상위 노드 해금</t>
+          <t>game/skill_tree.js — 특성 트리 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -17045,19 +17045,19 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>신규 모듈</t>
+          <t>특성 트리</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>game/mail.js — 정식 우편함 시스템 (생성 + 통합 동시)</t>
+          <t>3브랜치 (공격/방어/유틸) × 7노드 = 21노드</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -17067,19 +17067,19 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>우편함</t>
+          <t>특성 트리</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>시스템/선물 메일 + 첨부(골드/다이아/아이템) + 만료/수령 관리</t>
+          <t>레벨업 시 1포인트 자동 지급, 100💎로 리셋</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -17089,12 +17089,12 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>선물</t>
+          <t>게이트</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>일일 10회 / 골드 첨부 수수료 2% / 7일 만료</t>
+          <t>5/10/15/20/25 포인트 투자 시 상위 노드 해금</t>
         </is>
       </c>
     </row>
@@ -17111,19 +17111,19 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>mail_inbox/read/claim/delete/send_gift</t>
+          <t>game/mail.js — 정식 우편함 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -17133,19 +17133,19 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>신규 모듈</t>
+          <t>우편함</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>game/codex.js — 도감 시스템 (생성 + 통합 동시)</t>
+          <t>시스템/선물 메일 + 첨부(골드/다이아/아이템) + 만료/수령 관리</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -17155,19 +17155,19 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>선물</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>5개 카테고리 (몬스터/지역/장비/어종/펫) × 4단계 마일스톤</t>
+          <t>일일 10회 / 골드 첨부 수수료 2% / 7일 만료</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -17177,12 +17177,12 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 달성 시 영구 스탯 보너스 + 전 서버 알림</t>
+          <t>mail_inbox/read/claim/delete/send_gift</t>
         </is>
       </c>
     </row>
@@ -17199,19 +17199,19 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>trackQuest(explore_count) → zone 자동 등록 / fishing_cast → fish 자동 등록</t>
+          <t>game/codex.js — 도감 시스템 (생성 + 통합 동시)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -17221,19 +17221,19 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>신규 모듈</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
+          <t>5개 카테고리 (몬스터/지역/장비/어종/펫) × 4단계 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -17243,19 +17243,19 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>일일 상점</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
+          <t>마일스톤 달성 시 영구 스탯 보너스 + 전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -17265,12 +17265,12 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>일일 상점</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
+          <t>trackQuest(explore_count) → zone 자동 등록 / fishing_cast → fish 자동 등록</t>
         </is>
       </c>
     </row>
@@ -17287,19 +17287,19 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>신규 모듈</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
+          <t>game/dailyshop.js — 일일 상점 (생성 + 통합 동시 패치)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -17309,19 +17309,19 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
+          <t>15종 풀에서 매일 6슬롯 무작위 (결정적 시드 = 날짜)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -17331,19 +17331,19 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>일일 상점</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
+          <t>할인율 10~50% / 슬롯당 1회 구매 / 다이아 30개로 개인 갱신</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -17353,12 +17353,12 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
+          <t>daily_shop_status / daily_shop_buy / daily_shop_reroll</t>
         </is>
       </c>
     </row>
@@ -17375,12 +17375,12 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>auction_list / create / bid / my</t>
+          <t>game/auction.js → server.js 통합 (6번째 = 마지막 모듈 통합)</t>
         </is>
       </c>
     </row>
@@ -17397,19 +17397,19 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
+          <t>자동 정산 틱 (10초마다 tickAuctions())</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -17419,19 +17419,19 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
+          <t>이전 입찰자 자동 환불, 낙찰 시 아이템/골드 양방향 지급</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -17441,19 +17441,19 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
+          <t>auction_list / create / bid / my</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -17463,12 +17463,12 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_status / enter / advance / abandon</t>
+          <t>🎉 v1.20~v1.25 신규 모듈 6개 모두 통합 완료</t>
         </is>
       </c>
     </row>
@@ -17485,19 +17485,19 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
+          <t>game/boss_rush.js → server.js 통합 (5번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -17507,19 +17507,19 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
+          <t>메모리 세션 + 시간 검증 + 누적 보상 + 랭킹 (TOP 100)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -17529,19 +17529,19 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
+          <t>boss_rush_status / enter / advance / abandon</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -17551,12 +17551,12 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>season_status / season_buy_pass / season_claim</t>
+          <t>풀클리어 시 전 서버 알림, 10웨이브+ 일반 알림</t>
         </is>
       </c>
     </row>
@@ -17573,19 +17573,19 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
+          <t>game/season.js → server.js 통합 (4번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -17595,19 +17595,19 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
+          <t>trackQuest 자동 XP 적립 (PvP/보스/월드보스/던전/제작)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -17617,19 +17617,19 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>event_status 소켓 + /status 엔드포인트 노출</t>
+          <t>season_status / season_buy_pass / season_claim</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -17639,12 +17639,12 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>축제</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
+          <t>티어 승급 시 server_msg + season_tier_up 알림</t>
         </is>
       </c>
     </row>
@@ -17661,19 +17661,19 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
+          <t>game/event.js → server.js 통합 (3번째 모듈 통합)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -17683,19 +17683,19 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
+          <t>event_status 소켓 + /status 엔드포인트 노출</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -17705,19 +17705,19 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>축제</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
+          <t>NPC 대사 30% 확률로 축제 인사 (getNpcMsg 통합)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -17727,12 +17727,12 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
+          <t>오늘(4/8) 봄꽃 축제 활성 동작 확인</t>
         </is>
       </c>
     </row>
@@ -17749,19 +17749,19 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
+          <t>game/fishing.js → server.js 통합 (소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -17771,19 +17771,19 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
+          <t>fishing_status / fishing_cast / fishing_buy_rod 이벤트</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -17793,19 +17793,19 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
+          <t>지역 검증 (낚시 만/강변/산호초), 낚싯대 보유 검증, 미끼 소비</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -17815,19 +17815,19 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
+          <t>전설/신화 어종 낚시 시 전 서버 알림 + ach_fish50 추적</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -17837,19 +17837,19 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
+          <t>game/lottery.js → server.js 통합 (require + 소켓 핸들러 3종)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -17859,19 +17859,19 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
+          <t>lottery_status / lottery_free_spin / lottery_paid_spin 이벤트 추가</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -17881,19 +17881,19 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>경매장 시트 신규 추가</t>
+          <t>전설/영웅 보상 획득 시 전 서버 알림 + ach_lucky 업적 추적</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -17903,19 +17903,19 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
+          <t>입찰식 경매 시스템 (game/auction.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -17925,19 +17925,19 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
+          <t>3가지 기간(1h/6h/24h) + 등록2% + 낙찰5% + 스나이핑 방지</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -17952,14 +17952,14 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>낚시 시트 신규 추가</t>
+          <t>경매장 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -17969,19 +17969,19 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
+          <t>11종 어종 + 5등급 낚싯대 + 4종 미끼 (game/fishing.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -17991,19 +17991,19 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
+          <t>신화 크라켄 (밤+낚시터+드래곤대 한정), 바다의 군주 칭호 연계</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -18018,14 +18018,14 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>보스 러시 시트 신규 추가</t>
+          <t>낚시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -18035,19 +18035,19 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
+          <t>20웨이브 엔드리스 보스 러시 모드 (game/boss_rush.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -18057,19 +18057,19 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
+          <t>매일 무료 3회 + 랭킹 1위 챔피언 칭호</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -18084,14 +18084,14 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛 시트 신규 추가</t>
+          <t>보스 러시 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -18101,19 +18101,19 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
+          <t>10종 보상 + 가중치 시스템 (game/lottery.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -18123,19 +18123,19 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>모듈화</t>
+          <t>룰렛</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
+          <t>매일 무료 1회 / 유료 50💎 / 10연속 450💎 (10% 할인)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -18150,14 +18150,14 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트 시트 신규 추가</t>
+          <t>행운의 룰렛 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -18167,19 +18167,19 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>축제 이벤트</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
+          <t>5종 시즌 축제 추가 (신년/봄꽃/한여름/할로윈/겨울)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -18189,19 +18189,19 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>시즌 패스</t>
+          <t>모듈화</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
+          <t>game/event.js 신규 파일 (실제 달력 기반 자동 활성화)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -18216,14 +18216,14 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>시즌 패스 시트 신규 추가</t>
+          <t>축제 이벤트 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -18233,19 +18233,19 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
+          <t>15티어 배틀 패스 시스템 추가 (game/season.js 신규 모듈)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -18255,19 +18255,19 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>시즌 패스</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>무료 다이아 시트 신규 추가</t>
+          <t>30일 사이클, 무료+프리미엄(1500💎) 트랙</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.20</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -18277,19 +18277,19 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
+          <t>시즌 패스 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -18299,19 +18299,19 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>상점 시트 갱신</t>
+          <t>마일스톤 5종 추가 (Lv.40/50, 첫 환생, 첫 월드 보스, 업적 50)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.19</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -18321,19 +18321,19 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
+          <t>무료 다이아 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -18343,19 +18343,19 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>혈맹</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>최대 인원 50→100명 (Lv.10 기준)</t>
+          <t>프리미엄 5종 추가 (불사조/폭풍 스킨, 자동물약 24h, 보물상자, 재료 패키지)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -18370,14 +18370,14 @@
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>길드(혈맹) 시트 신규 추가</t>
+          <t>상점 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
@@ -18387,19 +18387,19 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>신규 NPC</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
+          <t>혈맹 Lv.6-10 + 신규 스킬 5종 (분노/신속/회복/운명/전설)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -18409,19 +18409,19 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>대사 시스템</t>
+          <t>혈맹</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
+          <t>최대 인원 50→100명 (Lv.10 기준)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
@@ -18436,14 +18436,14 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>NPC 시트 신규 추가 (11종)</t>
+          <t>길드(혈맹) 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -18453,19 +18453,19 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>각성기</t>
+          <t>신규 NPC</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
+          <t>점쟁이/감정사/수집가 3종 추가 (운세/감정/희귀품 매입)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>v1.15</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
@@ -18475,19 +18475,19 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>대사 시스템</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
+          <t>신규 NPC 상황별 대사 (밤/카르마/레벨/골드 연동)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.16</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -18497,19 +18497,19 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>업적</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
+          <t>NPC 시트 신규 추가 (11종)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>v1.14</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
@@ -18519,19 +18519,19 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>각성기</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
+          <t>클래스별 Lv.40 각성기 5종 추가 (천개의칼날/대지가르기/불멸의수호자/시간정지/신의은총)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.15</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -18541,19 +18541,19 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>월드 보스</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
+          <t>스킬 시트 전면 갱신 (12종→30종, 클레릭 포함)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
@@ -18563,19 +18563,19 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>교역</t>
+          <t>업적</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
+          <t>v1.9~v1.13 컨텐츠 연계 업적 5종 추가 (폭풍 정복자/연금술사/그림자/전설 동반자/이국 상인)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>v1.13</t>
+          <t>v1.14</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -18590,14 +18590,14 @@
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
+          <t>퀘스트 시트 전면 갱신 (9종→64종 반영)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
@@ -18607,19 +18607,19 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>연금술</t>
+          <t>월드 보스</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
+          <t>폭풍의 거인 / 시간의 수호자 2종 추가 (최대 HP / 최강 ATK)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>v1.12</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -18629,19 +18629,19 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>교역</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>연금술 시트 신규 추가</t>
+          <t>이국의 사치품 3종 추가 (불사조 깃털/공허의 정수/천공의 비단)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.13</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
@@ -18651,19 +18651,19 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>신규 펫</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
+          <t>월드 보스 시트 신규 추가, 교역 시트 갱신</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>v1.11</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -18673,19 +18673,19 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>신규 탈것</t>
+          <t>연금술</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>페가수스 (이동 +85%, 비행)</t>
+          <t>엘릭서 5종 추가 (타이탄/강철/질풍/지혜/행운, 15~30분 강력 버프)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.12</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
@@ -18695,19 +18695,19 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>신규 던전</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
+          <t>연금술 시트 신규 추가</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>v1.10</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -18717,19 +18717,19 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 펫</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
+          <t>불사조 (화염 +20%) / 유니콘 (회피 +10%) + 진화형</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.11</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
@@ -18739,19 +18739,19 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>전설 칭호</t>
+          <t>신규 탈것</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
+          <t>페가수스 (이동 +85%, 비행)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>v1.9</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -18761,78 +18761,78 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>신규 던전</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
+          <t>그림자 미궁 (Lv.38, 8인 파티, 7스테이지, 전설 드롭)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.10</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
+          <t>던전 시트 신규 추가 (7종 던전 정리)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>전설 칭호</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
+          <t>공허의 방랑자/불멸자/천공의 군주 3종 추가 (엔드게임)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>v1.8</t>
+          <t>v1.9</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>기획서</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
+          <t>51개 지역, 16종 칭호, 출석/세트/등급 시트 추가</t>
         </is>
       </c>
     </row>
@@ -18849,19 +18849,19 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
+          <t>패치 노트 갱신, 낮/밤 시계 + 진행 시간 표시</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
@@ -18871,19 +18871,19 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>상태이상</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
+          <t>자동 스킬 시전 (인간 플레이어용), 자동 스킬 토글 버튼</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -18898,14 +18898,14 @@
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
+          <t>미니맵 친구 위치 표시, 보스 표시 강화, DPS 미터 스파크라인</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+          <t>혈맹 창고 UI 패널, 보스 신규 디버프 적용</t>
         </is>
       </c>
     </row>
@@ -18937,12 +18937,12 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>컨텐츠</t>
+          <t>상태이상</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+          <t>신규 디버프 5종 (빙결/감전/출혈/약화/공포)</t>
         </is>
       </c>
     </row>
@@ -18964,27 +18964,93 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+          <t>포션 단축키 (1/2/3/4), 레벨별 추천 활동 가이드</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>장비 자동 최적화 (auto_equip_best), 알림 센터</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>컨텐츠</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>신규 업적 10종 (30→40), 신규 몬스터 존 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>인벤토리 검색 + 정렬, PvP 시즌 보드 시각화</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
           <t>v1.6 이전</t>
         </is>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C110" s="7" t="inlineStr">
+      <c r="C113" s="8" t="inlineStr">
         <is>
           <t>기반</t>
         </is>
       </c>
-      <c r="D110" s="7" t="inlineStr">
+      <c r="D113" s="8" t="inlineStr">
         <is>
           <t>마을/사냥/PvP/카르마/펫/탈것/제작/교역/길드/공성/투기장 등</t>
         </is>
@@ -19004,7 +19070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -19051,7 +19117,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>v1.39</t>
+          <t>v1.40</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -19061,24 +19127,24 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Phase 3</t>
+          <t>Phase 4</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>game/data/equipment.js 추출</t>
+          <t>game/data/quests.js 추출</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>-96줄 (9103→9007)</t>
+          <t>-139줄 (9007→8868)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>v1.39</t>
+          <t>v1.40</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -19088,24 +19154,24 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>장비 6종</t>
+          <t>퀘스트 3종</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>SLOTS/SETS/GRADE/RAND/STATS/DESC</t>
+          <t>QUESTS / SKILLS / CLASS_ADVANCE</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>generateRandomOptions 함수 유지</t>
+          <t>전부 순수 데이터</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>v1.39</t>
+          <t>v1.40</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -19115,24 +19181,24 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>-615줄 누적</t>
+          <t>-754줄 누적</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>9622 → 9007</t>
+          <t>9622 → 8868</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-7.8%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>v1.38</t>
+          <t>v1.39</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -19142,24 +19208,24 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Phase 2</t>
+          <t>Phase 3</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>game/data/zones.js 추출</t>
+          <t>game/data/equipment.js 추출</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>-414줄 (9517→9103)</t>
+          <t>-96줄 (9103→9007)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>v1.38</t>
+          <t>v1.39</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -19169,24 +19235,24 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>지역 8종</t>
+          <t>장비 6종</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>ZONES/ZONE_AMBIENCE/MONSTER_LORE/등</t>
+          <t>SLOTS/SETS/GRADE/RAND/STATS/DESC</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>함수(isOnRoad/isBlocked) 유지</t>
+          <t>generateRandomOptions 함수 유지</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>v1.38</t>
+          <t>v1.39</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -19196,24 +19262,24 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>-519줄 누적</t>
+          <t>-615줄 누적</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>9622 → 9103</t>
+          <t>9622 → 9007</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-6.4%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -19223,152 +19289,152 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Phase 1</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>game/data/world_data.js 추출</t>
+          <t>game/data/zones.js 추출</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>-105줄 (9622→9517)</t>
+          <t>-414줄 (9517→9103)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>마스터 플랜</t>
+          <t>분리</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>5단계 분리</t>
+          <t>지역 8종</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Phase 2: ZONES / 3: 장비 / 4: 퀘스트 / 5: 상점</t>
+          <t>ZONES/ZONE_AMBIENCE/MONSTER_LORE/등</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>각 phase = 1 커밋</t>
+          <t>함수(isOnRoad/isBlocked) 유지</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.38</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>버그 수정</t>
+          <t>진척</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>MONSTER_TIERS</t>
+          <t>-519줄 누적</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>깨진 한글 동시 수정</t>
+          <t>9622 → 9103</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>드래곤 / 고대 드래곤</t>
+          <t>-5.4%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>리팩토링</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>game/farm.js</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>농장 모듈 생성 + 즉시 통합</t>
+          <t>game/data/world_data.js 추출</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>7작물 / AFK 진행</t>
+          <t>-105줄 (9622→9517)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>작물 (전설)</t>
+          <t>마스터 플랜</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>용 과일</t>
+          <t>5단계 분리</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>4시간 / 80💎</t>
+          <t>Phase 2: ZONES / 3: 장비 / 4: 퀘스트 / 5: 상점</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>용재료 ×1 + 영혼석 ×3 + 3000G</t>
+          <t>각 phase = 1 커밋</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>작물 (희귀)</t>
+          <t>버그 수정</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>달꽃</t>
+          <t>MONSTER_TIERS</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>2시간 / 30💎</t>
+          <t>깨진 한글 동시 수정</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>마법재료 ×5 + 영혼석 ×1</t>
+          <t>드래곤 / 고대 드래곤</t>
         </is>
       </c>
     </row>
@@ -19380,103 +19446,103 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>비료</t>
+          <t>game/farm.js</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>20💎 / 50% 시간 단축</t>
+          <t>농장 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>슬롯당 1회</t>
+          <t>7작물 / AFK 진행</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>작물 (전설)</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>game/skill_tree.js</t>
+          <t>용 과일</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>특성 트리 모듈 생성 + 즉시 통합</t>
+          <t>4시간 / 80💎</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>3브랜치 × 7노드</t>
+          <t>용재료 ×1 + 영혼석 ×3 + 3000G</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>작물 (희귀)</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>레벨업 훅</t>
+          <t>달꽃</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>awardPoints(target, 1) 자동 호출</t>
+          <t>2시간 / 30💎</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>별도 학습 불필요</t>
+          <t>마법재료 ×5 + 영혼석 ×1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>마스터 노드</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>off_master</t>
+          <t>비료</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>전쟁의 화신</t>
+          <t>20💎 / 50% 시간 단축</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>ATK +30 / 크리 +5%</t>
+          <t>슬롯당 1회</t>
         </is>
       </c>
     </row>
@@ -19488,22 +19554,22 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>마스터 노드</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>def_master</t>
+          <t>game/skill_tree.js</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>불멸의 의지</t>
+          <t>특성 트리 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>DEF +30 / HP +300</t>
+          <t>3브랜치 × 7노드</t>
         </is>
       </c>
     </row>
@@ -19515,103 +19581,103 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>마스터 노드</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>util_master</t>
+          <t>레벨업 훅</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>운명의 인도자</t>
+          <t>awardPoints(target, 1) 자동 호출</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>EXP/GOLD +20% / 드롭 +10%</t>
+          <t>별도 학습 불필요</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>game/mail.js</t>
+          <t>off_master</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>우편함 모듈 생성 + 즉시 통합</t>
+          <t>전쟁의 화신</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>시스템/선물 + 첨부 + 만료</t>
+          <t>ATK +30 / 크리 +5%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>메일</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>시스템 메일</t>
+          <t>def_master</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>이벤트 보상/공지</t>
+          <t>불멸의 의지</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>14일 만료</t>
+          <t>DEF +30 / HP +300</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>메일</t>
+          <t>마스터 노드</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>선물 메일</t>
+          <t>util_master</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>플레이어 간 / 일일 10회</t>
+          <t>운명의 인도자</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>7일 만료, 수수료 2%</t>
+          <t>EXP/GOLD +20% / 드롭 +10%</t>
         </is>
       </c>
     </row>
@@ -19623,103 +19689,103 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>발송 시 자원 차감</t>
+          <t>game/mail.js</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>수신자 우편함 가득 → 거부</t>
+          <t>우편함 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>첨부 미수령 메일 삭제 거부</t>
+          <t>시스템/선물 + 첨부 + 만료</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>game/codex.js</t>
+          <t>시스템 메일</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>도감 모듈 생성 + 즉시 통합</t>
+          <t>이벤트 보상/공지</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>5카테고리 × 4마일스톤</t>
+          <t>14일 만료</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>선물 메일</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>explore_count → zone 자동 등록</t>
+          <t>플레이어 간 / 일일 10회</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>별도 학습 불필요</t>
+          <t>7일 만료, 수수료 2%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>fishing_cast 훅</t>
+          <t>발송 시 자원 차감</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>어종 자동 등록</t>
+          <t>수신자 우편함 가득 → 거부</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>v1.24와 자연 연동</t>
+          <t>첨부 미수령 메일 삭제 거부</t>
         </is>
       </c>
     </row>
@@ -19731,184 +19797,184 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>영구 스탯 보너스</t>
+          <t>game/codex.js</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>마일스톤 달성 시 누적</t>
+          <t>도감 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>codexBonuses 객체</t>
+          <t>5카테고리 × 4마일스톤</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>신규+통합</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>game/dailyshop.js</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>일일 상점 모듈 생성 + 즉시 통합</t>
+          <t>explore_count → zone 자동 등록</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
+          <t>별도 학습 불필요</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>결정적 랜덤</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>날짜 시드</t>
+          <t>fishing_cast 훅</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>모든 플레이어 동일 상품</t>
+          <t>어종 자동 등록</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>seededRandom + Fisher-Yates</t>
+          <t>v1.24와 자연 연동</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>개인 갱신</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>30💎</t>
+          <t>영구 스탯 보너스</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>개인 시드 생성</t>
+          <t>마일스톤 달성 시 누적</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>구매 기록 초기화</t>
+          <t>codexBonuses 객체</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>신규+통합</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>auction → server.js</t>
+          <t>game/dailyshop.js</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>6번째 (마지막) 모듈 통합</t>
+          <t>일일 상점 모듈 생성 + 즉시 통합</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>자동 정산 + 환불 + 양방향 지급</t>
+          <t>15종 풀 / 6슬롯 / 10~50% 할인</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>결정적 랜덤</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>tickAuctions</t>
+          <t>날짜 시드</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>10초마다 만료 정산</t>
+          <t>모든 플레이어 동일 상품</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>setInterval 통합</t>
+          <t>seededRandom + Fisher-Yates</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>개인 갱신</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>auction_create</t>
+          <t>30💎</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>경매 등록 (등록 수수료 자동 차감)</t>
+          <t>개인 시드 생성</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>3가지 기간</t>
+          <t>구매 기록 초기화</t>
         </is>
       </c>
     </row>
@@ -19920,22 +19986,22 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>auction_bid</t>
+          <t>auction → server.js</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>입찰 + 이전 입찰자 자동 환불</t>
+          <t>6번째 (마지막) 모듈 통합</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>스나이핑 방지 연장</t>
+          <t>자동 정산 + 환불 + 양방향 지급</t>
         </is>
       </c>
     </row>
@@ -19947,22 +20013,22 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>auction_my</t>
+          <t>tickAuctions</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>내 등록/입찰 내역 조회</t>
+          <t>10초마다 만료 정산</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>setInterval 통합</t>
         </is>
       </c>
     </row>
@@ -19974,103 +20040,103 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>마일스톤</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>신규 모듈 6/6</t>
+          <t>auction_create</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>100% 통합 완료</t>
+          <t>경매 등록 (등록 수수료 자동 차감)</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>lottery/fishing/event/season/boss_rush/auction</t>
+          <t>3가지 기간</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>boss_rush → server.js</t>
+          <t>auction_bid</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>5번째 모듈 통합</t>
+          <t>입찰 + 이전 입찰자 자동 환불</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>메모리 세션 기반</t>
+          <t>스나이핑 방지 연장</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>bossRushSessions</t>
+          <t>auction_my</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>진행 중 세션 저장</t>
+          <t>내 등록/입찰 내역 조회</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>currentWave/시간 추적</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>마일스톤</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>bossRushRanking</t>
+          <t>신규 모듈 6/6</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>글로벌 랭킹 TOP 100</t>
+          <t>100% 통합 완료</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>웨이브 → 시간 정렬</t>
+          <t>lottery/fishing/event/season/boss_rush/auction</t>
         </is>
       </c>
     </row>
@@ -20082,22 +20148,22 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>boss_rush_enter</t>
+          <t>boss_rush → server.js</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>무료/유료/다이아 입장</t>
+          <t>5번째 모듈 통합</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>동시 1개 세션 제한</t>
+          <t>메모리 세션 기반</t>
         </is>
       </c>
     </row>
@@ -20109,22 +20175,22 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>boss_rush_advance</t>
+          <t>bossRushSessions</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>웨이브 클리어 보고</t>
+          <t>진행 중 세션 저장</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>시간 초과 검증</t>
+          <t>currentWave/시간 추적</t>
         </is>
       </c>
     </row>
@@ -20136,103 +20202,103 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>풀클리어 보상</t>
+          <t>bossRushRanking</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 누적</t>
+          <t>글로벌 랭킹 TOP 100</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>웨이브 → 시간 정렬</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>season → server.js</t>
+          <t>boss_rush_enter</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>4번째 모듈 통합</t>
+          <t>무료/유료/다이아 입장</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>XP 자동 적립 + 보상 수령</t>
+          <t>동시 1개 세션 제한</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>자동화</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>trackQuest 훅</t>
+          <t>boss_rush_advance</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
+          <t>웨이브 클리어 보고</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>SEASON_XP_MAP 매핑</t>
+          <t>시간 초과 검증</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>v1.29</t>
+          <t>v1.30</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>season_status</t>
+          <t>풀클리어 보상</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>XP/티어/구매여부/수령내역 조회</t>
+          <t>20웨이브 누적</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>15티어 전체</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
@@ -20244,22 +20310,22 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>season_buy_pass</t>
+          <t>season → server.js</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>프리미엄 패스 구매 (1500💎)</t>
+          <t>4번째 모듈 통합</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>전 서버 알림</t>
+          <t>XP 자동 적립 + 보상 수령</t>
         </is>
       </c>
     </row>
@@ -20271,56 +20337,56 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>자동화</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>season_claim</t>
+          <t>trackQuest 훅</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>티어 보상 수령 (free/premium)</t>
+          <t>PvP/보스/월드보스/던전/제작 → 시즌 XP</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>자동 인벤토리 적용</t>
+          <t>SEASON_XP_MAP 매핑</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>event → server.js</t>
+          <t>season_status</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>3번째 모듈 통합</t>
+          <t>XP/티어/구매여부/수령내역 조회</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>축제 시스템 활성화</t>
+          <t>15티어 전체</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -20330,44 +20396,44 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>event_status</t>
+          <t>season_buy_pass</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>현재 활성 축제 조회</t>
+          <t>프리미엄 패스 구매 (1500💎)</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>이름/기간/버프/한정 보상</t>
+          <t>전 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>/status JSON</t>
+          <t>season_claim</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>festival 필드 추가</t>
+          <t>티어 보상 수령 (free/premium)</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>대시보드 확인용</t>
+          <t>자동 인벤토리 적용</t>
         </is>
       </c>
     </row>
@@ -20379,103 +20445,103 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>축제 인사</t>
+          <t>event → server.js</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>30% 확률로 NPC가 축제 대사 출력</t>
+          <t>3번째 모듈 통합</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>spring_blossom 등 5종</t>
+          <t>축제 시스템 활성화</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>fishing → server.js</t>
+          <t>event_status</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>현재 활성 축제 조회</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>두 번째 모듈 통합</t>
+          <t>이름/기간/버프/한정 보상</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>fishing_status</t>
+          <t>/status JSON</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>지역/낚싯대/미끼/시간대 조회</t>
+          <t>festival 필드 추가</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>대시보드 확인용</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>fishing_cast</t>
+          <t>축제 인사</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
+          <t>30% 확률로 NPC가 축제 대사 출력</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>전설/신화 → 서버 알림</t>
+          <t>spring_blossom 등 5종</t>
         </is>
       </c>
     </row>
@@ -20487,103 +20553,103 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>소켓</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>fishing_buy_rod</t>
+          <t>fishing → server.js</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>낚싯대 구매 (골드/다이아)</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>5등급 모두</t>
+          <t>두 번째 모듈 통합</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>lottery → server.js</t>
+          <t>fishing_status</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>require + 소켓 핸들러 3종</t>
+          <t>지역/낚싯대/미끼/시간대 조회</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>첫 모듈 통합 마일스톤</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>lottery_status</t>
+          <t>fishing_cast</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>상태/가격/상품 풀 조회</t>
+          <t>낚시 시도 (지역+낚싯대+미끼 검증)</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>클라이언트 표시용</t>
+          <t>전설/신화 → 서버 알림</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>소켓</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>lottery_free_spin</t>
+          <t>fishing_buy_rod</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>매일 무료 1회 스핀</t>
+          <t>낚싯대 구매 (골드/다이아)</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>자정 초기화</t>
+          <t>5등급 모두</t>
         </is>
       </c>
     </row>
@@ -20595,373 +20661,373 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>소켓 이벤트</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>lottery_paid_spin</t>
+          <t>lottery → server.js</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>유료 1회 / 10연속</t>
+          <t>require + 소켓 핸들러 3종</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>count: 1 또는 10</t>
+          <t>첫 모듈 통합 마일스톤</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>game/auction.js 신규</t>
+          <t>lottery_status</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
+          <t>상태/가격/상품 풀 조회</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>등록 2% + 낙찰 5%</t>
+          <t>클라이언트 표시용</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>v1.25</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>활성 한도</t>
+          <t>lottery_free_spin</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>플레이어당 10개</t>
+          <t>매일 무료 1회 스핀</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>자기 입찰 금지</t>
+          <t>자정 초기화</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.26</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>소켓 이벤트</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>game/fishing.js 신규</t>
+          <t>lottery_paid_spin</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
+          <t>유료 1회 / 10연속</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>신화 크라켄 = 20000G + 칭호</t>
+          <t>count: 1 또는 10</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>v1.24</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>전설의 비단잉어</t>
+          <t>game/auction.js 신규</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>드래곤 낚싯대 + 가중치 1</t>
+          <t>입찰식 / 3기간 / 5% 인상 / 스나이핑 방지</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>5000G + 평생 행운 +5%</t>
+          <t>등록 2% + 낙찰 5%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.25</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>game/boss_rush.js 신규</t>
+          <t>활성 한도</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>20웨이브 / HP ×1.35 스케일링</t>
+          <t>플레이어당 10개</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>최종 보상: 200💎 + 용재료 ×5</t>
+          <t>자기 입찰 금지</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>입장</t>
+          <t>game/fishing.js 신규</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 3회 / 1000G / 30💎</t>
+          <t>11종 어종 / 5등급 낚싯대 / 4종 미끼</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>랭킹 시스템</t>
+          <t>신화 크라켄 = 20000G + 칭호</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>v1.23</t>
+          <t>v1.24</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>보스 러시</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>챔피언 보상</t>
+          <t>전설의 비단잉어</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
+          <t>드래곤 낚싯대 + 가중치 1</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5000G + 평생 행운 +5%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>행운의 룰렛</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>game/lottery.js 신규</t>
+          <t>game/boss_rush.js 신규</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>10종 보상 / 가중치 1000</t>
+          <t>20웨이브 / HP ×1.35 스케일링</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>매일 무료 1회 + 유료</t>
+          <t>최종 보상: 200💎 + 용재료 ×5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>영웅 장비 상자</t>
+          <t>입장</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>확률 0.2% (가장 희귀)</t>
+          <t>매일 무료 3회 / 1000G / 30💎</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>전설 보상</t>
+          <t>랭킹 시스템</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>룰렛 (전설)</t>
+          <t>보스 러시</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>200 다이아</t>
+          <t>챔피언 보상</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>확률 0.8%</t>
+          <t>1위: 500💎 + 칭호 / 2위: 300💎 / 3위: 200💎</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>축제 이벤트</t>
+          <t>행운의 룰렛</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>신년 축제</t>
+          <t>game/lottery.js 신규</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>1/1 ~ 1/7</t>
+          <t>10종 보상 / 가중치 1000</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-  